--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39349723-5248-4F48-9DB1-301273B9FCB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2A06A8-3C91-42BD-AB63-FDF98753FCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7EB6C2C6-840C-4838-9636-758ACFA0B514}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Nombre</t>
   </si>
@@ -107,64 +107,61 @@
     <t>Ranking general</t>
   </si>
   <si>
-    <t>Gaby</t>
-  </si>
-  <si>
-    <t>Miriam</t>
-  </si>
-  <si>
-    <t>Rafa</t>
-  </si>
-  <si>
-    <t>Mirna</t>
-  </si>
-  <si>
-    <t>Luis</t>
-  </si>
-  <si>
-    <t>Claudia M</t>
-  </si>
-  <si>
-    <t>Julio</t>
-  </si>
-  <si>
-    <t>Sandra</t>
-  </si>
-  <si>
-    <t>Romario</t>
-  </si>
-  <si>
-    <t>Rubi</t>
-  </si>
-  <si>
-    <t>Jacobo</t>
-  </si>
-  <si>
-    <t>Olivo</t>
-  </si>
-  <si>
-    <t>Claudia</t>
-  </si>
-  <si>
-    <t>Mayra</t>
-  </si>
-  <si>
-    <t>Joel</t>
-  </si>
-  <si>
-    <t>Yazareth</t>
-  </si>
-  <si>
-    <t>Salas</t>
-  </si>
-  <si>
-    <t>Gabriel</t>
-  </si>
-  <si>
-    <t>Paco</t>
-  </si>
-  <si>
-    <t>Delia</t>
+    <t>Gaby Rodríguez</t>
+  </si>
+  <si>
+    <t>Miriam Sarreón</t>
+  </si>
+  <si>
+    <t>Rafa Martínez</t>
+  </si>
+  <si>
+    <t>Mirna Sarreón</t>
+  </si>
+  <si>
+    <t>Luis Sarreón</t>
+  </si>
+  <si>
+    <t>Claudia Martínez</t>
+  </si>
+  <si>
+    <t>Julio Guillén</t>
+  </si>
+  <si>
+    <t>Sandra Jaramillo</t>
+  </si>
+  <si>
+    <t>Romario Velázquez</t>
+  </si>
+  <si>
+    <t>Rubi Muciño</t>
+  </si>
+  <si>
+    <t>Jacobo Sarreón</t>
+  </si>
+  <si>
+    <t>Marco Olivo</t>
+  </si>
+  <si>
+    <t>Claudia Sarreón</t>
+  </si>
+  <si>
+    <t>Mayra Sarreón</t>
+  </si>
+  <si>
+    <t>Joel Palomares</t>
+  </si>
+  <si>
+    <t>Yazareth Sánchez</t>
+  </si>
+  <si>
+    <t>Marco Salas</t>
+  </si>
+  <si>
+    <t>Gabriel Sarreón</t>
+  </si>
+  <si>
+    <t>Paco Sarreón</t>
   </si>
 </sst>
 </file>
@@ -536,8 +533,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}">
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -639,15 +639,15 @@
         <v>479</v>
       </c>
       <c r="J2">
-        <f>SUM(B2:E2)</f>
+        <f t="shared" ref="J2:J20" si="0">SUM(B2:E2)</f>
         <v>1852</v>
       </c>
       <c r="K2">
-        <f>SUM(F2:I2)</f>
+        <f t="shared" ref="K2:K20" si="1">SUM(F2:I2)</f>
         <v>2187</v>
       </c>
       <c r="L2">
-        <f>SUM(J2:K2)</f>
+        <f t="shared" ref="L2:L20" si="2">SUM(J2:K2)</f>
         <v>4039</v>
       </c>
       <c r="M2">
@@ -713,15 +713,15 @@
         <v>683</v>
       </c>
       <c r="J3">
-        <f>SUM(B3:E3)</f>
+        <f t="shared" si="0"/>
         <v>1328</v>
       </c>
       <c r="K3">
-        <f>SUM(F3:I3)</f>
+        <f t="shared" si="1"/>
         <v>2672</v>
       </c>
       <c r="L3">
-        <f>SUM(J3:K3)</f>
+        <f t="shared" si="2"/>
         <v>4000</v>
       </c>
       <c r="M3">
@@ -787,15 +787,15 @@
         <v>756</v>
       </c>
       <c r="J4">
-        <f>SUM(B4:E4)</f>
+        <f t="shared" si="0"/>
         <v>1036</v>
       </c>
       <c r="K4">
-        <f>SUM(F4:I4)</f>
+        <f t="shared" si="1"/>
         <v>2186</v>
       </c>
       <c r="L4">
-        <f>SUM(J4:K4)</f>
+        <f t="shared" si="2"/>
         <v>3222</v>
       </c>
       <c r="M4">
@@ -861,15 +861,15 @@
         <v>297</v>
       </c>
       <c r="J5">
-        <f>SUM(B5:E5)</f>
+        <f t="shared" si="0"/>
         <v>1361</v>
       </c>
       <c r="K5">
-        <f>SUM(F5:I5)</f>
+        <f t="shared" si="1"/>
         <v>1450</v>
       </c>
       <c r="L5">
-        <f>SUM(J5:K5)</f>
+        <f t="shared" si="2"/>
         <v>2811</v>
       </c>
       <c r="M5">
@@ -935,15 +935,15 @@
         <v>205</v>
       </c>
       <c r="J6">
-        <f>SUM(B6:E6)</f>
+        <f t="shared" si="0"/>
         <v>1527</v>
       </c>
       <c r="K6">
-        <f>SUM(F6:I6)</f>
+        <f t="shared" si="1"/>
         <v>833</v>
       </c>
       <c r="L6">
-        <f>SUM(J6:K6)</f>
+        <f t="shared" si="2"/>
         <v>2360</v>
       </c>
       <c r="M6">
@@ -1009,15 +1009,15 @@
         <v>265</v>
       </c>
       <c r="J7">
-        <f>SUM(B7:E7)</f>
+        <f t="shared" si="0"/>
         <v>977</v>
       </c>
       <c r="K7">
-        <f>SUM(F7:I7)</f>
+        <f t="shared" si="1"/>
         <v>1005</v>
       </c>
       <c r="L7">
-        <f>SUM(J7:K7)</f>
+        <f t="shared" si="2"/>
         <v>1982</v>
       </c>
       <c r="M7">
@@ -1083,15 +1083,15 @@
         <v>29</v>
       </c>
       <c r="J8">
-        <f>SUM(B8:E8)</f>
+        <f t="shared" si="0"/>
         <v>923</v>
       </c>
       <c r="K8">
-        <f>SUM(F8:I8)</f>
+        <f t="shared" si="1"/>
         <v>987</v>
       </c>
       <c r="L8">
-        <f>SUM(J8:K8)</f>
+        <f t="shared" si="2"/>
         <v>1910</v>
       </c>
       <c r="M8">
@@ -1157,15 +1157,15 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <f>SUM(B9:E9)</f>
+        <f t="shared" si="0"/>
         <v>1320</v>
       </c>
       <c r="K9">
-        <f>SUM(F9:I9)</f>
+        <f t="shared" si="1"/>
         <v>354</v>
       </c>
       <c r="L9">
-        <f>SUM(J9:K9)</f>
+        <f t="shared" si="2"/>
         <v>1674</v>
       </c>
       <c r="M9">
@@ -1231,15 +1231,15 @@
         <v>243</v>
       </c>
       <c r="J10">
-        <f>SUM(B10:E10)</f>
+        <f t="shared" si="0"/>
         <v>490</v>
       </c>
       <c r="K10">
-        <f>SUM(F10:I10)</f>
+        <f t="shared" si="1"/>
         <v>768</v>
       </c>
       <c r="L10">
-        <f>SUM(J10:K10)</f>
+        <f t="shared" si="2"/>
         <v>1258</v>
       </c>
       <c r="M10">
@@ -1305,15 +1305,15 @@
         <v>195</v>
       </c>
       <c r="J11">
-        <f>SUM(B11:E11)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K11">
-        <f>SUM(F11:I11)</f>
+        <f t="shared" si="1"/>
         <v>1042</v>
       </c>
       <c r="L11">
-        <f>SUM(J11:K11)</f>
+        <f t="shared" si="2"/>
         <v>1042</v>
       </c>
       <c r="M11">
@@ -1379,15 +1379,15 @@
         <v>207</v>
       </c>
       <c r="J12">
-        <f>SUM(B12:E12)</f>
+        <f t="shared" si="0"/>
         <v>382</v>
       </c>
       <c r="K12">
-        <f>SUM(F12:I12)</f>
+        <f t="shared" si="1"/>
         <v>614</v>
       </c>
       <c r="L12">
-        <f>SUM(J12:K12)</f>
+        <f t="shared" si="2"/>
         <v>996</v>
       </c>
       <c r="M12">
@@ -1453,15 +1453,15 @@
         <v>183</v>
       </c>
       <c r="J13">
-        <f>SUM(B13:E13)</f>
+        <f t="shared" si="0"/>
         <v>347</v>
       </c>
       <c r="K13">
-        <f>SUM(F13:I13)</f>
+        <f t="shared" si="1"/>
         <v>544</v>
       </c>
       <c r="L13">
-        <f>SUM(J13:K13)</f>
+        <f t="shared" si="2"/>
         <v>891</v>
       </c>
       <c r="M13">
@@ -1527,15 +1527,15 @@
         <v>95</v>
       </c>
       <c r="J14">
-        <f>SUM(B14:E14)</f>
+        <f t="shared" si="0"/>
         <v>310</v>
       </c>
       <c r="K14">
-        <f>SUM(F14:I14)</f>
+        <f t="shared" si="1"/>
         <v>542</v>
       </c>
       <c r="L14">
-        <f>SUM(J14:K14)</f>
+        <f t="shared" si="2"/>
         <v>852</v>
       </c>
       <c r="M14">
@@ -1601,15 +1601,15 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <f>SUM(B15:E15)</f>
+        <f t="shared" si="0"/>
         <v>548</v>
       </c>
       <c r="K15">
-        <f>SUM(F15:I15)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L15">
-        <f>SUM(J15:K15)</f>
+        <f t="shared" si="2"/>
         <v>548</v>
       </c>
       <c r="M15">
@@ -1675,15 +1675,15 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <f>SUM(B16:E16)</f>
+        <f t="shared" si="0"/>
         <v>528</v>
       </c>
       <c r="K16">
-        <f>SUM(F16:I16)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L16">
-        <f>SUM(J16:K16)</f>
+        <f t="shared" si="2"/>
         <v>528</v>
       </c>
       <c r="M16">
@@ -1749,15 +1749,15 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <f>SUM(B17:E17)</f>
+        <f t="shared" si="0"/>
         <v>448</v>
       </c>
       <c r="K17">
-        <f>SUM(F17:I17)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L17">
-        <f>SUM(J17:K17)</f>
+        <f t="shared" si="2"/>
         <v>448</v>
       </c>
       <c r="M17">
@@ -1823,15 +1823,15 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <f>SUM(B18:E18)</f>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="K18">
-        <f>SUM(F18:I18)</f>
+        <f t="shared" si="1"/>
         <v>234</v>
       </c>
       <c r="L18">
-        <f>SUM(J18:K18)</f>
+        <f t="shared" si="2"/>
         <v>275</v>
       </c>
       <c r="M18">
@@ -1897,15 +1897,15 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <f>SUM(B19:E19)</f>
+        <f t="shared" si="0"/>
         <v>67</v>
       </c>
       <c r="K19">
-        <f>SUM(F19:I19)</f>
+        <f t="shared" si="1"/>
         <v>104</v>
       </c>
       <c r="L19">
-        <f>SUM(J19:K19)</f>
+        <f t="shared" si="2"/>
         <v>171</v>
       </c>
       <c r="M19">
@@ -1971,15 +1971,15 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <f>SUM(B20:E20)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K20">
-        <f>SUM(F20:I20)</f>
+        <f t="shared" si="1"/>
         <v>96</v>
       </c>
       <c r="L20">
-        <f>SUM(J20:K20)</f>
+        <f t="shared" si="2"/>
         <v>96</v>
       </c>
       <c r="M20">
@@ -2014,80 +2014,6 @@
       </c>
       <c r="W20">
         <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <f>SUM(B21:E21)</f>
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <f>SUM(F21:I21)</f>
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <f>SUM(J21:K21)</f>
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>15</v>
-      </c>
-      <c r="N21">
-        <v>15</v>
-      </c>
-      <c r="O21">
-        <v>13</v>
-      </c>
-      <c r="P21">
-        <v>13</v>
-      </c>
-      <c r="Q21">
-        <v>16</v>
-      </c>
-      <c r="R21">
-        <v>13</v>
-      </c>
-      <c r="S21">
-        <v>13</v>
-      </c>
-      <c r="T21">
-        <v>13</v>
-      </c>
-      <c r="U21">
-        <v>18</v>
-      </c>
-      <c r="V21">
-        <v>17</v>
-      </c>
-      <c r="W21">
-        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F2A06A8-3C91-42BD-AB63-FDF98753FCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DDD17D5-D33B-446A-87D1-BE0D50D854A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7EB6C2C6-840C-4838-9636-758ACFA0B514}"/>
   </bookViews>
@@ -636,7 +636,7 @@
         <v>493</v>
       </c>
       <c r="I2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J2">
         <f t="shared" ref="J2:J20" si="0">SUM(B2:E2)</f>
@@ -644,11 +644,11 @@
       </c>
       <c r="K2">
         <f t="shared" ref="K2:K20" si="1">SUM(F2:I2)</f>
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="L2">
         <f t="shared" ref="L2:L20" si="2">SUM(J2:K2)</f>
-        <v>4039</v>
+        <v>4038</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -784,7 +784,7 @@
         <v>488</v>
       </c>
       <c r="I4">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="J4">
         <f t="shared" si="0"/>
@@ -792,11 +792,11 @@
       </c>
       <c r="K4">
         <f t="shared" si="1"/>
-        <v>2186</v>
+        <v>2184</v>
       </c>
       <c r="L4">
         <f t="shared" si="2"/>
-        <v>3222</v>
+        <v>3220</v>
       </c>
       <c r="M4">
         <v>15</v>
@@ -932,7 +932,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
@@ -940,11 +940,11 @@
       </c>
       <c r="K6">
         <f t="shared" si="1"/>
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L6">
         <f t="shared" si="2"/>
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="M6">
         <v>7</v>
@@ -1450,7 +1450,7 @@
         <v>109</v>
       </c>
       <c r="I13">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J13">
         <f t="shared" si="0"/>
@@ -1458,11 +1458,11 @@
       </c>
       <c r="K13">
         <f t="shared" si="1"/>
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="L13">
         <f t="shared" si="2"/>
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="M13">
         <v>14</v>
@@ -1524,7 +1524,7 @@
         <v>156</v>
       </c>
       <c r="I14">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="J14">
         <f t="shared" si="0"/>
@@ -1532,11 +1532,11 @@
       </c>
       <c r="K14">
         <f t="shared" si="1"/>
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="L14">
         <f t="shared" si="2"/>
-        <v>852</v>
+        <v>862</v>
       </c>
       <c r="M14">
         <v>15</v>

--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DDD17D5-D33B-446A-87D1-BE0D50D854A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD29621-3F5F-40AE-94CF-25F82B8EB946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7EB6C2C6-840C-4838-9636-758ACFA0B514}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>Nombre</t>
   </si>
@@ -162,6 +162,21 @@
   </si>
   <si>
     <t>Paco Sarreón</t>
+  </si>
+  <si>
+    <t>Semana 9</t>
+  </si>
+  <si>
+    <t>Delia Narváez</t>
+  </si>
+  <si>
+    <t>Subt. M3</t>
+  </si>
+  <si>
+    <t>Ranking 9</t>
+  </si>
+  <si>
+    <t>Ranking Mens. 3</t>
   </si>
 </sst>
 </file>
@@ -533,13 +548,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}">
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:AA21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -568,49 +583,61 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
+        <v>45</v>
+      </c>
+      <c r="X1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="Y1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Z1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -639,31 +666,32 @@
         <v>478</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2:J20" si="0">SUM(B2:E2)</f>
+        <v>524</v>
+      </c>
+      <c r="K2">
+        <f>SUM(B2:E2)</f>
         <v>1852</v>
       </c>
-      <c r="K2">
-        <f t="shared" ref="K2:K20" si="1">SUM(F2:I2)</f>
+      <c r="L2">
+        <f>SUM(F2:I2)</f>
         <v>2186</v>
       </c>
-      <c r="L2">
-        <f t="shared" ref="L2:L20" si="2">SUM(J2:K2)</f>
-        <v>4038</v>
-      </c>
       <c r="M2">
+        <f>J2</f>
+        <v>524</v>
+      </c>
+      <c r="N2">
+        <f>SUM(K2:M2)</f>
+        <v>4562</v>
+      </c>
+      <c r="O2">
         <v>1</v>
-      </c>
-      <c r="N2">
-        <v>3</v>
-      </c>
-      <c r="O2">
-        <v>5</v>
       </c>
       <c r="P2">
         <v>3</v>
       </c>
       <c r="Q2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R2">
         <v>3</v>
@@ -675,16 +703,28 @@
         <v>3</v>
       </c>
       <c r="U2">
+        <v>2</v>
+      </c>
+      <c r="V2">
+        <v>3</v>
+      </c>
+      <c r="W2">
+        <v>3</v>
+      </c>
+      <c r="X2">
         <v>1</v>
       </c>
-      <c r="V2">
+      <c r="Y2">
         <v>2</v>
       </c>
-      <c r="W2">
+      <c r="Z2">
+        <v>3</v>
+      </c>
+      <c r="AA2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -713,52 +753,65 @@
         <v>683</v>
       </c>
       <c r="J3">
-        <f t="shared" si="0"/>
+        <v>513</v>
+      </c>
+      <c r="K3">
+        <f>SUM(B3:E3)</f>
         <v>1328</v>
       </c>
-      <c r="K3">
-        <f t="shared" si="1"/>
+      <c r="L3">
+        <f>SUM(F3:I3)</f>
         <v>2672</v>
       </c>
-      <c r="L3">
-        <f t="shared" si="2"/>
-        <v>4000</v>
-      </c>
       <c r="M3">
+        <f>J3</f>
+        <v>513</v>
+      </c>
+      <c r="N3">
+        <f>SUM(K3:M3)</f>
+        <v>4513</v>
+      </c>
+      <c r="O3">
         <v>12</v>
       </c>
-      <c r="N3">
+      <c r="P3">
         <v>5</v>
       </c>
-      <c r="O3">
+      <c r="Q3">
         <v>6</v>
       </c>
-      <c r="P3">
+      <c r="R3">
         <v>2</v>
-      </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>1</v>
       </c>
       <c r="S3">
         <v>1</v>
       </c>
       <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="V3">
         <v>2</v>
       </c>
-      <c r="U3">
+      <c r="W3">
+        <v>5</v>
+      </c>
+      <c r="X3">
         <v>4</v>
       </c>
-      <c r="V3">
+      <c r="Y3">
         <v>1</v>
       </c>
-      <c r="W3">
+      <c r="Z3">
+        <v>5</v>
+      </c>
+      <c r="AA3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -787,52 +840,65 @@
         <v>754</v>
       </c>
       <c r="J4">
-        <f t="shared" si="0"/>
+        <v>539</v>
+      </c>
+      <c r="K4">
+        <f>SUM(B4:E4)</f>
         <v>1036</v>
       </c>
-      <c r="K4">
-        <f t="shared" si="1"/>
+      <c r="L4">
+        <f>SUM(F4:I4)</f>
         <v>2184</v>
       </c>
-      <c r="L4">
-        <f t="shared" si="2"/>
-        <v>3220</v>
-      </c>
       <c r="M4">
+        <f>J4</f>
+        <v>539</v>
+      </c>
+      <c r="N4">
+        <f>SUM(K4:M4)</f>
+        <v>3759</v>
+      </c>
+      <c r="O4">
         <v>15</v>
       </c>
-      <c r="N4">
+      <c r="P4">
         <v>10</v>
       </c>
-      <c r="O4">
+      <c r="Q4">
         <v>8</v>
       </c>
-      <c r="P4">
+      <c r="R4">
         <v>1</v>
-      </c>
-      <c r="Q4">
-        <v>3</v>
-      </c>
-      <c r="R4">
-        <v>4</v>
       </c>
       <c r="S4">
         <v>3</v>
       </c>
       <c r="T4">
+        <v>4</v>
+      </c>
+      <c r="U4">
+        <v>3</v>
+      </c>
+      <c r="V4">
         <v>1</v>
       </c>
-      <c r="U4">
+      <c r="W4">
+        <v>2</v>
+      </c>
+      <c r="X4">
         <v>6</v>
       </c>
-      <c r="V4">
+      <c r="Y4">
         <v>3</v>
       </c>
-      <c r="W4">
+      <c r="Z4">
+        <v>2</v>
+      </c>
+      <c r="AA4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -861,52 +927,65 @@
         <v>297</v>
       </c>
       <c r="J5">
-        <f t="shared" si="0"/>
+        <v>470</v>
+      </c>
+      <c r="K5">
+        <f>SUM(B5:E5)</f>
         <v>1361</v>
       </c>
-      <c r="K5">
-        <f t="shared" si="1"/>
+      <c r="L5">
+        <f>SUM(F5:I5)</f>
         <v>1450</v>
       </c>
-      <c r="L5">
-        <f t="shared" si="2"/>
-        <v>2811</v>
-      </c>
       <c r="M5">
+        <f>J5</f>
+        <v>470</v>
+      </c>
+      <c r="N5">
+        <f>SUM(K5:M5)</f>
+        <v>3281</v>
+      </c>
+      <c r="O5">
         <v>9</v>
       </c>
-      <c r="N5">
+      <c r="P5">
         <v>4</v>
       </c>
-      <c r="O5">
+      <c r="Q5">
         <v>1</v>
-      </c>
-      <c r="P5">
-        <v>5</v>
-      </c>
-      <c r="Q5">
-        <v>7</v>
       </c>
       <c r="R5">
         <v>5</v>
       </c>
       <c r="S5">
+        <v>7</v>
+      </c>
+      <c r="T5">
+        <v>5</v>
+      </c>
+      <c r="U5">
         <v>4</v>
-      </c>
-      <c r="T5">
-        <v>4</v>
-      </c>
-      <c r="U5">
-        <v>3</v>
       </c>
       <c r="V5">
         <v>4</v>
       </c>
       <c r="W5">
+        <v>6</v>
+      </c>
+      <c r="X5">
+        <v>3</v>
+      </c>
+      <c r="Y5">
         <v>4</v>
       </c>
+      <c r="Z5">
+        <v>6</v>
+      </c>
+      <c r="AA5">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -935,170 +1014,197 @@
         <v>204</v>
       </c>
       <c r="J6">
-        <f t="shared" si="0"/>
+        <v>599</v>
+      </c>
+      <c r="K6">
+        <f>SUM(B6:E6)</f>
         <v>1527</v>
       </c>
-      <c r="K6">
-        <f t="shared" si="1"/>
+      <c r="L6">
+        <f>SUM(F6:I6)</f>
         <v>832</v>
       </c>
-      <c r="L6">
-        <f t="shared" si="2"/>
-        <v>2359</v>
-      </c>
       <c r="M6">
+        <f>J6</f>
+        <v>599</v>
+      </c>
+      <c r="N6">
+        <f>SUM(K6:M6)</f>
+        <v>2958</v>
+      </c>
+      <c r="O6">
         <v>7</v>
       </c>
-      <c r="N6">
+      <c r="P6">
         <v>1</v>
       </c>
-      <c r="O6">
+      <c r="Q6">
         <v>3</v>
       </c>
-      <c r="P6">
+      <c r="R6">
         <v>4</v>
       </c>
-      <c r="Q6">
+      <c r="S6">
         <v>4</v>
       </c>
-      <c r="R6">
+      <c r="T6">
         <v>9</v>
       </c>
-      <c r="S6">
-        <v>13</v>
-      </c>
-      <c r="T6">
-        <v>8</v>
-      </c>
       <c r="U6">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="V6">
         <v>8</v>
       </c>
       <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>2</v>
+      </c>
+      <c r="Y6">
+        <v>8</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7">
+        <v>140</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>496</v>
+      </c>
+      <c r="E7">
+        <v>287</v>
+      </c>
+      <c r="F7">
+        <v>90</v>
+      </c>
+      <c r="G7">
+        <v>571</v>
+      </c>
+      <c r="H7">
+        <v>297</v>
+      </c>
+      <c r="I7">
+        <v>29</v>
+      </c>
+      <c r="J7">
+        <v>432</v>
+      </c>
+      <c r="K7">
+        <f>SUM(B7:E7)</f>
+        <v>923</v>
+      </c>
+      <c r="L7">
+        <f>SUM(F7:I7)</f>
+        <v>987</v>
+      </c>
+      <c r="M7">
+        <f>J7</f>
+        <v>432</v>
+      </c>
+      <c r="N7">
+        <f>SUM(K7:M7)</f>
+        <v>2342</v>
+      </c>
+      <c r="O7">
+        <v>8</v>
+      </c>
+      <c r="P7">
+        <v>15</v>
+      </c>
+      <c r="Q7">
+        <v>4</v>
+      </c>
+      <c r="R7">
+        <v>6</v>
+      </c>
+      <c r="S7">
+        <v>14</v>
+      </c>
+      <c r="T7">
+        <v>2</v>
+      </c>
+      <c r="U7">
+        <v>6</v>
+      </c>
+      <c r="V7">
+        <v>12</v>
+      </c>
+      <c r="W7">
+        <v>7</v>
+      </c>
+      <c r="X7">
+        <v>8</v>
+      </c>
+      <c r="Y7">
+        <v>7</v>
+      </c>
+      <c r="Z7">
+        <v>7</v>
+      </c>
+      <c r="AA7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>28</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>205</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>280</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <v>284</v>
       </c>
-      <c r="E7">
+      <c r="E8">
         <v>208</v>
       </c>
-      <c r="F7">
+      <c r="F8">
         <v>318</v>
       </c>
-      <c r="G7">
+      <c r="G8">
         <v>162</v>
       </c>
-      <c r="H7">
+      <c r="H8">
         <v>260</v>
       </c>
-      <c r="I7">
+      <c r="I8">
         <v>265</v>
       </c>
-      <c r="J7">
-        <f t="shared" si="0"/>
+      <c r="J8">
+        <v>252</v>
+      </c>
+      <c r="K8">
+        <f>SUM(B8:E8)</f>
         <v>977</v>
       </c>
-      <c r="K7">
-        <f t="shared" si="1"/>
+      <c r="L8">
+        <f>SUM(F8:I8)</f>
         <v>1005</v>
       </c>
-      <c r="L7">
-        <f t="shared" si="2"/>
-        <v>1982</v>
-      </c>
-      <c r="M7">
-        <v>4</v>
-      </c>
-      <c r="N7">
-        <v>6</v>
-      </c>
-      <c r="O7">
-        <v>7</v>
-      </c>
-      <c r="P7">
-        <v>10</v>
-      </c>
-      <c r="Q7">
-        <v>6</v>
-      </c>
-      <c r="R7">
-        <v>10</v>
-      </c>
-      <c r="S7">
-        <v>7</v>
-      </c>
-      <c r="T7">
-        <v>5</v>
-      </c>
-      <c r="U7">
-        <v>7</v>
-      </c>
-      <c r="V7">
-        <v>6</v>
-      </c>
-      <c r="W7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8">
-        <v>140</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>496</v>
-      </c>
-      <c r="E8">
-        <v>287</v>
-      </c>
-      <c r="F8">
-        <v>90</v>
-      </c>
-      <c r="G8">
-        <v>571</v>
-      </c>
-      <c r="H8">
-        <v>297</v>
-      </c>
-      <c r="I8">
-        <v>29</v>
-      </c>
-      <c r="J8">
-        <f t="shared" si="0"/>
-        <v>923</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="1"/>
-        <v>987</v>
-      </c>
-      <c r="L8">
-        <f t="shared" si="2"/>
-        <v>1910</v>
-      </c>
       <c r="M8">
-        <v>8</v>
+        <f>J8</f>
+        <v>252</v>
       </c>
       <c r="N8">
-        <v>15</v>
+        <f>SUM(K8:M8)</f>
+        <v>2234</v>
       </c>
       <c r="O8">
         <v>4</v>
@@ -1107,28 +1213,40 @@
         <v>6</v>
       </c>
       <c r="Q8">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>6</v>
       </c>
       <c r="T8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V8">
+        <v>5</v>
+      </c>
+      <c r="W8">
+        <v>9</v>
+      </c>
+      <c r="X8">
         <v>7</v>
       </c>
-      <c r="W8">
+      <c r="Y8">
+        <v>6</v>
+      </c>
+      <c r="Z8">
+        <v>9</v>
+      </c>
+      <c r="AA8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -1157,43 +1275,44 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <f t="shared" si="0"/>
+        <v>352</v>
+      </c>
+      <c r="K9">
+        <f>SUM(B9:E9)</f>
         <v>1320</v>
       </c>
-      <c r="K9">
-        <f t="shared" si="1"/>
+      <c r="L9">
+        <f>SUM(F9:I9)</f>
         <v>354</v>
       </c>
-      <c r="L9">
-        <f t="shared" si="2"/>
-        <v>1674</v>
-      </c>
       <c r="M9">
-        <v>13</v>
+        <f>J9</f>
+        <v>352</v>
       </c>
       <c r="N9">
+        <f>SUM(K9:M9)</f>
+        <v>2026</v>
+      </c>
+      <c r="O9">
+        <v>13</v>
+      </c>
+      <c r="P9">
         <v>2</v>
       </c>
-      <c r="O9">
+      <c r="Q9">
         <v>2</v>
       </c>
-      <c r="P9">
+      <c r="R9">
         <v>9</v>
       </c>
-      <c r="Q9">
+      <c r="S9">
         <v>5</v>
       </c>
-      <c r="R9">
-        <v>13</v>
-      </c>
-      <c r="S9">
-        <v>13</v>
-      </c>
       <c r="T9">
         <v>13</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="V9">
         <v>13</v>
@@ -1201,8 +1320,20 @@
       <c r="W9">
         <v>8</v>
       </c>
+      <c r="X9">
+        <v>5</v>
+      </c>
+      <c r="Y9">
+        <v>13</v>
+      </c>
+      <c r="Z9">
+        <v>8</v>
+      </c>
+      <c r="AA9">
+        <v>8</v>
+      </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -1231,52 +1362,65 @@
         <v>243</v>
       </c>
       <c r="J10">
-        <f t="shared" si="0"/>
+        <v>518</v>
+      </c>
+      <c r="K10">
+        <f>SUM(B10:E10)</f>
         <v>490</v>
       </c>
-      <c r="K10">
-        <f t="shared" si="1"/>
+      <c r="L10">
+        <f>SUM(F10:I10)</f>
         <v>768</v>
       </c>
-      <c r="L10">
-        <f t="shared" si="2"/>
-        <v>1258</v>
-      </c>
       <c r="M10">
+        <f>J10</f>
+        <v>518</v>
+      </c>
+      <c r="N10">
+        <f>SUM(K10:M10)</f>
+        <v>1776</v>
+      </c>
+      <c r="O10">
         <v>10</v>
       </c>
-      <c r="N10">
+      <c r="P10">
         <v>8</v>
       </c>
-      <c r="O10">
+      <c r="Q10">
         <v>9</v>
       </c>
-      <c r="P10">
-        <v>13</v>
-      </c>
-      <c r="Q10">
+      <c r="R10">
+        <v>13</v>
+      </c>
+      <c r="S10">
         <v>15</v>
-      </c>
-      <c r="R10">
-        <v>6</v>
-      </c>
-      <c r="S10">
-        <v>8</v>
       </c>
       <c r="T10">
         <v>6</v>
       </c>
       <c r="U10">
+        <v>8</v>
+      </c>
+      <c r="V10">
+        <v>6</v>
+      </c>
+      <c r="W10">
+        <v>4</v>
+      </c>
+      <c r="X10">
         <v>11</v>
       </c>
-      <c r="V10">
+      <c r="Y10">
         <v>9</v>
       </c>
-      <c r="W10">
+      <c r="Z10">
+        <v>4</v>
+      </c>
+      <c r="AA10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -1305,52 +1449,65 @@
         <v>195</v>
       </c>
       <c r="J11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="K11">
-        <f t="shared" si="1"/>
+        <f>SUM(B11:E11)</f>
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <f>SUM(F11:I11)</f>
         <v>1042</v>
       </c>
-      <c r="L11">
-        <f t="shared" si="2"/>
-        <v>1042</v>
-      </c>
       <c r="M11">
+        <f>J11</f>
+        <v>179</v>
+      </c>
+      <c r="N11">
+        <f>SUM(K11:M11)</f>
+        <v>1221</v>
+      </c>
+      <c r="O11">
         <v>15</v>
       </c>
-      <c r="N11">
+      <c r="P11">
         <v>15</v>
       </c>
-      <c r="O11">
-        <v>13</v>
-      </c>
-      <c r="P11">
-        <v>13</v>
-      </c>
       <c r="Q11">
+        <v>13</v>
+      </c>
+      <c r="R11">
+        <v>13</v>
+      </c>
+      <c r="S11">
         <v>8</v>
       </c>
-      <c r="R11">
+      <c r="T11">
         <v>8</v>
       </c>
-      <c r="S11">
+      <c r="U11">
         <v>5</v>
       </c>
-      <c r="T11">
+      <c r="V11">
         <v>9</v>
       </c>
-      <c r="U11">
+      <c r="W11">
+        <v>11</v>
+      </c>
+      <c r="X11">
         <v>18</v>
       </c>
-      <c r="V11">
+      <c r="Y11">
         <v>5</v>
       </c>
-      <c r="W11">
+      <c r="Z11">
+        <v>11</v>
+      </c>
+      <c r="AA11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1379,37 +1536,38 @@
         <v>207</v>
       </c>
       <c r="J12">
-        <f t="shared" si="0"/>
+        <v>209</v>
+      </c>
+      <c r="K12">
+        <f>SUM(B12:E12)</f>
         <v>382</v>
       </c>
-      <c r="K12">
-        <f t="shared" si="1"/>
+      <c r="L12">
+        <f>SUM(F12:I12)</f>
         <v>614</v>
       </c>
-      <c r="L12">
-        <f t="shared" si="2"/>
-        <v>996</v>
-      </c>
       <c r="M12">
+        <f>J12</f>
+        <v>209</v>
+      </c>
+      <c r="N12">
+        <f>SUM(K12:M12)</f>
+        <v>1205</v>
+      </c>
+      <c r="O12">
         <v>5</v>
       </c>
-      <c r="N12">
+      <c r="P12">
         <v>9</v>
       </c>
-      <c r="O12">
-        <v>13</v>
-      </c>
-      <c r="P12">
-        <v>13</v>
-      </c>
       <c r="Q12">
+        <v>13</v>
+      </c>
+      <c r="R12">
+        <v>13</v>
+      </c>
+      <c r="S12">
         <v>12</v>
-      </c>
-      <c r="R12">
-        <v>7</v>
-      </c>
-      <c r="S12">
-        <v>13</v>
       </c>
       <c r="T12">
         <v>7</v>
@@ -1418,13 +1576,25 @@
         <v>13</v>
       </c>
       <c r="V12">
+        <v>7</v>
+      </c>
+      <c r="W12">
         <v>10</v>
       </c>
-      <c r="W12">
+      <c r="X12">
+        <v>13</v>
+      </c>
+      <c r="Y12">
+        <v>10</v>
+      </c>
+      <c r="Z12">
+        <v>10</v>
+      </c>
+      <c r="AA12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -1453,28 +1623,29 @@
         <v>181</v>
       </c>
       <c r="J13">
-        <f t="shared" si="0"/>
+        <v>158</v>
+      </c>
+      <c r="K13">
+        <f>SUM(B13:E13)</f>
         <v>347</v>
       </c>
-      <c r="K13">
-        <f t="shared" si="1"/>
+      <c r="L13">
+        <f>SUM(F13:I13)</f>
         <v>542</v>
       </c>
-      <c r="L13">
-        <f t="shared" si="2"/>
-        <v>889</v>
-      </c>
       <c r="M13">
+        <f>J13</f>
+        <v>158</v>
+      </c>
+      <c r="N13">
+        <f>SUM(K13:M13)</f>
+        <v>1047</v>
+      </c>
+      <c r="O13">
         <v>14</v>
       </c>
-      <c r="N13">
+      <c r="P13">
         <v>14</v>
-      </c>
-      <c r="O13">
-        <v>10</v>
-      </c>
-      <c r="P13">
-        <v>12</v>
       </c>
       <c r="Q13">
         <v>10</v>
@@ -1486,19 +1657,31 @@
         <v>10</v>
       </c>
       <c r="T13">
+        <v>12</v>
+      </c>
+      <c r="U13">
         <v>10</v>
       </c>
-      <c r="U13">
+      <c r="V13">
+        <v>10</v>
+      </c>
+      <c r="W13">
+        <v>13</v>
+      </c>
+      <c r="X13">
         <v>14</v>
       </c>
-      <c r="V13">
+      <c r="Y13">
         <v>11</v>
       </c>
-      <c r="W13">
+      <c r="Z13">
+        <v>13</v>
+      </c>
+      <c r="AA13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -1527,28 +1710,29 @@
         <v>105</v>
       </c>
       <c r="J14">
-        <f t="shared" si="0"/>
+        <v>114</v>
+      </c>
+      <c r="K14">
+        <f>SUM(B14:E14)</f>
         <v>310</v>
       </c>
-      <c r="K14">
-        <f t="shared" si="1"/>
+      <c r="L14">
+        <f>SUM(F14:I14)</f>
         <v>552</v>
       </c>
-      <c r="L14">
-        <f t="shared" si="2"/>
-        <v>862</v>
-      </c>
       <c r="M14">
+        <f>J14</f>
+        <v>114</v>
+      </c>
+      <c r="N14">
+        <f>SUM(K14:M14)</f>
+        <v>976</v>
+      </c>
+      <c r="O14">
         <v>15</v>
       </c>
-      <c r="N14">
-        <v>13</v>
-      </c>
-      <c r="O14">
-        <v>11</v>
-      </c>
       <c r="P14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q14">
         <v>11</v>
@@ -1557,22 +1741,34 @@
         <v>11</v>
       </c>
       <c r="S14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T14">
         <v>11</v>
       </c>
       <c r="U14">
+        <v>9</v>
+      </c>
+      <c r="V14">
+        <v>11</v>
+      </c>
+      <c r="W14">
+        <v>14</v>
+      </c>
+      <c r="X14">
         <v>15</v>
       </c>
-      <c r="V14">
+      <c r="Y14">
         <v>12</v>
       </c>
-      <c r="W14">
+      <c r="Z14">
+        <v>14</v>
+      </c>
+      <c r="AA14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -1601,52 +1797,65 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <f>SUM(B15:E15)</f>
         <v>548</v>
       </c>
-      <c r="K15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="L15">
-        <f t="shared" si="2"/>
+        <f>SUM(F15:I15)</f>
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <f>J15</f>
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <f>SUM(K15:M15)</f>
         <v>548</v>
       </c>
-      <c r="M15">
+      <c r="O15">
         <v>3</v>
       </c>
-      <c r="N15">
+      <c r="P15">
         <v>11</v>
       </c>
-      <c r="O15">
-        <v>13</v>
-      </c>
-      <c r="P15">
+      <c r="Q15">
+        <v>13</v>
+      </c>
+      <c r="R15">
         <v>7</v>
       </c>
-      <c r="Q15">
+      <c r="S15">
         <v>16</v>
       </c>
-      <c r="R15">
-        <v>13</v>
-      </c>
-      <c r="S15">
-        <v>13</v>
-      </c>
       <c r="T15">
         <v>13</v>
       </c>
       <c r="U15">
+        <v>13</v>
+      </c>
+      <c r="V15">
+        <v>13</v>
+      </c>
+      <c r="W15">
+        <v>16</v>
+      </c>
+      <c r="X15">
         <v>9</v>
       </c>
-      <c r="V15">
+      <c r="Y15">
         <v>17</v>
       </c>
-      <c r="W15">
+      <c r="Z15">
+        <v>16</v>
+      </c>
+      <c r="AA15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -1675,52 +1884,65 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <f>SUM(B16:E16)</f>
         <v>528</v>
       </c>
-      <c r="K16">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="L16">
-        <f t="shared" si="2"/>
+        <f>SUM(F16:I16)</f>
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <f>J16</f>
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <f>SUM(K16:M16)</f>
         <v>528</v>
       </c>
-      <c r="M16">
+      <c r="O16">
         <v>2</v>
       </c>
-      <c r="N16">
+      <c r="P16">
         <v>12</v>
       </c>
-      <c r="O16">
-        <v>13</v>
-      </c>
-      <c r="P16">
+      <c r="Q16">
+        <v>13</v>
+      </c>
+      <c r="R16">
         <v>8</v>
       </c>
-      <c r="Q16">
+      <c r="S16">
         <v>16</v>
       </c>
-      <c r="R16">
-        <v>13</v>
-      </c>
-      <c r="S16">
-        <v>13</v>
-      </c>
       <c r="T16">
         <v>13</v>
       </c>
       <c r="U16">
+        <v>13</v>
+      </c>
+      <c r="V16">
+        <v>13</v>
+      </c>
+      <c r="W16">
+        <v>16</v>
+      </c>
+      <c r="X16">
         <v>10</v>
       </c>
-      <c r="V16">
+      <c r="Y16">
         <v>17</v>
       </c>
-      <c r="W16">
+      <c r="Z16">
+        <v>16</v>
+      </c>
+      <c r="AA16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1749,52 +1971,65 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <f>SUM(B17:E17)</f>
         <v>448</v>
       </c>
-      <c r="K17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="L17">
-        <f t="shared" si="2"/>
+        <f>SUM(F17:I17)</f>
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <f>J17</f>
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <f>SUM(K17:M17)</f>
         <v>448</v>
       </c>
-      <c r="M17">
+      <c r="O17">
         <v>6</v>
       </c>
-      <c r="N17">
+      <c r="P17">
         <v>7</v>
       </c>
-      <c r="O17">
-        <v>13</v>
-      </c>
-      <c r="P17">
-        <v>13</v>
-      </c>
       <c r="Q17">
+        <v>13</v>
+      </c>
+      <c r="R17">
+        <v>13</v>
+      </c>
+      <c r="S17">
         <v>16</v>
       </c>
-      <c r="R17">
-        <v>13</v>
-      </c>
-      <c r="S17">
-        <v>13</v>
-      </c>
       <c r="T17">
         <v>13</v>
       </c>
       <c r="U17">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V17">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="W17">
         <v>16</v>
       </c>
+      <c r="X17">
+        <v>12</v>
+      </c>
+      <c r="Y17">
+        <v>17</v>
+      </c>
+      <c r="Z17">
+        <v>16</v>
+      </c>
+      <c r="AA17">
+        <v>16</v>
+      </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -1823,52 +2058,65 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="K18">
+        <f>SUM(B18:E18)</f>
         <v>41</v>
       </c>
-      <c r="K18">
-        <f t="shared" si="1"/>
+      <c r="L18">
+        <f>SUM(F18:I18)</f>
         <v>234</v>
       </c>
-      <c r="L18">
-        <f t="shared" si="2"/>
-        <v>275</v>
-      </c>
       <c r="M18">
+        <f>J18</f>
+        <v>19</v>
+      </c>
+      <c r="N18">
+        <f>SUM(K18:M18)</f>
+        <v>294</v>
+      </c>
+      <c r="O18">
         <v>15</v>
       </c>
-      <c r="N18">
+      <c r="P18">
         <v>15</v>
       </c>
-      <c r="O18">
+      <c r="Q18">
         <v>12</v>
       </c>
-      <c r="P18">
-        <v>13</v>
-      </c>
-      <c r="Q18">
+      <c r="R18">
+        <v>13</v>
+      </c>
+      <c r="S18">
         <v>9</v>
       </c>
-      <c r="R18">
-        <v>13</v>
-      </c>
-      <c r="S18">
+      <c r="T18">
+        <v>13</v>
+      </c>
+      <c r="U18">
         <v>12</v>
       </c>
-      <c r="T18">
-        <v>13</v>
-      </c>
-      <c r="U18">
+      <c r="V18">
+        <v>13</v>
+      </c>
+      <c r="W18">
+        <v>15</v>
+      </c>
+      <c r="X18">
         <v>17</v>
       </c>
-      <c r="V18">
+      <c r="Y18">
         <v>14</v>
       </c>
-      <c r="W18">
+      <c r="Z18">
+        <v>15</v>
+      </c>
+      <c r="AA18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -1897,126 +2145,242 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <f>SUM(B19:E19)</f>
         <v>67</v>
       </c>
-      <c r="K19">
-        <f t="shared" si="1"/>
+      <c r="L19">
+        <f>SUM(F19:I19)</f>
         <v>104</v>
       </c>
-      <c r="L19">
-        <f t="shared" si="2"/>
+      <c r="M19">
+        <f>J19</f>
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <f>SUM(K19:M19)</f>
         <v>171</v>
       </c>
-      <c r="M19">
+      <c r="O19">
         <v>11</v>
       </c>
-      <c r="N19">
+      <c r="P19">
         <v>15</v>
       </c>
-      <c r="O19">
-        <v>13</v>
-      </c>
-      <c r="P19">
-        <v>13</v>
-      </c>
       <c r="Q19">
+        <v>13</v>
+      </c>
+      <c r="R19">
+        <v>13</v>
+      </c>
+      <c r="S19">
         <v>16</v>
       </c>
-      <c r="R19">
-        <v>13</v>
-      </c>
-      <c r="S19">
+      <c r="T19">
+        <v>13</v>
+      </c>
+      <c r="U19">
         <v>11</v>
       </c>
-      <c r="T19">
-        <v>13</v>
-      </c>
-      <c r="U19">
+      <c r="V19">
+        <v>13</v>
+      </c>
+      <c r="W19">
         <v>16</v>
       </c>
-      <c r="V19">
+      <c r="X19">
+        <v>16</v>
+      </c>
+      <c r="Y19">
         <v>15</v>
       </c>
-      <c r="W19">
+      <c r="Z19">
+        <v>16</v>
+      </c>
+      <c r="AA19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>164</v>
+      </c>
+      <c r="K20">
+        <f>SUM(B20:E20)</f>
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <f>SUM(F20:I20)</f>
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <f>J20</f>
+        <v>164</v>
+      </c>
+      <c r="N20">
+        <f>SUM(K20:M20)</f>
+        <v>164</v>
+      </c>
+      <c r="O20">
+        <v>15</v>
+      </c>
+      <c r="P20">
+        <v>15</v>
+      </c>
+      <c r="Q20">
+        <v>13</v>
+      </c>
+      <c r="R20">
+        <v>13</v>
+      </c>
+      <c r="S20">
+        <v>13</v>
+      </c>
+      <c r="T20">
+        <v>13</v>
+      </c>
+      <c r="U20">
+        <v>13</v>
+      </c>
+      <c r="V20">
+        <v>13</v>
+      </c>
+      <c r="W20">
+        <v>12</v>
+      </c>
+      <c r="X20">
+        <v>18</v>
+      </c>
+      <c r="Y20">
+        <v>17</v>
+      </c>
+      <c r="Z20">
+        <v>12</v>
+      </c>
+      <c r="AA20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>41</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
         <v>96</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="1"/>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <f>SUM(B21:E21)</f>
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <f>SUM(F21:I21)</f>
         <v>96</v>
       </c>
-      <c r="L20">
-        <f t="shared" si="2"/>
+      <c r="M21">
+        <f>J21</f>
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <f>SUM(K21:M21)</f>
         <v>96</v>
       </c>
-      <c r="M20">
+      <c r="O21">
         <v>15</v>
       </c>
-      <c r="N20">
+      <c r="P21">
         <v>15</v>
       </c>
-      <c r="O20">
-        <v>13</v>
-      </c>
-      <c r="P20">
-        <v>13</v>
-      </c>
-      <c r="Q20">
-        <v>13</v>
-      </c>
-      <c r="R20">
-        <v>13</v>
-      </c>
-      <c r="S20">
-        <v>13</v>
-      </c>
-      <c r="T20">
-        <v>13</v>
-      </c>
-      <c r="U20">
+      <c r="Q21">
+        <v>13</v>
+      </c>
+      <c r="R21">
+        <v>13</v>
+      </c>
+      <c r="S21">
+        <v>13</v>
+      </c>
+      <c r="T21">
+        <v>13</v>
+      </c>
+      <c r="U21">
+        <v>13</v>
+      </c>
+      <c r="V21">
+        <v>13</v>
+      </c>
+      <c r="W21">
+        <v>16</v>
+      </c>
+      <c r="X21">
         <v>18</v>
       </c>
-      <c r="V20">
+      <c r="Y21">
         <v>16</v>
       </c>
-      <c r="W20">
+      <c r="Z21">
+        <v>16</v>
+      </c>
+      <c r="AA21">
         <v>19</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA24">
+    <sortCondition descending="1" ref="N1:N24"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD29621-3F5F-40AE-94CF-25F82B8EB946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267BAF3D-7313-4EA1-A58A-5E534A6B493D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7EB6C2C6-840C-4838-9636-758ACFA0B514}"/>
   </bookViews>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2220,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="K20">
         <f>SUM(B20:E20)</f>
@@ -2240,15 +2240,15 @@
       </c>
       <c r="L20">
         <f>SUM(F20:I20)</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M20">
         <f>J20</f>
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="N20">
         <f>SUM(K20:M20)</f>
-        <v>164</v>
+        <v>96</v>
       </c>
       <c r="O20">
         <v>15</v>
@@ -2275,24 +2275,24 @@
         <v>13</v>
       </c>
       <c r="W20">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="X20">
         <v>18</v>
       </c>
       <c r="Y20">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z20">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AA20">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="K21">
         <f>SUM(B21:E21)</f>
@@ -2327,15 +2327,15 @@
       </c>
       <c r="L21">
         <f>SUM(F21:I21)</f>
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="M21">
         <f>J21</f>
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="N21">
         <f>SUM(K21:M21)</f>
-        <v>96</v>
+        <v>164</v>
       </c>
       <c r="O21">
         <v>15</v>
@@ -2350,7 +2350,7 @@
         <v>13</v>
       </c>
       <c r="S21">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T21">
         <v>13</v>
@@ -2362,24 +2362,24 @@
         <v>13</v>
       </c>
       <c r="W21">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="X21">
         <v>18</v>
       </c>
       <c r="Y21">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z21">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AA21">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA24">
-    <sortCondition descending="1" ref="N1:N24"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA21">
+    <sortCondition ref="AA1:AA21"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267BAF3D-7313-4EA1-A58A-5E534A6B493D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB00DF5-F747-4B63-8334-52EA71A08932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7EB6C2C6-840C-4838-9636-758ACFA0B514}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="50">
   <si>
     <t>Nombre</t>
   </si>
@@ -177,6 +177,15 @@
   </si>
   <si>
     <t>Ranking Mens. 3</t>
+  </si>
+  <si>
+    <t>Sexo</t>
+  </si>
+  <si>
+    <t>Mujer</t>
+  </si>
+  <si>
+    <t>Hombre</t>
   </si>
 </sst>
 </file>
@@ -548,13 +557,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}">
-  <dimension ref="A1:AA21"/>
+  <dimension ref="A1:AB21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -636,8 +645,11 @@
       <c r="AA1" t="s">
         <v>22</v>
       </c>
+      <c r="AB1" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -669,19 +681,19 @@
         <v>524</v>
       </c>
       <c r="K2">
-        <f>SUM(B2:E2)</f>
+        <f t="shared" ref="K2:K21" si="0">SUM(B2:E2)</f>
         <v>1852</v>
       </c>
       <c r="L2">
-        <f>SUM(F2:I2)</f>
+        <f t="shared" ref="L2:L21" si="1">SUM(F2:I2)</f>
         <v>2186</v>
       </c>
       <c r="M2">
-        <f>J2</f>
+        <f t="shared" ref="M2:M21" si="2">J2</f>
         <v>524</v>
       </c>
       <c r="N2">
-        <f>SUM(K2:M2)</f>
+        <f t="shared" ref="N2:N21" si="3">SUM(K2:M2)</f>
         <v>4562</v>
       </c>
       <c r="O2">
@@ -723,8 +735,11 @@
       <c r="AA2">
         <v>1</v>
       </c>
+      <c r="AB2" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -756,19 +771,19 @@
         <v>513</v>
       </c>
       <c r="K3">
-        <f>SUM(B3:E3)</f>
+        <f t="shared" si="0"/>
         <v>1328</v>
       </c>
       <c r="L3">
-        <f>SUM(F3:I3)</f>
+        <f t="shared" si="1"/>
         <v>2672</v>
       </c>
       <c r="M3">
-        <f>J3</f>
+        <f t="shared" si="2"/>
         <v>513</v>
       </c>
       <c r="N3">
-        <f>SUM(K3:M3)</f>
+        <f t="shared" si="3"/>
         <v>4513</v>
       </c>
       <c r="O3">
@@ -810,8 +825,11 @@
       <c r="AA3">
         <v>2</v>
       </c>
+      <c r="AB3" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -843,19 +861,19 @@
         <v>539</v>
       </c>
       <c r="K4">
-        <f>SUM(B4:E4)</f>
+        <f t="shared" si="0"/>
         <v>1036</v>
       </c>
       <c r="L4">
-        <f>SUM(F4:I4)</f>
+        <f t="shared" si="1"/>
         <v>2184</v>
       </c>
       <c r="M4">
-        <f>J4</f>
+        <f t="shared" si="2"/>
         <v>539</v>
       </c>
       <c r="N4">
-        <f>SUM(K4:M4)</f>
+        <f t="shared" si="3"/>
         <v>3759</v>
       </c>
       <c r="O4">
@@ -897,8 +915,11 @@
       <c r="AA4">
         <v>3</v>
       </c>
+      <c r="AB4" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -930,19 +951,19 @@
         <v>470</v>
       </c>
       <c r="K5">
-        <f>SUM(B5:E5)</f>
+        <f t="shared" si="0"/>
         <v>1361</v>
       </c>
       <c r="L5">
-        <f>SUM(F5:I5)</f>
+        <f t="shared" si="1"/>
         <v>1450</v>
       </c>
       <c r="M5">
-        <f>J5</f>
+        <f t="shared" si="2"/>
         <v>470</v>
       </c>
       <c r="N5">
-        <f>SUM(K5:M5)</f>
+        <f t="shared" si="3"/>
         <v>3281</v>
       </c>
       <c r="O5">
@@ -984,8 +1005,11 @@
       <c r="AA5">
         <v>4</v>
       </c>
+      <c r="AB5" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1017,19 +1041,19 @@
         <v>599</v>
       </c>
       <c r="K6">
-        <f>SUM(B6:E6)</f>
+        <f t="shared" si="0"/>
         <v>1527</v>
       </c>
       <c r="L6">
-        <f>SUM(F6:I6)</f>
+        <f t="shared" si="1"/>
         <v>832</v>
       </c>
       <c r="M6">
-        <f>J6</f>
+        <f t="shared" si="2"/>
         <v>599</v>
       </c>
       <c r="N6">
-        <f>SUM(K6:M6)</f>
+        <f t="shared" si="3"/>
         <v>2958</v>
       </c>
       <c r="O6">
@@ -1071,8 +1095,11 @@
       <c r="AA6">
         <v>5</v>
       </c>
+      <c r="AB6" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1104,19 +1131,19 @@
         <v>432</v>
       </c>
       <c r="K7">
-        <f>SUM(B7:E7)</f>
+        <f t="shared" si="0"/>
         <v>923</v>
       </c>
       <c r="L7">
-        <f>SUM(F7:I7)</f>
+        <f t="shared" si="1"/>
         <v>987</v>
       </c>
       <c r="M7">
-        <f>J7</f>
+        <f t="shared" si="2"/>
         <v>432</v>
       </c>
       <c r="N7">
-        <f>SUM(K7:M7)</f>
+        <f t="shared" si="3"/>
         <v>2342</v>
       </c>
       <c r="O7">
@@ -1158,8 +1185,11 @@
       <c r="AA7">
         <v>6</v>
       </c>
+      <c r="AB7" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1191,19 +1221,19 @@
         <v>252</v>
       </c>
       <c r="K8">
-        <f>SUM(B8:E8)</f>
+        <f t="shared" si="0"/>
         <v>977</v>
       </c>
       <c r="L8">
-        <f>SUM(F8:I8)</f>
+        <f t="shared" si="1"/>
         <v>1005</v>
       </c>
       <c r="M8">
-        <f>J8</f>
+        <f t="shared" si="2"/>
         <v>252</v>
       </c>
       <c r="N8">
-        <f>SUM(K8:M8)</f>
+        <f t="shared" si="3"/>
         <v>2234</v>
       </c>
       <c r="O8">
@@ -1245,8 +1275,11 @@
       <c r="AA8">
         <v>7</v>
       </c>
+      <c r="AB8" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -1278,19 +1311,19 @@
         <v>352</v>
       </c>
       <c r="K9">
-        <f>SUM(B9:E9)</f>
+        <f t="shared" si="0"/>
         <v>1320</v>
       </c>
       <c r="L9">
-        <f>SUM(F9:I9)</f>
+        <f t="shared" si="1"/>
         <v>354</v>
       </c>
       <c r="M9">
-        <f>J9</f>
+        <f t="shared" si="2"/>
         <v>352</v>
       </c>
       <c r="N9">
-        <f>SUM(K9:M9)</f>
+        <f t="shared" si="3"/>
         <v>2026</v>
       </c>
       <c r="O9">
@@ -1332,8 +1365,11 @@
       <c r="AA9">
         <v>8</v>
       </c>
+      <c r="AB9" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -1365,19 +1401,19 @@
         <v>518</v>
       </c>
       <c r="K10">
-        <f>SUM(B10:E10)</f>
+        <f t="shared" si="0"/>
         <v>490</v>
       </c>
       <c r="L10">
-        <f>SUM(F10:I10)</f>
+        <f t="shared" si="1"/>
         <v>768</v>
       </c>
       <c r="M10">
-        <f>J10</f>
+        <f t="shared" si="2"/>
         <v>518</v>
       </c>
       <c r="N10">
-        <f>SUM(K10:M10)</f>
+        <f t="shared" si="3"/>
         <v>1776</v>
       </c>
       <c r="O10">
@@ -1419,8 +1455,11 @@
       <c r="AA10">
         <v>9</v>
       </c>
+      <c r="AB10" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -1452,19 +1491,19 @@
         <v>179</v>
       </c>
       <c r="K11">
-        <f>SUM(B11:E11)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L11">
-        <f>SUM(F11:I11)</f>
+        <f t="shared" si="1"/>
         <v>1042</v>
       </c>
       <c r="M11">
-        <f>J11</f>
+        <f t="shared" si="2"/>
         <v>179</v>
       </c>
       <c r="N11">
-        <f>SUM(K11:M11)</f>
+        <f t="shared" si="3"/>
         <v>1221</v>
       </c>
       <c r="O11">
@@ -1506,8 +1545,11 @@
       <c r="AA11">
         <v>10</v>
       </c>
+      <c r="AB11" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1539,19 +1581,19 @@
         <v>209</v>
       </c>
       <c r="K12">
-        <f>SUM(B12:E12)</f>
+        <f t="shared" si="0"/>
         <v>382</v>
       </c>
       <c r="L12">
-        <f>SUM(F12:I12)</f>
+        <f t="shared" si="1"/>
         <v>614</v>
       </c>
       <c r="M12">
-        <f>J12</f>
+        <f t="shared" si="2"/>
         <v>209</v>
       </c>
       <c r="N12">
-        <f>SUM(K12:M12)</f>
+        <f t="shared" si="3"/>
         <v>1205</v>
       </c>
       <c r="O12">
@@ -1593,8 +1635,11 @@
       <c r="AA12">
         <v>11</v>
       </c>
+      <c r="AB12" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -1626,19 +1671,19 @@
         <v>158</v>
       </c>
       <c r="K13">
-        <f>SUM(B13:E13)</f>
+        <f t="shared" si="0"/>
         <v>347</v>
       </c>
       <c r="L13">
-        <f>SUM(F13:I13)</f>
+        <f t="shared" si="1"/>
         <v>542</v>
       </c>
       <c r="M13">
-        <f>J13</f>
+        <f t="shared" si="2"/>
         <v>158</v>
       </c>
       <c r="N13">
-        <f>SUM(K13:M13)</f>
+        <f t="shared" si="3"/>
         <v>1047</v>
       </c>
       <c r="O13">
@@ -1680,8 +1725,11 @@
       <c r="AA13">
         <v>12</v>
       </c>
+      <c r="AB13" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -1713,19 +1761,19 @@
         <v>114</v>
       </c>
       <c r="K14">
-        <f>SUM(B14:E14)</f>
+        <f t="shared" si="0"/>
         <v>310</v>
       </c>
       <c r="L14">
-        <f>SUM(F14:I14)</f>
+        <f t="shared" si="1"/>
         <v>552</v>
       </c>
       <c r="M14">
-        <f>J14</f>
+        <f t="shared" si="2"/>
         <v>114</v>
       </c>
       <c r="N14">
-        <f>SUM(K14:M14)</f>
+        <f t="shared" si="3"/>
         <v>976</v>
       </c>
       <c r="O14">
@@ -1767,8 +1815,11 @@
       <c r="AA14">
         <v>13</v>
       </c>
+      <c r="AB14" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -1800,19 +1851,19 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <f>SUM(B15:E15)</f>
+        <f t="shared" si="0"/>
         <v>548</v>
       </c>
       <c r="L15">
-        <f>SUM(F15:I15)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M15">
-        <f>J15</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N15">
-        <f>SUM(K15:M15)</f>
+        <f t="shared" si="3"/>
         <v>548</v>
       </c>
       <c r="O15">
@@ -1854,8 +1905,11 @@
       <c r="AA15">
         <v>14</v>
       </c>
+      <c r="AB15" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -1887,19 +1941,19 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <f>SUM(B16:E16)</f>
+        <f t="shared" si="0"/>
         <v>528</v>
       </c>
       <c r="L16">
-        <f>SUM(F16:I16)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M16">
-        <f>J16</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N16">
-        <f>SUM(K16:M16)</f>
+        <f t="shared" si="3"/>
         <v>528</v>
       </c>
       <c r="O16">
@@ -1941,8 +1995,11 @@
       <c r="AA16">
         <v>15</v>
       </c>
+      <c r="AB16" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1974,19 +2031,19 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <f>SUM(B17:E17)</f>
+        <f t="shared" si="0"/>
         <v>448</v>
       </c>
       <c r="L17">
-        <f>SUM(F17:I17)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M17">
-        <f>J17</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N17">
-        <f>SUM(K17:M17)</f>
+        <f t="shared" si="3"/>
         <v>448</v>
       </c>
       <c r="O17">
@@ -2028,8 +2085,11 @@
       <c r="AA17">
         <v>16</v>
       </c>
+      <c r="AB17" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -2061,19 +2121,19 @@
         <v>19</v>
       </c>
       <c r="K18">
-        <f>SUM(B18:E18)</f>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="L18">
-        <f>SUM(F18:I18)</f>
+        <f t="shared" si="1"/>
         <v>234</v>
       </c>
       <c r="M18">
-        <f>J18</f>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="N18">
-        <f>SUM(K18:M18)</f>
+        <f t="shared" si="3"/>
         <v>294</v>
       </c>
       <c r="O18">
@@ -2115,8 +2175,11 @@
       <c r="AA18">
         <v>17</v>
       </c>
+      <c r="AB18" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -2148,19 +2211,19 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <f>SUM(B19:E19)</f>
+        <f t="shared" si="0"/>
         <v>67</v>
       </c>
       <c r="L19">
-        <f>SUM(F19:I19)</f>
+        <f t="shared" si="1"/>
         <v>104</v>
       </c>
       <c r="M19">
-        <f>J19</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N19">
-        <f>SUM(K19:M19)</f>
+        <f t="shared" si="3"/>
         <v>171</v>
       </c>
       <c r="O19">
@@ -2202,8 +2265,11 @@
       <c r="AA19">
         <v>18</v>
       </c>
+      <c r="AB19" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -2235,19 +2301,19 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <f>SUM(B20:E20)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L20">
-        <f>SUM(F20:I20)</f>
+        <f t="shared" si="1"/>
         <v>96</v>
       </c>
       <c r="M20">
-        <f>J20</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N20">
-        <f>SUM(K20:M20)</f>
+        <f t="shared" si="3"/>
         <v>96</v>
       </c>
       <c r="O20">
@@ -2289,8 +2355,11 @@
       <c r="AA20">
         <v>19</v>
       </c>
+      <c r="AB20" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -2322,19 +2391,19 @@
         <v>164</v>
       </c>
       <c r="K21">
-        <f>SUM(B21:E21)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L21">
-        <f>SUM(F21:I21)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M21">
-        <f>J21</f>
+        <f t="shared" si="2"/>
         <v>164</v>
       </c>
       <c r="N21">
-        <f>SUM(K21:M21)</f>
+        <f t="shared" si="3"/>
         <v>164</v>
       </c>
       <c r="O21">
@@ -2375,6 +2444,9 @@
       </c>
       <c r="AA21">
         <v>20</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB00DF5-F747-4B63-8334-52EA71A08932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BCBBD1F-D53A-4D84-B462-BF2999B9E271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7EB6C2C6-840C-4838-9636-758ACFA0B514}"/>
   </bookViews>
@@ -916,7 +916,7 @@
         <v>3</v>
       </c>
       <c r="AB4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.35">

--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BCBBD1F-D53A-4D84-B462-BF2999B9E271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BEC4994-8282-44B3-B07F-25D576CEFD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7EB6C2C6-840C-4838-9636-758ACFA0B514}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
   <si>
     <t>Nombre</t>
   </si>
@@ -186,6 +186,12 @@
   </si>
   <si>
     <t>Hombre</t>
+  </si>
+  <si>
+    <t>Semana 10</t>
+  </si>
+  <si>
+    <t>Ranking 10</t>
   </si>
 </sst>
 </file>
@@ -557,13 +563,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}">
-  <dimension ref="A1:AB21"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -595,61 +603,67 @@
         <v>42</v>
       </c>
       <c r="K1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>44</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" t="s">
-        <v>13</v>
-      </c>
       <c r="Q1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>15</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>16</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>17</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>18</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>19</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>45</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z1" t="s">
         <v>20</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>21</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>46</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>22</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -681,65 +695,71 @@
         <v>524</v>
       </c>
       <c r="K2">
-        <f t="shared" ref="K2:K21" si="0">SUM(B2:E2)</f>
+        <v>471</v>
+      </c>
+      <c r="L2">
+        <f t="shared" ref="L2:L21" si="0">SUM(B2:E2)</f>
         <v>1852</v>
       </c>
-      <c r="L2">
-        <f t="shared" ref="L2:L21" si="1">SUM(F2:I2)</f>
+      <c r="M2">
+        <f t="shared" ref="M2:M21" si="1">SUM(F2:I2)</f>
         <v>2186</v>
       </c>
-      <c r="M2">
-        <f t="shared" ref="M2:M21" si="2">J2</f>
-        <v>524</v>
-      </c>
       <c r="N2">
-        <f t="shared" ref="N2:N21" si="3">SUM(K2:M2)</f>
-        <v>4562</v>
+        <f t="shared" ref="N2:N21" si="2">SUM(J2:K2)</f>
+        <v>995</v>
       </c>
       <c r="O2">
+        <f t="shared" ref="O2:O21" si="3">SUM(L2:N2)</f>
+        <v>5033</v>
+      </c>
+      <c r="P2">
         <v>1</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>3</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>5</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>3</v>
       </c>
-      <c r="S2">
+      <c r="T2">
         <v>2</v>
       </c>
-      <c r="T2">
+      <c r="U2">
         <v>3</v>
       </c>
-      <c r="U2">
+      <c r="V2">
         <v>2</v>
-      </c>
-      <c r="V2">
-        <v>3</v>
       </c>
       <c r="W2">
         <v>3</v>
       </c>
       <c r="X2">
+        <v>3</v>
+      </c>
+      <c r="Y2">
+        <v>3</v>
+      </c>
+      <c r="Z2">
         <v>1</v>
       </c>
-      <c r="Y2">
+      <c r="AA2">
         <v>2</v>
       </c>
-      <c r="Z2">
+      <c r="AB2">
         <v>3</v>
       </c>
-      <c r="AA2">
+      <c r="AC2">
         <v>1</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AD2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -771,35 +791,35 @@
         <v>513</v>
       </c>
       <c r="K3">
+        <v>360</v>
+      </c>
+      <c r="L3">
         <f t="shared" si="0"/>
         <v>1328</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <f t="shared" si="1"/>
         <v>2672</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <f t="shared" si="2"/>
-        <v>513</v>
-      </c>
-      <c r="N3">
+        <v>873</v>
+      </c>
+      <c r="O3">
         <f t="shared" si="3"/>
-        <v>4513</v>
-      </c>
-      <c r="O3">
+        <v>4873</v>
+      </c>
+      <c r="P3">
         <v>12</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>5</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>6</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>2</v>
-      </c>
-      <c r="S3">
-        <v>1</v>
       </c>
       <c r="T3">
         <v>1</v>
@@ -808,28 +828,34 @@
         <v>1</v>
       </c>
       <c r="V3">
+        <v>1</v>
+      </c>
+      <c r="W3">
         <v>2</v>
       </c>
-      <c r="W3">
+      <c r="X3">
         <v>5</v>
       </c>
-      <c r="X3">
+      <c r="Y3">
+        <v>5</v>
+      </c>
+      <c r="Z3">
         <v>4</v>
       </c>
-      <c r="Y3">
+      <c r="AA3">
         <v>1</v>
       </c>
-      <c r="Z3">
-        <v>5</v>
-      </c>
-      <c r="AA3">
+      <c r="AB3">
+        <v>4</v>
+      </c>
+      <c r="AC3">
         <v>2</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AD3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -861,65 +887,71 @@
         <v>539</v>
       </c>
       <c r="K4">
+        <v>225</v>
+      </c>
+      <c r="L4">
         <f t="shared" si="0"/>
         <v>1036</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <f t="shared" si="1"/>
         <v>2184</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <f t="shared" si="2"/>
-        <v>539</v>
-      </c>
-      <c r="N4">
+        <v>764</v>
+      </c>
+      <c r="O4">
         <f t="shared" si="3"/>
-        <v>3759</v>
-      </c>
-      <c r="O4">
+        <v>3984</v>
+      </c>
+      <c r="P4">
         <v>15</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>10</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>8</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>1</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>3</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>4</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>3</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <v>1</v>
       </c>
-      <c r="W4">
+      <c r="X4">
         <v>2</v>
       </c>
-      <c r="X4">
+      <c r="Y4">
+        <v>7</v>
+      </c>
+      <c r="Z4">
         <v>6</v>
-      </c>
-      <c r="Y4">
-        <v>3</v>
-      </c>
-      <c r="Z4">
-        <v>2</v>
       </c>
       <c r="AA4">
         <v>3</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AB4">
+        <v>6</v>
+      </c>
+      <c r="AC4">
+        <v>3</v>
+      </c>
+      <c r="AD4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -951,65 +983,71 @@
         <v>470</v>
       </c>
       <c r="K5">
+        <v>201</v>
+      </c>
+      <c r="L5">
         <f t="shared" si="0"/>
         <v>1361</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <f t="shared" si="1"/>
         <v>1450</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <f t="shared" si="2"/>
-        <v>470</v>
-      </c>
-      <c r="N5">
+        <v>671</v>
+      </c>
+      <c r="O5">
         <f t="shared" si="3"/>
-        <v>3281</v>
-      </c>
-      <c r="O5">
+        <v>3482</v>
+      </c>
+      <c r="P5">
         <v>9</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>4</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>1</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>5</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>7</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <v>5</v>
-      </c>
-      <c r="U5">
-        <v>4</v>
       </c>
       <c r="V5">
         <v>4</v>
       </c>
       <c r="W5">
+        <v>4</v>
+      </c>
+      <c r="X5">
         <v>6</v>
       </c>
-      <c r="X5">
+      <c r="Y5">
+        <v>8</v>
+      </c>
+      <c r="Z5">
         <v>3</v>
-      </c>
-      <c r="Y5">
-        <v>4</v>
-      </c>
-      <c r="Z5">
-        <v>6</v>
       </c>
       <c r="AA5">
         <v>4</v>
       </c>
-      <c r="AB5" t="s">
+      <c r="AB5">
+        <v>7</v>
+      </c>
+      <c r="AC5">
+        <v>4</v>
+      </c>
+      <c r="AD5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1041,335 +1079,359 @@
         <v>599</v>
       </c>
       <c r="K6">
+        <v>398</v>
+      </c>
+      <c r="L6">
         <f t="shared" si="0"/>
         <v>1527</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <f t="shared" si="1"/>
         <v>832</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <f t="shared" si="2"/>
-        <v>599</v>
-      </c>
-      <c r="N6">
+        <v>997</v>
+      </c>
+      <c r="O6">
         <f t="shared" si="3"/>
-        <v>2958</v>
-      </c>
-      <c r="O6">
+        <v>3356</v>
+      </c>
+      <c r="P6">
         <v>7</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>1</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>3</v>
-      </c>
-      <c r="R6">
-        <v>4</v>
       </c>
       <c r="S6">
         <v>4</v>
       </c>
       <c r="T6">
+        <v>4</v>
+      </c>
+      <c r="U6">
         <v>9</v>
       </c>
-      <c r="U6">
-        <v>13</v>
-      </c>
       <c r="V6">
+        <v>13</v>
+      </c>
+      <c r="W6">
         <v>8</v>
       </c>
-      <c r="W6">
+      <c r="X6">
         <v>1</v>
       </c>
-      <c r="X6">
+      <c r="Y6">
+        <v>4</v>
+      </c>
+      <c r="Z6">
         <v>2</v>
       </c>
-      <c r="Y6">
+      <c r="AA6">
         <v>8</v>
       </c>
-      <c r="Z6">
-        <v>1</v>
-      </c>
-      <c r="AA6">
+      <c r="AB6">
+        <v>2</v>
+      </c>
+      <c r="AC6">
         <v>5</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AD6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7">
+        <v>46</v>
+      </c>
+      <c r="C7">
+        <v>478</v>
+      </c>
+      <c r="D7">
+        <v>565</v>
+      </c>
+      <c r="E7">
+        <v>231</v>
+      </c>
+      <c r="F7">
+        <v>354</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>352</v>
+      </c>
+      <c r="K7">
+        <v>493</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="0"/>
+        <v>1320</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="1"/>
+        <v>354</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="2"/>
+        <v>845</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="3"/>
+        <v>2519</v>
+      </c>
+      <c r="P7">
+        <v>13</v>
+      </c>
+      <c r="Q7">
+        <v>2</v>
+      </c>
+      <c r="R7">
+        <v>2</v>
+      </c>
+      <c r="S7">
+        <v>9</v>
+      </c>
+      <c r="T7">
+        <v>5</v>
+      </c>
+      <c r="U7">
+        <v>13</v>
+      </c>
+      <c r="V7">
+        <v>13</v>
+      </c>
+      <c r="W7">
+        <v>13</v>
+      </c>
+      <c r="X7">
+        <v>8</v>
+      </c>
+      <c r="Y7">
+        <v>2</v>
+      </c>
+      <c r="Z7">
+        <v>5</v>
+      </c>
+      <c r="AA7">
+        <v>13</v>
+      </c>
+      <c r="AB7">
+        <v>5</v>
+      </c>
+      <c r="AC7">
+        <v>6</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>29</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>140</v>
       </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
         <v>496</v>
       </c>
-      <c r="E7">
+      <c r="E8">
         <v>287</v>
       </c>
-      <c r="F7">
+      <c r="F8">
         <v>90</v>
       </c>
-      <c r="G7">
+      <c r="G8">
         <v>571</v>
       </c>
-      <c r="H7">
+      <c r="H8">
         <v>297</v>
       </c>
-      <c r="I7">
+      <c r="I8">
         <v>29</v>
       </c>
-      <c r="J7">
+      <c r="J8">
         <v>432</v>
       </c>
-      <c r="K7">
+      <c r="K8">
+        <v>142</v>
+      </c>
+      <c r="L8">
         <f t="shared" si="0"/>
         <v>923</v>
       </c>
-      <c r="L7">
+      <c r="M8">
         <f t="shared" si="1"/>
         <v>987</v>
       </c>
-      <c r="M7">
+      <c r="N8">
         <f t="shared" si="2"/>
-        <v>432</v>
-      </c>
-      <c r="N7">
+        <v>574</v>
+      </c>
+      <c r="O8">
         <f t="shared" si="3"/>
-        <v>2342</v>
-      </c>
-      <c r="O7">
+        <v>2484</v>
+      </c>
+      <c r="P8">
         <v>8</v>
       </c>
-      <c r="P7">
+      <c r="Q8">
         <v>15</v>
       </c>
-      <c r="Q7">
+      <c r="R8">
         <v>4</v>
       </c>
-      <c r="R7">
+      <c r="S8">
         <v>6</v>
       </c>
-      <c r="S7">
+      <c r="T8">
         <v>14</v>
       </c>
-      <c r="T7">
+      <c r="U8">
         <v>2</v>
       </c>
-      <c r="U7">
+      <c r="V8">
         <v>6</v>
       </c>
-      <c r="V7">
+      <c r="W8">
         <v>12</v>
       </c>
-      <c r="W7">
+      <c r="X8">
         <v>7</v>
       </c>
-      <c r="X7">
+      <c r="Y8">
+        <v>9</v>
+      </c>
+      <c r="Z8">
         <v>8</v>
       </c>
-      <c r="Y7">
+      <c r="AA8">
         <v>7</v>
       </c>
-      <c r="Z7">
+      <c r="AB8">
+        <v>8</v>
+      </c>
+      <c r="AC8">
         <v>7</v>
       </c>
-      <c r="AA7">
-        <v>6</v>
-      </c>
-      <c r="AB7" t="s">
+      <c r="AD8" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>28</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>205</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <v>280</v>
       </c>
-      <c r="D8">
+      <c r="D9">
         <v>284</v>
       </c>
-      <c r="E8">
+      <c r="E9">
         <v>208</v>
       </c>
-      <c r="F8">
+      <c r="F9">
         <v>318</v>
       </c>
-      <c r="G8">
+      <c r="G9">
         <v>162</v>
       </c>
-      <c r="H8">
+      <c r="H9">
         <v>260</v>
       </c>
-      <c r="I8">
+      <c r="I9">
         <v>265</v>
       </c>
-      <c r="J8">
+      <c r="J9">
         <v>252</v>
       </c>
-      <c r="K8">
+      <c r="K9">
+        <v>250</v>
+      </c>
+      <c r="L9">
         <f t="shared" si="0"/>
         <v>977</v>
       </c>
-      <c r="L8">
+      <c r="M9">
         <f t="shared" si="1"/>
         <v>1005</v>
       </c>
-      <c r="M8">
+      <c r="N9">
         <f t="shared" si="2"/>
-        <v>252</v>
-      </c>
-      <c r="N8">
+        <v>502</v>
+      </c>
+      <c r="O9">
         <f t="shared" si="3"/>
-        <v>2234</v>
-      </c>
-      <c r="O8">
+        <v>2484</v>
+      </c>
+      <c r="P9">
         <v>4</v>
       </c>
-      <c r="P8">
+      <c r="Q9">
         <v>6</v>
       </c>
-      <c r="Q8">
+      <c r="R9">
         <v>7</v>
       </c>
-      <c r="R8">
+      <c r="S9">
         <v>10</v>
       </c>
-      <c r="S8">
+      <c r="T9">
         <v>6</v>
       </c>
-      <c r="T8">
+      <c r="U9">
         <v>10</v>
       </c>
-      <c r="U8">
+      <c r="V9">
         <v>7</v>
       </c>
-      <c r="V8">
+      <c r="W9">
         <v>5</v>
       </c>
-      <c r="W8">
+      <c r="X9">
         <v>9</v>
       </c>
-      <c r="X8">
+      <c r="Y9">
+        <v>6</v>
+      </c>
+      <c r="Z9">
         <v>7</v>
       </c>
-      <c r="Y8">
+      <c r="AA9">
         <v>6</v>
       </c>
-      <c r="Z8">
+      <c r="AB9">
         <v>9</v>
       </c>
-      <c r="AA8">
-        <v>7</v>
-      </c>
-      <c r="AB8" t="s">
+      <c r="AC9">
+        <v>8</v>
+      </c>
+      <c r="AD9" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9">
-        <v>46</v>
-      </c>
-      <c r="C9">
-        <v>478</v>
-      </c>
-      <c r="D9">
-        <v>565</v>
-      </c>
-      <c r="E9">
-        <v>231</v>
-      </c>
-      <c r="F9">
-        <v>354</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>352</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="0"/>
-        <v>1320</v>
-      </c>
-      <c r="L9">
-        <f t="shared" si="1"/>
-        <v>354</v>
-      </c>
-      <c r="M9">
-        <f t="shared" si="2"/>
-        <v>352</v>
-      </c>
-      <c r="N9">
-        <f t="shared" si="3"/>
-        <v>2026</v>
-      </c>
-      <c r="O9">
-        <v>13</v>
-      </c>
-      <c r="P9">
-        <v>2</v>
-      </c>
-      <c r="Q9">
-        <v>2</v>
-      </c>
-      <c r="R9">
-        <v>9</v>
-      </c>
-      <c r="S9">
-        <v>5</v>
-      </c>
-      <c r="T9">
-        <v>13</v>
-      </c>
-      <c r="U9">
-        <v>13</v>
-      </c>
-      <c r="V9">
-        <v>13</v>
-      </c>
-      <c r="W9">
-        <v>8</v>
-      </c>
-      <c r="X9">
-        <v>5</v>
-      </c>
-      <c r="Y9">
-        <v>13</v>
-      </c>
-      <c r="Z9">
-        <v>8</v>
-      </c>
-      <c r="AA9">
-        <v>8</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -1401,65 +1463,71 @@
         <v>518</v>
       </c>
       <c r="K10">
+        <v>533</v>
+      </c>
+      <c r="L10">
         <f t="shared" si="0"/>
         <v>490</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <f t="shared" si="1"/>
         <v>768</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <f t="shared" si="2"/>
-        <v>518</v>
-      </c>
-      <c r="N10">
+        <v>1051</v>
+      </c>
+      <c r="O10">
         <f t="shared" si="3"/>
-        <v>1776</v>
-      </c>
-      <c r="O10">
+        <v>2309</v>
+      </c>
+      <c r="P10">
         <v>10</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>8</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <v>9</v>
       </c>
-      <c r="R10">
-        <v>13</v>
-      </c>
       <c r="S10">
+        <v>13</v>
+      </c>
+      <c r="T10">
         <v>15</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <v>6</v>
       </c>
-      <c r="U10">
+      <c r="V10">
         <v>8</v>
       </c>
-      <c r="V10">
+      <c r="W10">
         <v>6</v>
       </c>
-      <c r="W10">
+      <c r="X10">
         <v>4</v>
       </c>
-      <c r="X10">
+      <c r="Y10">
+        <v>1</v>
+      </c>
+      <c r="Z10">
         <v>11</v>
-      </c>
-      <c r="Y10">
-        <v>9</v>
-      </c>
-      <c r="Z10">
-        <v>4</v>
       </c>
       <c r="AA10">
         <v>9</v>
       </c>
-      <c r="AB10" t="s">
+      <c r="AB10">
+        <v>1</v>
+      </c>
+      <c r="AC10">
+        <v>9</v>
+      </c>
+      <c r="AD10" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -1488,68 +1556,74 @@
         <v>195</v>
       </c>
       <c r="J11">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="K11">
+        <v>96</v>
+      </c>
+      <c r="L11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <f t="shared" si="1"/>
         <v>1042</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <f t="shared" si="2"/>
-        <v>179</v>
-      </c>
-      <c r="N11">
+        <v>273</v>
+      </c>
+      <c r="O11">
         <f t="shared" si="3"/>
-        <v>1221</v>
-      </c>
-      <c r="O11">
-        <v>15</v>
+        <v>1315</v>
       </c>
       <c r="P11">
         <v>15</v>
       </c>
       <c r="Q11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R11">
         <v>13</v>
       </c>
       <c r="S11">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T11">
         <v>8</v>
       </c>
       <c r="U11">
+        <v>8</v>
+      </c>
+      <c r="V11">
         <v>5</v>
       </c>
-      <c r="V11">
+      <c r="W11">
         <v>9</v>
       </c>
-      <c r="W11">
+      <c r="X11">
         <v>11</v>
       </c>
-      <c r="X11">
+      <c r="Y11">
+        <v>12</v>
+      </c>
+      <c r="Z11">
         <v>18</v>
       </c>
-      <c r="Y11">
+      <c r="AA11">
         <v>5</v>
       </c>
-      <c r="Z11">
-        <v>11</v>
-      </c>
-      <c r="AA11">
+      <c r="AB11">
         <v>10</v>
       </c>
-      <c r="AB11" t="s">
+      <c r="AC11">
+        <v>10</v>
+      </c>
+      <c r="AD11" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1581,65 +1655,71 @@
         <v>209</v>
       </c>
       <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
         <f t="shared" si="0"/>
         <v>382</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <f t="shared" si="1"/>
         <v>614</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <f t="shared" si="2"/>
         <v>209</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <f t="shared" si="3"/>
         <v>1205</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>5</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>9</v>
       </c>
-      <c r="Q12">
-        <v>13</v>
-      </c>
       <c r="R12">
         <v>13</v>
       </c>
       <c r="S12">
+        <v>13</v>
+      </c>
+      <c r="T12">
         <v>12</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <v>7</v>
       </c>
-      <c r="U12">
-        <v>13</v>
-      </c>
       <c r="V12">
+        <v>13</v>
+      </c>
+      <c r="W12">
         <v>7</v>
       </c>
-      <c r="W12">
+      <c r="X12">
         <v>10</v>
       </c>
-      <c r="X12">
-        <v>13</v>
-      </c>
       <c r="Y12">
+        <v>14</v>
+      </c>
+      <c r="Z12">
+        <v>13</v>
+      </c>
+      <c r="AA12">
         <v>10</v>
       </c>
-      <c r="Z12">
-        <v>10</v>
-      </c>
-      <c r="AA12">
+      <c r="AB12">
+        <v>13</v>
+      </c>
+      <c r="AC12">
         <v>11</v>
       </c>
-      <c r="AB12" t="s">
+      <c r="AD12" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -1671,65 +1751,71 @@
         <v>158</v>
       </c>
       <c r="K13">
+        <v>107</v>
+      </c>
+      <c r="L13">
         <f t="shared" si="0"/>
         <v>347</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <f t="shared" si="1"/>
         <v>542</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <f t="shared" si="2"/>
-        <v>158</v>
-      </c>
-      <c r="N13">
+        <v>265</v>
+      </c>
+      <c r="O13">
         <f t="shared" si="3"/>
-        <v>1047</v>
-      </c>
-      <c r="O13">
-        <v>14</v>
+        <v>1154</v>
       </c>
       <c r="P13">
         <v>14</v>
       </c>
       <c r="Q13">
+        <v>14</v>
+      </c>
+      <c r="R13">
         <v>10</v>
       </c>
-      <c r="R13">
+      <c r="S13">
         <v>12</v>
       </c>
-      <c r="S13">
+      <c r="T13">
         <v>10</v>
       </c>
-      <c r="T13">
+      <c r="U13">
         <v>12</v>
-      </c>
-      <c r="U13">
-        <v>10</v>
       </c>
       <c r="V13">
         <v>10</v>
       </c>
       <c r="W13">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y13">
         <v>11</v>
       </c>
       <c r="Z13">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA13">
+        <v>11</v>
+      </c>
+      <c r="AB13">
+        <v>11</v>
+      </c>
+      <c r="AC13">
         <v>12</v>
       </c>
-      <c r="AB13" t="s">
+      <c r="AD13" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -1761,29 +1847,29 @@
         <v>114</v>
       </c>
       <c r="K14">
+        <v>112</v>
+      </c>
+      <c r="L14">
         <f t="shared" si="0"/>
         <v>310</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <f t="shared" si="1"/>
         <v>552</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <f t="shared" si="2"/>
-        <v>114</v>
-      </c>
-      <c r="N14">
+        <v>226</v>
+      </c>
+      <c r="O14">
         <f t="shared" si="3"/>
-        <v>976</v>
-      </c>
-      <c r="O14">
+        <v>1088</v>
+      </c>
+      <c r="P14">
         <v>15</v>
       </c>
-      <c r="P14">
-        <v>13</v>
-      </c>
       <c r="Q14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R14">
         <v>11</v>
@@ -1795,31 +1881,37 @@
         <v>11</v>
       </c>
       <c r="U14">
+        <v>11</v>
+      </c>
+      <c r="V14">
         <v>9</v>
       </c>
-      <c r="V14">
+      <c r="W14">
         <v>11</v>
       </c>
-      <c r="W14">
+      <c r="X14">
         <v>14</v>
       </c>
-      <c r="X14">
+      <c r="Y14">
+        <v>10</v>
+      </c>
+      <c r="Z14">
         <v>15</v>
       </c>
-      <c r="Y14">
+      <c r="AA14">
         <v>12</v>
       </c>
-      <c r="Z14">
-        <v>14</v>
-      </c>
-      <c r="AA14">
-        <v>13</v>
-      </c>
-      <c r="AB14" t="s">
+      <c r="AB14">
+        <v>12</v>
+      </c>
+      <c r="AC14">
+        <v>13</v>
+      </c>
+      <c r="AD14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -1851,39 +1943,39 @@
         <v>0</v>
       </c>
       <c r="K15">
+        <v>83</v>
+      </c>
+      <c r="L15">
         <f t="shared" si="0"/>
         <v>548</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N15">
+        <v>83</v>
+      </c>
+      <c r="O15">
         <f t="shared" si="3"/>
-        <v>548</v>
-      </c>
-      <c r="O15">
+        <v>631</v>
+      </c>
+      <c r="P15">
         <v>3</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>11</v>
       </c>
-      <c r="Q15">
-        <v>13</v>
-      </c>
       <c r="R15">
+        <v>13</v>
+      </c>
+      <c r="S15">
         <v>7</v>
       </c>
-      <c r="S15">
+      <c r="T15">
         <v>16</v>
       </c>
-      <c r="T15">
-        <v>13</v>
-      </c>
       <c r="U15">
         <v>13</v>
       </c>
@@ -1891,25 +1983,31 @@
         <v>13</v>
       </c>
       <c r="W15">
+        <v>13</v>
+      </c>
+      <c r="X15">
         <v>16</v>
       </c>
-      <c r="X15">
+      <c r="Y15">
+        <v>13</v>
+      </c>
+      <c r="Z15">
         <v>9</v>
       </c>
-      <c r="Y15">
+      <c r="AA15">
         <v>17</v>
       </c>
-      <c r="Z15">
-        <v>16</v>
-      </c>
-      <c r="AA15">
+      <c r="AB15">
+        <v>15</v>
+      </c>
+      <c r="AC15">
         <v>14</v>
       </c>
-      <c r="AB15" t="s">
+      <c r="AD15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -1941,39 +2039,39 @@
         <v>0</v>
       </c>
       <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
         <f t="shared" si="0"/>
         <v>528</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <f t="shared" si="3"/>
         <v>528</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>2</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>12</v>
       </c>
-      <c r="Q16">
-        <v>13</v>
-      </c>
       <c r="R16">
+        <v>13</v>
+      </c>
+      <c r="S16">
         <v>8</v>
       </c>
-      <c r="S16">
+      <c r="T16">
         <v>16</v>
       </c>
-      <c r="T16">
-        <v>13</v>
-      </c>
       <c r="U16">
         <v>13</v>
       </c>
@@ -1981,25 +2079,31 @@
         <v>13</v>
       </c>
       <c r="W16">
+        <v>13</v>
+      </c>
+      <c r="X16">
         <v>16</v>
       </c>
-      <c r="X16">
+      <c r="Y16">
+        <v>14</v>
+      </c>
+      <c r="Z16">
         <v>10</v>
       </c>
-      <c r="Y16">
+      <c r="AA16">
         <v>17</v>
       </c>
-      <c r="Z16">
-        <v>16</v>
-      </c>
-      <c r="AA16">
+      <c r="AB16">
+        <v>17</v>
+      </c>
+      <c r="AC16">
         <v>15</v>
       </c>
-      <c r="AB16" t="s">
+      <c r="AD16" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -2031,39 +2135,39 @@
         <v>0</v>
       </c>
       <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
         <f t="shared" si="0"/>
         <v>448</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <f t="shared" si="3"/>
         <v>448</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>6</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>7</v>
       </c>
-      <c r="Q17">
-        <v>13</v>
-      </c>
       <c r="R17">
         <v>13</v>
       </c>
       <c r="S17">
+        <v>13</v>
+      </c>
+      <c r="T17">
         <v>16</v>
       </c>
-      <c r="T17">
-        <v>13</v>
-      </c>
       <c r="U17">
         <v>13</v>
       </c>
@@ -2071,25 +2175,31 @@
         <v>13</v>
       </c>
       <c r="W17">
+        <v>13</v>
+      </c>
+      <c r="X17">
         <v>16</v>
       </c>
-      <c r="X17">
+      <c r="Y17">
+        <v>14</v>
+      </c>
+      <c r="Z17">
         <v>12</v>
       </c>
-      <c r="Y17">
+      <c r="AA17">
         <v>17</v>
       </c>
-      <c r="Z17">
+      <c r="AB17">
+        <v>17</v>
+      </c>
+      <c r="AC17">
         <v>16</v>
       </c>
-      <c r="AA17">
-        <v>16</v>
-      </c>
-      <c r="AB17" t="s">
+      <c r="AD17" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -2121,65 +2231,71 @@
         <v>19</v>
       </c>
       <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <f t="shared" si="1"/>
         <v>234</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <f t="shared" si="3"/>
         <v>294</v>
       </c>
-      <c r="O18">
-        <v>15</v>
-      </c>
       <c r="P18">
         <v>15</v>
       </c>
       <c r="Q18">
+        <v>15</v>
+      </c>
+      <c r="R18">
         <v>12</v>
       </c>
-      <c r="R18">
-        <v>13</v>
-      </c>
       <c r="S18">
+        <v>13</v>
+      </c>
+      <c r="T18">
         <v>9</v>
       </c>
-      <c r="T18">
-        <v>13</v>
-      </c>
       <c r="U18">
+        <v>13</v>
+      </c>
+      <c r="V18">
         <v>12</v>
       </c>
-      <c r="V18">
-        <v>13</v>
-      </c>
       <c r="W18">
+        <v>13</v>
+      </c>
+      <c r="X18">
         <v>15</v>
-      </c>
-      <c r="X18">
-        <v>17</v>
       </c>
       <c r="Y18">
         <v>14</v>
       </c>
       <c r="Z18">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA18">
+        <v>14</v>
+      </c>
+      <c r="AB18">
+        <v>16</v>
+      </c>
+      <c r="AC18">
         <v>17</v>
       </c>
-      <c r="AB18" t="s">
+      <c r="AD18" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -2211,247 +2327,265 @@
         <v>0</v>
       </c>
       <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <f t="shared" si="1"/>
         <v>104</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <f t="shared" si="3"/>
         <v>171</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>11</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>15</v>
       </c>
-      <c r="Q19">
-        <v>13</v>
-      </c>
       <c r="R19">
         <v>13</v>
       </c>
       <c r="S19">
+        <v>13</v>
+      </c>
+      <c r="T19">
         <v>16</v>
       </c>
-      <c r="T19">
-        <v>13</v>
-      </c>
       <c r="U19">
+        <v>13</v>
+      </c>
+      <c r="V19">
         <v>11</v>
       </c>
-      <c r="V19">
-        <v>13</v>
-      </c>
       <c r="W19">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="X19">
         <v>16</v>
       </c>
       <c r="Y19">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z19">
         <v>16</v>
       </c>
       <c r="AA19">
+        <v>15</v>
+      </c>
+      <c r="AB19">
+        <v>17</v>
+      </c>
+      <c r="AC19">
         <v>18</v>
       </c>
-      <c r="AB19" t="s">
+      <c r="AD19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>164</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="2"/>
+        <v>164</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="3"/>
+        <v>164</v>
+      </c>
+      <c r="P20">
+        <v>15</v>
+      </c>
+      <c r="Q20">
+        <v>15</v>
+      </c>
+      <c r="R20">
+        <v>13</v>
+      </c>
+      <c r="S20">
+        <v>13</v>
+      </c>
+      <c r="T20">
+        <v>16</v>
+      </c>
+      <c r="U20">
+        <v>13</v>
+      </c>
+      <c r="V20">
+        <v>13</v>
+      </c>
+      <c r="W20">
+        <v>13</v>
+      </c>
+      <c r="X20">
+        <v>12</v>
+      </c>
+      <c r="Y20">
+        <v>14</v>
+      </c>
+      <c r="Z20">
+        <v>18</v>
+      </c>
+      <c r="AA20">
+        <v>17</v>
+      </c>
+      <c r="AB20">
+        <v>14</v>
+      </c>
+      <c r="AC20">
+        <v>19</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>41</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
         <v>96</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L20">
+      <c r="M21">
         <f t="shared" si="1"/>
         <v>96</v>
       </c>
-      <c r="M20">
+      <c r="N21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N20">
+      <c r="O21">
         <f t="shared" si="3"/>
         <v>96</v>
       </c>
-      <c r="O20">
-        <v>15</v>
-      </c>
-      <c r="P20">
-        <v>15</v>
-      </c>
-      <c r="Q20">
-        <v>13</v>
-      </c>
-      <c r="R20">
-        <v>13</v>
-      </c>
-      <c r="S20">
-        <v>13</v>
-      </c>
-      <c r="T20">
-        <v>13</v>
-      </c>
-      <c r="U20">
-        <v>13</v>
-      </c>
-      <c r="V20">
-        <v>13</v>
-      </c>
-      <c r="W20">
-        <v>16</v>
-      </c>
-      <c r="X20">
-        <v>18</v>
-      </c>
-      <c r="Y20">
-        <v>16</v>
-      </c>
-      <c r="Z20">
-        <v>16</v>
-      </c>
-      <c r="AA20">
-        <v>19</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>164</v>
-      </c>
-      <c r="K21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <f t="shared" si="2"/>
-        <v>164</v>
-      </c>
-      <c r="N21">
-        <f t="shared" si="3"/>
-        <v>164</v>
-      </c>
-      <c r="O21">
-        <v>15</v>
-      </c>
       <c r="P21">
         <v>15</v>
       </c>
       <c r="Q21">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R21">
         <v>13</v>
       </c>
       <c r="S21">
+        <v>13</v>
+      </c>
+      <c r="T21">
+        <v>13</v>
+      </c>
+      <c r="U21">
+        <v>13</v>
+      </c>
+      <c r="V21">
+        <v>13</v>
+      </c>
+      <c r="W21">
+        <v>13</v>
+      </c>
+      <c r="X21">
         <v>16</v>
       </c>
-      <c r="T21">
-        <v>13</v>
-      </c>
-      <c r="U21">
-        <v>13</v>
-      </c>
-      <c r="V21">
-        <v>13</v>
-      </c>
-      <c r="W21">
-        <v>12</v>
-      </c>
-      <c r="X21">
+      <c r="Y21">
+        <v>14</v>
+      </c>
+      <c r="Z21">
         <v>18</v>
       </c>
-      <c r="Y21">
+      <c r="AA21">
+        <v>16</v>
+      </c>
+      <c r="AB21">
         <v>17</v>
       </c>
-      <c r="Z21">
-        <v>12</v>
-      </c>
-      <c r="AA21">
+      <c r="AC21">
         <v>20</v>
       </c>
-      <c r="AB21" t="s">
-        <v>48</v>
+      <c r="AD21" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA21">
-    <sortCondition ref="AA1:AA21"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD23">
+    <sortCondition descending="1" ref="O1:O23"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BEC4994-8282-44B3-B07F-25D576CEFD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E48FF2D-D69B-4280-97AD-733A69F47EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7EB6C2C6-840C-4838-9636-758ACFA0B514}"/>
   </bookViews>
@@ -182,16 +182,16 @@
     <t>Sexo</t>
   </si>
   <si>
-    <t>Mujer</t>
-  </si>
-  <si>
-    <t>Hombre</t>
-  </si>
-  <si>
     <t>Semana 10</t>
   </si>
   <si>
     <t>Ranking 10</t>
+  </si>
+  <si>
+    <t>Mujeres</t>
+  </si>
+  <si>
+    <t>Hombres</t>
   </si>
 </sst>
 </file>
@@ -603,7 +603,7 @@
         <v>42</v>
       </c>
       <c r="K1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s">
         <v>9</v>
@@ -645,7 +645,7 @@
         <v>45</v>
       </c>
       <c r="Y1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Z1" t="s">
         <v>20</v>
@@ -756,7 +756,7 @@
         <v>1</v>
       </c>
       <c r="AD2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.35">
@@ -852,7 +852,7 @@
         <v>2</v>
       </c>
       <c r="AD3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.35">
@@ -948,7 +948,7 @@
         <v>3</v>
       </c>
       <c r="AD4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.35">
@@ -1044,7 +1044,7 @@
         <v>4</v>
       </c>
       <c r="AD5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.35">
@@ -1140,7 +1140,7 @@
         <v>5</v>
       </c>
       <c r="AD6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.35">
@@ -1236,7 +1236,7 @@
         <v>6</v>
       </c>
       <c r="AD7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.35">
@@ -1332,7 +1332,7 @@
         <v>7</v>
       </c>
       <c r="AD8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.35">
@@ -1428,7 +1428,7 @@
         <v>8</v>
       </c>
       <c r="AD9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.35">
@@ -1524,7 +1524,7 @@
         <v>9</v>
       </c>
       <c r="AD10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.35">
@@ -1620,7 +1620,7 @@
         <v>10</v>
       </c>
       <c r="AD11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.35">
@@ -1716,7 +1716,7 @@
         <v>11</v>
       </c>
       <c r="AD12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.35">
@@ -1812,7 +1812,7 @@
         <v>12</v>
       </c>
       <c r="AD13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.35">
@@ -1908,7 +1908,7 @@
         <v>13</v>
       </c>
       <c r="AD14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.35">
@@ -2004,7 +2004,7 @@
         <v>14</v>
       </c>
       <c r="AD15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.35">
@@ -2100,7 +2100,7 @@
         <v>15</v>
       </c>
       <c r="AD16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.35">
@@ -2196,7 +2196,7 @@
         <v>16</v>
       </c>
       <c r="AD17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.35">
@@ -2292,7 +2292,7 @@
         <v>17</v>
       </c>
       <c r="AD18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.35">
@@ -2388,7 +2388,7 @@
         <v>18</v>
       </c>
       <c r="AD19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.35">
@@ -2484,7 +2484,7 @@
         <v>19</v>
       </c>
       <c r="AD20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.35">
@@ -2580,7 +2580,7 @@
         <v>20</v>
       </c>
       <c r="AD21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E48FF2D-D69B-4280-97AD-733A69F47EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D29EDC-8964-4C7A-BB54-DE0DE1F360D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7EB6C2C6-840C-4838-9636-758ACFA0B514}"/>
   </bookViews>
@@ -948,7 +948,7 @@
         <v>3</v>
       </c>
       <c r="AD4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.35">

--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D29EDC-8964-4C7A-BB54-DE0DE1F360D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E994C07-09FF-45E9-98DC-2CD69D6C5044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7EB6C2C6-840C-4838-9636-758ACFA0B514}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="65">
   <si>
     <t>Nombre</t>
   </si>
@@ -192,6 +192,45 @@
   </si>
   <si>
     <t>Hombres</t>
+  </si>
+  <si>
+    <t>Semana 11</t>
+  </si>
+  <si>
+    <t>Ranking 11</t>
+  </si>
+  <si>
+    <t>Edades</t>
+  </si>
+  <si>
+    <t>21-30</t>
+  </si>
+  <si>
+    <t>31-40</t>
+  </si>
+  <si>
+    <t>41-50</t>
+  </si>
+  <si>
+    <t>Regiones</t>
+  </si>
+  <si>
+    <t>Qro.</t>
+  </si>
+  <si>
+    <t>CDMX</t>
+  </si>
+  <si>
+    <t>Ver.</t>
+  </si>
+  <si>
+    <t>Tol.</t>
+  </si>
+  <si>
+    <t>S.L.P.</t>
+  </si>
+  <si>
+    <t>E.U.A.</t>
   </si>
 </sst>
 </file>
@@ -563,15 +602,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}">
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AH21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7265625" customWidth="1"/>
+    <col min="26" max="26" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -606,256 +647,292 @@
         <v>48</v>
       </c>
       <c r="L1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>44</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" t="s">
-        <v>13</v>
-      </c>
       <c r="R1" t="s">
+        <v>13</v>
+      </c>
+      <c r="S1" t="s">
         <v>14</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>15</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>16</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>17</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>18</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>19</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>45</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>49</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AB1" t="s">
         <v>20</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>21</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>46</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>22</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>47</v>
       </c>
+      <c r="AG1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2">
-        <v>567</v>
+        <v>60</v>
       </c>
       <c r="C2">
-        <v>383</v>
+        <v>293</v>
       </c>
       <c r="D2">
-        <v>488</v>
+        <v>326</v>
       </c>
       <c r="E2">
-        <v>414</v>
+        <v>649</v>
       </c>
       <c r="F2">
-        <v>664</v>
+        <v>684</v>
       </c>
       <c r="G2">
-        <v>551</v>
+        <v>692</v>
       </c>
       <c r="H2">
-        <v>493</v>
+        <v>613</v>
       </c>
       <c r="I2">
-        <v>478</v>
+        <v>683</v>
       </c>
       <c r="J2">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="K2">
-        <v>471</v>
+        <v>360</v>
       </c>
       <c r="L2">
-        <f t="shared" ref="L2:L21" si="0">SUM(B2:E2)</f>
-        <v>1852</v>
+        <v>805</v>
       </c>
       <c r="M2">
-        <f t="shared" ref="M2:M21" si="1">SUM(F2:I2)</f>
-        <v>2186</v>
+        <f t="shared" ref="M2:M21" si="0">SUM(B2:E2)</f>
+        <v>1328</v>
       </c>
       <c r="N2">
-        <f t="shared" ref="N2:N21" si="2">SUM(J2:K2)</f>
-        <v>995</v>
+        <f t="shared" ref="N2:N21" si="1">SUM(F2:I2)</f>
+        <v>2672</v>
       </c>
       <c r="O2">
-        <f t="shared" ref="O2:O21" si="3">SUM(L2:N2)</f>
-        <v>5033</v>
+        <f t="shared" ref="O2:O21" si="2">SUM(J2:L2)</f>
+        <v>1678</v>
       </c>
       <c r="P2">
-        <v>1</v>
+        <f t="shared" ref="P2:P21" si="3">SUM(M2:O2)</f>
+        <v>5678</v>
       </c>
       <c r="Q2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R2">
         <v>5</v>
       </c>
       <c r="S2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T2">
         <v>2</v>
       </c>
       <c r="U2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2">
         <v>2</v>
       </c>
-      <c r="W2">
-        <v>3</v>
-      </c>
-      <c r="X2">
-        <v>3</v>
-      </c>
       <c r="Y2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA2">
         <v>2</v>
       </c>
       <c r="AB2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC2">
         <v>1</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AD2">
+        <v>1</v>
+      </c>
+      <c r="AE2">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="s">
         <v>50</v>
       </c>
+      <c r="AG2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>63</v>
+      </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3">
-        <v>60</v>
+        <v>567</v>
       </c>
       <c r="C3">
-        <v>293</v>
+        <v>383</v>
       </c>
       <c r="D3">
-        <v>326</v>
+        <v>488</v>
       </c>
       <c r="E3">
-        <v>649</v>
+        <v>414</v>
       </c>
       <c r="F3">
-        <v>684</v>
+        <v>664</v>
       </c>
       <c r="G3">
-        <v>692</v>
+        <v>551</v>
       </c>
       <c r="H3">
-        <v>613</v>
+        <v>493</v>
       </c>
       <c r="I3">
-        <v>683</v>
+        <v>478</v>
       </c>
       <c r="J3">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="K3">
-        <v>360</v>
+        <v>471</v>
       </c>
       <c r="L3">
+        <v>586</v>
+      </c>
+      <c r="M3">
         <f t="shared" si="0"/>
-        <v>1328</v>
-      </c>
-      <c r="M3">
+        <v>1852</v>
+      </c>
+      <c r="N3">
         <f t="shared" si="1"/>
-        <v>2672</v>
-      </c>
-      <c r="N3">
+        <v>2186</v>
+      </c>
+      <c r="O3">
         <f t="shared" si="2"/>
-        <v>873</v>
-      </c>
-      <c r="O3">
+        <v>1581</v>
+      </c>
+      <c r="P3">
         <f t="shared" si="3"/>
-        <v>4873</v>
-      </c>
-      <c r="P3">
-        <v>12</v>
+        <v>5619</v>
       </c>
       <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>3</v>
+      </c>
+      <c r="S3">
         <v>5</v>
       </c>
-      <c r="R3">
-        <v>6</v>
-      </c>
-      <c r="S3">
+      <c r="T3">
+        <v>3</v>
+      </c>
+      <c r="U3">
         <v>2</v>
       </c>
-      <c r="T3">
-        <v>1</v>
-      </c>
-      <c r="U3">
-        <v>1</v>
-      </c>
       <c r="V3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W3">
         <v>2</v>
       </c>
       <c r="X3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z3">
+        <v>3</v>
+      </c>
+      <c r="AA3">
         <v>4</v>
       </c>
-      <c r="AA3">
+      <c r="AB3">
         <v>1</v>
-      </c>
-      <c r="AB3">
-        <v>4</v>
       </c>
       <c r="AC3">
         <v>2</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AD3">
+        <v>4</v>
+      </c>
+      <c r="AE3">
+        <v>2</v>
+      </c>
+      <c r="AF3" t="s">
         <v>50</v>
       </c>
+      <c r="AG3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -890,56 +967,56 @@
         <v>225</v>
       </c>
       <c r="L4">
+        <v>830</v>
+      </c>
+      <c r="M4">
         <f t="shared" si="0"/>
         <v>1036</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <f t="shared" si="1"/>
         <v>2184</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <f t="shared" si="2"/>
-        <v>764</v>
-      </c>
-      <c r="O4">
+        <v>1594</v>
+      </c>
+      <c r="P4">
         <f t="shared" si="3"/>
-        <v>3984</v>
-      </c>
-      <c r="P4">
+        <v>4814</v>
+      </c>
+      <c r="Q4">
         <v>15</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>10</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>8</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>1</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>3</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>4</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <v>3</v>
       </c>
-      <c r="W4">
+      <c r="X4">
         <v>1</v>
       </c>
-      <c r="X4">
+      <c r="Y4">
         <v>2</v>
       </c>
-      <c r="Y4">
+      <c r="Z4">
         <v>7</v>
       </c>
-      <c r="Z4">
-        <v>6</v>
-      </c>
       <c r="AA4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB4">
         <v>6</v>
@@ -947,587 +1024,671 @@
       <c r="AC4">
         <v>3</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AD4">
+        <v>3</v>
+      </c>
+      <c r="AE4">
+        <v>3</v>
+      </c>
+      <c r="AF4" t="s">
         <v>51</v>
       </c>
+      <c r="AG4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>62</v>
+      </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5">
+        <v>157</v>
+      </c>
+      <c r="C5">
+        <v>481</v>
+      </c>
+      <c r="D5">
+        <v>532</v>
+      </c>
+      <c r="E5">
+        <v>357</v>
+      </c>
+      <c r="F5">
+        <v>393</v>
+      </c>
+      <c r="G5">
+        <v>235</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>204</v>
+      </c>
+      <c r="J5">
+        <v>599</v>
+      </c>
+      <c r="K5">
+        <v>398</v>
+      </c>
+      <c r="L5">
+        <v>604</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="0"/>
+        <v>1527</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="1"/>
+        <v>832</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="2"/>
+        <v>1601</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="3"/>
+        <v>3960</v>
+      </c>
+      <c r="Q5">
+        <v>7</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>3</v>
+      </c>
+      <c r="T5">
+        <v>4</v>
+      </c>
+      <c r="U5">
+        <v>4</v>
+      </c>
+      <c r="V5">
+        <v>9</v>
+      </c>
+      <c r="W5">
+        <v>13</v>
+      </c>
+      <c r="X5">
+        <v>8</v>
+      </c>
+      <c r="Y5">
+        <v>1</v>
+      </c>
+      <c r="Z5">
+        <v>4</v>
+      </c>
+      <c r="AA5">
+        <v>3</v>
+      </c>
+      <c r="AB5">
+        <v>2</v>
+      </c>
+      <c r="AC5">
+        <v>8</v>
+      </c>
+      <c r="AD5">
+        <v>2</v>
+      </c>
+      <c r="AE5">
+        <v>4</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>26</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>104</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>344</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>588</v>
       </c>
-      <c r="E5">
+      <c r="E6">
         <v>325</v>
       </c>
-      <c r="F5">
+      <c r="F6">
         <v>315</v>
       </c>
-      <c r="G5">
+      <c r="G6">
         <v>441</v>
       </c>
-      <c r="H5">
+      <c r="H6">
         <v>397</v>
       </c>
-      <c r="I5">
+      <c r="I6">
         <v>297</v>
       </c>
-      <c r="J5">
+      <c r="J6">
         <v>470</v>
       </c>
-      <c r="K5">
+      <c r="K6">
         <v>201</v>
       </c>
-      <c r="L5">
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
         <f t="shared" si="0"/>
         <v>1361</v>
       </c>
-      <c r="M5">
+      <c r="N6">
         <f t="shared" si="1"/>
         <v>1450</v>
       </c>
-      <c r="N5">
+      <c r="O6">
         <f t="shared" si="2"/>
         <v>671</v>
       </c>
-      <c r="O5">
+      <c r="P6">
         <f t="shared" si="3"/>
         <v>3482</v>
       </c>
-      <c r="P5">
+      <c r="Q6">
         <v>9</v>
       </c>
-      <c r="Q5">
+      <c r="R6">
         <v>4</v>
       </c>
-      <c r="R5">
+      <c r="S6">
         <v>1</v>
       </c>
-      <c r="S5">
+      <c r="T6">
         <v>5</v>
       </c>
-      <c r="T5">
+      <c r="U6">
         <v>7</v>
       </c>
-      <c r="U5">
+      <c r="V6">
         <v>5</v>
       </c>
-      <c r="V5">
+      <c r="W6">
         <v>4</v>
       </c>
-      <c r="W5">
+      <c r="X6">
         <v>4</v>
       </c>
-      <c r="X5">
+      <c r="Y6">
         <v>6</v>
       </c>
-      <c r="Y5">
+      <c r="Z6">
         <v>8</v>
       </c>
-      <c r="Z5">
+      <c r="AA6">
+        <v>13</v>
+      </c>
+      <c r="AB6">
         <v>3</v>
       </c>
-      <c r="AA5">
+      <c r="AC6">
         <v>4</v>
       </c>
-      <c r="AB5">
-        <v>7</v>
-      </c>
-      <c r="AC5">
+      <c r="AD6">
+        <v>8</v>
+      </c>
+      <c r="AE6">
+        <v>5</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7">
+        <v>96</v>
+      </c>
+      <c r="C7">
+        <v>203</v>
+      </c>
+      <c r="D7">
+        <v>191</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>24</v>
+      </c>
+      <c r="G7">
+        <v>328</v>
+      </c>
+      <c r="H7">
+        <v>173</v>
+      </c>
+      <c r="I7">
+        <v>243</v>
+      </c>
+      <c r="J7">
+        <v>518</v>
+      </c>
+      <c r="K7">
+        <v>533</v>
+      </c>
+      <c r="L7">
+        <v>520</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="1"/>
+        <v>768</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="2"/>
+        <v>1571</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="3"/>
+        <v>2829</v>
+      </c>
+      <c r="Q7">
+        <v>10</v>
+      </c>
+      <c r="R7">
+        <v>8</v>
+      </c>
+      <c r="S7">
+        <v>9</v>
+      </c>
+      <c r="T7">
+        <v>13</v>
+      </c>
+      <c r="U7">
+        <v>15</v>
+      </c>
+      <c r="V7">
+        <v>6</v>
+      </c>
+      <c r="W7">
+        <v>8</v>
+      </c>
+      <c r="X7">
+        <v>6</v>
+      </c>
+      <c r="Y7">
         <v>4</v>
       </c>
-      <c r="AD5" t="s">
-        <v>50</v>
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7">
+        <v>5</v>
+      </c>
+      <c r="AB7">
+        <v>11</v>
+      </c>
+      <c r="AC7">
+        <v>9</v>
+      </c>
+      <c r="AD7">
+        <v>5</v>
+      </c>
+      <c r="AE7">
+        <v>6</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6">
-        <v>157</v>
-      </c>
-      <c r="C6">
-        <v>481</v>
-      </c>
-      <c r="D6">
-        <v>532</v>
-      </c>
-      <c r="E6">
-        <v>357</v>
-      </c>
-      <c r="F6">
-        <v>393</v>
-      </c>
-      <c r="G6">
-        <v>235</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>204</v>
-      </c>
-      <c r="J6">
-        <v>599</v>
-      </c>
-      <c r="K6">
-        <v>398</v>
-      </c>
-      <c r="L6">
-        <f t="shared" si="0"/>
-        <v>1527</v>
-      </c>
-      <c r="M6">
-        <f t="shared" si="1"/>
-        <v>832</v>
-      </c>
-      <c r="N6">
-        <f t="shared" si="2"/>
-        <v>997</v>
-      </c>
-      <c r="O6">
-        <f t="shared" si="3"/>
-        <v>3356</v>
-      </c>
-      <c r="P6">
-        <v>7</v>
-      </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6">
-        <v>3</v>
-      </c>
-      <c r="S6">
-        <v>4</v>
-      </c>
-      <c r="T6">
-        <v>4</v>
-      </c>
-      <c r="U6">
-        <v>9</v>
-      </c>
-      <c r="V6">
-        <v>13</v>
-      </c>
-      <c r="W6">
-        <v>8</v>
-      </c>
-      <c r="X6">
-        <v>1</v>
-      </c>
-      <c r="Y6">
-        <v>4</v>
-      </c>
-      <c r="Z6">
-        <v>2</v>
-      </c>
-      <c r="AA6">
-        <v>8</v>
-      </c>
-      <c r="AB6">
-        <v>2</v>
-      </c>
-      <c r="AC6">
-        <v>5</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>30</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>46</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>478</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <v>565</v>
       </c>
-      <c r="E7">
+      <c r="E8">
         <v>231</v>
       </c>
-      <c r="F7">
+      <c r="F8">
         <v>354</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
         <v>352</v>
       </c>
-      <c r="K7">
+      <c r="K8">
         <v>493</v>
       </c>
-      <c r="L7">
+      <c r="L8">
+        <v>239</v>
+      </c>
+      <c r="M8">
         <f t="shared" si="0"/>
         <v>1320</v>
       </c>
-      <c r="M7">
+      <c r="N8">
         <f t="shared" si="1"/>
         <v>354</v>
       </c>
-      <c r="N7">
+      <c r="O8">
         <f t="shared" si="2"/>
-        <v>845</v>
-      </c>
-      <c r="O7">
+        <v>1084</v>
+      </c>
+      <c r="P8">
         <f t="shared" si="3"/>
-        <v>2519</v>
-      </c>
-      <c r="P7">
-        <v>13</v>
-      </c>
-      <c r="Q7">
+        <v>2758</v>
+      </c>
+      <c r="Q8">
+        <v>13</v>
+      </c>
+      <c r="R8">
         <v>2</v>
       </c>
-      <c r="R7">
+      <c r="S8">
         <v>2</v>
       </c>
-      <c r="S7">
+      <c r="T8">
         <v>9</v>
       </c>
-      <c r="T7">
+      <c r="U8">
         <v>5</v>
       </c>
-      <c r="U7">
-        <v>13</v>
-      </c>
-      <c r="V7">
-        <v>13</v>
-      </c>
-      <c r="W7">
-        <v>13</v>
-      </c>
-      <c r="X7">
+      <c r="V8">
+        <v>13</v>
+      </c>
+      <c r="W8">
+        <v>13</v>
+      </c>
+      <c r="X8">
+        <v>13</v>
+      </c>
+      <c r="Y8">
         <v>8</v>
       </c>
-      <c r="Y7">
+      <c r="Z8">
         <v>2</v>
       </c>
-      <c r="Z7">
+      <c r="AA8">
+        <v>8</v>
+      </c>
+      <c r="AB8">
         <v>5</v>
       </c>
-      <c r="AA7">
-        <v>13</v>
-      </c>
-      <c r="AB7">
+      <c r="AC8">
+        <v>13</v>
+      </c>
+      <c r="AD8">
+        <v>6</v>
+      </c>
+      <c r="AE8">
+        <v>7</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9">
+        <v>205</v>
+      </c>
+      <c r="C9">
+        <v>280</v>
+      </c>
+      <c r="D9">
+        <v>284</v>
+      </c>
+      <c r="E9">
+        <v>208</v>
+      </c>
+      <c r="F9">
+        <v>318</v>
+      </c>
+      <c r="G9">
+        <v>162</v>
+      </c>
+      <c r="H9">
+        <v>260</v>
+      </c>
+      <c r="I9">
+        <v>265</v>
+      </c>
+      <c r="J9">
+        <v>252</v>
+      </c>
+      <c r="K9">
+        <v>250</v>
+      </c>
+      <c r="L9">
+        <v>249</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="0"/>
+        <v>977</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="1"/>
+        <v>1005</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="2"/>
+        <v>751</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="3"/>
+        <v>2733</v>
+      </c>
+      <c r="Q9">
+        <v>4</v>
+      </c>
+      <c r="R9">
+        <v>6</v>
+      </c>
+      <c r="S9">
+        <v>7</v>
+      </c>
+      <c r="T9">
+        <v>10</v>
+      </c>
+      <c r="U9">
+        <v>6</v>
+      </c>
+      <c r="V9">
+        <v>10</v>
+      </c>
+      <c r="W9">
+        <v>7</v>
+      </c>
+      <c r="X9">
         <v>5</v>
       </c>
-      <c r="AC7">
+      <c r="Y9">
+        <v>9</v>
+      </c>
+      <c r="Z9">
         <v>6</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AA9">
+        <v>7</v>
+      </c>
+      <c r="AB9">
+        <v>7</v>
+      </c>
+      <c r="AC9">
+        <v>6</v>
+      </c>
+      <c r="AD9">
+        <v>7</v>
+      </c>
+      <c r="AE9">
+        <v>8</v>
+      </c>
+      <c r="AF9" t="s">
         <v>50</v>
       </c>
+      <c r="AG9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>63</v>
+      </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>29</v>
       </c>
-      <c r="B8">
+      <c r="B10">
         <v>140</v>
       </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
         <v>496</v>
       </c>
-      <c r="E8">
+      <c r="E10">
         <v>287</v>
       </c>
-      <c r="F8">
+      <c r="F10">
         <v>90</v>
       </c>
-      <c r="G8">
+      <c r="G10">
         <v>571</v>
       </c>
-      <c r="H8">
+      <c r="H10">
         <v>297</v>
       </c>
-      <c r="I8">
+      <c r="I10">
         <v>29</v>
       </c>
-      <c r="J8">
+      <c r="J10">
         <v>432</v>
       </c>
-      <c r="K8">
+      <c r="K10">
         <v>142</v>
       </c>
-      <c r="L8">
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
         <f t="shared" si="0"/>
         <v>923</v>
       </c>
-      <c r="M8">
+      <c r="N10">
         <f t="shared" si="1"/>
         <v>987</v>
       </c>
-      <c r="N8">
+      <c r="O10">
         <f t="shared" si="2"/>
         <v>574</v>
       </c>
-      <c r="O8">
+      <c r="P10">
         <f t="shared" si="3"/>
         <v>2484</v>
       </c>
-      <c r="P8">
-        <v>8</v>
-      </c>
-      <c r="Q8">
-        <v>15</v>
-      </c>
-      <c r="R8">
-        <v>4</v>
-      </c>
-      <c r="S8">
-        <v>6</v>
-      </c>
-      <c r="T8">
-        <v>14</v>
-      </c>
-      <c r="U8">
-        <v>2</v>
-      </c>
-      <c r="V8">
-        <v>6</v>
-      </c>
-      <c r="W8">
-        <v>12</v>
-      </c>
-      <c r="X8">
-        <v>7</v>
-      </c>
-      <c r="Y8">
-        <v>9</v>
-      </c>
-      <c r="Z8">
-        <v>8</v>
-      </c>
-      <c r="AA8">
-        <v>7</v>
-      </c>
-      <c r="AB8">
-        <v>8</v>
-      </c>
-      <c r="AC8">
-        <v>7</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9">
-        <v>205</v>
-      </c>
-      <c r="C9">
-        <v>280</v>
-      </c>
-      <c r="D9">
-        <v>284</v>
-      </c>
-      <c r="E9">
-        <v>208</v>
-      </c>
-      <c r="F9">
-        <v>318</v>
-      </c>
-      <c r="G9">
-        <v>162</v>
-      </c>
-      <c r="H9">
-        <v>260</v>
-      </c>
-      <c r="I9">
-        <v>265</v>
-      </c>
-      <c r="J9">
-        <v>252</v>
-      </c>
-      <c r="K9">
-        <v>250</v>
-      </c>
-      <c r="L9">
-        <f t="shared" si="0"/>
-        <v>977</v>
-      </c>
-      <c r="M9">
-        <f t="shared" si="1"/>
-        <v>1005</v>
-      </c>
-      <c r="N9">
-        <f t="shared" si="2"/>
-        <v>502</v>
-      </c>
-      <c r="O9">
-        <f t="shared" si="3"/>
-        <v>2484</v>
-      </c>
-      <c r="P9">
-        <v>4</v>
-      </c>
-      <c r="Q9">
-        <v>6</v>
-      </c>
-      <c r="R9">
-        <v>7</v>
-      </c>
-      <c r="S9">
-        <v>10</v>
-      </c>
-      <c r="T9">
-        <v>6</v>
-      </c>
-      <c r="U9">
-        <v>10</v>
-      </c>
-      <c r="V9">
-        <v>7</v>
-      </c>
-      <c r="W9">
-        <v>5</v>
-      </c>
-      <c r="X9">
-        <v>9</v>
-      </c>
-      <c r="Y9">
-        <v>6</v>
-      </c>
-      <c r="Z9">
-        <v>7</v>
-      </c>
-      <c r="AA9">
-        <v>6</v>
-      </c>
-      <c r="AB9">
-        <v>9</v>
-      </c>
-      <c r="AC9">
-        <v>8</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10">
-        <v>96</v>
-      </c>
-      <c r="C10">
-        <v>203</v>
-      </c>
-      <c r="D10">
-        <v>191</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>24</v>
-      </c>
-      <c r="G10">
-        <v>328</v>
-      </c>
-      <c r="H10">
-        <v>173</v>
-      </c>
-      <c r="I10">
-        <v>243</v>
-      </c>
-      <c r="J10">
-        <v>518</v>
-      </c>
-      <c r="K10">
-        <v>533</v>
-      </c>
-      <c r="L10">
-        <f t="shared" si="0"/>
-        <v>490</v>
-      </c>
-      <c r="M10">
-        <f t="shared" si="1"/>
-        <v>768</v>
-      </c>
-      <c r="N10">
-        <f t="shared" si="2"/>
-        <v>1051</v>
-      </c>
-      <c r="O10">
-        <f t="shared" si="3"/>
-        <v>2309</v>
-      </c>
-      <c r="P10">
-        <v>10</v>
-      </c>
       <c r="Q10">
         <v>8</v>
       </c>
       <c r="R10">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="S10">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T10">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="U10">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="W10">
         <v>6</v>
       </c>
       <c r="X10">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Y10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z10">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA10">
+        <v>13</v>
+      </c>
+      <c r="AB10">
+        <v>8</v>
+      </c>
+      <c r="AC10">
+        <v>7</v>
+      </c>
+      <c r="AD10">
+        <v>10</v>
+      </c>
+      <c r="AE10">
         <v>9</v>
       </c>
-      <c r="AB10">
-        <v>1</v>
-      </c>
-      <c r="AC10">
-        <v>9</v>
-      </c>
-      <c r="AD10" t="s">
+      <c r="AF10" t="s">
         <v>51</v>
       </c>
+      <c r="AG10" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -1562,68 +1723,80 @@
         <v>96</v>
       </c>
       <c r="L11">
+        <v>390</v>
+      </c>
+      <c r="M11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <f t="shared" si="1"/>
         <v>1042</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <f t="shared" si="2"/>
-        <v>273</v>
-      </c>
-      <c r="O11">
+        <v>663</v>
+      </c>
+      <c r="P11">
         <f t="shared" si="3"/>
-        <v>1315</v>
-      </c>
-      <c r="P11">
-        <v>15</v>
+        <v>1705</v>
       </c>
       <c r="Q11">
         <v>15</v>
       </c>
       <c r="R11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S11">
         <v>13</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="U11">
         <v>8</v>
       </c>
       <c r="V11">
+        <v>8</v>
+      </c>
+      <c r="W11">
         <v>5</v>
       </c>
-      <c r="W11">
+      <c r="X11">
         <v>9</v>
       </c>
-      <c r="X11">
+      <c r="Y11">
         <v>11</v>
       </c>
-      <c r="Y11">
+      <c r="Z11">
         <v>12</v>
       </c>
-      <c r="Z11">
+      <c r="AA11">
+        <v>6</v>
+      </c>
+      <c r="AB11">
         <v>18</v>
       </c>
-      <c r="AA11">
+      <c r="AC11">
         <v>5</v>
       </c>
-      <c r="AB11">
+      <c r="AD11">
+        <v>9</v>
+      </c>
+      <c r="AE11">
         <v>10</v>
       </c>
-      <c r="AC11">
-        <v>10</v>
-      </c>
-      <c r="AD11" t="s">
+      <c r="AF11" t="s">
         <v>50</v>
       </c>
+      <c r="AG11" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>62</v>
+      </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1658,68 +1831,80 @@
         <v>0</v>
       </c>
       <c r="L12">
+        <v>187</v>
+      </c>
+      <c r="M12">
         <f t="shared" si="0"/>
         <v>382</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <f t="shared" si="1"/>
         <v>614</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <f t="shared" si="2"/>
-        <v>209</v>
-      </c>
-      <c r="O12">
+        <v>396</v>
+      </c>
+      <c r="P12">
         <f t="shared" si="3"/>
-        <v>1205</v>
-      </c>
-      <c r="P12">
+        <v>1392</v>
+      </c>
+      <c r="Q12">
         <v>5</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>9</v>
       </c>
-      <c r="R12">
-        <v>13</v>
-      </c>
       <c r="S12">
         <v>13</v>
       </c>
       <c r="T12">
+        <v>13</v>
+      </c>
+      <c r="U12">
         <v>12</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <v>7</v>
       </c>
-      <c r="V12">
-        <v>13</v>
-      </c>
       <c r="W12">
+        <v>13</v>
+      </c>
+      <c r="X12">
         <v>7</v>
       </c>
-      <c r="X12">
+      <c r="Y12">
         <v>10</v>
       </c>
-      <c r="Y12">
+      <c r="Z12">
         <v>14</v>
       </c>
-      <c r="Z12">
-        <v>13</v>
-      </c>
       <c r="AA12">
+        <v>9</v>
+      </c>
+      <c r="AB12">
+        <v>13</v>
+      </c>
+      <c r="AC12">
         <v>10</v>
       </c>
-      <c r="AB12">
-        <v>13</v>
-      </c>
-      <c r="AC12">
+      <c r="AD12">
+        <v>12</v>
+      </c>
+      <c r="AE12">
         <v>11</v>
       </c>
-      <c r="AD12" t="s">
+      <c r="AF12" t="s">
         <v>51</v>
       </c>
+      <c r="AG12" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -1754,68 +1939,80 @@
         <v>107</v>
       </c>
       <c r="L13">
+        <v>160</v>
+      </c>
+      <c r="M13">
         <f t="shared" si="0"/>
         <v>347</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <f t="shared" si="1"/>
         <v>542</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <f t="shared" si="2"/>
-        <v>265</v>
-      </c>
-      <c r="O13">
+        <v>425</v>
+      </c>
+      <c r="P13">
         <f t="shared" si="3"/>
-        <v>1154</v>
-      </c>
-      <c r="P13">
-        <v>14</v>
+        <v>1314</v>
       </c>
       <c r="Q13">
         <v>14</v>
       </c>
       <c r="R13">
+        <v>14</v>
+      </c>
+      <c r="S13">
         <v>10</v>
       </c>
-      <c r="S13">
+      <c r="T13">
         <v>12</v>
       </c>
-      <c r="T13">
+      <c r="U13">
         <v>10</v>
       </c>
-      <c r="U13">
+      <c r="V13">
         <v>12</v>
-      </c>
-      <c r="V13">
-        <v>10</v>
       </c>
       <c r="W13">
         <v>10</v>
       </c>
       <c r="X13">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y13">
+        <v>13</v>
+      </c>
+      <c r="Z13">
         <v>11</v>
       </c>
-      <c r="Z13">
+      <c r="AA13">
+        <v>10</v>
+      </c>
+      <c r="AB13">
         <v>14</v>
       </c>
-      <c r="AA13">
+      <c r="AC13">
         <v>11</v>
       </c>
-      <c r="AB13">
+      <c r="AD13">
         <v>11</v>
       </c>
-      <c r="AC13">
+      <c r="AE13">
         <v>12</v>
       </c>
-      <c r="AD13" t="s">
+      <c r="AF13" t="s">
         <v>51</v>
       </c>
+      <c r="AG13" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>63</v>
+      </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -1850,29 +2047,29 @@
         <v>112</v>
       </c>
       <c r="L14">
+        <v>140</v>
+      </c>
+      <c r="M14">
         <f t="shared" si="0"/>
         <v>310</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <f t="shared" si="1"/>
         <v>552</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <f t="shared" si="2"/>
-        <v>226</v>
-      </c>
-      <c r="O14">
+        <v>366</v>
+      </c>
+      <c r="P14">
         <f t="shared" si="3"/>
-        <v>1088</v>
-      </c>
-      <c r="P14">
+        <v>1228</v>
+      </c>
+      <c r="Q14">
         <v>15</v>
       </c>
-      <c r="Q14">
-        <v>13</v>
-      </c>
       <c r="R14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S14">
         <v>11</v>
@@ -1884,34 +2081,46 @@
         <v>11</v>
       </c>
       <c r="V14">
+        <v>11</v>
+      </c>
+      <c r="W14">
         <v>9</v>
       </c>
-      <c r="W14">
+      <c r="X14">
         <v>11</v>
       </c>
-      <c r="X14">
+      <c r="Y14">
         <v>14</v>
       </c>
-      <c r="Y14">
+      <c r="Z14">
         <v>10</v>
       </c>
-      <c r="Z14">
+      <c r="AA14">
+        <v>11</v>
+      </c>
+      <c r="AB14">
         <v>15</v>
       </c>
-      <c r="AA14">
+      <c r="AC14">
         <v>12</v>
       </c>
-      <c r="AB14">
-        <v>12</v>
-      </c>
-      <c r="AC14">
-        <v>13</v>
-      </c>
-      <c r="AD14" t="s">
+      <c r="AD14">
+        <v>13</v>
+      </c>
+      <c r="AE14">
+        <v>13</v>
+      </c>
+      <c r="AF14" t="s">
         <v>50</v>
       </c>
+      <c r="AG14" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>63</v>
+      </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -1946,39 +2155,39 @@
         <v>83</v>
       </c>
       <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
         <f t="shared" si="0"/>
         <v>548</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <f t="shared" si="3"/>
         <v>631</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>3</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>11</v>
       </c>
-      <c r="R15">
-        <v>13</v>
-      </c>
       <c r="S15">
+        <v>13</v>
+      </c>
+      <c r="T15">
         <v>7</v>
       </c>
-      <c r="T15">
+      <c r="U15">
         <v>16</v>
       </c>
-      <c r="U15">
-        <v>13</v>
-      </c>
       <c r="V15">
         <v>13</v>
       </c>
@@ -1986,28 +2195,40 @@
         <v>13</v>
       </c>
       <c r="X15">
+        <v>13</v>
+      </c>
+      <c r="Y15">
         <v>16</v>
       </c>
-      <c r="Y15">
-        <v>13</v>
-      </c>
       <c r="Z15">
+        <v>13</v>
+      </c>
+      <c r="AA15">
+        <v>13</v>
+      </c>
+      <c r="AB15">
         <v>9</v>
       </c>
-      <c r="AA15">
+      <c r="AC15">
         <v>17</v>
       </c>
-      <c r="AB15">
+      <c r="AD15">
         <v>15</v>
       </c>
-      <c r="AC15">
+      <c r="AE15">
         <v>14</v>
       </c>
-      <c r="AD15" t="s">
+      <c r="AF15" t="s">
         <v>50</v>
       </c>
+      <c r="AG15" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>63</v>
+      </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -2042,39 +2263,39 @@
         <v>0</v>
       </c>
       <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
         <f t="shared" si="0"/>
         <v>528</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <f t="shared" si="3"/>
         <v>528</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>2</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>12</v>
       </c>
-      <c r="R16">
-        <v>13</v>
-      </c>
       <c r="S16">
+        <v>13</v>
+      </c>
+      <c r="T16">
         <v>8</v>
       </c>
-      <c r="T16">
+      <c r="U16">
         <v>16</v>
       </c>
-      <c r="U16">
-        <v>13</v>
-      </c>
       <c r="V16">
         <v>13</v>
       </c>
@@ -2082,28 +2303,40 @@
         <v>13</v>
       </c>
       <c r="X16">
+        <v>13</v>
+      </c>
+      <c r="Y16">
         <v>16</v>
       </c>
-      <c r="Y16">
+      <c r="Z16">
         <v>14</v>
       </c>
-      <c r="Z16">
+      <c r="AA16">
+        <v>13</v>
+      </c>
+      <c r="AB16">
         <v>10</v>
       </c>
-      <c r="AA16">
+      <c r="AC16">
         <v>17</v>
       </c>
-      <c r="AB16">
-        <v>17</v>
-      </c>
-      <c r="AC16">
+      <c r="AD16">
+        <v>18</v>
+      </c>
+      <c r="AE16">
         <v>15</v>
       </c>
-      <c r="AD16" t="s">
+      <c r="AF16" t="s">
         <v>51</v>
       </c>
+      <c r="AG16" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>63</v>
+      </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -2138,39 +2371,39 @@
         <v>0</v>
       </c>
       <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
         <f t="shared" si="0"/>
         <v>448</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <f t="shared" si="3"/>
         <v>448</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>6</v>
       </c>
-      <c r="Q17">
+      <c r="R17">
         <v>7</v>
       </c>
-      <c r="R17">
-        <v>13</v>
-      </c>
       <c r="S17">
         <v>13</v>
       </c>
       <c r="T17">
+        <v>13</v>
+      </c>
+      <c r="U17">
         <v>16</v>
       </c>
-      <c r="U17">
-        <v>13</v>
-      </c>
       <c r="V17">
         <v>13</v>
       </c>
@@ -2178,28 +2411,40 @@
         <v>13</v>
       </c>
       <c r="X17">
+        <v>13</v>
+      </c>
+      <c r="Y17">
         <v>16</v>
       </c>
-      <c r="Y17">
+      <c r="Z17">
         <v>14</v>
       </c>
-      <c r="Z17">
+      <c r="AA17">
+        <v>13</v>
+      </c>
+      <c r="AB17">
         <v>12</v>
       </c>
-      <c r="AA17">
+      <c r="AC17">
         <v>17</v>
       </c>
-      <c r="AB17">
-        <v>17</v>
-      </c>
-      <c r="AC17">
+      <c r="AD17">
+        <v>18</v>
+      </c>
+      <c r="AE17">
         <v>16</v>
       </c>
-      <c r="AD17" t="s">
+      <c r="AF17" t="s">
         <v>50</v>
       </c>
+      <c r="AG17" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -2234,68 +2479,80 @@
         <v>0</v>
       </c>
       <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <f t="shared" si="1"/>
         <v>234</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <f t="shared" si="3"/>
         <v>294</v>
       </c>
-      <c r="P18">
-        <v>15</v>
-      </c>
       <c r="Q18">
         <v>15</v>
       </c>
       <c r="R18">
+        <v>15</v>
+      </c>
+      <c r="S18">
         <v>12</v>
       </c>
-      <c r="S18">
-        <v>13</v>
-      </c>
       <c r="T18">
+        <v>13</v>
+      </c>
+      <c r="U18">
         <v>9</v>
       </c>
-      <c r="U18">
-        <v>13</v>
-      </c>
       <c r="V18">
+        <v>13</v>
+      </c>
+      <c r="W18">
         <v>12</v>
       </c>
-      <c r="W18">
-        <v>13</v>
-      </c>
       <c r="X18">
+        <v>13</v>
+      </c>
+      <c r="Y18">
         <v>15</v>
       </c>
-      <c r="Y18">
+      <c r="Z18">
         <v>14</v>
       </c>
-      <c r="Z18">
+      <c r="AA18">
+        <v>13</v>
+      </c>
+      <c r="AB18">
         <v>17</v>
       </c>
-      <c r="AA18">
+      <c r="AC18">
         <v>14</v>
       </c>
-      <c r="AB18">
-        <v>16</v>
-      </c>
-      <c r="AC18">
+      <c r="AD18">
         <v>17</v>
       </c>
-      <c r="AD18" t="s">
+      <c r="AE18">
+        <v>17</v>
+      </c>
+      <c r="AF18" t="s">
         <v>51</v>
       </c>
+      <c r="AG18" t="s">
+        <v>56</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>63</v>
+      </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -2330,68 +2587,80 @@
         <v>0</v>
       </c>
       <c r="L19">
+        <v>79</v>
+      </c>
+      <c r="M19">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <f t="shared" si="1"/>
         <v>104</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O19">
+        <v>79</v>
+      </c>
+      <c r="P19">
         <f t="shared" si="3"/>
-        <v>171</v>
-      </c>
-      <c r="P19">
+        <v>250</v>
+      </c>
+      <c r="Q19">
         <v>11</v>
       </c>
-      <c r="Q19">
+      <c r="R19">
         <v>15</v>
       </c>
-      <c r="R19">
-        <v>13</v>
-      </c>
       <c r="S19">
         <v>13</v>
       </c>
       <c r="T19">
+        <v>13</v>
+      </c>
+      <c r="U19">
         <v>16</v>
       </c>
-      <c r="U19">
-        <v>13</v>
-      </c>
       <c r="V19">
+        <v>13</v>
+      </c>
+      <c r="W19">
         <v>11</v>
       </c>
-      <c r="W19">
-        <v>13</v>
-      </c>
       <c r="X19">
+        <v>13</v>
+      </c>
+      <c r="Y19">
         <v>16</v>
       </c>
-      <c r="Y19">
+      <c r="Z19">
         <v>14</v>
       </c>
-      <c r="Z19">
+      <c r="AA19">
+        <v>12</v>
+      </c>
+      <c r="AB19">
         <v>16</v>
       </c>
-      <c r="AA19">
+      <c r="AC19">
         <v>15</v>
       </c>
-      <c r="AB19">
-        <v>17</v>
-      </c>
-      <c r="AC19">
+      <c r="AD19">
+        <v>16</v>
+      </c>
+      <c r="AE19">
         <v>18</v>
       </c>
-      <c r="AD19" t="s">
+      <c r="AF19" t="s">
         <v>51</v>
       </c>
+      <c r="AG19" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -2426,39 +2695,39 @@
         <v>0</v>
       </c>
       <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <f t="shared" si="2"/>
         <v>164</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <f t="shared" si="3"/>
         <v>164</v>
       </c>
-      <c r="P20">
-        <v>15</v>
-      </c>
       <c r="Q20">
         <v>15</v>
       </c>
       <c r="R20">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S20">
         <v>13</v>
       </c>
       <c r="T20">
+        <v>13</v>
+      </c>
+      <c r="U20">
         <v>16</v>
       </c>
-      <c r="U20">
-        <v>13</v>
-      </c>
       <c r="V20">
         <v>13</v>
       </c>
@@ -2466,28 +2735,40 @@
         <v>13</v>
       </c>
       <c r="X20">
+        <v>13</v>
+      </c>
+      <c r="Y20">
         <v>12</v>
       </c>
-      <c r="Y20">
+      <c r="Z20">
         <v>14</v>
       </c>
-      <c r="Z20">
+      <c r="AA20">
+        <v>13</v>
+      </c>
+      <c r="AB20">
         <v>18</v>
       </c>
-      <c r="AA20">
+      <c r="AC20">
         <v>17</v>
       </c>
-      <c r="AB20">
+      <c r="AD20">
         <v>14</v>
       </c>
-      <c r="AC20">
+      <c r="AE20">
         <v>19</v>
       </c>
-      <c r="AD20" t="s">
+      <c r="AF20" t="s">
         <v>50</v>
       </c>
+      <c r="AG20" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>64</v>
+      </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -2522,29 +2803,29 @@
         <v>0</v>
       </c>
       <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <f t="shared" si="1"/>
         <v>96</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <f t="shared" si="3"/>
         <v>96</v>
       </c>
-      <c r="P21">
-        <v>15</v>
-      </c>
       <c r="Q21">
         <v>15</v>
       </c>
       <c r="R21">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S21">
         <v>13</v>
@@ -2562,30 +2843,42 @@
         <v>13</v>
       </c>
       <c r="X21">
+        <v>13</v>
+      </c>
+      <c r="Y21">
         <v>16</v>
       </c>
-      <c r="Y21">
+      <c r="Z21">
         <v>14</v>
       </c>
-      <c r="Z21">
+      <c r="AA21">
+        <v>13</v>
+      </c>
+      <c r="AB21">
         <v>18</v>
       </c>
-      <c r="AA21">
+      <c r="AC21">
         <v>16</v>
       </c>
-      <c r="AB21">
-        <v>17</v>
-      </c>
-      <c r="AC21">
+      <c r="AD21">
+        <v>18</v>
+      </c>
+      <c r="AE21">
         <v>20</v>
       </c>
-      <c r="AD21" t="s">
+      <c r="AF21" t="s">
         <v>51</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>57</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD23">
-    <sortCondition descending="1" ref="O1:O23"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AF22">
+    <sortCondition descending="1" ref="P1:P22"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E994C07-09FF-45E9-98DC-2CD69D6C5044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510D7E20-5C72-4F2D-9CAD-0C1C4FA75705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7EB6C2C6-840C-4838-9636-758ACFA0B514}"/>
   </bookViews>
@@ -230,7 +230,7 @@
     <t>S.L.P.</t>
   </si>
   <si>
-    <t>E.U.A.</t>
+    <t>Dallas</t>
   </si>
 </sst>
 </file>

--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{510D7E20-5C72-4F2D-9CAD-0C1C4FA75705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8A50E4-8A1A-40F6-81E7-D86D5A7B593F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7EB6C2C6-840C-4838-9636-758ACFA0B514}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="67">
   <si>
     <t>Nombre</t>
   </si>
@@ -231,6 +231,12 @@
   </si>
   <si>
     <t>Dallas</t>
+  </si>
+  <si>
+    <t>Ranking 12</t>
+  </si>
+  <si>
+    <t>Semana 12</t>
   </si>
 </sst>
 </file>
@@ -602,17 +608,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}">
-  <dimension ref="A1:AH21"/>
+  <dimension ref="A1:AJ21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.1796875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7265625" customWidth="1"/>
-    <col min="26" max="26" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.54296875" customWidth="1"/>
+    <col min="12" max="13" width="9.7265625" customWidth="1"/>
+    <col min="14" max="15" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="26" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="9.54296875" customWidth="1"/>
+    <col min="30" max="32" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="8.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -650,73 +665,79 @@
         <v>52</v>
       </c>
       <c r="M1" t="s">
+        <v>66</v>
+      </c>
+      <c r="N1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>10</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>44</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>12</v>
       </c>
-      <c r="R1" t="s">
-        <v>13</v>
-      </c>
       <c r="S1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" t="s">
         <v>14</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>15</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>16</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>17</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>18</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>45</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>49</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>53</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD1" t="s">
         <v>20</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>21</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>46</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>22</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>47</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>54</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -754,35 +775,35 @@
         <v>805</v>
       </c>
       <c r="M2">
-        <f t="shared" ref="M2:M21" si="0">SUM(B2:E2)</f>
+        <v>586</v>
+      </c>
+      <c r="N2">
+        <f>SUM(B2:E2)</f>
         <v>1328</v>
       </c>
-      <c r="N2">
-        <f t="shared" ref="N2:N21" si="1">SUM(F2:I2)</f>
+      <c r="O2">
+        <f>SUM(F2:I2)</f>
         <v>2672</v>
       </c>
-      <c r="O2">
-        <f t="shared" ref="O2:O21" si="2">SUM(J2:L2)</f>
-        <v>1678</v>
-      </c>
       <c r="P2">
-        <f t="shared" ref="P2:P21" si="3">SUM(M2:O2)</f>
-        <v>5678</v>
+        <f>SUM(J2:M2)</f>
+        <v>2264</v>
       </c>
       <c r="Q2">
+        <f>SUM(N2:P2)</f>
+        <v>6264</v>
+      </c>
+      <c r="R2">
         <v>12</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>5</v>
       </c>
-      <c r="S2">
+      <c r="T2">
         <v>6</v>
       </c>
-      <c r="T2">
+      <c r="U2">
         <v>2</v>
-      </c>
-      <c r="U2">
-        <v>1</v>
       </c>
       <c r="V2">
         <v>1</v>
@@ -791,40 +812,46 @@
         <v>1</v>
       </c>
       <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
         <v>2</v>
-      </c>
-      <c r="Y2">
-        <v>5</v>
       </c>
       <c r="Z2">
         <v>5</v>
       </c>
       <c r="AA2">
+        <v>5</v>
+      </c>
+      <c r="AB2">
         <v>2</v>
       </c>
-      <c r="AB2">
+      <c r="AC2">
+        <v>2</v>
+      </c>
+      <c r="AD2">
         <v>4</v>
-      </c>
-      <c r="AC2">
-        <v>1</v>
-      </c>
-      <c r="AD2">
-        <v>1</v>
       </c>
       <c r="AE2">
         <v>1</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AF2">
+        <v>2</v>
+      </c>
+      <c r="AG2">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="s">
         <v>50</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AI2" t="s">
         <v>55</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AJ2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -862,44 +889,44 @@
         <v>586</v>
       </c>
       <c r="M3">
-        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="N3">
+        <f>SUM(B3:E3)</f>
         <v>1852</v>
       </c>
-      <c r="N3">
-        <f t="shared" si="1"/>
+      <c r="O3">
+        <f>SUM(F3:I3)</f>
         <v>2186</v>
       </c>
-      <c r="O3">
-        <f t="shared" si="2"/>
-        <v>1581</v>
-      </c>
       <c r="P3">
-        <f t="shared" si="3"/>
-        <v>5619</v>
+        <f>SUM(J3:M3)</f>
+        <v>2061</v>
       </c>
       <c r="Q3">
+        <f>SUM(N3:P3)</f>
+        <v>6099</v>
+      </c>
+      <c r="R3">
         <v>1</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>3</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>5</v>
       </c>
-      <c r="T3">
+      <c r="U3">
         <v>3</v>
       </c>
-      <c r="U3">
+      <c r="V3">
         <v>2</v>
       </c>
-      <c r="V3">
+      <c r="W3">
         <v>3</v>
       </c>
-      <c r="W3">
+      <c r="X3">
         <v>2</v>
-      </c>
-      <c r="X3">
-        <v>3</v>
       </c>
       <c r="Y3">
         <v>3</v>
@@ -908,31 +935,37 @@
         <v>3</v>
       </c>
       <c r="AA3">
+        <v>3</v>
+      </c>
+      <c r="AB3">
         <v>4</v>
       </c>
-      <c r="AB3">
+      <c r="AC3">
+        <v>3</v>
+      </c>
+      <c r="AD3">
         <v>1</v>
-      </c>
-      <c r="AC3">
-        <v>2</v>
-      </c>
-      <c r="AD3">
-        <v>4</v>
       </c>
       <c r="AE3">
         <v>2</v>
       </c>
-      <c r="AF3" t="s">
+      <c r="AF3">
+        <v>3</v>
+      </c>
+      <c r="AG3">
+        <v>2</v>
+      </c>
+      <c r="AH3" t="s">
         <v>50</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AI3" t="s">
         <v>56</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="AJ3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -970,77 +1003,83 @@
         <v>830</v>
       </c>
       <c r="M4">
-        <f t="shared" si="0"/>
+        <v>736</v>
+      </c>
+      <c r="N4">
+        <f>SUM(B4:E4)</f>
         <v>1036</v>
       </c>
-      <c r="N4">
-        <f t="shared" si="1"/>
+      <c r="O4">
+        <f>SUM(F4:I4)</f>
         <v>2184</v>
       </c>
-      <c r="O4">
-        <f t="shared" si="2"/>
-        <v>1594</v>
-      </c>
       <c r="P4">
-        <f t="shared" si="3"/>
-        <v>4814</v>
+        <f>SUM(J4:M4)</f>
+        <v>2330</v>
       </c>
       <c r="Q4">
+        <f>SUM(N4:P4)</f>
+        <v>5550</v>
+      </c>
+      <c r="R4">
         <v>15</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>10</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>8</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>1</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>3</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <v>4</v>
       </c>
-      <c r="W4">
+      <c r="X4">
         <v>3</v>
       </c>
-      <c r="X4">
+      <c r="Y4">
         <v>1</v>
       </c>
-      <c r="Y4">
+      <c r="Z4">
         <v>2</v>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <v>7</v>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <v>1</v>
       </c>
-      <c r="AB4">
+      <c r="AC4">
+        <v>1</v>
+      </c>
+      <c r="AD4">
         <v>6</v>
-      </c>
-      <c r="AC4">
-        <v>3</v>
-      </c>
-      <c r="AD4">
-        <v>3</v>
       </c>
       <c r="AE4">
         <v>3</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AF4">
+        <v>1</v>
+      </c>
+      <c r="AG4">
+        <v>3</v>
+      </c>
+      <c r="AH4" t="s">
         <v>51</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AI4" t="s">
         <v>56</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="AJ4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -1078,77 +1117,83 @@
         <v>604</v>
       </c>
       <c r="M5">
-        <f t="shared" si="0"/>
+        <v>425</v>
+      </c>
+      <c r="N5">
+        <f>SUM(B5:E5)</f>
         <v>1527</v>
       </c>
-      <c r="N5">
-        <f t="shared" si="1"/>
+      <c r="O5">
+        <f>SUM(F5:I5)</f>
         <v>832</v>
       </c>
-      <c r="O5">
-        <f t="shared" si="2"/>
-        <v>1601</v>
-      </c>
       <c r="P5">
-        <f t="shared" si="3"/>
-        <v>3960</v>
+        <f>SUM(J5:M5)</f>
+        <v>2026</v>
       </c>
       <c r="Q5">
+        <f>SUM(N5:P5)</f>
+        <v>4385</v>
+      </c>
+      <c r="R5">
         <v>7</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>1</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>3</v>
-      </c>
-      <c r="T5">
-        <v>4</v>
       </c>
       <c r="U5">
         <v>4</v>
       </c>
       <c r="V5">
+        <v>4</v>
+      </c>
+      <c r="W5">
         <v>9</v>
       </c>
-      <c r="W5">
-        <v>13</v>
-      </c>
       <c r="X5">
+        <v>13</v>
+      </c>
+      <c r="Y5">
         <v>8</v>
       </c>
-      <c r="Y5">
+      <c r="Z5">
         <v>1</v>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <v>4</v>
       </c>
-      <c r="AA5">
+      <c r="AB5">
         <v>3</v>
       </c>
-      <c r="AB5">
-        <v>2</v>
-      </c>
       <c r="AC5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AD5">
         <v>2</v>
       </c>
       <c r="AE5">
+        <v>8</v>
+      </c>
+      <c r="AF5">
         <v>4</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="AG5">
+        <v>4</v>
+      </c>
+      <c r="AH5" t="s">
         <v>51</v>
       </c>
-      <c r="AG5" t="s">
+      <c r="AI5" t="s">
         <v>57</v>
       </c>
-      <c r="AH5" t="s">
+      <c r="AJ5" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1186,77 +1231,83 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="N6">
+        <f>SUM(B6:E6)</f>
         <v>1361</v>
       </c>
-      <c r="N6">
-        <f t="shared" si="1"/>
+      <c r="O6">
+        <f>SUM(F6:I6)</f>
         <v>1450</v>
       </c>
-      <c r="O6">
-        <f t="shared" si="2"/>
-        <v>671</v>
-      </c>
       <c r="P6">
-        <f t="shared" si="3"/>
-        <v>3482</v>
+        <f>SUM(J6:M6)</f>
+        <v>761</v>
       </c>
       <c r="Q6">
+        <f>SUM(N6:P6)</f>
+        <v>3572</v>
+      </c>
+      <c r="R6">
         <v>9</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <v>4</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <v>1</v>
       </c>
-      <c r="T6">
+      <c r="U6">
         <v>5</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <v>7</v>
       </c>
-      <c r="V6">
+      <c r="W6">
         <v>5</v>
-      </c>
-      <c r="W6">
-        <v>4</v>
       </c>
       <c r="X6">
         <v>4</v>
       </c>
       <c r="Y6">
+        <v>4</v>
+      </c>
+      <c r="Z6">
         <v>6</v>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <v>8</v>
       </c>
-      <c r="AA6">
-        <v>13</v>
-      </c>
       <c r="AB6">
+        <v>13</v>
+      </c>
+      <c r="AC6">
+        <v>12</v>
+      </c>
+      <c r="AD6">
         <v>3</v>
       </c>
-      <c r="AC6">
+      <c r="AE6">
         <v>4</v>
       </c>
-      <c r="AD6">
-        <v>8</v>
-      </c>
-      <c r="AE6">
+      <c r="AF6">
+        <v>10</v>
+      </c>
+      <c r="AG6">
         <v>5</v>
       </c>
-      <c r="AF6" t="s">
+      <c r="AH6" t="s">
         <v>50</v>
       </c>
-      <c r="AG6" t="s">
+      <c r="AI6" t="s">
         <v>57</v>
       </c>
-      <c r="AH6" t="s">
+      <c r="AJ6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -1294,293 +1345,311 @@
         <v>520</v>
       </c>
       <c r="M7">
-        <f t="shared" si="0"/>
+        <v>444</v>
+      </c>
+      <c r="N7">
+        <f>SUM(B7:E7)</f>
         <v>490</v>
       </c>
-      <c r="N7">
-        <f t="shared" si="1"/>
+      <c r="O7">
+        <f>SUM(F7:I7)</f>
         <v>768</v>
       </c>
-      <c r="O7">
-        <f t="shared" si="2"/>
-        <v>1571</v>
-      </c>
       <c r="P7">
-        <f t="shared" si="3"/>
-        <v>2829</v>
+        <f>SUM(J7:M7)</f>
+        <v>2015</v>
       </c>
       <c r="Q7">
+        <f>SUM(N7:P7)</f>
+        <v>3273</v>
+      </c>
+      <c r="R7">
         <v>10</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <v>8</v>
       </c>
-      <c r="S7">
+      <c r="T7">
         <v>9</v>
       </c>
-      <c r="T7">
-        <v>13</v>
-      </c>
       <c r="U7">
+        <v>13</v>
+      </c>
+      <c r="V7">
         <v>15</v>
       </c>
-      <c r="V7">
+      <c r="W7">
         <v>6</v>
       </c>
-      <c r="W7">
+      <c r="X7">
         <v>8</v>
       </c>
-      <c r="X7">
+      <c r="Y7">
         <v>6</v>
       </c>
-      <c r="Y7">
+      <c r="Z7">
         <v>4</v>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <v>1</v>
       </c>
-      <c r="AA7">
+      <c r="AB7">
         <v>5</v>
       </c>
-      <c r="AB7">
+      <c r="AC7">
+        <v>4</v>
+      </c>
+      <c r="AD7">
         <v>11</v>
       </c>
-      <c r="AC7">
+      <c r="AE7">
         <v>9</v>
       </c>
-      <c r="AD7">
+      <c r="AF7">
         <v>5</v>
       </c>
-      <c r="AE7">
+      <c r="AG7">
         <v>6</v>
       </c>
-      <c r="AF7" t="s">
+      <c r="AH7" t="s">
         <v>51</v>
       </c>
-      <c r="AG7" t="s">
+      <c r="AI7" t="s">
         <v>56</v>
       </c>
-      <c r="AH7" t="s">
+      <c r="AJ7" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8">
+        <v>205</v>
+      </c>
+      <c r="C8">
+        <v>280</v>
+      </c>
+      <c r="D8">
+        <v>284</v>
+      </c>
+      <c r="E8">
+        <v>208</v>
+      </c>
+      <c r="F8">
+        <v>318</v>
+      </c>
+      <c r="G8">
+        <v>162</v>
+      </c>
+      <c r="H8">
+        <v>260</v>
+      </c>
+      <c r="I8">
+        <v>265</v>
+      </c>
+      <c r="J8">
+        <v>252</v>
+      </c>
+      <c r="K8">
+        <v>250</v>
+      </c>
+      <c r="L8">
+        <v>249</v>
+      </c>
+      <c r="M8">
+        <v>277</v>
+      </c>
+      <c r="N8">
+        <f>SUM(B8:E8)</f>
+        <v>977</v>
+      </c>
+      <c r="O8">
+        <f>SUM(F8:I8)</f>
+        <v>1005</v>
+      </c>
+      <c r="P8">
+        <f>SUM(J8:M8)</f>
+        <v>1028</v>
+      </c>
+      <c r="Q8">
+        <f>SUM(N8:P8)</f>
+        <v>3010</v>
+      </c>
+      <c r="R8">
+        <v>4</v>
+      </c>
+      <c r="S8">
+        <v>6</v>
+      </c>
+      <c r="T8">
+        <v>7</v>
+      </c>
+      <c r="U8">
+        <v>10</v>
+      </c>
+      <c r="V8">
+        <v>6</v>
+      </c>
+      <c r="W8">
+        <v>10</v>
+      </c>
+      <c r="X8">
+        <v>7</v>
+      </c>
+      <c r="Y8">
+        <v>5</v>
+      </c>
+      <c r="Z8">
+        <v>9</v>
+      </c>
+      <c r="AA8">
+        <v>6</v>
+      </c>
+      <c r="AB8">
+        <v>7</v>
+      </c>
+      <c r="AC8">
+        <v>9</v>
+      </c>
+      <c r="AD8">
+        <v>7</v>
+      </c>
+      <c r="AE8">
+        <v>6</v>
+      </c>
+      <c r="AF8">
+        <v>8</v>
+      </c>
+      <c r="AG8">
+        <v>7</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>30</v>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>46</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <v>478</v>
       </c>
-      <c r="D8">
+      <c r="D9">
         <v>565</v>
       </c>
-      <c r="E8">
+      <c r="E9">
         <v>231</v>
       </c>
-      <c r="F8">
+      <c r="F9">
         <v>354</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
         <v>352</v>
       </c>
-      <c r="K8">
+      <c r="K9">
         <v>493</v>
       </c>
-      <c r="L8">
+      <c r="L9">
         <v>239</v>
       </c>
-      <c r="M8">
-        <f t="shared" si="0"/>
+      <c r="M9">
+        <v>171</v>
+      </c>
+      <c r="N9">
+        <f>SUM(B9:E9)</f>
         <v>1320</v>
       </c>
-      <c r="N8">
-        <f t="shared" si="1"/>
+      <c r="O9">
+        <f>SUM(F9:I9)</f>
         <v>354</v>
       </c>
-      <c r="O8">
-        <f t="shared" si="2"/>
-        <v>1084</v>
-      </c>
-      <c r="P8">
-        <f t="shared" si="3"/>
-        <v>2758</v>
-      </c>
-      <c r="Q8">
-        <v>13</v>
-      </c>
-      <c r="R8">
+      <c r="P9">
+        <f>SUM(J9:M9)</f>
+        <v>1255</v>
+      </c>
+      <c r="Q9">
+        <f>SUM(N9:P9)</f>
+        <v>2929</v>
+      </c>
+      <c r="R9">
+        <v>13</v>
+      </c>
+      <c r="S9">
         <v>2</v>
       </c>
-      <c r="S8">
+      <c r="T9">
         <v>2</v>
       </c>
-      <c r="T8">
+      <c r="U9">
         <v>9</v>
       </c>
-      <c r="U8">
+      <c r="V9">
         <v>5</v>
       </c>
-      <c r="V8">
-        <v>13</v>
-      </c>
-      <c r="W8">
-        <v>13</v>
-      </c>
-      <c r="X8">
-        <v>13</v>
-      </c>
-      <c r="Y8">
+      <c r="W9">
+        <v>13</v>
+      </c>
+      <c r="X9">
+        <v>13</v>
+      </c>
+      <c r="Y9">
+        <v>13</v>
+      </c>
+      <c r="Z9">
         <v>8</v>
       </c>
-      <c r="Z8">
+      <c r="AA9">
         <v>2</v>
       </c>
-      <c r="AA8">
+      <c r="AB9">
         <v>8</v>
       </c>
-      <c r="AB8">
+      <c r="AC9">
+        <v>10</v>
+      </c>
+      <c r="AD9">
         <v>5</v>
       </c>
-      <c r="AC8">
-        <v>13</v>
-      </c>
-      <c r="AD8">
+      <c r="AE9">
+        <v>13</v>
+      </c>
+      <c r="AF9">
         <v>6</v>
       </c>
-      <c r="AE8">
-        <v>7</v>
-      </c>
-      <c r="AF8" t="s">
+      <c r="AG9">
+        <v>8</v>
+      </c>
+      <c r="AH9" t="s">
         <v>50</v>
       </c>
-      <c r="AG8" t="s">
+      <c r="AI9" t="s">
         <v>57</v>
       </c>
-      <c r="AH8" t="s">
+      <c r="AJ9" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9">
-        <v>205</v>
-      </c>
-      <c r="C9">
-        <v>280</v>
-      </c>
-      <c r="D9">
-        <v>284</v>
-      </c>
-      <c r="E9">
-        <v>208</v>
-      </c>
-      <c r="F9">
-        <v>318</v>
-      </c>
-      <c r="G9">
-        <v>162</v>
-      </c>
-      <c r="H9">
-        <v>260</v>
-      </c>
-      <c r="I9">
-        <v>265</v>
-      </c>
-      <c r="J9">
-        <v>252</v>
-      </c>
-      <c r="K9">
-        <v>250</v>
-      </c>
-      <c r="L9">
-        <v>249</v>
-      </c>
-      <c r="M9">
-        <f t="shared" si="0"/>
-        <v>977</v>
-      </c>
-      <c r="N9">
-        <f t="shared" si="1"/>
-        <v>1005</v>
-      </c>
-      <c r="O9">
-        <f t="shared" si="2"/>
-        <v>751</v>
-      </c>
-      <c r="P9">
-        <f t="shared" si="3"/>
-        <v>2733</v>
-      </c>
-      <c r="Q9">
-        <v>4</v>
-      </c>
-      <c r="R9">
-        <v>6</v>
-      </c>
-      <c r="S9">
-        <v>7</v>
-      </c>
-      <c r="T9">
-        <v>10</v>
-      </c>
-      <c r="U9">
-        <v>6</v>
-      </c>
-      <c r="V9">
-        <v>10</v>
-      </c>
-      <c r="W9">
-        <v>7</v>
-      </c>
-      <c r="X9">
-        <v>5</v>
-      </c>
-      <c r="Y9">
-        <v>9</v>
-      </c>
-      <c r="Z9">
-        <v>6</v>
-      </c>
-      <c r="AA9">
-        <v>7</v>
-      </c>
-      <c r="AB9">
-        <v>7</v>
-      </c>
-      <c r="AC9">
-        <v>6</v>
-      </c>
-      <c r="AD9">
-        <v>7</v>
-      </c>
-      <c r="AE9">
-        <v>8</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>56</v>
-      </c>
-      <c r="AH9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1618,77 +1687,83 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="N10">
+        <f>SUM(B10:E10)</f>
         <v>923</v>
       </c>
-      <c r="N10">
-        <f t="shared" si="1"/>
+      <c r="O10">
+        <f>SUM(F10:I10)</f>
         <v>987</v>
       </c>
-      <c r="O10">
-        <f t="shared" si="2"/>
-        <v>574</v>
-      </c>
       <c r="P10">
-        <f t="shared" si="3"/>
-        <v>2484</v>
+        <f>SUM(J10:M10)</f>
+        <v>622</v>
       </c>
       <c r="Q10">
+        <f>SUM(N10:P10)</f>
+        <v>2532</v>
+      </c>
+      <c r="R10">
         <v>8</v>
       </c>
-      <c r="R10">
+      <c r="S10">
         <v>15</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>4</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <v>6</v>
       </c>
-      <c r="U10">
+      <c r="V10">
         <v>14</v>
       </c>
-      <c r="V10">
+      <c r="W10">
         <v>2</v>
       </c>
-      <c r="W10">
+      <c r="X10">
         <v>6</v>
       </c>
-      <c r="X10">
+      <c r="Y10">
         <v>12</v>
       </c>
-      <c r="Y10">
+      <c r="Z10">
         <v>7</v>
       </c>
-      <c r="Z10">
+      <c r="AA10">
         <v>9</v>
       </c>
-      <c r="AA10">
-        <v>13</v>
-      </c>
       <c r="AB10">
+        <v>13</v>
+      </c>
+      <c r="AC10">
+        <v>16</v>
+      </c>
+      <c r="AD10">
         <v>8</v>
       </c>
-      <c r="AC10">
+      <c r="AE10">
         <v>7</v>
       </c>
-      <c r="AD10">
-        <v>10</v>
-      </c>
-      <c r="AE10">
+      <c r="AF10">
+        <v>12</v>
+      </c>
+      <c r="AG10">
         <v>9</v>
       </c>
-      <c r="AF10" t="s">
+      <c r="AH10" t="s">
         <v>51</v>
       </c>
-      <c r="AG10" t="s">
+      <c r="AI10" t="s">
         <v>55</v>
       </c>
-      <c r="AH10" t="s">
+      <c r="AJ10" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -1726,401 +1801,425 @@
         <v>390</v>
       </c>
       <c r="M11">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>366</v>
       </c>
       <c r="N11">
-        <f t="shared" si="1"/>
+        <f>SUM(B11:E11)</f>
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <f>SUM(F11:I11)</f>
         <v>1042</v>
       </c>
-      <c r="O11">
-        <f t="shared" si="2"/>
-        <v>663</v>
-      </c>
       <c r="P11">
-        <f t="shared" si="3"/>
-        <v>1705</v>
+        <f>SUM(J11:M11)</f>
+        <v>1029</v>
       </c>
       <c r="Q11">
-        <v>15</v>
+        <f>SUM(N11:P11)</f>
+        <v>2071</v>
       </c>
       <c r="R11">
         <v>15</v>
       </c>
       <c r="S11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T11">
         <v>13</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V11">
         <v>8</v>
       </c>
       <c r="W11">
+        <v>8</v>
+      </c>
+      <c r="X11">
         <v>5</v>
       </c>
-      <c r="X11">
+      <c r="Y11">
         <v>9</v>
       </c>
-      <c r="Y11">
+      <c r="Z11">
         <v>11</v>
       </c>
-      <c r="Z11">
+      <c r="AA11">
         <v>12</v>
       </c>
-      <c r="AA11">
+      <c r="AB11">
         <v>6</v>
       </c>
-      <c r="AB11">
+      <c r="AC11">
+        <v>7</v>
+      </c>
+      <c r="AD11">
         <v>18</v>
       </c>
-      <c r="AC11">
+      <c r="AE11">
         <v>5</v>
       </c>
-      <c r="AD11">
-        <v>9</v>
-      </c>
-      <c r="AE11">
+      <c r="AF11">
+        <v>7</v>
+      </c>
+      <c r="AG11">
         <v>10</v>
       </c>
-      <c r="AF11" t="s">
+      <c r="AH11" t="s">
         <v>50</v>
       </c>
-      <c r="AG11" t="s">
+      <c r="AI11" t="s">
         <v>56</v>
       </c>
-      <c r="AH11" t="s">
+      <c r="AJ11" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12">
         <v>33</v>
       </c>
-      <c r="B12">
-        <v>190</v>
-      </c>
       <c r="C12">
-        <v>192</v>
+        <v>30</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="F12">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="G12">
-        <v>297</v>
+        <v>114</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="I12">
-        <v>207</v>
+        <v>181</v>
       </c>
       <c r="J12">
-        <v>209</v>
+        <v>158</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="L12">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="M12">
-        <f t="shared" si="0"/>
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="N12">
-        <f t="shared" si="1"/>
-        <v>614</v>
+        <f>SUM(B12:E12)</f>
+        <v>347</v>
       </c>
       <c r="O12">
-        <f t="shared" si="2"/>
-        <v>396</v>
+        <f>SUM(F12:I12)</f>
+        <v>542</v>
       </c>
       <c r="P12">
-        <f t="shared" si="3"/>
-        <v>1392</v>
+        <f>SUM(J12:M12)</f>
+        <v>815</v>
       </c>
       <c r="Q12">
-        <v>5</v>
+        <f>SUM(N12:P12)</f>
+        <v>1704</v>
       </c>
       <c r="R12">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="S12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T12">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="U12">
         <v>12</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y12">
         <v>10</v>
       </c>
       <c r="Z12">
+        <v>13</v>
+      </c>
+      <c r="AA12">
+        <v>11</v>
+      </c>
+      <c r="AB12">
+        <v>10</v>
+      </c>
+      <c r="AC12">
+        <v>6</v>
+      </c>
+      <c r="AD12">
         <v>14</v>
-      </c>
-      <c r="AA12">
-        <v>9</v>
-      </c>
-      <c r="AB12">
-        <v>13</v>
-      </c>
-      <c r="AC12">
-        <v>10</v>
-      </c>
-      <c r="AD12">
-        <v>12</v>
       </c>
       <c r="AE12">
         <v>11</v>
       </c>
-      <c r="AF12" t="s">
+      <c r="AF12">
+        <v>9</v>
+      </c>
+      <c r="AG12">
+        <v>11</v>
+      </c>
+      <c r="AH12" t="s">
         <v>51</v>
       </c>
-      <c r="AG12" t="s">
+      <c r="AI12" t="s">
         <v>56</v>
       </c>
-      <c r="AH12" t="s">
-        <v>60</v>
+      <c r="AJ12" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D13">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="E13">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="F13">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G13">
+        <v>156</v>
+      </c>
+      <c r="H13">
+        <v>156</v>
+      </c>
+      <c r="I13">
+        <v>105</v>
+      </c>
+      <c r="J13">
         <v>114</v>
       </c>
-      <c r="H13">
-        <v>109</v>
-      </c>
-      <c r="I13">
-        <v>181</v>
-      </c>
-      <c r="J13">
-        <v>158</v>
-      </c>
       <c r="K13">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="L13">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="M13">
-        <f t="shared" si="0"/>
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="N13">
-        <f t="shared" si="1"/>
-        <v>542</v>
+        <f>SUM(B13:E13)</f>
+        <v>310</v>
       </c>
       <c r="O13">
-        <f t="shared" si="2"/>
-        <v>425</v>
+        <f>SUM(F13:I13)</f>
+        <v>552</v>
       </c>
       <c r="P13">
-        <f t="shared" si="3"/>
-        <v>1314</v>
+        <f>SUM(J13:M13)</f>
+        <v>709</v>
       </c>
       <c r="Q13">
+        <f>SUM(N13:P13)</f>
+        <v>1571</v>
+      </c>
+      <c r="R13">
+        <v>15</v>
+      </c>
+      <c r="S13">
+        <v>13</v>
+      </c>
+      <c r="T13">
+        <v>11</v>
+      </c>
+      <c r="U13">
+        <v>11</v>
+      </c>
+      <c r="V13">
+        <v>11</v>
+      </c>
+      <c r="W13">
+        <v>11</v>
+      </c>
+      <c r="X13">
+        <v>9</v>
+      </c>
+      <c r="Y13">
+        <v>11</v>
+      </c>
+      <c r="Z13">
         <v>14</v>
-      </c>
-      <c r="R13">
-        <v>14</v>
-      </c>
-      <c r="S13">
-        <v>10</v>
-      </c>
-      <c r="T13">
-        <v>12</v>
-      </c>
-      <c r="U13">
-        <v>10</v>
-      </c>
-      <c r="V13">
-        <v>12</v>
-      </c>
-      <c r="W13">
-        <v>10</v>
-      </c>
-      <c r="X13">
-        <v>10</v>
-      </c>
-      <c r="Y13">
-        <v>13</v>
-      </c>
-      <c r="Z13">
-        <v>11</v>
       </c>
       <c r="AA13">
         <v>10</v>
       </c>
       <c r="AB13">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AC13">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AD13">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AE13">
         <v>12</v>
       </c>
-      <c r="AF13" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG13" t="s">
+      <c r="AF13">
+        <v>11</v>
+      </c>
+      <c r="AG13">
+        <v>12</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI13" t="s">
         <v>56</v>
       </c>
-      <c r="AH13" t="s">
+      <c r="AJ13" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="C14">
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="D14">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="G14">
-        <v>156</v>
+        <v>297</v>
       </c>
       <c r="H14">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="J14">
-        <v>114</v>
+        <v>209</v>
       </c>
       <c r="K14">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="M14">
-        <f t="shared" si="0"/>
-        <v>310</v>
+        <v>56</v>
       </c>
       <c r="N14">
-        <f t="shared" si="1"/>
-        <v>552</v>
+        <f>SUM(B14:E14)</f>
+        <v>382</v>
       </c>
       <c r="O14">
-        <f t="shared" si="2"/>
-        <v>366</v>
+        <f>SUM(F14:I14)</f>
+        <v>614</v>
       </c>
       <c r="P14">
-        <f t="shared" si="3"/>
-        <v>1228</v>
+        <f>SUM(J14:M14)</f>
+        <v>452</v>
       </c>
       <c r="Q14">
-        <v>15</v>
+        <f>SUM(N14:P14)</f>
+        <v>1448</v>
       </c>
       <c r="R14">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="S14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y14">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Z14">
         <v>10</v>
       </c>
       <c r="AA14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AB14">
+        <v>9</v>
+      </c>
+      <c r="AC14">
         <v>15</v>
       </c>
-      <c r="AC14">
-        <v>12</v>
-      </c>
       <c r="AD14">
         <v>13</v>
       </c>
       <c r="AE14">
-        <v>13</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG14" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF14">
+        <v>13</v>
+      </c>
+      <c r="AG14">
+        <v>13</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI14" t="s">
         <v>56</v>
       </c>
-      <c r="AH14" t="s">
-        <v>63</v>
+      <c r="AJ14" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2158,39 +2257,39 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="N15">
+        <f>SUM(B15:E15)</f>
         <v>548</v>
       </c>
-      <c r="N15">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="O15">
-        <f t="shared" si="2"/>
-        <v>83</v>
+        <f>SUM(F15:I15)</f>
+        <v>0</v>
       </c>
       <c r="P15">
-        <f t="shared" si="3"/>
-        <v>631</v>
+        <f>SUM(J15:M15)</f>
+        <v>153</v>
       </c>
       <c r="Q15">
+        <f>SUM(N15:P15)</f>
+        <v>701</v>
+      </c>
+      <c r="R15">
         <v>3</v>
       </c>
-      <c r="R15">
+      <c r="S15">
         <v>11</v>
       </c>
-      <c r="S15">
-        <v>13</v>
-      </c>
       <c r="T15">
+        <v>13</v>
+      </c>
+      <c r="U15">
         <v>7</v>
       </c>
-      <c r="U15">
+      <c r="V15">
         <v>16</v>
       </c>
-      <c r="V15">
-        <v>13</v>
-      </c>
       <c r="W15">
         <v>13</v>
       </c>
@@ -2198,37 +2297,43 @@
         <v>13</v>
       </c>
       <c r="Y15">
+        <v>13</v>
+      </c>
+      <c r="Z15">
         <v>16</v>
       </c>
-      <c r="Z15">
-        <v>13</v>
-      </c>
       <c r="AA15">
         <v>13</v>
       </c>
       <c r="AB15">
+        <v>13</v>
+      </c>
+      <c r="AC15">
+        <v>13</v>
+      </c>
+      <c r="AD15">
         <v>9</v>
       </c>
-      <c r="AC15">
+      <c r="AE15">
         <v>17</v>
       </c>
-      <c r="AD15">
+      <c r="AF15">
         <v>15</v>
       </c>
-      <c r="AE15">
+      <c r="AG15">
         <v>14</v>
       </c>
-      <c r="AF15" t="s">
+      <c r="AH15" t="s">
         <v>50</v>
       </c>
-      <c r="AG15" t="s">
+      <c r="AI15" t="s">
         <v>56</v>
       </c>
-      <c r="AH15" t="s">
+      <c r="AJ15" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -2266,39 +2371,39 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+      <c r="N16">
+        <f>SUM(B16:E16)</f>
         <v>528</v>
       </c>
-      <c r="N16">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="O16">
-        <f t="shared" si="2"/>
+        <f>SUM(F16:I16)</f>
         <v>0</v>
       </c>
       <c r="P16">
-        <f t="shared" si="3"/>
-        <v>528</v>
+        <f>SUM(J16:M16)</f>
+        <v>68</v>
       </c>
       <c r="Q16">
+        <f>SUM(N16:P16)</f>
+        <v>596</v>
+      </c>
+      <c r="R16">
         <v>2</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <v>12</v>
       </c>
-      <c r="S16">
-        <v>13</v>
-      </c>
       <c r="T16">
+        <v>13</v>
+      </c>
+      <c r="U16">
         <v>8</v>
       </c>
-      <c r="U16">
+      <c r="V16">
         <v>16</v>
       </c>
-      <c r="V16">
-        <v>13</v>
-      </c>
       <c r="W16">
         <v>13</v>
       </c>
@@ -2306,37 +2411,43 @@
         <v>13</v>
       </c>
       <c r="Y16">
+        <v>13</v>
+      </c>
+      <c r="Z16">
         <v>16</v>
       </c>
-      <c r="Z16">
+      <c r="AA16">
         <v>14</v>
       </c>
-      <c r="AA16">
-        <v>13</v>
-      </c>
       <c r="AB16">
+        <v>13</v>
+      </c>
+      <c r="AC16">
+        <v>14</v>
+      </c>
+      <c r="AD16">
         <v>10</v>
       </c>
-      <c r="AC16">
+      <c r="AE16">
         <v>17</v>
       </c>
-      <c r="AD16">
-        <v>18</v>
-      </c>
-      <c r="AE16">
+      <c r="AF16">
+        <v>17</v>
+      </c>
+      <c r="AG16">
         <v>15</v>
       </c>
-      <c r="AF16" t="s">
+      <c r="AH16" t="s">
         <v>51</v>
       </c>
-      <c r="AG16" t="s">
+      <c r="AI16" t="s">
         <v>56</v>
       </c>
-      <c r="AH16" t="s">
+      <c r="AJ16" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -2374,39 +2485,39 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <f>SUM(B17:E17)</f>
         <v>448</v>
       </c>
-      <c r="N17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="O17">
-        <f t="shared" si="2"/>
+        <f>SUM(F17:I17)</f>
         <v>0</v>
       </c>
       <c r="P17">
-        <f t="shared" si="3"/>
+        <f>SUM(J17:M17)</f>
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <f>SUM(N17:P17)</f>
         <v>448</v>
       </c>
-      <c r="Q17">
+      <c r="R17">
         <v>6</v>
       </c>
-      <c r="R17">
+      <c r="S17">
         <v>7</v>
       </c>
-      <c r="S17">
-        <v>13</v>
-      </c>
       <c r="T17">
         <v>13</v>
       </c>
       <c r="U17">
+        <v>13</v>
+      </c>
+      <c r="V17">
         <v>16</v>
       </c>
-      <c r="V17">
-        <v>13</v>
-      </c>
       <c r="W17">
         <v>13</v>
       </c>
@@ -2414,39 +2525,45 @@
         <v>13</v>
       </c>
       <c r="Y17">
+        <v>13</v>
+      </c>
+      <c r="Z17">
         <v>16</v>
       </c>
-      <c r="Z17">
+      <c r="AA17">
         <v>14</v>
       </c>
-      <c r="AA17">
-        <v>13</v>
-      </c>
       <c r="AB17">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC17">
         <v>17</v>
       </c>
       <c r="AD17">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AE17">
+        <v>17</v>
+      </c>
+      <c r="AF17">
+        <v>19</v>
+      </c>
+      <c r="AG17">
         <v>16</v>
       </c>
-      <c r="AF17" t="s">
+      <c r="AH17" t="s">
         <v>50</v>
       </c>
-      <c r="AG17" t="s">
+      <c r="AI17" t="s">
         <v>56</v>
       </c>
-      <c r="AH17" t="s">
+      <c r="AJ17" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2455,25 +2572,25 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>19</v>
+        <v>164</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -2482,293 +2599,311 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <f t="shared" si="0"/>
-        <v>41</v>
+        <v>155</v>
       </c>
       <c r="N18">
-        <f t="shared" si="1"/>
-        <v>234</v>
+        <f>SUM(B18:E18)</f>
+        <v>0</v>
       </c>
       <c r="O18">
-        <f t="shared" si="2"/>
-        <v>19</v>
+        <f>SUM(F18:I18)</f>
+        <v>0</v>
       </c>
       <c r="P18">
-        <f t="shared" si="3"/>
-        <v>294</v>
+        <f>SUM(J18:M18)</f>
+        <v>319</v>
       </c>
       <c r="Q18">
-        <v>15</v>
+        <f>SUM(N18:P18)</f>
+        <v>319</v>
       </c>
       <c r="R18">
         <v>15</v>
       </c>
       <c r="S18">
+        <v>15</v>
+      </c>
+      <c r="T18">
+        <v>13</v>
+      </c>
+      <c r="U18">
+        <v>13</v>
+      </c>
+      <c r="V18">
+        <v>16</v>
+      </c>
+      <c r="W18">
+        <v>13</v>
+      </c>
+      <c r="X18">
+        <v>13</v>
+      </c>
+      <c r="Y18">
+        <v>13</v>
+      </c>
+      <c r="Z18">
         <v>12</v>
       </c>
-      <c r="T18">
-        <v>13</v>
-      </c>
-      <c r="U18">
-        <v>9</v>
-      </c>
-      <c r="V18">
-        <v>13</v>
-      </c>
-      <c r="W18">
-        <v>12</v>
-      </c>
-      <c r="X18">
-        <v>13</v>
-      </c>
-      <c r="Y18">
-        <v>15</v>
-      </c>
-      <c r="Z18">
+      <c r="AA18">
         <v>14</v>
       </c>
-      <c r="AA18">
-        <v>13</v>
-      </c>
       <c r="AB18">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AC18">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AD18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE18">
         <v>17</v>
       </c>
-      <c r="AF18" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>56</v>
+      <c r="AF18">
+        <v>14</v>
+      </c>
+      <c r="AG18">
+        <v>17</v>
       </c>
       <c r="AH18" t="s">
-        <v>63</v>
+        <v>50</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>57</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="I19">
         <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M19">
-        <f t="shared" si="0"/>
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="N19">
-        <f t="shared" si="1"/>
-        <v>104</v>
+        <f>SUM(B19:E19)</f>
+        <v>41</v>
       </c>
       <c r="O19">
-        <f t="shared" si="2"/>
-        <v>79</v>
+        <f>SUM(F19:I19)</f>
+        <v>234</v>
       </c>
       <c r="P19">
-        <f t="shared" si="3"/>
-        <v>250</v>
+        <f>SUM(J19:M19)</f>
+        <v>19</v>
       </c>
       <c r="Q19">
-        <v>11</v>
+        <f>SUM(N19:P19)</f>
+        <v>294</v>
       </c>
       <c r="R19">
         <v>15</v>
       </c>
       <c r="S19">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T19">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U19">
+        <v>13</v>
+      </c>
+      <c r="V19">
+        <v>9</v>
+      </c>
+      <c r="W19">
+        <v>13</v>
+      </c>
+      <c r="X19">
+        <v>12</v>
+      </c>
+      <c r="Y19">
+        <v>13</v>
+      </c>
+      <c r="Z19">
+        <v>15</v>
+      </c>
+      <c r="AA19">
+        <v>14</v>
+      </c>
+      <c r="AB19">
+        <v>13</v>
+      </c>
+      <c r="AC19">
+        <v>17</v>
+      </c>
+      <c r="AD19">
+        <v>17</v>
+      </c>
+      <c r="AE19">
+        <v>14</v>
+      </c>
+      <c r="AF19">
+        <v>18</v>
+      </c>
+      <c r="AG19">
+        <v>18</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20">
+        <v>67</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>104</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>79</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <f>SUM(B20:E20)</f>
+        <v>67</v>
+      </c>
+      <c r="O20">
+        <f>SUM(F20:I20)</f>
+        <v>104</v>
+      </c>
+      <c r="P20">
+        <f>SUM(J20:M20)</f>
+        <v>79</v>
+      </c>
+      <c r="Q20">
+        <f>SUM(N20:P20)</f>
+        <v>250</v>
+      </c>
+      <c r="R20">
+        <v>11</v>
+      </c>
+      <c r="S20">
+        <v>15</v>
+      </c>
+      <c r="T20">
+        <v>13</v>
+      </c>
+      <c r="U20">
+        <v>13</v>
+      </c>
+      <c r="V20">
         <v>16</v>
       </c>
-      <c r="V19">
-        <v>13</v>
-      </c>
-      <c r="W19">
+      <c r="W20">
+        <v>13</v>
+      </c>
+      <c r="X20">
         <v>11</v>
       </c>
-      <c r="X19">
-        <v>13</v>
-      </c>
-      <c r="Y19">
+      <c r="Y20">
+        <v>13</v>
+      </c>
+      <c r="Z20">
         <v>16</v>
       </c>
-      <c r="Z19">
+      <c r="AA20">
         <v>14</v>
       </c>
-      <c r="AA19">
+      <c r="AB20">
         <v>12</v>
-      </c>
-      <c r="AB19">
-        <v>16</v>
-      </c>
-      <c r="AC19">
-        <v>15</v>
-      </c>
-      <c r="AD19">
-        <v>16</v>
-      </c>
-      <c r="AE19">
-        <v>18</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>57</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>164</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <f t="shared" si="2"/>
-        <v>164</v>
-      </c>
-      <c r="P20">
-        <f t="shared" si="3"/>
-        <v>164</v>
-      </c>
-      <c r="Q20">
-        <v>15</v>
-      </c>
-      <c r="R20">
-        <v>15</v>
-      </c>
-      <c r="S20">
-        <v>13</v>
-      </c>
-      <c r="T20">
-        <v>13</v>
-      </c>
-      <c r="U20">
-        <v>16</v>
-      </c>
-      <c r="V20">
-        <v>13</v>
-      </c>
-      <c r="W20">
-        <v>13</v>
-      </c>
-      <c r="X20">
-        <v>13</v>
-      </c>
-      <c r="Y20">
-        <v>12</v>
-      </c>
-      <c r="Z20">
-        <v>14</v>
-      </c>
-      <c r="AA20">
-        <v>13</v>
-      </c>
-      <c r="AB20">
-        <v>18</v>
       </c>
       <c r="AC20">
         <v>17</v>
       </c>
       <c r="AD20">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE20">
+        <v>15</v>
+      </c>
+      <c r="AF20">
+        <v>16</v>
+      </c>
+      <c r="AG20">
         <v>19</v>
       </c>
-      <c r="AF20" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG20" t="s">
+      <c r="AH20" t="s">
+        <v>51</v>
+      </c>
+      <c r="AI20" t="s">
         <v>57</v>
       </c>
-      <c r="AH20" t="s">
-        <v>64</v>
+      <c r="AJ20" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -2806,29 +2941,29 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N21">
-        <f t="shared" si="1"/>
+        <f>SUM(B21:E21)</f>
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <f>SUM(F21:I21)</f>
         <v>96</v>
       </c>
-      <c r="O21">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
       <c r="P21">
-        <f t="shared" si="3"/>
+        <f>SUM(J21:M21)</f>
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <f>SUM(N21:P21)</f>
         <v>96</v>
-      </c>
-      <c r="Q21">
-        <v>15</v>
       </c>
       <c r="R21">
         <v>15</v>
       </c>
       <c r="S21">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T21">
         <v>13</v>
@@ -2846,39 +2981,45 @@
         <v>13</v>
       </c>
       <c r="Y21">
+        <v>13</v>
+      </c>
+      <c r="Z21">
         <v>16</v>
       </c>
-      <c r="Z21">
+      <c r="AA21">
         <v>14</v>
       </c>
-      <c r="AA21">
-        <v>13</v>
-      </c>
       <c r="AB21">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AC21">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AD21">
         <v>18</v>
       </c>
       <c r="AE21">
+        <v>16</v>
+      </c>
+      <c r="AF21">
+        <v>19</v>
+      </c>
+      <c r="AG21">
         <v>20</v>
       </c>
-      <c r="AF21" t="s">
+      <c r="AH21" t="s">
         <v>51</v>
       </c>
-      <c r="AG21" t="s">
+      <c r="AI21" t="s">
         <v>57</v>
       </c>
-      <c r="AH21" t="s">
+      <c r="AJ21" t="s">
         <v>62</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AF22">
-    <sortCondition descending="1" ref="P1:P22"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AJ23">
+    <sortCondition descending="1" ref="Q1:Q23"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8A50E4-8A1A-40F6-81E7-D86D5A7B593F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CABD65F-E072-490C-8FD0-0796C34C3EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7EB6C2C6-840C-4838-9636-758ACFA0B514}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="2" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$1:$AJ$21</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -772,26 +775,26 @@
         <v>360</v>
       </c>
       <c r="L2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="M2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="N2">
-        <f>SUM(B2:E2)</f>
+        <f t="shared" ref="N2:N21" si="0">SUM(B2:E2)</f>
         <v>1328</v>
       </c>
       <c r="O2">
-        <f>SUM(F2:I2)</f>
+        <f t="shared" ref="O2:O21" si="1">SUM(F2:I2)</f>
         <v>2672</v>
       </c>
       <c r="P2">
-        <f>SUM(J2:M2)</f>
-        <v>2264</v>
+        <f t="shared" ref="P2:P21" si="2">SUM(J2:M2)</f>
+        <v>2261</v>
       </c>
       <c r="Q2">
-        <f>SUM(N2:P2)</f>
-        <v>6264</v>
+        <f t="shared" ref="Q2:Q21" si="3">SUM(N2:P2)</f>
+        <v>6261</v>
       </c>
       <c r="R2">
         <v>12</v>
@@ -886,26 +889,26 @@
         <v>471</v>
       </c>
       <c r="L3">
-        <v>586</v>
+        <v>519</v>
       </c>
       <c r="M3">
-        <v>480</v>
+        <v>525</v>
       </c>
       <c r="N3">
-        <f>SUM(B3:E3)</f>
+        <f t="shared" si="0"/>
         <v>1852</v>
       </c>
       <c r="O3">
-        <f>SUM(F3:I3)</f>
+        <f t="shared" si="1"/>
         <v>2186</v>
       </c>
       <c r="P3">
-        <f>SUM(J3:M3)</f>
-        <v>2061</v>
+        <f t="shared" si="2"/>
+        <v>2039</v>
       </c>
       <c r="Q3">
-        <f>SUM(N3:P3)</f>
-        <v>6099</v>
+        <f t="shared" si="3"/>
+        <v>6077</v>
       </c>
       <c r="R3">
         <v>1</v>
@@ -1000,26 +1003,26 @@
         <v>225</v>
       </c>
       <c r="L4">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="M4">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="N4">
-        <f>SUM(B4:E4)</f>
+        <f t="shared" si="0"/>
         <v>1036</v>
       </c>
       <c r="O4">
-        <f>SUM(F4:I4)</f>
+        <f t="shared" si="1"/>
         <v>2184</v>
       </c>
       <c r="P4">
-        <f>SUM(J4:M4)</f>
-        <v>2330</v>
+        <f t="shared" si="2"/>
+        <v>2324</v>
       </c>
       <c r="Q4">
-        <f>SUM(N4:P4)</f>
-        <v>5550</v>
+        <f t="shared" si="3"/>
+        <v>5544</v>
       </c>
       <c r="R4">
         <v>15</v>
@@ -1114,26 +1117,26 @@
         <v>398</v>
       </c>
       <c r="L5">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="M5">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="N5">
-        <f>SUM(B5:E5)</f>
+        <f t="shared" si="0"/>
         <v>1527</v>
       </c>
       <c r="O5">
-        <f>SUM(F5:I5)</f>
+        <f t="shared" si="1"/>
         <v>832</v>
       </c>
       <c r="P5">
-        <f>SUM(J5:M5)</f>
-        <v>2026</v>
+        <f t="shared" si="2"/>
+        <v>2024</v>
       </c>
       <c r="Q5">
-        <f>SUM(N5:P5)</f>
-        <v>4385</v>
+        <f t="shared" si="3"/>
+        <v>4383</v>
       </c>
       <c r="R5">
         <v>7</v>
@@ -1234,19 +1237,19 @@
         <v>90</v>
       </c>
       <c r="N6">
-        <f>SUM(B6:E6)</f>
+        <f t="shared" si="0"/>
         <v>1361</v>
       </c>
       <c r="O6">
-        <f>SUM(F6:I6)</f>
+        <f t="shared" si="1"/>
         <v>1450</v>
       </c>
       <c r="P6">
-        <f>SUM(J6:M6)</f>
+        <f t="shared" si="2"/>
         <v>761</v>
       </c>
       <c r="Q6">
-        <f>SUM(N6:P6)</f>
+        <f t="shared" si="3"/>
         <v>3572</v>
       </c>
       <c r="R6">
@@ -1342,26 +1345,26 @@
         <v>533</v>
       </c>
       <c r="L7">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="M7">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="N7">
-        <f>SUM(B7:E7)</f>
+        <f t="shared" si="0"/>
         <v>490</v>
       </c>
       <c r="O7">
-        <f>SUM(F7:I7)</f>
+        <f t="shared" si="1"/>
         <v>768</v>
       </c>
       <c r="P7">
-        <f>SUM(J7:M7)</f>
-        <v>2015</v>
+        <f t="shared" si="2"/>
+        <v>2013</v>
       </c>
       <c r="Q7">
-        <f>SUM(N7:P7)</f>
-        <v>3273</v>
+        <f t="shared" si="3"/>
+        <v>3271</v>
       </c>
       <c r="R7">
         <v>10</v>
@@ -1456,26 +1459,26 @@
         <v>250</v>
       </c>
       <c r="L8">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M8">
         <v>277</v>
       </c>
       <c r="N8">
-        <f>SUM(B8:E8)</f>
+        <f t="shared" si="0"/>
         <v>977</v>
       </c>
       <c r="O8">
-        <f>SUM(F8:I8)</f>
+        <f t="shared" si="1"/>
         <v>1005</v>
       </c>
       <c r="P8">
-        <f>SUM(J8:M8)</f>
-        <v>1028</v>
+        <f t="shared" si="2"/>
+        <v>1026</v>
       </c>
       <c r="Q8">
-        <f>SUM(N8:P8)</f>
-        <v>3010</v>
+        <f t="shared" si="3"/>
+        <v>3008</v>
       </c>
       <c r="R8">
         <v>4</v>
@@ -1576,19 +1579,19 @@
         <v>171</v>
       </c>
       <c r="N9">
-        <f>SUM(B9:E9)</f>
+        <f t="shared" si="0"/>
         <v>1320</v>
       </c>
       <c r="O9">
-        <f>SUM(F9:I9)</f>
+        <f t="shared" si="1"/>
         <v>354</v>
       </c>
       <c r="P9">
-        <f>SUM(J9:M9)</f>
+        <f t="shared" si="2"/>
         <v>1255</v>
       </c>
       <c r="Q9">
-        <f>SUM(N9:P9)</f>
+        <f t="shared" si="3"/>
         <v>2929</v>
       </c>
       <c r="R9">
@@ -1672,7 +1675,7 @@
         <v>571</v>
       </c>
       <c r="H10">
-        <v>297</v>
+        <v>207</v>
       </c>
       <c r="I10">
         <v>29</v>
@@ -1690,20 +1693,20 @@
         <v>48</v>
       </c>
       <c r="N10">
-        <f>SUM(B10:E10)</f>
+        <f t="shared" si="0"/>
         <v>923</v>
       </c>
       <c r="O10">
-        <f>SUM(F10:I10)</f>
-        <v>987</v>
+        <f t="shared" si="1"/>
+        <v>897</v>
       </c>
       <c r="P10">
-        <f>SUM(J10:M10)</f>
+        <f t="shared" si="2"/>
         <v>622</v>
       </c>
       <c r="Q10">
-        <f>SUM(N10:P10)</f>
-        <v>2532</v>
+        <f t="shared" si="3"/>
+        <v>2442</v>
       </c>
       <c r="R10">
         <v>8</v>
@@ -1798,26 +1801,26 @@
         <v>96</v>
       </c>
       <c r="L11">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="M11">
         <v>366</v>
       </c>
       <c r="N11">
-        <f>SUM(B11:E11)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O11">
-        <f>SUM(F11:I11)</f>
+        <f t="shared" si="1"/>
         <v>1042</v>
       </c>
       <c r="P11">
-        <f>SUM(J11:M11)</f>
-        <v>1029</v>
+        <f t="shared" si="2"/>
+        <v>1027</v>
       </c>
       <c r="Q11">
-        <f>SUM(N11:P11)</f>
-        <v>2071</v>
+        <f t="shared" si="3"/>
+        <v>2069</v>
       </c>
       <c r="R11">
         <v>15</v>
@@ -1912,26 +1915,26 @@
         <v>107</v>
       </c>
       <c r="L12">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M12">
         <v>390</v>
       </c>
       <c r="N12">
-        <f>SUM(B12:E12)</f>
+        <f t="shared" si="0"/>
         <v>347</v>
       </c>
       <c r="O12">
-        <f>SUM(F12:I12)</f>
+        <f t="shared" si="1"/>
         <v>542</v>
       </c>
       <c r="P12">
-        <f>SUM(J12:M12)</f>
-        <v>815</v>
+        <f t="shared" si="2"/>
+        <v>814</v>
       </c>
       <c r="Q12">
-        <f>SUM(N12:P12)</f>
-        <v>1704</v>
+        <f t="shared" si="3"/>
+        <v>1703</v>
       </c>
       <c r="R12">
         <v>14</v>
@@ -2029,23 +2032,23 @@
         <v>140</v>
       </c>
       <c r="M13">
-        <v>343</v>
+        <v>270</v>
       </c>
       <c r="N13">
-        <f>SUM(B13:E13)</f>
+        <f t="shared" si="0"/>
         <v>310</v>
       </c>
       <c r="O13">
-        <f>SUM(F13:I13)</f>
+        <f t="shared" si="1"/>
         <v>552</v>
       </c>
       <c r="P13">
-        <f>SUM(J13:M13)</f>
-        <v>709</v>
+        <f t="shared" si="2"/>
+        <v>636</v>
       </c>
       <c r="Q13">
-        <f>SUM(N13:P13)</f>
-        <v>1571</v>
+        <f t="shared" si="3"/>
+        <v>1498</v>
       </c>
       <c r="R13">
         <v>15</v>
@@ -2146,19 +2149,19 @@
         <v>56</v>
       </c>
       <c r="N14">
-        <f>SUM(B14:E14)</f>
+        <f t="shared" si="0"/>
         <v>382</v>
       </c>
       <c r="O14">
-        <f>SUM(F14:I14)</f>
+        <f t="shared" si="1"/>
         <v>614</v>
       </c>
       <c r="P14">
-        <f>SUM(J14:M14)</f>
+        <f t="shared" si="2"/>
         <v>452</v>
       </c>
       <c r="Q14">
-        <f>SUM(N14:P14)</f>
+        <f t="shared" si="3"/>
         <v>1448</v>
       </c>
       <c r="R14">
@@ -2260,19 +2263,19 @@
         <v>70</v>
       </c>
       <c r="N15">
-        <f>SUM(B15:E15)</f>
+        <f t="shared" si="0"/>
         <v>548</v>
       </c>
       <c r="O15">
-        <f>SUM(F15:I15)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P15">
-        <f>SUM(J15:M15)</f>
+        <f t="shared" si="2"/>
         <v>153</v>
       </c>
       <c r="Q15">
-        <f>SUM(N15:P15)</f>
+        <f t="shared" si="3"/>
         <v>701</v>
       </c>
       <c r="R15">
@@ -2374,19 +2377,19 @@
         <v>68</v>
       </c>
       <c r="N16">
-        <f>SUM(B16:E16)</f>
+        <f t="shared" si="0"/>
         <v>528</v>
       </c>
       <c r="O16">
-        <f>SUM(F16:I16)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P16">
-        <f>SUM(J16:M16)</f>
+        <f t="shared" si="2"/>
         <v>68</v>
       </c>
       <c r="Q16">
-        <f>SUM(N16:P16)</f>
+        <f t="shared" si="3"/>
         <v>596</v>
       </c>
       <c r="R16">
@@ -2488,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <f>SUM(B17:E17)</f>
+        <f t="shared" si="0"/>
         <v>448</v>
       </c>
       <c r="O17">
-        <f>SUM(F17:I17)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P17">
-        <f>SUM(J17:M17)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q17">
-        <f>SUM(N17:P17)</f>
+        <f t="shared" si="3"/>
         <v>448</v>
       </c>
       <c r="R17">
@@ -2602,19 +2605,19 @@
         <v>155</v>
       </c>
       <c r="N18">
-        <f>SUM(B18:E18)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O18">
-        <f>SUM(F18:I18)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P18">
-        <f>SUM(J18:M18)</f>
+        <f t="shared" si="2"/>
         <v>319</v>
       </c>
       <c r="Q18">
-        <f>SUM(N18:P18)</f>
+        <f t="shared" si="3"/>
         <v>319</v>
       </c>
       <c r="R18">
@@ -2716,19 +2719,19 @@
         <v>0</v>
       </c>
       <c r="N19">
-        <f>SUM(B19:E19)</f>
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="O19">
-        <f>SUM(F19:I19)</f>
+        <f t="shared" si="1"/>
         <v>234</v>
       </c>
       <c r="P19">
-        <f>SUM(J19:M19)</f>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="Q19">
-        <f>SUM(N19:P19)</f>
+        <f t="shared" si="3"/>
         <v>294</v>
       </c>
       <c r="R19">
@@ -2830,19 +2833,19 @@
         <v>0</v>
       </c>
       <c r="N20">
-        <f>SUM(B20:E20)</f>
+        <f t="shared" si="0"/>
         <v>67</v>
       </c>
       <c r="O20">
-        <f>SUM(F20:I20)</f>
+        <f t="shared" si="1"/>
         <v>104</v>
       </c>
       <c r="P20">
-        <f>SUM(J20:M20)</f>
+        <f t="shared" si="2"/>
         <v>79</v>
       </c>
       <c r="Q20">
-        <f>SUM(N20:P20)</f>
+        <f t="shared" si="3"/>
         <v>250</v>
       </c>
       <c r="R20">
@@ -2944,19 +2947,19 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <f>SUM(B21:E21)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O21">
-        <f>SUM(F21:I21)</f>
+        <f t="shared" si="1"/>
         <v>96</v>
       </c>
       <c r="P21">
-        <f>SUM(J21:M21)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q21">
-        <f>SUM(N21:P21)</f>
+        <f t="shared" si="3"/>
         <v>96</v>
       </c>
       <c r="R21">
@@ -3018,6 +3021,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AJ21" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AJ23">
     <sortCondition descending="1" ref="Q1:Q23"/>
   </sortState>

--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63F4D4A-3F73-4673-B3DF-E7D1F13151F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8678F1E0-CC7E-4FF6-BF0B-E0FF124047DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6DC662A2-343A-4284-B4F3-E8BBCF4A3089}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="2" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2'!$A$1:$L$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2'!$A$1:$N$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="46">
   <si>
     <t>Nombre</t>
   </si>
@@ -77,9 +77,6 @@
     <t>Regiones</t>
   </si>
   <si>
-    <t>Edgardo Guillén</t>
-  </si>
-  <si>
     <t>Hombres</t>
   </si>
   <si>
@@ -104,18 +101,12 @@
     <t>Gaby Rodríguez</t>
   </si>
   <si>
-    <t>Romario Velázquez</t>
-  </si>
-  <si>
     <t>Luis Sarreón</t>
   </si>
   <si>
     <t>41-50</t>
   </si>
   <si>
-    <t>Sandra Jaramillo</t>
-  </si>
-  <si>
     <t>Tol.</t>
   </si>
   <si>
@@ -125,52 +116,67 @@
     <t>Joel Palomares</t>
   </si>
   <si>
-    <t>Mayra Sarreón</t>
-  </si>
-  <si>
     <t>Rubi Muciño</t>
   </si>
   <si>
-    <t>Claudia Martínez</t>
-  </si>
-  <si>
     <t>Paco Sarreón</t>
   </si>
   <si>
     <t>Marco Salas</t>
   </si>
   <si>
-    <t>Mirna Sarreón</t>
-  </si>
-  <si>
-    <t>Julio Guillén</t>
-  </si>
-  <si>
     <t>Marco Olivo</t>
   </si>
   <si>
-    <t>Claudia Sarreón</t>
-  </si>
-  <si>
-    <t>Jacobo Sarreón</t>
-  </si>
-  <si>
     <t>CDMX</t>
   </si>
   <si>
-    <t>Yazareth Sánchez</t>
-  </si>
-  <si>
     <t>Delia Narváez</t>
   </si>
   <si>
     <t>Dallas</t>
   </si>
   <si>
-    <t>Gabriel Sarreón</t>
-  </si>
-  <si>
     <t>Ver.</t>
+  </si>
+  <si>
+    <t>Ed Guillén</t>
+  </si>
+  <si>
+    <t>Roma Velázquez</t>
+  </si>
+  <si>
+    <t>San Jaramillo</t>
+  </si>
+  <si>
+    <t>May Sarreón</t>
+  </si>
+  <si>
+    <t>Clau Martínez</t>
+  </si>
+  <si>
+    <t>Mir Sarreón</t>
+  </si>
+  <si>
+    <t>J.C. Guillén</t>
+  </si>
+  <si>
+    <t>Clau Sarreón</t>
+  </si>
+  <si>
+    <t>Jack Sarreón</t>
+  </si>
+  <si>
+    <t>Yaz Sánchez</t>
+  </si>
+  <si>
+    <t>Gabo Sarreón</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
+  </si>
+  <si>
+    <t>Ranking 3</t>
   </si>
 </sst>
 </file>
@@ -542,22 +548,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0244A2-6A9A-442F-B635-0C9297E0559B}">
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.54296875" customWidth="1"/>
+    <col min="10" max="10" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.6328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -568,36 +575,42 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B2">
         <v>695</v>
@@ -606,38 +619,44 @@
         <v>602</v>
       </c>
       <c r="D2">
-        <f>SUM(B2:C2)</f>
-        <v>1297</v>
+        <v>689</v>
       </c>
       <c r="E2">
-        <f>SUM(D2:D2)</f>
-        <v>1297</v>
+        <f>SUM(B2:D2)</f>
+        <v>1986</v>
       </c>
       <c r="F2">
+        <f>SUM(E2:E2)</f>
+        <v>1986</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>3</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-      <c r="J2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" t="s">
         <v>14</v>
       </c>
-      <c r="L2" t="s">
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>16</v>
       </c>
       <c r="B3">
         <v>693</v>
@@ -646,38 +665,44 @@
         <v>528</v>
       </c>
       <c r="D3">
-        <f>SUM(B3:C3)</f>
-        <v>1221</v>
+        <v>657</v>
       </c>
       <c r="E3">
-        <f>SUM(D3:D3)</f>
-        <v>1221</v>
+        <f>SUM(B3:D3)</f>
+        <v>1878</v>
       </c>
       <c r="F3">
+        <f>SUM(E3:E3)</f>
+        <v>1878</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>6</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+      <c r="L3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" t="s">
         <v>17</v>
       </c>
-      <c r="K3" t="s">
+      <c r="N3" t="s">
         <v>18</v>
       </c>
-      <c r="L3" t="s">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>20</v>
       </c>
       <c r="B4">
         <v>524</v>
@@ -686,38 +711,44 @@
         <v>623</v>
       </c>
       <c r="D4">
-        <f>SUM(B4:C4)</f>
-        <v>1147</v>
+        <v>614</v>
       </c>
       <c r="E4">
-        <f>SUM(D4:D4)</f>
-        <v>1147</v>
+        <f>SUM(B4:D4)</f>
+        <v>1761</v>
       </c>
       <c r="F4">
+        <f>SUM(E4:E4)</f>
+        <v>1761</v>
+      </c>
+      <c r="G4">
         <v>4</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>2</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
       </c>
       <c r="I4">
         <v>3</v>
       </c>
-      <c r="J4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>3</v>
+      </c>
+      <c r="L4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" t="s">
         <v>14</v>
       </c>
-      <c r="L4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>576</v>
@@ -726,38 +757,44 @@
         <v>554</v>
       </c>
       <c r="D5">
-        <f>SUM(B5:C5)</f>
-        <v>1130</v>
+        <v>563</v>
       </c>
       <c r="E5">
-        <f>SUM(D5:D5)</f>
-        <v>1130</v>
+        <f>SUM(B5:D5)</f>
+        <v>1693</v>
       </c>
       <c r="F5">
+        <f>SUM(E5:E5)</f>
+        <v>1693</v>
+      </c>
+      <c r="G5">
         <v>3</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>5</v>
-      </c>
-      <c r="H5">
-        <v>4</v>
       </c>
       <c r="I5">
         <v>4</v>
       </c>
-      <c r="J5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" t="s">
+        <v>13</v>
+      </c>
+      <c r="N5" t="s">
         <v>14</v>
       </c>
-      <c r="L5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>411</v>
@@ -766,38 +803,44 @@
         <v>645</v>
       </c>
       <c r="D6">
-        <f>SUM(B6:C6)</f>
-        <v>1056</v>
+        <v>427</v>
       </c>
       <c r="E6">
-        <f>SUM(D6:D6)</f>
-        <v>1056</v>
+        <f>SUM(B6:D6)</f>
+        <v>1483</v>
       </c>
       <c r="F6">
+        <f>SUM(E6:E6)</f>
+        <v>1483</v>
+      </c>
+      <c r="G6">
         <v>5</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>1</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
       </c>
       <c r="I6">
         <v>5</v>
       </c>
-      <c r="J6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K6" t="s">
-        <v>23</v>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="M6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="B7">
         <v>406</v>
@@ -806,38 +849,44 @@
         <v>579</v>
       </c>
       <c r="D7">
-        <f>SUM(B7:C7)</f>
-        <v>985</v>
+        <v>328</v>
       </c>
       <c r="E7">
-        <f>SUM(D7:D7)</f>
-        <v>985</v>
+        <f>SUM(B7:D7)</f>
+        <v>1313</v>
       </c>
       <c r="F7">
+        <f>SUM(E7:E7)</f>
+        <v>1313</v>
+      </c>
+      <c r="G7">
         <v>6</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>4</v>
-      </c>
-      <c r="H7">
-        <v>6</v>
       </c>
       <c r="I7">
         <v>6</v>
       </c>
-      <c r="J7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="J7">
+        <v>6</v>
+      </c>
+      <c r="K7">
+        <v>6</v>
+      </c>
+      <c r="L7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>23</v>
-      </c>
-      <c r="L7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>26</v>
       </c>
       <c r="B8">
         <v>345</v>
@@ -846,95 +895,107 @@
         <v>223</v>
       </c>
       <c r="D8">
-        <f>SUM(B8:C8)</f>
-        <v>568</v>
+        <v>204</v>
       </c>
       <c r="E8">
-        <f>SUM(D8:D8)</f>
-        <v>568</v>
+        <f>SUM(B8:D8)</f>
+        <v>772</v>
       </c>
       <c r="F8">
+        <f>SUM(E8:E8)</f>
+        <v>772</v>
+      </c>
+      <c r="G8">
         <v>7</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>8</v>
-      </c>
-      <c r="H8">
-        <v>7</v>
       </c>
       <c r="I8">
         <v>7</v>
       </c>
-      <c r="J8" t="s">
-        <v>13</v>
-      </c>
-      <c r="K8" t="s">
-        <v>14</v>
+      <c r="J8">
+        <v>7</v>
+      </c>
+      <c r="K8">
+        <v>7</v>
       </c>
       <c r="L8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="M8" t="s">
+        <v>13</v>
+      </c>
+      <c r="N8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B9">
         <v>62</v>
       </c>
       <c r="C9">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D9">
-        <f>SUM(B9:C9)</f>
-        <v>284</v>
+        <v>161</v>
       </c>
       <c r="E9">
-        <f>SUM(D9:D9)</f>
-        <v>284</v>
+        <f>SUM(B9:D9)</f>
+        <v>441</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <f>SUM(E9:E9)</f>
+        <v>441</v>
       </c>
       <c r="G9">
         <v>9</v>
       </c>
       <c r="H9">
+        <v>10</v>
+      </c>
+      <c r="I9">
+        <v>9</v>
+      </c>
+      <c r="J9">
         <v>8</v>
       </c>
-      <c r="I9">
+      <c r="K9">
         <v>8</v>
       </c>
-      <c r="J9" t="s">
-        <v>13</v>
-      </c>
-      <c r="K9" t="s">
-        <v>14</v>
-      </c>
       <c r="L9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="M9" t="s">
+        <v>13</v>
+      </c>
+      <c r="N9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B10">
         <v>62</v>
       </c>
       <c r="C10">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D10">
-        <f>SUM(B10:C10)</f>
-        <v>280</v>
+        <v>148</v>
       </c>
       <c r="E10">
-        <f>SUM(D10:D10)</f>
-        <v>280</v>
+        <f>SUM(B10:D10)</f>
+        <v>432</v>
       </c>
       <c r="F10">
-        <v>9</v>
+        <f>SUM(E10:E10)</f>
+        <v>432</v>
       </c>
       <c r="G10">
         <v>10</v>
@@ -943,21 +1004,27 @@
         <v>9</v>
       </c>
       <c r="I10">
+        <v>10</v>
+      </c>
+      <c r="J10">
         <v>9</v>
       </c>
-      <c r="J10" t="s">
-        <v>17</v>
-      </c>
-      <c r="K10" t="s">
-        <v>14</v>
+      <c r="K10">
+        <v>9</v>
       </c>
       <c r="L10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="M10" t="s">
+        <v>13</v>
+      </c>
+      <c r="N10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -966,38 +1033,44 @@
         <v>225</v>
       </c>
       <c r="D11">
-        <f>SUM(B11:C11)</f>
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="E11">
-        <f>SUM(D11:D11)</f>
-        <v>225</v>
+        <f>SUM(B11:D11)</f>
+        <v>417</v>
       </c>
       <c r="F11">
-        <v>13</v>
+        <f>SUM(E11:E11)</f>
+        <v>417</v>
       </c>
       <c r="G11">
+        <v>13</v>
+      </c>
+      <c r="H11">
         <v>7</v>
       </c>
-      <c r="H11">
+      <c r="I11">
+        <v>8</v>
+      </c>
+      <c r="J11">
         <v>10</v>
       </c>
-      <c r="I11">
+      <c r="K11">
         <v>10</v>
       </c>
-      <c r="J11" t="s">
-        <v>17</v>
-      </c>
-      <c r="K11" t="s">
-        <v>14</v>
-      </c>
       <c r="L11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+      <c r="M11" t="s">
+        <v>13</v>
+      </c>
+      <c r="N11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B12">
         <v>100</v>
@@ -1006,437 +1079,506 @@
         <v>111</v>
       </c>
       <c r="D12">
-        <f>SUM(B12:C12)</f>
-        <v>211</v>
+        <v>111</v>
       </c>
       <c r="E12">
-        <f>SUM(D12:D12)</f>
-        <v>211</v>
+        <f>SUM(B12:D12)</f>
+        <v>322</v>
       </c>
       <c r="F12">
+        <f>SUM(E12:E12)</f>
+        <v>322</v>
+      </c>
+      <c r="G12">
         <v>8</v>
-      </c>
-      <c r="G12">
-        <v>11</v>
       </c>
       <c r="H12">
         <v>11</v>
       </c>
       <c r="I12">
+        <v>12</v>
+      </c>
+      <c r="J12">
         <v>11</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12">
+        <v>11</v>
+      </c>
+      <c r="L12" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" t="s">
+        <v>13</v>
+      </c>
+      <c r="N12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>122</v>
+      </c>
+      <c r="E13">
+        <f>SUM(B13:D13)</f>
+        <v>122</v>
+      </c>
+      <c r="F13">
+        <f>SUM(E13:E13)</f>
+        <v>122</v>
+      </c>
+      <c r="G13">
+        <v>13</v>
+      </c>
+      <c r="H13">
+        <v>13</v>
+      </c>
+      <c r="I13">
+        <v>11</v>
+      </c>
+      <c r="J13">
+        <v>12</v>
+      </c>
+      <c r="K13">
+        <v>12</v>
+      </c>
+      <c r="L13" t="s">
+        <v>12</v>
+      </c>
+      <c r="M13" t="s">
         <v>17</v>
       </c>
-      <c r="K12" t="s">
+      <c r="N13" t="s">
         <v>14</v>
       </c>
-      <c r="L12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>84</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <f>SUM(B14:D14)</f>
+        <v>84</v>
+      </c>
+      <c r="F14">
+        <f>SUM(E14:E14)</f>
+        <v>84</v>
+      </c>
+      <c r="G14">
+        <v>13</v>
+      </c>
+      <c r="H14">
+        <v>12</v>
+      </c>
+      <c r="I14">
+        <v>13</v>
+      </c>
+      <c r="J14">
+        <v>13</v>
+      </c>
+      <c r="K14">
+        <v>13</v>
+      </c>
+      <c r="L14" t="s">
+        <v>12</v>
+      </c>
+      <c r="M14" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15">
+        <v>39</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <f>SUM(B15:D15)</f>
+        <v>39</v>
+      </c>
+      <c r="F15">
+        <f>SUM(E15:E15)</f>
+        <v>39</v>
+      </c>
+      <c r="G15">
+        <v>11</v>
+      </c>
+      <c r="H15">
+        <v>13</v>
+      </c>
+      <c r="I15">
+        <v>13</v>
+      </c>
+      <c r="J15">
+        <v>14</v>
+      </c>
+      <c r="K15">
+        <v>14</v>
+      </c>
+      <c r="L15" t="s">
+        <v>12</v>
+      </c>
+      <c r="M15" t="s">
+        <v>13</v>
+      </c>
+      <c r="N15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16">
+        <v>28</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <f>SUM(B16:D16)</f>
+        <v>28</v>
+      </c>
+      <c r="F16">
+        <f>SUM(E16:E16)</f>
+        <v>28</v>
+      </c>
+      <c r="G16">
+        <v>12</v>
+      </c>
+      <c r="H16">
+        <v>13</v>
+      </c>
+      <c r="I16">
+        <v>13</v>
+      </c>
+      <c r="J16">
+        <v>15</v>
+      </c>
+      <c r="K16">
+        <v>15</v>
+      </c>
+      <c r="L16" t="s">
+        <v>16</v>
+      </c>
+      <c r="M16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <f>SUM(B17:D17)</f>
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <f>SUM(E17:E17)</f>
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>13</v>
+      </c>
+      <c r="H17">
+        <v>13</v>
+      </c>
+      <c r="I17">
+        <v>13</v>
+      </c>
+      <c r="J17">
+        <v>16</v>
+      </c>
+      <c r="K17">
+        <v>16</v>
+      </c>
+      <c r="L17" t="s">
+        <v>12</v>
+      </c>
+      <c r="M17" t="s">
+        <v>13</v>
+      </c>
+      <c r="N17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <f>SUM(B18:D18)</f>
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <f>SUM(E18:E18)</f>
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>13</v>
+      </c>
+      <c r="I18">
+        <v>13</v>
+      </c>
+      <c r="J18">
+        <v>16</v>
+      </c>
+      <c r="K18">
+        <v>16</v>
+      </c>
+      <c r="L18" t="s">
+        <v>16</v>
+      </c>
+      <c r="M18" t="s">
+        <v>13</v>
+      </c>
+      <c r="N18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <f>SUM(B19:D19)</f>
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <f>SUM(E19:E19)</f>
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>13</v>
+      </c>
+      <c r="H19">
+        <v>13</v>
+      </c>
+      <c r="I19">
+        <v>13</v>
+      </c>
+      <c r="J19">
+        <v>16</v>
+      </c>
+      <c r="K19">
+        <v>16</v>
+      </c>
+      <c r="L19" t="s">
+        <v>12</v>
+      </c>
+      <c r="M19" t="s">
+        <v>13</v>
+      </c>
+      <c r="N19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <f>SUM(B20:D20)</f>
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <f>SUM(E20:E20)</f>
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>13</v>
+      </c>
+      <c r="H20">
+        <v>13</v>
+      </c>
+      <c r="I20">
+        <v>13</v>
+      </c>
+      <c r="J20">
+        <v>16</v>
+      </c>
+      <c r="K20">
+        <v>16</v>
+      </c>
+      <c r="L20" t="s">
+        <v>16</v>
+      </c>
+      <c r="M20" t="s">
+        <v>13</v>
+      </c>
+      <c r="N20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <f>SUM(B21:D21)</f>
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <f>SUM(E21:E21)</f>
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>13</v>
+      </c>
+      <c r="H21">
+        <v>13</v>
+      </c>
+      <c r="I21">
+        <v>13</v>
+      </c>
+      <c r="J21">
+        <v>16</v>
+      </c>
+      <c r="K21">
+        <v>16</v>
+      </c>
+      <c r="L21" t="s">
+        <v>16</v>
+      </c>
+      <c r="M21" t="s">
+        <v>21</v>
+      </c>
+      <c r="N21" t="s">
         <v>31</v>
       </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>84</v>
-      </c>
-      <c r="D13">
-        <f>SUM(B13:C13)</f>
-        <v>84</v>
-      </c>
-      <c r="E13">
-        <f>SUM(D13:D13)</f>
-        <v>84</v>
-      </c>
-      <c r="F13">
-        <v>13</v>
-      </c>
-      <c r="G13">
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <f>SUM(B22:D22)</f>
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <f>SUM(E22:E22)</f>
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>13</v>
+      </c>
+      <c r="H22">
+        <v>13</v>
+      </c>
+      <c r="I22">
+        <v>13</v>
+      </c>
+      <c r="J22">
+        <v>16</v>
+      </c>
+      <c r="K22">
+        <v>16</v>
+      </c>
+      <c r="L22" t="s">
         <v>12</v>
       </c>
-      <c r="H13">
-        <v>12</v>
-      </c>
-      <c r="I13">
-        <v>12</v>
-      </c>
-      <c r="J13" t="s">
-        <v>13</v>
-      </c>
-      <c r="K13" t="s">
-        <v>23</v>
-      </c>
-      <c r="L13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="M22" t="s">
+        <v>21</v>
+      </c>
+      <c r="N22" t="s">
         <v>32</v>
       </c>
-      <c r="B14">
-        <v>39</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <f>SUM(B14:C14)</f>
-        <v>39</v>
-      </c>
-      <c r="E14">
-        <f>SUM(D14:D14)</f>
-        <v>39</v>
-      </c>
-      <c r="F14">
-        <v>11</v>
-      </c>
-      <c r="G14">
-        <v>13</v>
-      </c>
-      <c r="H14">
-        <v>13</v>
-      </c>
-      <c r="I14">
-        <v>13</v>
-      </c>
-      <c r="J14" t="s">
-        <v>13</v>
-      </c>
-      <c r="K14" t="s">
-        <v>14</v>
-      </c>
-      <c r="L14" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15">
-        <v>28</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <f>SUM(B15:C15)</f>
-        <v>28</v>
-      </c>
-      <c r="E15">
-        <f>SUM(D15:D15)</f>
-        <v>28</v>
-      </c>
-      <c r="F15">
-        <v>12</v>
-      </c>
-      <c r="G15">
-        <v>13</v>
-      </c>
-      <c r="H15">
-        <v>14</v>
-      </c>
-      <c r="I15">
-        <v>14</v>
-      </c>
-      <c r="J15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K15" t="s">
-        <v>23</v>
-      </c>
-      <c r="L15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <f>SUM(B16:C16)</f>
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <f>SUM(D16:D16)</f>
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>13</v>
-      </c>
-      <c r="G16">
-        <v>13</v>
-      </c>
-      <c r="H16">
-        <v>15</v>
-      </c>
-      <c r="I16">
-        <v>15</v>
-      </c>
-      <c r="J16" t="s">
-        <v>13</v>
-      </c>
-      <c r="K16" t="s">
-        <v>18</v>
-      </c>
-      <c r="L16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <f>SUM(B17:C17)</f>
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <f>SUM(D17:D17)</f>
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>13</v>
-      </c>
-      <c r="G17">
-        <v>13</v>
-      </c>
-      <c r="H17">
-        <v>15</v>
-      </c>
-      <c r="I17">
-        <v>15</v>
-      </c>
-      <c r="J17" t="s">
-        <v>13</v>
-      </c>
-      <c r="K17" t="s">
-        <v>14</v>
-      </c>
-      <c r="L17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <f>SUM(B18:C18)</f>
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <f>SUM(D18:D18)</f>
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>13</v>
-      </c>
-      <c r="G18">
-        <v>13</v>
-      </c>
-      <c r="H18">
-        <v>15</v>
-      </c>
-      <c r="I18">
-        <v>15</v>
-      </c>
-      <c r="J18" t="s">
-        <v>17</v>
-      </c>
-      <c r="K18" t="s">
-        <v>14</v>
-      </c>
-      <c r="L18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <f>SUM(B19:C19)</f>
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <f>SUM(D19:D19)</f>
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>13</v>
-      </c>
-      <c r="G19">
-        <v>13</v>
-      </c>
-      <c r="H19">
-        <v>15</v>
-      </c>
-      <c r="I19">
-        <v>15</v>
-      </c>
-      <c r="J19" t="s">
-        <v>13</v>
-      </c>
-      <c r="K19" t="s">
-        <v>14</v>
-      </c>
-      <c r="L19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <f>SUM(B20:C20)</f>
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <f>SUM(D20:D20)</f>
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>13</v>
-      </c>
-      <c r="G20">
-        <v>13</v>
-      </c>
-      <c r="H20">
-        <v>15</v>
-      </c>
-      <c r="I20">
-        <v>15</v>
-      </c>
-      <c r="J20" t="s">
-        <v>17</v>
-      </c>
-      <c r="K20" t="s">
-        <v>14</v>
-      </c>
-      <c r="L20" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <f>SUM(B21:C21)</f>
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <f>SUM(D21:D21)</f>
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>13</v>
-      </c>
-      <c r="G21">
-        <v>13</v>
-      </c>
-      <c r="H21">
-        <v>15</v>
-      </c>
-      <c r="I21">
-        <v>15</v>
-      </c>
-      <c r="J21" t="s">
-        <v>17</v>
-      </c>
-      <c r="K21" t="s">
-        <v>23</v>
-      </c>
-      <c r="L21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <f>SUM(B22:C22)</f>
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <f>SUM(D22:D22)</f>
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>13</v>
-      </c>
-      <c r="G22">
-        <v>13</v>
-      </c>
-      <c r="H22">
-        <v>15</v>
-      </c>
-      <c r="I22">
-        <v>15</v>
-      </c>
-      <c r="J22" t="s">
-        <v>13</v>
-      </c>
-      <c r="K22" t="s">
-        <v>23</v>
-      </c>
-      <c r="L22" t="s">
-        <v>43</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L21" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}"/>
+  <autoFilter ref="A1:N21" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N22">
+    <sortCondition descending="1" ref="E1:E22"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8678F1E0-CC7E-4FF6-BF0B-E0FF124047DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DA074C-9C4F-4C84-A668-BD3E8945C5AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6DC662A2-343A-4284-B4F3-E8BBCF4A3089}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="2" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2'!$A$1:$N$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2'!$A$1:$T$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="52">
   <si>
     <t>Nombre</t>
   </si>
@@ -177,6 +177,24 @@
   </si>
   <si>
     <t>Ranking 3</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
+  </si>
+  <si>
+    <t>Ranking 4</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
+  </si>
+  <si>
+    <t>Subt. M 2</t>
+  </si>
+  <si>
+    <t>Ranking 5</t>
+  </si>
+  <si>
+    <t>Ranking Mens. 2</t>
   </si>
 </sst>
 </file>
@@ -548,23 +566,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0244A2-6A9A-442F-B635-0C9297E0559B}">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.54296875" customWidth="1"/>
-    <col min="10" max="10" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.1796875" customWidth="1"/>
+    <col min="9" max="9" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="8.54296875" customWidth="1"/>
+    <col min="15" max="15" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.90625" customWidth="1"/>
+    <col min="17" max="17" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -578,37 +598,55 @@
         <v>44</v>
       </c>
       <c r="E1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>45</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
+      <c r="P1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" t="s">
+      <c r="R1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" t="s">
+      <c r="S1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" t="s">
+      <c r="T1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -622,39 +660,58 @@
         <v>689</v>
       </c>
       <c r="E2">
-        <f>SUM(B2:D2)</f>
-        <v>1986</v>
+        <v>755</v>
       </c>
       <c r="F2">
-        <f>SUM(E2:E2)</f>
-        <v>1986</v>
+        <v>456</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <f>SUM(B2:E2)</f>
+        <v>2741</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <f>F2</f>
+        <v>456</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <f>SUM(G2:H2)</f>
+        <v>3197</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
         <v>1</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>4</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>4</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2" t="s">
         <v>12</v>
       </c>
-      <c r="M2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -668,39 +725,58 @@
         <v>657</v>
       </c>
       <c r="E3">
-        <f>SUM(B3:D3)</f>
-        <v>1878</v>
+        <v>618</v>
       </c>
       <c r="F3">
-        <f>SUM(E3:E3)</f>
-        <v>1878</v>
+        <v>557</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <f>SUM(B3:E3)</f>
+        <v>2496</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <f>F3</f>
+        <v>557</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <f>SUM(G3:H3)</f>
+        <v>3053</v>
       </c>
       <c r="J3">
         <v>2</v>
       </c>
       <c r="K3">
+        <v>6</v>
+      </c>
+      <c r="L3">
         <v>2</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3">
+        <v>2</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+      <c r="O3">
+        <v>2</v>
+      </c>
+      <c r="P3">
+        <v>2</v>
+      </c>
+      <c r="Q3">
+        <v>2</v>
+      </c>
+      <c r="R3" t="s">
         <v>16</v>
       </c>
-      <c r="M3" t="s">
+      <c r="S3" t="s">
         <v>17</v>
       </c>
-      <c r="N3" t="s">
+      <c r="T3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -714,131 +790,188 @@
         <v>614</v>
       </c>
       <c r="E4">
-        <f>SUM(B4:D4)</f>
-        <v>1761</v>
+        <v>494</v>
       </c>
       <c r="F4">
-        <f>SUM(E4:E4)</f>
-        <v>1761</v>
+        <v>438</v>
       </c>
       <c r="G4">
+        <f>SUM(B4:E4)</f>
+        <v>2255</v>
+      </c>
+      <c r="H4">
+        <f>F4</f>
+        <v>438</v>
+      </c>
+      <c r="I4">
+        <f>SUM(G4:H4)</f>
+        <v>2693</v>
+      </c>
+      <c r="J4">
         <v>4</v>
       </c>
-      <c r="H4">
+      <c r="K4">
         <v>2</v>
       </c>
-      <c r="I4">
+      <c r="L4">
         <v>3</v>
       </c>
-      <c r="J4">
+      <c r="M4">
         <v>3</v>
       </c>
-      <c r="K4">
+      <c r="N4">
+        <v>5</v>
+      </c>
+      <c r="O4">
         <v>3</v>
       </c>
-      <c r="L4" t="s">
+      <c r="P4">
+        <v>5</v>
+      </c>
+      <c r="Q4">
+        <v>3</v>
+      </c>
+      <c r="R4" t="s">
         <v>16</v>
       </c>
-      <c r="M4" t="s">
-        <v>13</v>
-      </c>
-      <c r="N4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S4" t="s">
+        <v>13</v>
+      </c>
+      <c r="T4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <v>411</v>
+      </c>
+      <c r="C5">
+        <v>645</v>
+      </c>
+      <c r="D5">
+        <v>427</v>
+      </c>
+      <c r="E5">
+        <v>393</v>
+      </c>
+      <c r="F5">
+        <v>481</v>
+      </c>
+      <c r="G5">
+        <f>SUM(B5:E5)</f>
+        <v>1876</v>
+      </c>
+      <c r="H5">
+        <f>F5</f>
+        <v>481</v>
+      </c>
+      <c r="I5">
+        <f>SUM(G5:H5)</f>
+        <v>2357</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5">
+        <v>5</v>
+      </c>
+      <c r="P5">
+        <v>3</v>
+      </c>
+      <c r="Q5">
+        <v>4</v>
+      </c>
+      <c r="R5" t="s">
+        <v>12</v>
+      </c>
+      <c r="S5" t="s">
+        <v>21</v>
+      </c>
+      <c r="T5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>34</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>576</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>554</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>563</v>
       </c>
-      <c r="E5">
-        <f>SUM(B5:D5)</f>
-        <v>1693</v>
-      </c>
-      <c r="F5">
-        <f>SUM(E5:E5)</f>
-        <v>1693</v>
-      </c>
-      <c r="G5">
+      <c r="E6">
+        <v>324</v>
+      </c>
+      <c r="F6">
+        <v>301</v>
+      </c>
+      <c r="G6">
+        <f>SUM(B6:E6)</f>
+        <v>2017</v>
+      </c>
+      <c r="H6">
+        <f>F6</f>
+        <v>301</v>
+      </c>
+      <c r="I6">
+        <f>SUM(G6:H6)</f>
+        <v>2318</v>
+      </c>
+      <c r="J6">
         <v>3</v>
-      </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-      <c r="L5" t="s">
-        <v>12</v>
-      </c>
-      <c r="M5" t="s">
-        <v>13</v>
-      </c>
-      <c r="N5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6">
-        <v>411</v>
-      </c>
-      <c r="C6">
-        <v>645</v>
-      </c>
-      <c r="D6">
-        <v>427</v>
-      </c>
-      <c r="E6">
-        <f>SUM(B6:D6)</f>
-        <v>1483</v>
-      </c>
-      <c r="F6">
-        <f>SUM(E6:E6)</f>
-        <v>1483</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>5</v>
       </c>
       <c r="K6">
         <v>5</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+      <c r="N6">
+        <v>6</v>
+      </c>
+      <c r="O6">
+        <v>4</v>
+      </c>
+      <c r="P6">
+        <v>6</v>
+      </c>
+      <c r="Q6">
+        <v>5</v>
+      </c>
+      <c r="R6" t="s">
         <v>12</v>
       </c>
-      <c r="M6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="S6" t="s">
+        <v>13</v>
+      </c>
+      <c r="T6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -852,39 +985,58 @@
         <v>328</v>
       </c>
       <c r="E7">
-        <f>SUM(B7:D7)</f>
-        <v>1313</v>
+        <v>287</v>
       </c>
       <c r="F7">
-        <f>SUM(E7:E7)</f>
-        <v>1313</v>
+        <v>648</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <f>SUM(B7:E7)</f>
+        <v>1600</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <f>F7</f>
+        <v>648</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <f>SUM(G7:H7)</f>
+        <v>2248</v>
       </c>
       <c r="J7">
         <v>6</v>
       </c>
       <c r="K7">
+        <v>4</v>
+      </c>
+      <c r="L7">
         <v>6</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7">
+        <v>7</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>6</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>6</v>
+      </c>
+      <c r="R7" t="s">
         <v>16</v>
       </c>
-      <c r="M7" t="s">
+      <c r="S7" t="s">
         <v>21</v>
       </c>
-      <c r="N7" t="s">
+      <c r="T7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -898,223 +1050,318 @@
         <v>204</v>
       </c>
       <c r="E8">
-        <f>SUM(B8:D8)</f>
-        <v>772</v>
+        <v>238</v>
       </c>
       <c r="F8">
-        <f>SUM(E8:E8)</f>
-        <v>772</v>
+        <v>70</v>
       </c>
       <c r="G8">
-        <v>7</v>
+        <f>SUM(B8:E8)</f>
+        <v>1010</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <f>F8</f>
+        <v>70</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <f>SUM(G8:H8)</f>
+        <v>1080</v>
       </c>
       <c r="J8">
         <v>7</v>
       </c>
       <c r="K8">
+        <v>8</v>
+      </c>
+      <c r="L8">
         <v>7</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8">
+        <v>8</v>
+      </c>
+      <c r="N8">
+        <v>13</v>
+      </c>
+      <c r="O8">
+        <v>7</v>
+      </c>
+      <c r="P8">
+        <v>13</v>
+      </c>
+      <c r="Q8">
+        <v>7</v>
+      </c>
+      <c r="R8" t="s">
         <v>12</v>
       </c>
-      <c r="M8" t="s">
-        <v>13</v>
-      </c>
-      <c r="N8" t="s">
+      <c r="S8" t="s">
+        <v>13</v>
+      </c>
+      <c r="T8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>225</v>
+      </c>
+      <c r="D9">
+        <v>192</v>
+      </c>
+      <c r="E9">
+        <v>381</v>
+      </c>
+      <c r="F9">
+        <v>177</v>
+      </c>
+      <c r="G9">
+        <f>SUM(B9:E9)</f>
+        <v>798</v>
+      </c>
+      <c r="H9">
+        <f>F9</f>
+        <v>177</v>
+      </c>
+      <c r="I9">
+        <f>SUM(G9:H9)</f>
+        <v>975</v>
+      </c>
+      <c r="J9">
+        <v>13</v>
+      </c>
+      <c r="K9">
+        <v>7</v>
+      </c>
+      <c r="L9">
+        <v>8</v>
+      </c>
+      <c r="M9">
+        <v>5</v>
+      </c>
+      <c r="N9">
+        <v>10</v>
+      </c>
+      <c r="O9">
+        <v>8</v>
+      </c>
+      <c r="P9">
+        <v>10</v>
+      </c>
+      <c r="Q9">
+        <v>8</v>
+      </c>
+      <c r="R9" t="s">
+        <v>16</v>
+      </c>
+      <c r="S9" t="s">
+        <v>13</v>
+      </c>
+      <c r="T9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>36</v>
-      </c>
-      <c r="B9">
-        <v>62</v>
-      </c>
-      <c r="C9">
-        <v>218</v>
-      </c>
-      <c r="D9">
-        <v>161</v>
-      </c>
-      <c r="E9">
-        <f>SUM(B9:D9)</f>
-        <v>441</v>
-      </c>
-      <c r="F9">
-        <f>SUM(E9:E9)</f>
-        <v>441</v>
-      </c>
-      <c r="G9">
-        <v>9</v>
-      </c>
-      <c r="H9">
-        <v>10</v>
-      </c>
-      <c r="I9">
-        <v>9</v>
-      </c>
-      <c r="J9">
-        <v>8</v>
-      </c>
-      <c r="K9">
-        <v>8</v>
-      </c>
-      <c r="L9" t="s">
-        <v>16</v>
-      </c>
-      <c r="M9" t="s">
-        <v>13</v>
-      </c>
-      <c r="N9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>24</v>
       </c>
       <c r="B10">
         <v>62</v>
       </c>
       <c r="C10">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D10">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="E10">
-        <f>SUM(B10:D10)</f>
-        <v>432</v>
+        <v>62</v>
       </c>
       <c r="F10">
-        <f>SUM(E10:E10)</f>
-        <v>432</v>
+        <v>282</v>
       </c>
       <c r="G10">
-        <v>10</v>
+        <f>SUM(B10:E10)</f>
+        <v>503</v>
       </c>
       <c r="H10">
-        <v>9</v>
+        <f>F10</f>
+        <v>282</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <f>SUM(G10:H10)</f>
+        <v>785</v>
       </c>
       <c r="J10">
         <v>9</v>
       </c>
       <c r="K10">
+        <v>10</v>
+      </c>
+      <c r="L10">
         <v>9</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10">
+        <v>11</v>
+      </c>
+      <c r="N10">
+        <v>8</v>
+      </c>
+      <c r="O10">
+        <v>19</v>
+      </c>
+      <c r="P10">
+        <v>8</v>
+      </c>
+      <c r="Q10">
+        <v>9</v>
+      </c>
+      <c r="R10" t="s">
+        <v>16</v>
+      </c>
+      <c r="S10" t="s">
+        <v>13</v>
+      </c>
+      <c r="T10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11">
+        <v>100</v>
+      </c>
+      <c r="C11">
+        <v>111</v>
+      </c>
+      <c r="D11">
+        <v>111</v>
+      </c>
+      <c r="E11">
+        <v>207</v>
+      </c>
+      <c r="F11">
+        <v>252</v>
+      </c>
+      <c r="G11">
+        <f>SUM(B11:E11)</f>
+        <v>529</v>
+      </c>
+      <c r="H11">
+        <f>F11</f>
+        <v>252</v>
+      </c>
+      <c r="I11">
+        <f>SUM(G11:H11)</f>
+        <v>781</v>
+      </c>
+      <c r="J11">
+        <v>8</v>
+      </c>
+      <c r="K11">
+        <v>11</v>
+      </c>
+      <c r="L11">
         <v>12</v>
       </c>
-      <c r="M10" t="s">
-        <v>13</v>
-      </c>
-      <c r="N10" t="s">
+      <c r="M11">
+        <v>9</v>
+      </c>
+      <c r="N11">
+        <v>9</v>
+      </c>
+      <c r="O11">
+        <v>9</v>
+      </c>
+      <c r="P11">
+        <v>9</v>
+      </c>
+      <c r="Q11">
+        <v>10</v>
+      </c>
+      <c r="R11" t="s">
+        <v>16</v>
+      </c>
+      <c r="S11" t="s">
+        <v>13</v>
+      </c>
+      <c r="T11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>225</v>
-      </c>
-      <c r="D11">
-        <v>192</v>
-      </c>
-      <c r="E11">
-        <f>SUM(B11:D11)</f>
-        <v>417</v>
-      </c>
-      <c r="F11">
-        <f>SUM(E11:E11)</f>
-        <v>417</v>
-      </c>
-      <c r="G11">
-        <v>13</v>
-      </c>
-      <c r="H11">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12">
+        <v>62</v>
+      </c>
+      <c r="C12">
+        <v>222</v>
+      </c>
+      <c r="D12">
+        <v>148</v>
+      </c>
+      <c r="E12">
+        <v>64</v>
+      </c>
+      <c r="F12">
+        <v>285</v>
+      </c>
+      <c r="G12">
+        <f>SUM(B12:E12)</f>
+        <v>496</v>
+      </c>
+      <c r="H12">
+        <f>F12</f>
+        <v>285</v>
+      </c>
+      <c r="I12">
+        <f>SUM(G12:H12)</f>
+        <v>781</v>
+      </c>
+      <c r="J12">
+        <v>10</v>
+      </c>
+      <c r="K12">
+        <v>9</v>
+      </c>
+      <c r="L12">
+        <v>10</v>
+      </c>
+      <c r="M12">
+        <v>10</v>
+      </c>
+      <c r="N12">
         <v>7</v>
       </c>
-      <c r="I11">
-        <v>8</v>
-      </c>
-      <c r="J11">
-        <v>10</v>
-      </c>
-      <c r="K11">
-        <v>10</v>
-      </c>
-      <c r="L11" t="s">
-        <v>16</v>
-      </c>
-      <c r="M11" t="s">
-        <v>13</v>
-      </c>
-      <c r="N11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12">
-        <v>100</v>
-      </c>
-      <c r="C12">
-        <v>111</v>
-      </c>
-      <c r="D12">
-        <v>111</v>
-      </c>
-      <c r="E12">
-        <f>SUM(B12:D12)</f>
-        <v>322</v>
-      </c>
-      <c r="F12">
-        <f>SUM(E12:E12)</f>
-        <v>322</v>
-      </c>
-      <c r="G12">
-        <v>8</v>
-      </c>
-      <c r="H12">
+      <c r="O12">
         <v>11</v>
       </c>
-      <c r="I12">
+      <c r="P12">
+        <v>7</v>
+      </c>
+      <c r="Q12">
+        <v>11</v>
+      </c>
+      <c r="R12" t="s">
         <v>12</v>
       </c>
-      <c r="J12">
-        <v>11</v>
-      </c>
-      <c r="K12">
-        <v>11</v>
-      </c>
-      <c r="L12" t="s">
-        <v>16</v>
-      </c>
-      <c r="M12" t="s">
-        <v>13</v>
-      </c>
-      <c r="N12" t="s">
+      <c r="S12" t="s">
+        <v>13</v>
+      </c>
+      <c r="T12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1128,223 +1375,318 @@
         <v>122</v>
       </c>
       <c r="E13">
-        <f>SUM(B13:D13)</f>
-        <v>122</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <f>SUM(E13:E13)</f>
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="G13">
-        <v>13</v>
+        <f>SUM(B13:E13)</f>
+        <v>145</v>
       </c>
       <c r="H13">
-        <v>13</v>
+        <f>F13</f>
+        <v>141</v>
       </c>
       <c r="I13">
+        <f>SUM(G13:H13)</f>
+        <v>286</v>
+      </c>
+      <c r="J13">
+        <v>13</v>
+      </c>
+      <c r="K13">
+        <v>13</v>
+      </c>
+      <c r="L13">
         <v>11</v>
       </c>
-      <c r="J13">
+      <c r="M13">
+        <v>13</v>
+      </c>
+      <c r="N13">
+        <v>11</v>
+      </c>
+      <c r="O13">
         <v>12</v>
       </c>
-      <c r="K13">
+      <c r="P13">
+        <v>11</v>
+      </c>
+      <c r="Q13">
         <v>12</v>
       </c>
-      <c r="L13" t="s">
+      <c r="R13" t="s">
         <v>12</v>
       </c>
-      <c r="M13" t="s">
+      <c r="S13" t="s">
         <v>17</v>
       </c>
-      <c r="N13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="T13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14">
+        <v>28</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>139</v>
+      </c>
+      <c r="G14">
+        <f>SUM(B14:E14)</f>
+        <v>28</v>
+      </c>
+      <c r="H14">
+        <f>F14</f>
+        <v>139</v>
+      </c>
+      <c r="I14">
+        <f>SUM(G14:H14)</f>
+        <v>167</v>
+      </c>
+      <c r="J14">
+        <v>12</v>
+      </c>
+      <c r="K14">
+        <v>13</v>
+      </c>
+      <c r="L14">
+        <v>13</v>
+      </c>
+      <c r="M14">
+        <v>13</v>
+      </c>
+      <c r="N14">
+        <v>12</v>
+      </c>
+      <c r="O14">
+        <v>16</v>
+      </c>
+      <c r="P14">
+        <v>12</v>
+      </c>
+      <c r="Q14">
+        <v>13</v>
+      </c>
+      <c r="R14" t="s">
+        <v>16</v>
+      </c>
+      <c r="S14" t="s">
+        <v>21</v>
+      </c>
+      <c r="T14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>26</v>
       </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
         <v>84</v>
       </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <f>SUM(B14:D14)</f>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <f>SUM(B15:E15)</f>
         <v>84</v>
       </c>
-      <c r="F14">
-        <f>SUM(E14:E14)</f>
+      <c r="H15">
+        <f>F15</f>
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <f>SUM(G15:H15)</f>
         <v>84</v>
       </c>
-      <c r="G14">
-        <v>13</v>
-      </c>
-      <c r="H14">
+      <c r="J15">
+        <v>13</v>
+      </c>
+      <c r="K15">
         <v>12</v>
       </c>
-      <c r="I14">
-        <v>13</v>
-      </c>
-      <c r="J14">
-        <v>13</v>
-      </c>
-      <c r="K14">
-        <v>13</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="L15">
+        <v>13</v>
+      </c>
+      <c r="M15">
+        <v>13</v>
+      </c>
+      <c r="N15">
+        <v>14</v>
+      </c>
+      <c r="O15">
+        <v>13</v>
+      </c>
+      <c r="P15">
+        <v>14</v>
+      </c>
+      <c r="Q15">
+        <v>14</v>
+      </c>
+      <c r="R15" t="s">
         <v>12</v>
       </c>
-      <c r="M14" t="s">
+      <c r="S15" t="s">
         <v>21</v>
       </c>
-      <c r="N14" t="s">
+      <c r="T15" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>59</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <f>SUM(B16:E16)</f>
+        <v>59</v>
+      </c>
+      <c r="H16">
+        <f>F16</f>
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <f>SUM(G16:H16)</f>
+        <v>59</v>
+      </c>
+      <c r="J16">
+        <v>13</v>
+      </c>
+      <c r="K16">
+        <v>13</v>
+      </c>
+      <c r="L16">
+        <v>13</v>
+      </c>
+      <c r="M16">
+        <v>12</v>
+      </c>
+      <c r="N16">
+        <v>14</v>
+      </c>
+      <c r="O16">
+        <v>14</v>
+      </c>
+      <c r="P16">
+        <v>14</v>
+      </c>
+      <c r="Q16">
+        <v>15</v>
+      </c>
+      <c r="R16" t="s">
+        <v>12</v>
+      </c>
+      <c r="S16" t="s">
+        <v>13</v>
+      </c>
+      <c r="T16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>27</v>
       </c>
-      <c r="B15">
+      <c r="B17">
         <v>39</v>
       </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <f>SUM(B15:D15)</f>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <f>SUM(B17:E17)</f>
         <v>39</v>
       </c>
-      <c r="F15">
-        <f>SUM(E15:E15)</f>
+      <c r="H17">
+        <f>F17</f>
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <f>SUM(G17:H17)</f>
         <v>39</v>
       </c>
-      <c r="G15">
+      <c r="J17">
         <v>11</v>
       </c>
-      <c r="H15">
-        <v>13</v>
-      </c>
-      <c r="I15">
-        <v>13</v>
-      </c>
-      <c r="J15">
-        <v>14</v>
-      </c>
-      <c r="K15">
-        <v>14</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="K17">
+        <v>13</v>
+      </c>
+      <c r="L17">
+        <v>13</v>
+      </c>
+      <c r="M17">
+        <v>13</v>
+      </c>
+      <c r="N17">
+        <v>14</v>
+      </c>
+      <c r="O17">
+        <v>15</v>
+      </c>
+      <c r="P17">
+        <v>14</v>
+      </c>
+      <c r="Q17">
+        <v>16</v>
+      </c>
+      <c r="R17" t="s">
         <v>12</v>
       </c>
-      <c r="M15" t="s">
-        <v>13</v>
-      </c>
-      <c r="N15" t="s">
+      <c r="S17" t="s">
+        <v>13</v>
+      </c>
+      <c r="T17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16">
-        <v>28</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <f>SUM(B16:D16)</f>
-        <v>28</v>
-      </c>
-      <c r="F16">
-        <f>SUM(E16:E16)</f>
-        <v>28</v>
-      </c>
-      <c r="G16">
-        <v>12</v>
-      </c>
-      <c r="H16">
-        <v>13</v>
-      </c>
-      <c r="I16">
-        <v>13</v>
-      </c>
-      <c r="J16">
-        <v>15</v>
-      </c>
-      <c r="K16">
-        <v>15</v>
-      </c>
-      <c r="L16" t="s">
-        <v>16</v>
-      </c>
-      <c r="M16" t="s">
-        <v>21</v>
-      </c>
-      <c r="N16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <f>SUM(B17:D17)</f>
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <f>SUM(E17:E17)</f>
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>13</v>
-      </c>
-      <c r="H17">
-        <v>13</v>
-      </c>
-      <c r="I17">
-        <v>13</v>
-      </c>
-      <c r="J17">
-        <v>16</v>
-      </c>
-      <c r="K17">
-        <v>16</v>
-      </c>
-      <c r="L17" t="s">
-        <v>12</v>
-      </c>
-      <c r="M17" t="s">
-        <v>13</v>
-      </c>
-      <c r="N17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1358,39 +1700,58 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <f>SUM(B18:D18)</f>
         <v>0</v>
       </c>
       <c r="F18">
-        <f>SUM(E18:E18)</f>
         <v>0</v>
       </c>
       <c r="G18">
-        <v>13</v>
+        <f>SUM(B18:E18)</f>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>13</v>
+        <f>F18</f>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>13</v>
+        <f>SUM(G18:H18)</f>
+        <v>0</v>
       </c>
       <c r="J18">
+        <v>13</v>
+      </c>
+      <c r="K18">
+        <v>13</v>
+      </c>
+      <c r="L18">
+        <v>13</v>
+      </c>
+      <c r="M18">
+        <v>13</v>
+      </c>
+      <c r="N18">
+        <v>14</v>
+      </c>
+      <c r="O18">
+        <v>17</v>
+      </c>
+      <c r="P18">
+        <v>14</v>
+      </c>
+      <c r="Q18">
+        <v>17</v>
+      </c>
+      <c r="R18" t="s">
         <v>16</v>
       </c>
-      <c r="K18">
-        <v>16</v>
-      </c>
-      <c r="L18" t="s">
-        <v>16</v>
-      </c>
-      <c r="M18" t="s">
-        <v>13</v>
-      </c>
-      <c r="N18" t="s">
+      <c r="S18" t="s">
+        <v>13</v>
+      </c>
+      <c r="T18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -1404,39 +1765,58 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <f>SUM(B19:D19)</f>
         <v>0</v>
       </c>
       <c r="F19">
-        <f>SUM(E19:E19)</f>
         <v>0</v>
       </c>
       <c r="G19">
-        <v>13</v>
+        <f>SUM(B19:E19)</f>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>13</v>
+        <f>F19</f>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>13</v>
+        <f>SUM(G19:H19)</f>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K19">
-        <v>16</v>
-      </c>
-      <c r="L19" t="s">
+        <v>13</v>
+      </c>
+      <c r="L19">
+        <v>13</v>
+      </c>
+      <c r="M19">
+        <v>13</v>
+      </c>
+      <c r="N19">
+        <v>14</v>
+      </c>
+      <c r="O19">
+        <v>17</v>
+      </c>
+      <c r="P19">
+        <v>14</v>
+      </c>
+      <c r="Q19">
+        <v>17</v>
+      </c>
+      <c r="R19" t="s">
         <v>12</v>
       </c>
-      <c r="M19" t="s">
-        <v>13</v>
-      </c>
-      <c r="N19" t="s">
+      <c r="S19" t="s">
+        <v>13</v>
+      </c>
+      <c r="T19" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -1450,39 +1830,58 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <f>SUM(B20:D20)</f>
         <v>0</v>
       </c>
       <c r="F20">
-        <f>SUM(E20:E20)</f>
         <v>0</v>
       </c>
       <c r="G20">
-        <v>13</v>
+        <f>SUM(B20:E20)</f>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>13</v>
+        <f>F20</f>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>13</v>
+        <f>SUM(G20:H20)</f>
+        <v>0</v>
       </c>
       <c r="J20">
+        <v>13</v>
+      </c>
+      <c r="K20">
+        <v>13</v>
+      </c>
+      <c r="L20">
+        <v>13</v>
+      </c>
+      <c r="M20">
+        <v>13</v>
+      </c>
+      <c r="N20">
+        <v>14</v>
+      </c>
+      <c r="O20">
+        <v>17</v>
+      </c>
+      <c r="P20">
+        <v>14</v>
+      </c>
+      <c r="Q20">
+        <v>17</v>
+      </c>
+      <c r="R20" t="s">
         <v>16</v>
       </c>
-      <c r="K20">
-        <v>16</v>
-      </c>
-      <c r="L20" t="s">
-        <v>16</v>
-      </c>
-      <c r="M20" t="s">
-        <v>13</v>
-      </c>
-      <c r="N20" t="s">
+      <c r="S20" t="s">
+        <v>13</v>
+      </c>
+      <c r="T20" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -1496,39 +1895,58 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <f>SUM(B21:D21)</f>
         <v>0</v>
       </c>
       <c r="F21">
-        <f>SUM(E21:E21)</f>
         <v>0</v>
       </c>
       <c r="G21">
-        <v>13</v>
+        <f>SUM(B21:E21)</f>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>13</v>
+        <f>F21</f>
+        <v>0</v>
       </c>
       <c r="I21">
-        <v>13</v>
+        <f>SUM(G21:H21)</f>
+        <v>0</v>
       </c>
       <c r="J21">
+        <v>13</v>
+      </c>
+      <c r="K21">
+        <v>13</v>
+      </c>
+      <c r="L21">
+        <v>13</v>
+      </c>
+      <c r="M21">
+        <v>13</v>
+      </c>
+      <c r="N21">
+        <v>14</v>
+      </c>
+      <c r="O21">
+        <v>17</v>
+      </c>
+      <c r="P21">
+        <v>14</v>
+      </c>
+      <c r="Q21">
+        <v>17</v>
+      </c>
+      <c r="R21" t="s">
         <v>16</v>
       </c>
-      <c r="K21">
-        <v>16</v>
-      </c>
-      <c r="L21" t="s">
-        <v>16</v>
-      </c>
-      <c r="M21" t="s">
+      <c r="S21" t="s">
         <v>21</v>
       </c>
-      <c r="N21" t="s">
+      <c r="T21" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -1542,42 +1960,61 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <f>SUM(B22:D22)</f>
         <v>0</v>
       </c>
       <c r="F22">
-        <f>SUM(E22:E22)</f>
         <v>0</v>
       </c>
       <c r="G22">
-        <v>13</v>
+        <f>SUM(B22:E22)</f>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>13</v>
+        <f>F22</f>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>13</v>
+        <f>SUM(G22:H22)</f>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K22">
-        <v>16</v>
-      </c>
-      <c r="L22" t="s">
+        <v>13</v>
+      </c>
+      <c r="L22">
+        <v>13</v>
+      </c>
+      <c r="M22">
+        <v>13</v>
+      </c>
+      <c r="N22">
+        <v>14</v>
+      </c>
+      <c r="O22">
+        <v>17</v>
+      </c>
+      <c r="P22">
+        <v>14</v>
+      </c>
+      <c r="Q22">
+        <v>17</v>
+      </c>
+      <c r="R22" t="s">
         <v>12</v>
       </c>
-      <c r="M22" t="s">
+      <c r="S22" t="s">
         <v>21</v>
       </c>
-      <c r="N22" t="s">
+      <c r="T22" t="s">
         <v>32</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N21" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N22">
-    <sortCondition descending="1" ref="E1:E22"/>
+  <autoFilter ref="A1:T21" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T22">
+    <sortCondition descending="1" ref="I1:I22"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DA074C-9C4F-4C84-A668-BD3E8945C5AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D922ACF0-6B98-4389-8D19-BE678E78E85B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6DC662A2-343A-4284-B4F3-E8BBCF4A3089}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="2" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2'!$A$1:$T$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2'!$A$1:$T$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1213,7 +1213,7 @@
         <v>8</v>
       </c>
       <c r="O10">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>8</v>
@@ -2012,7 +2012,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T21" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}"/>
+  <autoFilter ref="A1:T22" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T22">
     <sortCondition descending="1" ref="I1:I22"/>
   </sortState>

--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D922ACF0-6B98-4389-8D19-BE678E78E85B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36AC1859-2DCB-4730-8FFD-EC2423F4A2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6DC662A2-343A-4284-B4F3-E8BBCF4A3089}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="2" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2'!$A$1:$T$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2'!$A$1:$V$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="54">
   <si>
     <t>Nombre</t>
   </si>
@@ -195,6 +195,12 @@
   </si>
   <si>
     <t>Ranking Mens. 2</t>
+  </si>
+  <si>
+    <t>Semana 6</t>
+  </si>
+  <si>
+    <t>Ranking 6</t>
   </si>
 </sst>
 </file>
@@ -566,25 +572,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0244A2-6A9A-442F-B635-0C9297E0559B}">
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.1796875" customWidth="1"/>
-    <col min="9" max="9" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="8.54296875" customWidth="1"/>
-    <col min="15" max="15" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.90625" customWidth="1"/>
-    <col min="17" max="17" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.1796875" customWidth="1"/>
+    <col min="10" max="10" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="8.54296875" customWidth="1"/>
+    <col min="17" max="17" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.90625" customWidth="1"/>
+    <col min="19" max="19" width="13.6328125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -604,179 +610,197 @@
         <v>48</v>
       </c>
       <c r="G1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>49</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>45</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>47</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>50</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q1" t="s">
         <v>7</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>51</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>8</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>9</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>10</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2">
+        <v>693</v>
+      </c>
+      <c r="C2">
+        <v>528</v>
+      </c>
+      <c r="D2">
+        <v>657</v>
+      </c>
+      <c r="E2">
+        <v>618</v>
+      </c>
+      <c r="F2">
+        <v>557</v>
+      </c>
+      <c r="G2">
+        <v>665</v>
+      </c>
+      <c r="H2">
+        <f>SUM(B2:E2)</f>
+        <v>2496</v>
+      </c>
+      <c r="I2">
+        <f>SUM(F2:G2)</f>
+        <v>1222</v>
+      </c>
+      <c r="J2">
+        <f>SUM(H2:I2)</f>
+        <v>3718</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+      <c r="N2">
+        <v>2</v>
+      </c>
+      <c r="O2">
+        <v>2</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>2</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2" t="s">
+        <v>16</v>
+      </c>
+      <c r="U2" t="s">
+        <v>17</v>
+      </c>
+      <c r="V2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>33</v>
       </c>
-      <c r="B2">
+      <c r="B3">
         <v>695</v>
       </c>
-      <c r="C2">
+      <c r="C3">
         <v>602</v>
       </c>
-      <c r="D2">
+      <c r="D3">
         <v>689</v>
       </c>
-      <c r="E2">
+      <c r="E3">
         <v>755</v>
       </c>
-      <c r="F2">
+      <c r="F3">
         <v>456</v>
       </c>
-      <c r="G2">
-        <f>SUM(B2:E2)</f>
+      <c r="G3">
+        <v>454</v>
+      </c>
+      <c r="H3">
+        <f>SUM(B3:E3)</f>
         <v>2741</v>
       </c>
-      <c r="H2">
-        <f>F2</f>
-        <v>456</v>
-      </c>
-      <c r="I2">
-        <f>SUM(G2:H2)</f>
-        <v>3197</v>
-      </c>
-      <c r="J2">
+      <c r="I3">
+        <f>SUM(F3:G3)</f>
+        <v>910</v>
+      </c>
+      <c r="J3">
+        <f>SUM(H3:I3)</f>
+        <v>3651</v>
+      </c>
+      <c r="K3">
         <v>1</v>
       </c>
-      <c r="K2">
+      <c r="L3">
         <v>3</v>
       </c>
-      <c r="L2">
+      <c r="M3">
         <v>1</v>
       </c>
-      <c r="M2">
+      <c r="N3">
         <v>1</v>
       </c>
-      <c r="N2">
+      <c r="O3">
         <v>4</v>
       </c>
-      <c r="O2">
+      <c r="P3">
+        <v>3</v>
+      </c>
+      <c r="Q3">
         <v>1</v>
       </c>
-      <c r="P2">
+      <c r="R3">
         <v>4</v>
       </c>
-      <c r="Q2">
-        <v>1</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="S3">
+        <v>2</v>
+      </c>
+      <c r="T3" t="s">
         <v>12</v>
       </c>
-      <c r="S2" t="s">
-        <v>13</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="U3" t="s">
+        <v>13</v>
+      </c>
+      <c r="V3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3">
-        <v>693</v>
-      </c>
-      <c r="C3">
-        <v>528</v>
-      </c>
-      <c r="D3">
-        <v>657</v>
-      </c>
-      <c r="E3">
-        <v>618</v>
-      </c>
-      <c r="F3">
-        <v>557</v>
-      </c>
-      <c r="G3">
-        <f>SUM(B3:E3)</f>
-        <v>2496</v>
-      </c>
-      <c r="H3">
-        <f>F3</f>
-        <v>557</v>
-      </c>
-      <c r="I3">
-        <f>SUM(G3:H3)</f>
-        <v>3053</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>6</v>
-      </c>
-      <c r="L3">
-        <v>2</v>
-      </c>
-      <c r="M3">
-        <v>2</v>
-      </c>
-      <c r="N3">
-        <v>2</v>
-      </c>
-      <c r="O3">
-        <v>2</v>
-      </c>
-      <c r="P3">
-        <v>2</v>
-      </c>
-      <c r="Q3">
-        <v>2</v>
-      </c>
-      <c r="R3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S3" t="s">
-        <v>17</v>
-      </c>
-      <c r="T3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -796,52 +820,58 @@
         <v>438</v>
       </c>
       <c r="G4">
+        <v>180</v>
+      </c>
+      <c r="H4">
         <f>SUM(B4:E4)</f>
         <v>2255</v>
       </c>
-      <c r="H4">
-        <f>F4</f>
-        <v>438</v>
-      </c>
       <c r="I4">
-        <f>SUM(G4:H4)</f>
-        <v>2693</v>
+        <f>SUM(F4:G4)</f>
+        <v>618</v>
       </c>
       <c r="J4">
+        <f>SUM(H4:I4)</f>
+        <v>2873</v>
+      </c>
+      <c r="K4">
         <v>4</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>2</v>
-      </c>
-      <c r="L4">
-        <v>3</v>
       </c>
       <c r="M4">
         <v>3</v>
       </c>
       <c r="N4">
+        <v>3</v>
+      </c>
+      <c r="O4">
         <v>5</v>
       </c>
-      <c r="O4">
-        <v>3</v>
-      </c>
       <c r="P4">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Q4">
         <v>3</v>
       </c>
-      <c r="R4" t="s">
+      <c r="R4">
+        <v>6</v>
+      </c>
+      <c r="S4">
+        <v>3</v>
+      </c>
+      <c r="T4" t="s">
         <v>16</v>
       </c>
-      <c r="S4" t="s">
-        <v>13</v>
-      </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
+        <v>13</v>
+      </c>
+      <c r="V4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -861,52 +891,58 @@
         <v>481</v>
       </c>
       <c r="G5">
+        <v>491</v>
+      </c>
+      <c r="H5">
         <f>SUM(B5:E5)</f>
         <v>1876</v>
       </c>
-      <c r="H5">
-        <f>F5</f>
-        <v>481</v>
-      </c>
       <c r="I5">
-        <f>SUM(G5:H5)</f>
-        <v>2357</v>
+        <f>SUM(F5:G5)</f>
+        <v>972</v>
       </c>
       <c r="J5">
+        <f>SUM(H5:I5)</f>
+        <v>2848</v>
+      </c>
+      <c r="K5">
         <v>5</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>1</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>5</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>4</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>3</v>
       </c>
-      <c r="O5">
+      <c r="P5">
+        <v>2</v>
+      </c>
+      <c r="Q5">
         <v>5</v>
       </c>
-      <c r="P5">
+      <c r="R5">
         <v>3</v>
       </c>
-      <c r="Q5">
+      <c r="S5">
         <v>4</v>
       </c>
-      <c r="R5" t="s">
+      <c r="T5" t="s">
         <v>12</v>
       </c>
-      <c r="S5" t="s">
+      <c r="U5" t="s">
         <v>21</v>
       </c>
-      <c r="T5" t="s">
+      <c r="V5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -926,52 +962,58 @@
         <v>301</v>
       </c>
       <c r="G6">
+        <v>443</v>
+      </c>
+      <c r="H6">
         <f>SUM(B6:E6)</f>
         <v>2017</v>
       </c>
-      <c r="H6">
-        <f>F6</f>
-        <v>301</v>
-      </c>
       <c r="I6">
-        <f>SUM(G6:H6)</f>
-        <v>2318</v>
+        <f>SUM(F6:G6)</f>
+        <v>744</v>
       </c>
       <c r="J6">
+        <f>SUM(H6:I6)</f>
+        <v>2761</v>
+      </c>
+      <c r="K6">
         <v>3</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>5</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>4</v>
-      </c>
-      <c r="M6">
-        <v>6</v>
       </c>
       <c r="N6">
         <v>6</v>
       </c>
       <c r="O6">
+        <v>6</v>
+      </c>
+      <c r="P6">
         <v>4</v>
       </c>
-      <c r="P6">
-        <v>6</v>
-      </c>
       <c r="Q6">
+        <v>4</v>
+      </c>
+      <c r="R6">
         <v>5</v>
       </c>
-      <c r="R6" t="s">
+      <c r="S6">
+        <v>5</v>
+      </c>
+      <c r="T6" t="s">
         <v>12</v>
       </c>
-      <c r="S6" t="s">
-        <v>13</v>
-      </c>
-      <c r="T6" t="s">
+      <c r="U6" t="s">
+        <v>13</v>
+      </c>
+      <c r="V6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -991,52 +1033,58 @@
         <v>648</v>
       </c>
       <c r="G7">
+        <v>352</v>
+      </c>
+      <c r="H7">
         <f>SUM(B7:E7)</f>
         <v>1600</v>
       </c>
-      <c r="H7">
-        <f>F7</f>
-        <v>648</v>
-      </c>
       <c r="I7">
-        <f>SUM(G7:H7)</f>
-        <v>2248</v>
+        <f>SUM(F7:G7)</f>
+        <v>1000</v>
       </c>
       <c r="J7">
+        <f>SUM(H7:I7)</f>
+        <v>2600</v>
+      </c>
+      <c r="K7">
         <v>6</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>4</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>6</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>7</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>1</v>
       </c>
-      <c r="O7">
-        <v>6</v>
-      </c>
       <c r="P7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
         <v>6</v>
       </c>
-      <c r="R7" t="s">
+      <c r="R7">
+        <v>2</v>
+      </c>
+      <c r="S7">
+        <v>6</v>
+      </c>
+      <c r="T7" t="s">
         <v>16</v>
       </c>
-      <c r="S7" t="s">
+      <c r="U7" t="s">
         <v>21</v>
       </c>
-      <c r="T7" t="s">
+      <c r="V7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1056,52 +1104,58 @@
         <v>70</v>
       </c>
       <c r="G8">
+        <v>224</v>
+      </c>
+      <c r="H8">
         <f>SUM(B8:E8)</f>
         <v>1010</v>
       </c>
-      <c r="H8">
-        <f>F8</f>
-        <v>70</v>
-      </c>
       <c r="I8">
-        <f>SUM(G8:H8)</f>
-        <v>1080</v>
+        <f>SUM(F8:G8)</f>
+        <v>294</v>
       </c>
       <c r="J8">
+        <f>SUM(H8:I8)</f>
+        <v>1304</v>
+      </c>
+      <c r="K8">
         <v>7</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>8</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>7</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>8</v>
       </c>
-      <c r="N8">
-        <v>13</v>
-      </c>
       <c r="O8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="P8">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>7</v>
       </c>
-      <c r="R8" t="s">
+      <c r="R8">
+        <v>13</v>
+      </c>
+      <c r="S8">
+        <v>7</v>
+      </c>
+      <c r="T8" t="s">
         <v>12</v>
       </c>
-      <c r="S8" t="s">
-        <v>13</v>
-      </c>
-      <c r="T8" t="s">
+      <c r="U8" t="s">
+        <v>13</v>
+      </c>
+      <c r="V8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1121,52 +1175,58 @@
         <v>177</v>
       </c>
       <c r="G9">
+        <v>305</v>
+      </c>
+      <c r="H9">
         <f>SUM(B9:E9)</f>
         <v>798</v>
       </c>
-      <c r="H9">
-        <f>F9</f>
-        <v>177</v>
-      </c>
       <c r="I9">
-        <f>SUM(G9:H9)</f>
-        <v>975</v>
+        <f>SUM(F9:G9)</f>
+        <v>482</v>
       </c>
       <c r="J9">
-        <v>13</v>
+        <f>SUM(H9:I9)</f>
+        <v>1280</v>
       </c>
       <c r="K9">
+        <v>13</v>
+      </c>
+      <c r="L9">
         <v>7</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>8</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>5</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>10</v>
       </c>
-      <c r="O9">
-        <v>8</v>
-      </c>
       <c r="P9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>8</v>
       </c>
-      <c r="R9" t="s">
+      <c r="R9">
+        <v>8</v>
+      </c>
+      <c r="S9">
+        <v>8</v>
+      </c>
+      <c r="T9" t="s">
         <v>16</v>
       </c>
-      <c r="S9" t="s">
-        <v>13</v>
-      </c>
-      <c r="T9" t="s">
+      <c r="U9" t="s">
+        <v>13</v>
+      </c>
+      <c r="V9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -1186,182 +1246,200 @@
         <v>282</v>
       </c>
       <c r="G10">
+        <v>196</v>
+      </c>
+      <c r="H10">
         <f>SUM(B10:E10)</f>
         <v>503</v>
       </c>
-      <c r="H10">
-        <f>F10</f>
-        <v>282</v>
-      </c>
       <c r="I10">
-        <f>SUM(G10:H10)</f>
-        <v>785</v>
+        <f>SUM(F10:G10)</f>
+        <v>478</v>
       </c>
       <c r="J10">
+        <f>SUM(H10:I10)</f>
+        <v>981</v>
+      </c>
+      <c r="K10">
         <v>9</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>10</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>9</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>11</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>8</v>
       </c>
-      <c r="O10">
+      <c r="P10">
+        <v>11</v>
+      </c>
+      <c r="Q10">
         <v>10</v>
       </c>
-      <c r="P10">
+      <c r="R10">
+        <v>9</v>
+      </c>
+      <c r="S10">
+        <v>9</v>
+      </c>
+      <c r="T10" t="s">
+        <v>16</v>
+      </c>
+      <c r="U10" t="s">
+        <v>13</v>
+      </c>
+      <c r="V10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11">
+        <v>62</v>
+      </c>
+      <c r="C11">
+        <v>222</v>
+      </c>
+      <c r="D11">
+        <v>148</v>
+      </c>
+      <c r="E11">
+        <v>64</v>
+      </c>
+      <c r="F11">
+        <v>285</v>
+      </c>
+      <c r="G11">
+        <v>198</v>
+      </c>
+      <c r="H11">
+        <f>SUM(B11:E11)</f>
+        <v>496</v>
+      </c>
+      <c r="I11">
+        <f>SUM(F11:G11)</f>
+        <v>483</v>
+      </c>
+      <c r="J11">
+        <f>SUM(H11:I11)</f>
+        <v>979</v>
+      </c>
+      <c r="K11">
+        <v>10</v>
+      </c>
+      <c r="L11">
+        <v>9</v>
+      </c>
+      <c r="M11">
+        <v>10</v>
+      </c>
+      <c r="N11">
+        <v>10</v>
+      </c>
+      <c r="O11">
+        <v>7</v>
+      </c>
+      <c r="P11">
+        <v>10</v>
+      </c>
+      <c r="Q11">
+        <v>11</v>
+      </c>
+      <c r="R11">
+        <v>7</v>
+      </c>
+      <c r="S11">
+        <v>10</v>
+      </c>
+      <c r="T11" t="s">
+        <v>12</v>
+      </c>
+      <c r="U11" t="s">
+        <v>13</v>
+      </c>
+      <c r="V11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12">
+        <v>100</v>
+      </c>
+      <c r="C12">
+        <v>111</v>
+      </c>
+      <c r="D12">
+        <v>111</v>
+      </c>
+      <c r="E12">
+        <v>207</v>
+      </c>
+      <c r="F12">
+        <v>252</v>
+      </c>
+      <c r="G12">
+        <v>177</v>
+      </c>
+      <c r="H12">
+        <f>SUM(B12:E12)</f>
+        <v>529</v>
+      </c>
+      <c r="I12">
+        <f>SUM(F12:G12)</f>
+        <v>429</v>
+      </c>
+      <c r="J12">
+        <f>SUM(H12:I12)</f>
+        <v>958</v>
+      </c>
+      <c r="K12">
         <v>8</v>
       </c>
-      <c r="Q10">
+      <c r="L12">
+        <v>11</v>
+      </c>
+      <c r="M12">
+        <v>12</v>
+      </c>
+      <c r="N12">
         <v>9</v>
       </c>
-      <c r="R10" t="s">
+      <c r="O12">
+        <v>9</v>
+      </c>
+      <c r="P12">
+        <v>13</v>
+      </c>
+      <c r="Q12">
+        <v>9</v>
+      </c>
+      <c r="R12">
+        <v>10</v>
+      </c>
+      <c r="S12">
+        <v>11</v>
+      </c>
+      <c r="T12" t="s">
         <v>16</v>
       </c>
-      <c r="S10" t="s">
-        <v>13</v>
-      </c>
-      <c r="T10" t="s">
+      <c r="U12" t="s">
+        <v>13</v>
+      </c>
+      <c r="V12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11">
-        <v>100</v>
-      </c>
-      <c r="C11">
-        <v>111</v>
-      </c>
-      <c r="D11">
-        <v>111</v>
-      </c>
-      <c r="E11">
-        <v>207</v>
-      </c>
-      <c r="F11">
-        <v>252</v>
-      </c>
-      <c r="G11">
-        <f>SUM(B11:E11)</f>
-        <v>529</v>
-      </c>
-      <c r="H11">
-        <f>F11</f>
-        <v>252</v>
-      </c>
-      <c r="I11">
-        <f>SUM(G11:H11)</f>
-        <v>781</v>
-      </c>
-      <c r="J11">
-        <v>8</v>
-      </c>
-      <c r="K11">
-        <v>11</v>
-      </c>
-      <c r="L11">
-        <v>12</v>
-      </c>
-      <c r="M11">
-        <v>9</v>
-      </c>
-      <c r="N11">
-        <v>9</v>
-      </c>
-      <c r="O11">
-        <v>9</v>
-      </c>
-      <c r="P11">
-        <v>9</v>
-      </c>
-      <c r="Q11">
-        <v>10</v>
-      </c>
-      <c r="R11" t="s">
-        <v>16</v>
-      </c>
-      <c r="S11" t="s">
-        <v>13</v>
-      </c>
-      <c r="T11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12">
-        <v>62</v>
-      </c>
-      <c r="C12">
-        <v>222</v>
-      </c>
-      <c r="D12">
-        <v>148</v>
-      </c>
-      <c r="E12">
-        <v>64</v>
-      </c>
-      <c r="F12">
-        <v>285</v>
-      </c>
-      <c r="G12">
-        <f>SUM(B12:E12)</f>
-        <v>496</v>
-      </c>
-      <c r="H12">
-        <f>F12</f>
-        <v>285</v>
-      </c>
-      <c r="I12">
-        <f>SUM(G12:H12)</f>
-        <v>781</v>
-      </c>
-      <c r="J12">
-        <v>10</v>
-      </c>
-      <c r="K12">
-        <v>9</v>
-      </c>
-      <c r="L12">
-        <v>10</v>
-      </c>
-      <c r="M12">
-        <v>10</v>
-      </c>
-      <c r="N12">
-        <v>7</v>
-      </c>
-      <c r="O12">
-        <v>11</v>
-      </c>
-      <c r="P12">
-        <v>7</v>
-      </c>
-      <c r="Q12">
-        <v>11</v>
-      </c>
-      <c r="R12" t="s">
-        <v>12</v>
-      </c>
-      <c r="S12" t="s">
-        <v>13</v>
-      </c>
-      <c r="T12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1381,52 +1459,58 @@
         <v>141</v>
       </c>
       <c r="G13">
+        <v>166</v>
+      </c>
+      <c r="H13">
         <f>SUM(B13:E13)</f>
         <v>145</v>
       </c>
-      <c r="H13">
-        <f>F13</f>
-        <v>141</v>
-      </c>
       <c r="I13">
-        <f>SUM(G13:H13)</f>
-        <v>286</v>
+        <f>SUM(F13:G13)</f>
+        <v>307</v>
       </c>
       <c r="J13">
-        <v>13</v>
+        <f>SUM(H13:I13)</f>
+        <v>452</v>
       </c>
       <c r="K13">
         <v>13</v>
       </c>
       <c r="L13">
+        <v>13</v>
+      </c>
+      <c r="M13">
         <v>11</v>
       </c>
-      <c r="M13">
-        <v>13</v>
-      </c>
       <c r="N13">
+        <v>13</v>
+      </c>
+      <c r="O13">
         <v>11</v>
       </c>
-      <c r="O13">
-        <v>12</v>
-      </c>
       <c r="P13">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q13">
         <v>12</v>
       </c>
-      <c r="R13" t="s">
+      <c r="R13">
         <v>12</v>
       </c>
-      <c r="S13" t="s">
+      <c r="S13">
+        <v>12</v>
+      </c>
+      <c r="T13" t="s">
+        <v>12</v>
+      </c>
+      <c r="U13" t="s">
         <v>17</v>
       </c>
-      <c r="T13" t="s">
+      <c r="V13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -1446,23 +1530,23 @@
         <v>139</v>
       </c>
       <c r="G14">
+        <v>204</v>
+      </c>
+      <c r="H14">
         <f>SUM(B14:E14)</f>
         <v>28</v>
       </c>
-      <c r="H14">
-        <f>F14</f>
-        <v>139</v>
-      </c>
       <c r="I14">
-        <f>SUM(G14:H14)</f>
-        <v>167</v>
+        <f>SUM(F14:G14)</f>
+        <v>343</v>
       </c>
       <c r="J14">
+        <f>SUM(H14:I14)</f>
+        <v>371</v>
+      </c>
+      <c r="K14">
         <v>12</v>
       </c>
-      <c r="K14">
-        <v>13</v>
-      </c>
       <c r="L14">
         <v>13</v>
       </c>
@@ -1470,158 +1554,176 @@
         <v>13</v>
       </c>
       <c r="N14">
+        <v>13</v>
+      </c>
+      <c r="O14">
         <v>12</v>
       </c>
-      <c r="O14">
+      <c r="P14">
+        <v>9</v>
+      </c>
+      <c r="Q14">
         <v>16</v>
       </c>
-      <c r="P14">
+      <c r="R14">
+        <v>11</v>
+      </c>
+      <c r="S14">
+        <v>13</v>
+      </c>
+      <c r="T14" t="s">
+        <v>16</v>
+      </c>
+      <c r="U14" t="s">
+        <v>21</v>
+      </c>
+      <c r="V14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>59</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>253</v>
+      </c>
+      <c r="H15">
+        <f>SUM(B15:E15)</f>
+        <v>59</v>
+      </c>
+      <c r="I15">
+        <f>SUM(F15:G15)</f>
+        <v>253</v>
+      </c>
+      <c r="J15">
+        <f>SUM(H15:I15)</f>
+        <v>312</v>
+      </c>
+      <c r="K15">
+        <v>13</v>
+      </c>
+      <c r="L15">
+        <v>13</v>
+      </c>
+      <c r="M15">
+        <v>13</v>
+      </c>
+      <c r="N15">
         <v>12</v>
       </c>
-      <c r="Q14">
-        <v>13</v>
-      </c>
-      <c r="R14" t="s">
-        <v>16</v>
-      </c>
-      <c r="S14" t="s">
-        <v>21</v>
-      </c>
-      <c r="T14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>84</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <f>SUM(B15:E15)</f>
-        <v>84</v>
-      </c>
-      <c r="H15">
-        <f>F15</f>
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <f>SUM(G15:H15)</f>
-        <v>84</v>
-      </c>
-      <c r="J15">
-        <v>13</v>
-      </c>
-      <c r="K15">
-        <v>12</v>
-      </c>
-      <c r="L15">
-        <v>13</v>
-      </c>
-      <c r="M15">
-        <v>13</v>
-      </c>
-      <c r="N15">
+      <c r="O15">
         <v>14</v>
       </c>
-      <c r="O15">
-        <v>13</v>
-      </c>
       <c r="P15">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>14</v>
       </c>
-      <c r="R15" t="s">
+      <c r="R15">
+        <v>14</v>
+      </c>
+      <c r="S15">
+        <v>14</v>
+      </c>
+      <c r="T15" t="s">
         <v>12</v>
       </c>
-      <c r="S15" t="s">
-        <v>21</v>
-      </c>
-      <c r="T15" t="s">
-        <v>22</v>
+      <c r="U15" t="s">
+        <v>13</v>
+      </c>
+      <c r="V15" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
         <f>SUM(B16:E16)</f>
-        <v>59</v>
-      </c>
-      <c r="H16">
-        <f>F16</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="I16">
-        <f>SUM(G16:H16)</f>
-        <v>59</v>
+        <f>SUM(F16:G16)</f>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>13</v>
+        <f>SUM(H16:I16)</f>
+        <v>84</v>
       </c>
       <c r="K16">
         <v>13</v>
       </c>
       <c r="L16">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N16">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O16">
         <v>14</v>
       </c>
       <c r="P16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q16">
+        <v>13</v>
+      </c>
+      <c r="R16">
         <v>15</v>
       </c>
-      <c r="R16" t="s">
+      <c r="S16">
+        <v>15</v>
+      </c>
+      <c r="T16" t="s">
         <v>12</v>
       </c>
-      <c r="S16" t="s">
-        <v>13</v>
-      </c>
-      <c r="T16" t="s">
-        <v>18</v>
+      <c r="U16" t="s">
+        <v>21</v>
+      </c>
+      <c r="V16" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -1641,23 +1743,23 @@
         <v>0</v>
       </c>
       <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
         <f>SUM(B17:E17)</f>
         <v>39</v>
       </c>
-      <c r="H17">
-        <f>F17</f>
-        <v>0</v>
-      </c>
       <c r="I17">
-        <f>SUM(G17:H17)</f>
+        <f>SUM(F17:G17)</f>
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <f>SUM(H17:I17)</f>
         <v>39</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>11</v>
       </c>
-      <c r="K17">
-        <v>13</v>
-      </c>
       <c r="L17">
         <v>13</v>
       </c>
@@ -1665,28 +1767,34 @@
         <v>13</v>
       </c>
       <c r="N17">
+        <v>13</v>
+      </c>
+      <c r="O17">
         <v>14</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>15</v>
       </c>
-      <c r="P17">
-        <v>14</v>
-      </c>
       <c r="Q17">
+        <v>15</v>
+      </c>
+      <c r="R17">
+        <v>15</v>
+      </c>
+      <c r="S17">
         <v>16</v>
       </c>
-      <c r="R17" t="s">
+      <c r="T17" t="s">
         <v>12</v>
       </c>
-      <c r="S17" t="s">
-        <v>13</v>
-      </c>
-      <c r="T17" t="s">
+      <c r="U17" t="s">
+        <v>13</v>
+      </c>
+      <c r="V17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1706,19 +1814,19 @@
         <v>0</v>
       </c>
       <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
         <f>SUM(B18:E18)</f>
         <v>0</v>
       </c>
-      <c r="H18">
-        <f>F18</f>
-        <v>0</v>
-      </c>
       <c r="I18">
-        <f>SUM(G18:H18)</f>
+        <f>SUM(F18:G18)</f>
         <v>0</v>
       </c>
       <c r="J18">
-        <v>13</v>
+        <f>SUM(H18:I18)</f>
+        <v>0</v>
       </c>
       <c r="K18">
         <v>13</v>
@@ -1730,28 +1838,34 @@
         <v>13</v>
       </c>
       <c r="N18">
+        <v>13</v>
+      </c>
+      <c r="O18">
         <v>14</v>
       </c>
-      <c r="O18">
-        <v>17</v>
-      </c>
       <c r="P18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q18">
         <v>17</v>
       </c>
-      <c r="R18" t="s">
+      <c r="R18">
+        <v>15</v>
+      </c>
+      <c r="S18">
+        <v>17</v>
+      </c>
+      <c r="T18" t="s">
         <v>16</v>
       </c>
-      <c r="S18" t="s">
-        <v>13</v>
-      </c>
-      <c r="T18" t="s">
+      <c r="U18" t="s">
+        <v>13</v>
+      </c>
+      <c r="V18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -1771,19 +1885,19 @@
         <v>0</v>
       </c>
       <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
         <f>SUM(B19:E19)</f>
         <v>0</v>
       </c>
-      <c r="H19">
-        <f>F19</f>
-        <v>0</v>
-      </c>
       <c r="I19">
-        <f>SUM(G19:H19)</f>
+        <f>SUM(F19:G19)</f>
         <v>0</v>
       </c>
       <c r="J19">
-        <v>13</v>
+        <f>SUM(H19:I19)</f>
+        <v>0</v>
       </c>
       <c r="K19">
         <v>13</v>
@@ -1795,28 +1909,34 @@
         <v>13</v>
       </c>
       <c r="N19">
+        <v>13</v>
+      </c>
+      <c r="O19">
         <v>14</v>
       </c>
-      <c r="O19">
-        <v>17</v>
-      </c>
       <c r="P19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q19">
         <v>17</v>
       </c>
-      <c r="R19" t="s">
+      <c r="R19">
+        <v>15</v>
+      </c>
+      <c r="S19">
+        <v>17</v>
+      </c>
+      <c r="T19" t="s">
         <v>12</v>
       </c>
-      <c r="S19" t="s">
-        <v>13</v>
-      </c>
-      <c r="T19" t="s">
+      <c r="U19" t="s">
+        <v>13</v>
+      </c>
+      <c r="V19" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -1836,19 +1956,19 @@
         <v>0</v>
       </c>
       <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
         <f>SUM(B20:E20)</f>
         <v>0</v>
       </c>
-      <c r="H20">
-        <f>F20</f>
-        <v>0</v>
-      </c>
       <c r="I20">
-        <f>SUM(G20:H20)</f>
+        <f>SUM(F20:G20)</f>
         <v>0</v>
       </c>
       <c r="J20">
-        <v>13</v>
+        <f>SUM(H20:I20)</f>
+        <v>0</v>
       </c>
       <c r="K20">
         <v>13</v>
@@ -1860,28 +1980,34 @@
         <v>13</v>
       </c>
       <c r="N20">
+        <v>13</v>
+      </c>
+      <c r="O20">
         <v>14</v>
       </c>
-      <c r="O20">
-        <v>17</v>
-      </c>
       <c r="P20">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q20">
         <v>17</v>
       </c>
-      <c r="R20" t="s">
+      <c r="R20">
+        <v>15</v>
+      </c>
+      <c r="S20">
+        <v>17</v>
+      </c>
+      <c r="T20" t="s">
         <v>16</v>
       </c>
-      <c r="S20" t="s">
-        <v>13</v>
-      </c>
-      <c r="T20" t="s">
+      <c r="U20" t="s">
+        <v>13</v>
+      </c>
+      <c r="V20" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -1901,19 +2027,19 @@
         <v>0</v>
       </c>
       <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
         <f>SUM(B21:E21)</f>
         <v>0</v>
       </c>
-      <c r="H21">
-        <f>F21</f>
-        <v>0</v>
-      </c>
       <c r="I21">
-        <f>SUM(G21:H21)</f>
+        <f>SUM(F21:G21)</f>
         <v>0</v>
       </c>
       <c r="J21">
-        <v>13</v>
+        <f>SUM(H21:I21)</f>
+        <v>0</v>
       </c>
       <c r="K21">
         <v>13</v>
@@ -1925,28 +2051,34 @@
         <v>13</v>
       </c>
       <c r="N21">
+        <v>13</v>
+      </c>
+      <c r="O21">
         <v>14</v>
       </c>
-      <c r="O21">
-        <v>17</v>
-      </c>
       <c r="P21">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q21">
         <v>17</v>
       </c>
-      <c r="R21" t="s">
+      <c r="R21">
+        <v>15</v>
+      </c>
+      <c r="S21">
+        <v>17</v>
+      </c>
+      <c r="T21" t="s">
         <v>16</v>
       </c>
-      <c r="S21" t="s">
+      <c r="U21" t="s">
         <v>21</v>
       </c>
-      <c r="T21" t="s">
+      <c r="V21" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -1966,19 +2098,19 @@
         <v>0</v>
       </c>
       <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
         <f>SUM(B22:E22)</f>
         <v>0</v>
       </c>
-      <c r="H22">
-        <f>F22</f>
-        <v>0</v>
-      </c>
       <c r="I22">
-        <f>SUM(G22:H22)</f>
+        <f>SUM(F22:G22)</f>
         <v>0</v>
       </c>
       <c r="J22">
-        <v>13</v>
+        <f>SUM(H22:I22)</f>
+        <v>0</v>
       </c>
       <c r="K22">
         <v>13</v>
@@ -1990,31 +2122,41 @@
         <v>13</v>
       </c>
       <c r="N22">
+        <v>13</v>
+      </c>
+      <c r="O22">
         <v>14</v>
       </c>
-      <c r="O22">
-        <v>17</v>
-      </c>
       <c r="P22">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q22">
         <v>17</v>
       </c>
-      <c r="R22" t="s">
+      <c r="R22">
+        <v>15</v>
+      </c>
+      <c r="S22">
+        <v>17</v>
+      </c>
+      <c r="T22" t="s">
         <v>12</v>
       </c>
-      <c r="S22" t="s">
+      <c r="U22" t="s">
         <v>21</v>
       </c>
-      <c r="T22" t="s">
+      <c r="V22" t="s">
         <v>32</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T22" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T22">
-    <sortCondition descending="1" ref="I1:I22"/>
+  <autoFilter ref="A1:V22" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V22">
+      <sortCondition descending="1" ref="J1:J22"/>
+    </sortState>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V22">
+    <sortCondition descending="1" ref="J1:J22"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36AC1859-2DCB-4730-8FFD-EC2423F4A2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DCD75B-F497-4CFA-B3C8-487283FFD892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6DC662A2-343A-4284-B4F3-E8BBCF4A3089}"/>
   </bookViews>
@@ -678,7 +678,7 @@
         <v>557</v>
       </c>
       <c r="G2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="H2">
         <f>SUM(B2:E2)</f>
@@ -686,11 +686,11 @@
       </c>
       <c r="I2">
         <f>SUM(F2:G2)</f>
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="J2">
         <f>SUM(H2:I2)</f>
-        <v>3718</v>
+        <v>3720</v>
       </c>
       <c r="K2">
         <v>2</v>
@@ -749,7 +749,7 @@
         <v>456</v>
       </c>
       <c r="G3">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H3">
         <f>SUM(B3:E3)</f>
@@ -757,11 +757,11 @@
       </c>
       <c r="I3">
         <f>SUM(F3:G3)</f>
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="J3">
         <f>SUM(H3:I3)</f>
-        <v>3651</v>
+        <v>3652</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -820,7 +820,7 @@
         <v>438</v>
       </c>
       <c r="G4">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="H4">
         <f>SUM(B4:E4)</f>
@@ -828,11 +828,11 @@
       </c>
       <c r="I4">
         <f>SUM(F4:G4)</f>
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="J4">
         <f>SUM(H4:I4)</f>
-        <v>2873</v>
+        <v>2882</v>
       </c>
       <c r="K4">
         <v>4</v>
@@ -962,7 +962,7 @@
         <v>301</v>
       </c>
       <c r="G6">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H6">
         <f>SUM(B6:E6)</f>
@@ -970,11 +970,11 @@
       </c>
       <c r="I6">
         <f>SUM(F6:G6)</f>
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="J6">
         <f>SUM(H6:I6)</f>
-        <v>2761</v>
+        <v>2763</v>
       </c>
       <c r="K6">
         <v>3</v>
@@ -1033,7 +1033,7 @@
         <v>648</v>
       </c>
       <c r="G7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H7">
         <f>SUM(B7:E7)</f>
@@ -1041,11 +1041,11 @@
       </c>
       <c r="I7">
         <f>SUM(F7:G7)</f>
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="J7">
         <f>SUM(H7:I7)</f>
-        <v>2600</v>
+        <v>2602</v>
       </c>
       <c r="K7">
         <v>6</v>
@@ -1104,7 +1104,7 @@
         <v>70</v>
       </c>
       <c r="G8">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H8">
         <f>SUM(B8:E8)</f>
@@ -1112,11 +1112,11 @@
       </c>
       <c r="I8">
         <f>SUM(F8:G8)</f>
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J8">
         <f>SUM(H8:I8)</f>
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="K8">
         <v>7</v>
@@ -1134,7 +1134,7 @@
         <v>13</v>
       </c>
       <c r="P8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q8">
         <v>7</v>
@@ -1175,7 +1175,7 @@
         <v>177</v>
       </c>
       <c r="G9">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H9">
         <f>SUM(B9:E9)</f>
@@ -1183,11 +1183,11 @@
       </c>
       <c r="I9">
         <f>SUM(F9:G9)</f>
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J9">
         <f>SUM(H9:I9)</f>
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="K9">
         <v>13</v>
@@ -1246,7 +1246,7 @@
         <v>282</v>
       </c>
       <c r="G10">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H10">
         <f>SUM(B10:E10)</f>
@@ -1254,11 +1254,11 @@
       </c>
       <c r="I10">
         <f>SUM(F10:G10)</f>
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="J10">
         <f>SUM(H10:I10)</f>
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="K10">
         <v>9</v>
@@ -1317,7 +1317,7 @@
         <v>285</v>
       </c>
       <c r="G11">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H11">
         <f>SUM(B11:E11)</f>
@@ -1325,11 +1325,11 @@
       </c>
       <c r="I11">
         <f>SUM(F11:G11)</f>
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J11">
         <f>SUM(H11:I11)</f>
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="K11">
         <v>10</v>
@@ -1388,7 +1388,7 @@
         <v>252</v>
       </c>
       <c r="G12">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H12">
         <f>SUM(B12:E12)</f>
@@ -1396,11 +1396,11 @@
       </c>
       <c r="I12">
         <f>SUM(F12:G12)</f>
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="J12">
         <f>SUM(H12:I12)</f>
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="K12">
         <v>8</v>
@@ -1459,7 +1459,7 @@
         <v>141</v>
       </c>
       <c r="G13">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H13">
         <f>SUM(B13:E13)</f>
@@ -1467,11 +1467,11 @@
       </c>
       <c r="I13">
         <f>SUM(F13:G13)</f>
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J13">
         <f>SUM(H13:I13)</f>
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K13">
         <v>13</v>
@@ -1530,7 +1530,7 @@
         <v>139</v>
       </c>
       <c r="G14">
-        <v>204</v>
+        <v>280</v>
       </c>
       <c r="H14">
         <f>SUM(B14:E14)</f>
@@ -1538,11 +1538,11 @@
       </c>
       <c r="I14">
         <f>SUM(F14:G14)</f>
-        <v>343</v>
+        <v>419</v>
       </c>
       <c r="J14">
         <f>SUM(H14:I14)</f>
-        <v>371</v>
+        <v>447</v>
       </c>
       <c r="K14">
         <v>12</v>
@@ -1560,7 +1560,7 @@
         <v>12</v>
       </c>
       <c r="P14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q14">
         <v>16</v>
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H15">
         <f>SUM(B15:E15)</f>
@@ -1609,11 +1609,11 @@
       </c>
       <c r="I15">
         <f>SUM(F15:G15)</f>
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J15">
         <f>SUM(H15:I15)</f>
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K15">
         <v>13</v>
@@ -1631,7 +1631,7 @@
         <v>14</v>
       </c>
       <c r="P15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <v>14</v>
@@ -2152,11 +2152,11 @@
   </sheetData>
   <autoFilter ref="A1:V22" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V22">
-      <sortCondition descending="1" ref="J1:J22"/>
+      <sortCondition descending="1" ref="I1:I22"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V22">
-    <sortCondition descending="1" ref="J1:J22"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V23">
+    <sortCondition descending="1" ref="J1:J23"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DCD75B-F497-4CFA-B3C8-487283FFD892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F137C3-C139-4E93-A1AA-DE6255C9CBAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6DC662A2-343A-4284-B4F3-E8BBCF4A3089}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="2" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2'!$A$1:$V$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2'!$A$1:$X$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="56">
   <si>
     <t>Nombre</t>
   </si>
@@ -201,6 +201,12 @@
   </si>
   <si>
     <t>Ranking 6</t>
+  </si>
+  <si>
+    <t>Semana 7</t>
+  </si>
+  <si>
+    <t>Ranking 7</t>
   </si>
 </sst>
 </file>
@@ -572,25 +578,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0244A2-6A9A-442F-B635-0C9297E0559B}">
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:X22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.1796875" customWidth="1"/>
-    <col min="10" max="10" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="8.54296875" customWidth="1"/>
-    <col min="17" max="17" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.90625" customWidth="1"/>
-    <col min="19" max="19" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.1796875" customWidth="1"/>
+    <col min="11" max="11" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="8.54296875" customWidth="1"/>
+    <col min="19" max="19" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.90625" customWidth="1"/>
+    <col min="21" max="21" width="13.6328125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -613,105 +619,111 @@
         <v>52</v>
       </c>
       <c r="H1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>49</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>4</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>6</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>45</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>47</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>50</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>53</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
+        <v>55</v>
+      </c>
+      <c r="S1" t="s">
         <v>7</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>51</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>8</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>9</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>10</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C2">
-        <v>528</v>
+        <v>602</v>
       </c>
       <c r="D2">
-        <v>657</v>
+        <v>689</v>
       </c>
       <c r="E2">
-        <v>618</v>
+        <v>755</v>
       </c>
       <c r="F2">
-        <v>557</v>
+        <v>456</v>
       </c>
       <c r="G2">
-        <v>667</v>
+        <v>455</v>
       </c>
       <c r="H2">
+        <v>696</v>
+      </c>
+      <c r="I2">
         <f>SUM(B2:E2)</f>
-        <v>2496</v>
-      </c>
-      <c r="I2">
-        <f>SUM(F2:G2)</f>
-        <v>1224</v>
+        <v>2741</v>
       </c>
       <c r="J2">
-        <f>SUM(H2:I2)</f>
-        <v>3720</v>
+        <f>SUM(F2:H2)</f>
+        <v>1607</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <f>SUM(I2:J2)</f>
+        <v>4348</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -719,67 +731,73 @@
       <c r="S2">
         <v>1</v>
       </c>
-      <c r="T2" t="s">
-        <v>16</v>
-      </c>
-      <c r="U2" t="s">
-        <v>17</v>
+      <c r="T2">
+        <v>2</v>
+      </c>
+      <c r="U2">
+        <v>1</v>
       </c>
       <c r="V2" t="s">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="W2" t="s">
+        <v>13</v>
+      </c>
+      <c r="X2" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B3">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C3">
-        <v>602</v>
+        <v>528</v>
       </c>
       <c r="D3">
-        <v>689</v>
+        <v>657</v>
       </c>
       <c r="E3">
-        <v>755</v>
+        <v>618</v>
       </c>
       <c r="F3">
-        <v>456</v>
+        <v>557</v>
       </c>
       <c r="G3">
-        <v>455</v>
+        <v>667</v>
       </c>
       <c r="H3">
+        <v>515</v>
+      </c>
+      <c r="I3">
         <f>SUM(B3:E3)</f>
-        <v>2741</v>
-      </c>
-      <c r="I3">
-        <f>SUM(F3:G3)</f>
-        <v>911</v>
+        <v>2496</v>
       </c>
       <c r="J3">
-        <f>SUM(H3:I3)</f>
-        <v>3652</v>
+        <f>SUM(F3:H3)</f>
+        <v>1739</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <f>SUM(I3:J3)</f>
+        <v>4235</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q3">
         <v>1</v>
@@ -790,17 +808,23 @@
       <c r="S3">
         <v>2</v>
       </c>
-      <c r="T3" t="s">
-        <v>12</v>
-      </c>
-      <c r="U3" t="s">
-        <v>13</v>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
+        <v>2</v>
       </c>
       <c r="V3" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="W3" t="s">
+        <v>17</v>
+      </c>
+      <c r="X3" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -823,55 +847,61 @@
         <v>189</v>
       </c>
       <c r="H4">
+        <v>553</v>
+      </c>
+      <c r="I4">
         <f>SUM(B4:E4)</f>
         <v>2255</v>
       </c>
-      <c r="I4">
-        <f>SUM(F4:G4)</f>
-        <v>627</v>
-      </c>
       <c r="J4">
-        <f>SUM(H4:I4)</f>
-        <v>2882</v>
+        <f>SUM(F4:H4)</f>
+        <v>1180</v>
       </c>
       <c r="K4">
+        <f>SUM(I4:J4)</f>
+        <v>3435</v>
+      </c>
+      <c r="L4">
         <v>4</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>2</v>
-      </c>
-      <c r="M4">
-        <v>3</v>
       </c>
       <c r="N4">
         <v>3</v>
       </c>
       <c r="O4">
+        <v>3</v>
+      </c>
+      <c r="P4">
         <v>5</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>12</v>
       </c>
-      <c r="Q4">
-        <v>3</v>
-      </c>
       <c r="R4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S4">
         <v>3</v>
       </c>
-      <c r="T4" t="s">
+      <c r="T4">
+        <v>6</v>
+      </c>
+      <c r="U4">
+        <v>3</v>
+      </c>
+      <c r="V4" t="s">
         <v>16</v>
       </c>
-      <c r="U4" t="s">
-        <v>13</v>
-      </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -894,55 +924,61 @@
         <v>491</v>
       </c>
       <c r="H5">
+        <v>456</v>
+      </c>
+      <c r="I5">
         <f>SUM(B5:E5)</f>
         <v>1876</v>
       </c>
-      <c r="I5">
-        <f>SUM(F5:G5)</f>
-        <v>972</v>
-      </c>
       <c r="J5">
-        <f>SUM(H5:I5)</f>
-        <v>2848</v>
+        <f>SUM(F5:H5)</f>
+        <v>1428</v>
       </c>
       <c r="K5">
+        <f>SUM(I5:J5)</f>
+        <v>3304</v>
+      </c>
+      <c r="L5">
         <v>5</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>1</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>5</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>4</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>3</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>2</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>5</v>
       </c>
-      <c r="R5">
-        <v>3</v>
-      </c>
       <c r="S5">
+        <v>5</v>
+      </c>
+      <c r="T5">
         <v>4</v>
       </c>
-      <c r="T5" t="s">
+      <c r="U5">
+        <v>4</v>
+      </c>
+      <c r="V5" t="s">
         <v>12</v>
       </c>
-      <c r="U5" t="s">
+      <c r="W5" t="s">
         <v>21</v>
       </c>
-      <c r="V5" t="s">
+      <c r="X5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -965,55 +1001,61 @@
         <v>445</v>
       </c>
       <c r="H6">
+        <v>534</v>
+      </c>
+      <c r="I6">
         <f>SUM(B6:E6)</f>
         <v>2017</v>
       </c>
-      <c r="I6">
-        <f>SUM(F6:G6)</f>
-        <v>746</v>
-      </c>
       <c r="J6">
-        <f>SUM(H6:I6)</f>
-        <v>2763</v>
+        <f>SUM(F6:H6)</f>
+        <v>1280</v>
       </c>
       <c r="K6">
+        <f>SUM(I6:J6)</f>
+        <v>3297</v>
+      </c>
+      <c r="L6">
         <v>3</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>5</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>4</v>
-      </c>
-      <c r="N6">
-        <v>6</v>
       </c>
       <c r="O6">
         <v>6</v>
       </c>
       <c r="P6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>4</v>
       </c>
       <c r="R6">
+        <v>3</v>
+      </c>
+      <c r="S6">
+        <v>4</v>
+      </c>
+      <c r="T6">
         <v>5</v>
       </c>
-      <c r="S6">
+      <c r="U6">
         <v>5</v>
       </c>
-      <c r="T6" t="s">
+      <c r="V6" t="s">
         <v>12</v>
       </c>
-      <c r="U6" t="s">
-        <v>13</v>
-      </c>
-      <c r="V6" t="s">
+      <c r="W6" t="s">
+        <v>13</v>
+      </c>
+      <c r="X6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -1036,55 +1078,61 @@
         <v>354</v>
       </c>
       <c r="H7">
+        <v>455</v>
+      </c>
+      <c r="I7">
         <f>SUM(B7:E7)</f>
         <v>1600</v>
       </c>
-      <c r="I7">
-        <f>SUM(F7:G7)</f>
-        <v>1002</v>
-      </c>
       <c r="J7">
-        <f>SUM(H7:I7)</f>
-        <v>2602</v>
+        <f>SUM(F7:H7)</f>
+        <v>1457</v>
       </c>
       <c r="K7">
+        <f>SUM(I7:J7)</f>
+        <v>3057</v>
+      </c>
+      <c r="L7">
         <v>6</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>4</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>6</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>7</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>1</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>5</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>6</v>
-      </c>
-      <c r="R7">
-        <v>2</v>
       </c>
       <c r="S7">
         <v>6</v>
       </c>
-      <c r="T7" t="s">
+      <c r="T7">
+        <v>3</v>
+      </c>
+      <c r="U7">
+        <v>6</v>
+      </c>
+      <c r="V7" t="s">
         <v>16</v>
       </c>
-      <c r="U7" t="s">
+      <c r="W7" t="s">
         <v>21</v>
       </c>
-      <c r="V7" t="s">
+      <c r="X7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1107,55 +1155,61 @@
         <v>225</v>
       </c>
       <c r="H8">
+        <v>287</v>
+      </c>
+      <c r="I8">
         <f>SUM(B8:E8)</f>
         <v>1010</v>
       </c>
-      <c r="I8">
-        <f>SUM(F8:G8)</f>
-        <v>295</v>
-      </c>
       <c r="J8">
-        <f>SUM(H8:I8)</f>
-        <v>1305</v>
+        <f>SUM(F8:H8)</f>
+        <v>582</v>
       </c>
       <c r="K8">
+        <f>SUM(I8:J8)</f>
+        <v>1592</v>
+      </c>
+      <c r="L8">
         <v>7</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>8</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>7</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>8</v>
       </c>
-      <c r="O8">
-        <v>13</v>
-      </c>
       <c r="P8">
+        <v>13</v>
+      </c>
+      <c r="Q8">
         <v>9</v>
       </c>
-      <c r="Q8">
-        <v>7</v>
-      </c>
       <c r="R8">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="S8">
         <v>7</v>
       </c>
-      <c r="T8" t="s">
+      <c r="T8">
+        <v>10</v>
+      </c>
+      <c r="U8">
+        <v>7</v>
+      </c>
+      <c r="V8" t="s">
         <v>12</v>
       </c>
-      <c r="U8" t="s">
-        <v>13</v>
-      </c>
-      <c r="V8" t="s">
+      <c r="W8" t="s">
+        <v>13</v>
+      </c>
+      <c r="X8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1178,108 +1232,114 @@
         <v>306</v>
       </c>
       <c r="H9">
+        <v>297</v>
+      </c>
+      <c r="I9">
         <f>SUM(B9:E9)</f>
         <v>798</v>
       </c>
-      <c r="I9">
-        <f>SUM(F9:G9)</f>
-        <v>483</v>
-      </c>
       <c r="J9">
-        <f>SUM(H9:I9)</f>
-        <v>1281</v>
+        <f>SUM(F9:H9)</f>
+        <v>780</v>
       </c>
       <c r="K9">
-        <v>13</v>
+        <f>SUM(I9:J9)</f>
+        <v>1578</v>
       </c>
       <c r="L9">
+        <v>13</v>
+      </c>
+      <c r="M9">
         <v>7</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>8</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>5</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>10</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>6</v>
       </c>
-      <c r="Q9">
-        <v>8</v>
-      </c>
       <c r="R9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S9">
         <v>8</v>
       </c>
-      <c r="T9" t="s">
+      <c r="T9">
+        <v>7</v>
+      </c>
+      <c r="U9">
+        <v>8</v>
+      </c>
+      <c r="V9" t="s">
         <v>16</v>
       </c>
-      <c r="U9" t="s">
-        <v>13</v>
-      </c>
-      <c r="V9" t="s">
+      <c r="W9" t="s">
+        <v>13</v>
+      </c>
+      <c r="X9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="C10">
-        <v>218</v>
+        <v>111</v>
       </c>
       <c r="D10">
-        <v>161</v>
+        <v>111</v>
       </c>
       <c r="E10">
-        <v>62</v>
+        <v>207</v>
       </c>
       <c r="F10">
-        <v>282</v>
+        <v>252</v>
       </c>
       <c r="G10">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="H10">
+        <v>256</v>
+      </c>
+      <c r="I10">
         <f>SUM(B10:E10)</f>
-        <v>503</v>
-      </c>
-      <c r="I10">
-        <f>SUM(F10:G10)</f>
-        <v>480</v>
+        <v>529</v>
       </c>
       <c r="J10">
-        <f>SUM(H10:I10)</f>
-        <v>983</v>
+        <f>SUM(F10:H10)</f>
+        <v>687</v>
       </c>
       <c r="K10">
+        <f>SUM(I10:J10)</f>
+        <v>1216</v>
+      </c>
+      <c r="L10">
+        <v>8</v>
+      </c>
+      <c r="M10">
+        <v>11</v>
+      </c>
+      <c r="N10">
+        <v>12</v>
+      </c>
+      <c r="O10">
         <v>9</v>
       </c>
-      <c r="L10">
-        <v>10</v>
-      </c>
-      <c r="M10">
+      <c r="P10">
         <v>9</v>
       </c>
-      <c r="N10">
-        <v>11</v>
-      </c>
-      <c r="O10">
-        <v>8</v>
-      </c>
-      <c r="P10">
-        <v>11</v>
-      </c>
       <c r="Q10">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R10">
         <v>9</v>
@@ -1287,52 +1347,58 @@
       <c r="S10">
         <v>9</v>
       </c>
-      <c r="T10" t="s">
+      <c r="T10">
+        <v>8</v>
+      </c>
+      <c r="U10">
+        <v>9</v>
+      </c>
+      <c r="V10" t="s">
         <v>16</v>
       </c>
-      <c r="U10" t="s">
-        <v>13</v>
-      </c>
-      <c r="V10" t="s">
+      <c r="W10" t="s">
+        <v>13</v>
+      </c>
+      <c r="X10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B11">
         <v>62</v>
       </c>
       <c r="C11">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D11">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="E11">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F11">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G11">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <f>SUM(B11:E11)</f>
-        <v>496</v>
-      </c>
-      <c r="I11">
-        <f>SUM(F11:G11)</f>
-        <v>484</v>
+        <v>503</v>
       </c>
       <c r="J11">
-        <f>SUM(H11:I11)</f>
-        <v>980</v>
+        <f>SUM(F11:H11)</f>
+        <v>480</v>
       </c>
       <c r="K11">
-        <v>10</v>
+        <f>SUM(I11:J11)</f>
+        <v>983</v>
       </c>
       <c r="L11">
         <v>9</v>
@@ -1341,247 +1407,271 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q11">
         <v>11</v>
       </c>
       <c r="R11">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="S11">
         <v>10</v>
       </c>
-      <c r="T11" t="s">
+      <c r="T11">
         <v>12</v>
       </c>
-      <c r="U11" t="s">
-        <v>13</v>
+      <c r="U11">
+        <v>10</v>
       </c>
       <c r="V11" t="s">
+        <v>16</v>
+      </c>
+      <c r="W11" t="s">
+        <v>13</v>
+      </c>
+      <c r="X11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="B12">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="C12">
-        <v>111</v>
+        <v>222</v>
       </c>
       <c r="D12">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="E12">
-        <v>207</v>
+        <v>64</v>
       </c>
       <c r="F12">
-        <v>252</v>
+        <v>285</v>
       </c>
       <c r="G12">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
         <f>SUM(B12:E12)</f>
-        <v>529</v>
-      </c>
-      <c r="I12">
-        <f>SUM(F12:G12)</f>
-        <v>431</v>
+        <v>496</v>
       </c>
       <c r="J12">
-        <f>SUM(H12:I12)</f>
-        <v>960</v>
+        <f>SUM(F12:H12)</f>
+        <v>484</v>
       </c>
       <c r="K12">
-        <v>8</v>
+        <f>SUM(I12:J12)</f>
+        <v>980</v>
       </c>
       <c r="L12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="N12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="S12">
         <v>11</v>
       </c>
-      <c r="T12" t="s">
+      <c r="T12">
+        <v>11</v>
+      </c>
+      <c r="U12">
+        <v>11</v>
+      </c>
+      <c r="V12" t="s">
+        <v>12</v>
+      </c>
+      <c r="W12" t="s">
+        <v>13</v>
+      </c>
+      <c r="X12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13">
+        <v>28</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>139</v>
+      </c>
+      <c r="G13">
+        <v>280</v>
+      </c>
+      <c r="H13">
+        <v>231</v>
+      </c>
+      <c r="I13">
+        <f>SUM(B13:E13)</f>
+        <v>28</v>
+      </c>
+      <c r="J13">
+        <f>SUM(F13:H13)</f>
+        <v>650</v>
+      </c>
+      <c r="K13">
+        <f>SUM(I13:J13)</f>
+        <v>678</v>
+      </c>
+      <c r="L13">
+        <v>12</v>
+      </c>
+      <c r="M13">
+        <v>13</v>
+      </c>
+      <c r="N13">
+        <v>13</v>
+      </c>
+      <c r="O13">
+        <v>13</v>
+      </c>
+      <c r="P13">
+        <v>12</v>
+      </c>
+      <c r="Q13">
+        <v>7</v>
+      </c>
+      <c r="R13">
+        <v>10</v>
+      </c>
+      <c r="S13">
         <v>16</v>
       </c>
-      <c r="U12" t="s">
-        <v>13</v>
-      </c>
-      <c r="V12" t="s">
+      <c r="T13">
+        <v>9</v>
+      </c>
+      <c r="U13">
+        <v>12</v>
+      </c>
+      <c r="V13" t="s">
+        <v>16</v>
+      </c>
+      <c r="W13" t="s">
+        <v>21</v>
+      </c>
+      <c r="X13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>39</v>
       </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
         <v>122</v>
       </c>
-      <c r="E13">
+      <c r="E14">
         <v>23</v>
       </c>
-      <c r="F13">
+      <c r="F14">
         <v>141</v>
       </c>
-      <c r="G13">
+      <c r="G14">
         <v>168</v>
       </c>
-      <c r="H13">
-        <f>SUM(B13:E13)</f>
+      <c r="H14">
+        <v>139</v>
+      </c>
+      <c r="I14">
+        <f>SUM(B14:E14)</f>
         <v>145</v>
       </c>
-      <c r="I13">
-        <f>SUM(F13:G13)</f>
-        <v>309</v>
-      </c>
-      <c r="J13">
-        <f>SUM(H13:I13)</f>
-        <v>454</v>
-      </c>
-      <c r="K13">
-        <v>13</v>
-      </c>
-      <c r="L13">
-        <v>13</v>
-      </c>
-      <c r="M13">
+      <c r="J14">
+        <f>SUM(F14:H14)</f>
+        <v>448</v>
+      </c>
+      <c r="K14">
+        <f>SUM(I14:J14)</f>
+        <v>593</v>
+      </c>
+      <c r="L14">
+        <v>13</v>
+      </c>
+      <c r="M14">
+        <v>13</v>
+      </c>
+      <c r="N14">
         <v>11</v>
       </c>
-      <c r="N13">
-        <v>13</v>
-      </c>
-      <c r="O13">
+      <c r="O14">
+        <v>13</v>
+      </c>
+      <c r="P14">
         <v>11</v>
       </c>
-      <c r="P13">
+      <c r="Q14">
         <v>14</v>
-      </c>
-      <c r="Q13">
-        <v>12</v>
-      </c>
-      <c r="R13">
-        <v>12</v>
-      </c>
-      <c r="S13">
-        <v>12</v>
-      </c>
-      <c r="T13" t="s">
-        <v>12</v>
-      </c>
-      <c r="U13" t="s">
-        <v>17</v>
-      </c>
-      <c r="V13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14">
-        <v>28</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>139</v>
-      </c>
-      <c r="G14">
-        <v>280</v>
-      </c>
-      <c r="H14">
-        <f>SUM(B14:E14)</f>
-        <v>28</v>
-      </c>
-      <c r="I14">
-        <f>SUM(F14:G14)</f>
-        <v>419</v>
-      </c>
-      <c r="J14">
-        <f>SUM(H14:I14)</f>
-        <v>447</v>
-      </c>
-      <c r="K14">
-        <v>12</v>
-      </c>
-      <c r="L14">
-        <v>13</v>
-      </c>
-      <c r="M14">
-        <v>13</v>
-      </c>
-      <c r="N14">
-        <v>13</v>
-      </c>
-      <c r="O14">
-        <v>12</v>
-      </c>
-      <c r="P14">
-        <v>7</v>
-      </c>
-      <c r="Q14">
-        <v>16</v>
       </c>
       <c r="R14">
         <v>11</v>
       </c>
       <c r="S14">
-        <v>13</v>
-      </c>
-      <c r="T14" t="s">
-        <v>16</v>
-      </c>
-      <c r="U14" t="s">
-        <v>21</v>
+        <v>12</v>
+      </c>
+      <c r="T14">
+        <v>13</v>
+      </c>
+      <c r="U14">
+        <v>13</v>
       </c>
       <c r="V14" t="s">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="W14" t="s">
+        <v>17</v>
+      </c>
+      <c r="X14" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1604,19 +1694,19 @@
         <v>254</v>
       </c>
       <c r="H15">
+        <v>62</v>
+      </c>
+      <c r="I15">
         <f>SUM(B15:E15)</f>
         <v>59</v>
       </c>
-      <c r="I15">
-        <f>SUM(F15:G15)</f>
-        <v>254</v>
-      </c>
       <c r="J15">
-        <f>SUM(H15:I15)</f>
-        <v>313</v>
+        <f>SUM(F15:H15)</f>
+        <v>316</v>
       </c>
       <c r="K15">
-        <v>13</v>
+        <f>SUM(I15:J15)</f>
+        <v>375</v>
       </c>
       <c r="L15">
         <v>13</v>
@@ -1625,34 +1715,40 @@
         <v>13</v>
       </c>
       <c r="N15">
+        <v>13</v>
+      </c>
+      <c r="O15">
         <v>12</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>14</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>8</v>
       </c>
-      <c r="Q15">
-        <v>14</v>
-      </c>
       <c r="R15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="S15">
         <v>14</v>
       </c>
-      <c r="T15" t="s">
+      <c r="T15">
+        <v>14</v>
+      </c>
+      <c r="U15">
+        <v>14</v>
+      </c>
+      <c r="V15" t="s">
         <v>12</v>
       </c>
-      <c r="U15" t="s">
-        <v>13</v>
-      </c>
-      <c r="V15" t="s">
+      <c r="W15" t="s">
+        <v>13</v>
+      </c>
+      <c r="X15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -1675,55 +1771,61 @@
         <v>0</v>
       </c>
       <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
         <f>SUM(B16:E16)</f>
         <v>84</v>
       </c>
-      <c r="I16">
-        <f>SUM(F16:G16)</f>
-        <v>0</v>
-      </c>
       <c r="J16">
-        <f>SUM(H16:I16)</f>
+        <f>SUM(F16:H16)</f>
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <f>SUM(I16:J16)</f>
         <v>84</v>
       </c>
-      <c r="K16">
-        <v>13</v>
-      </c>
       <c r="L16">
+        <v>13</v>
+      </c>
+      <c r="M16">
         <v>12</v>
       </c>
-      <c r="M16">
-        <v>13</v>
-      </c>
       <c r="N16">
         <v>13</v>
       </c>
       <c r="O16">
+        <v>13</v>
+      </c>
+      <c r="P16">
         <v>14</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>15</v>
       </c>
-      <c r="Q16">
-        <v>13</v>
-      </c>
       <c r="R16">
+        <v>13</v>
+      </c>
+      <c r="S16">
+        <v>13</v>
+      </c>
+      <c r="T16">
         <v>15</v>
       </c>
-      <c r="S16">
+      <c r="U16">
         <v>15</v>
       </c>
-      <c r="T16" t="s">
+      <c r="V16" t="s">
         <v>12</v>
       </c>
-      <c r="U16" t="s">
+      <c r="W16" t="s">
         <v>21</v>
       </c>
-      <c r="V16" t="s">
+      <c r="X16" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -1746,23 +1848,23 @@
         <v>0</v>
       </c>
       <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
         <f>SUM(B17:E17)</f>
         <v>39</v>
       </c>
-      <c r="I17">
-        <f>SUM(F17:G17)</f>
-        <v>0</v>
-      </c>
       <c r="J17">
-        <f>SUM(H17:I17)</f>
+        <f>SUM(F17:H17)</f>
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <f>SUM(I17:J17)</f>
         <v>39</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>11</v>
       </c>
-      <c r="L17">
-        <v>13</v>
-      </c>
       <c r="M17">
         <v>13</v>
       </c>
@@ -1770,31 +1872,37 @@
         <v>13</v>
       </c>
       <c r="O17">
+        <v>13</v>
+      </c>
+      <c r="P17">
         <v>14</v>
-      </c>
-      <c r="P17">
-        <v>15</v>
       </c>
       <c r="Q17">
         <v>15</v>
       </c>
       <c r="R17">
+        <v>13</v>
+      </c>
+      <c r="S17">
         <v>15</v>
       </c>
-      <c r="S17">
+      <c r="T17">
         <v>16</v>
       </c>
-      <c r="T17" t="s">
+      <c r="U17">
+        <v>16</v>
+      </c>
+      <c r="V17" t="s">
         <v>12</v>
       </c>
-      <c r="U17" t="s">
-        <v>13</v>
-      </c>
-      <c r="V17" t="s">
+      <c r="W17" t="s">
+        <v>13</v>
+      </c>
+      <c r="X17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1817,19 +1925,19 @@
         <v>0</v>
       </c>
       <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
         <f>SUM(B18:E18)</f>
         <v>0</v>
       </c>
-      <c r="I18">
-        <f>SUM(F18:G18)</f>
-        <v>0</v>
-      </c>
       <c r="J18">
-        <f>SUM(H18:I18)</f>
+        <f>SUM(F18:H18)</f>
         <v>0</v>
       </c>
       <c r="K18">
-        <v>13</v>
+        <f>SUM(I18:J18)</f>
+        <v>0</v>
       </c>
       <c r="L18">
         <v>13</v>
@@ -1841,31 +1949,37 @@
         <v>13</v>
       </c>
       <c r="O18">
+        <v>13</v>
+      </c>
+      <c r="P18">
         <v>14</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>15</v>
       </c>
-      <c r="Q18">
-        <v>17</v>
-      </c>
       <c r="R18">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="S18">
         <v>17</v>
       </c>
-      <c r="T18" t="s">
+      <c r="T18">
         <v>16</v>
       </c>
-      <c r="U18" t="s">
-        <v>13</v>
+      <c r="U18">
+        <v>17</v>
       </c>
       <c r="V18" t="s">
+        <v>16</v>
+      </c>
+      <c r="W18" t="s">
+        <v>13</v>
+      </c>
+      <c r="X18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>41</v>
       </c>
@@ -1888,19 +2002,19 @@
         <v>0</v>
       </c>
       <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
         <f>SUM(B19:E19)</f>
         <v>0</v>
       </c>
-      <c r="I19">
-        <f>SUM(F19:G19)</f>
-        <v>0</v>
-      </c>
       <c r="J19">
-        <f>SUM(H19:I19)</f>
+        <f>SUM(F19:H19)</f>
         <v>0</v>
       </c>
       <c r="K19">
-        <v>13</v>
+        <f>SUM(I19:J19)</f>
+        <v>0</v>
       </c>
       <c r="L19">
         <v>13</v>
@@ -1912,31 +2026,37 @@
         <v>13</v>
       </c>
       <c r="O19">
+        <v>13</v>
+      </c>
+      <c r="P19">
         <v>14</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>15</v>
       </c>
-      <c r="Q19">
-        <v>17</v>
-      </c>
       <c r="R19">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="S19">
         <v>17</v>
       </c>
-      <c r="T19" t="s">
+      <c r="T19">
+        <v>16</v>
+      </c>
+      <c r="U19">
+        <v>17</v>
+      </c>
+      <c r="V19" t="s">
         <v>12</v>
       </c>
-      <c r="U19" t="s">
-        <v>13</v>
-      </c>
-      <c r="V19" t="s">
+      <c r="W19" t="s">
+        <v>13</v>
+      </c>
+      <c r="X19" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -1959,19 +2079,19 @@
         <v>0</v>
       </c>
       <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
         <f>SUM(B20:E20)</f>
         <v>0</v>
       </c>
-      <c r="I20">
-        <f>SUM(F20:G20)</f>
-        <v>0</v>
-      </c>
       <c r="J20">
-        <f>SUM(H20:I20)</f>
+        <f>SUM(F20:H20)</f>
         <v>0</v>
       </c>
       <c r="K20">
-        <v>13</v>
+        <f>SUM(I20:J20)</f>
+        <v>0</v>
       </c>
       <c r="L20">
         <v>13</v>
@@ -1983,31 +2103,37 @@
         <v>13</v>
       </c>
       <c r="O20">
+        <v>13</v>
+      </c>
+      <c r="P20">
         <v>14</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>15</v>
       </c>
-      <c r="Q20">
-        <v>17</v>
-      </c>
       <c r="R20">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="S20">
         <v>17</v>
       </c>
-      <c r="T20" t="s">
+      <c r="T20">
         <v>16</v>
       </c>
-      <c r="U20" t="s">
-        <v>13</v>
+      <c r="U20">
+        <v>17</v>
       </c>
       <c r="V20" t="s">
+        <v>16</v>
+      </c>
+      <c r="W20" t="s">
+        <v>13</v>
+      </c>
+      <c r="X20" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -2030,19 +2156,19 @@
         <v>0</v>
       </c>
       <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
         <f>SUM(B21:E21)</f>
         <v>0</v>
       </c>
-      <c r="I21">
-        <f>SUM(F21:G21)</f>
-        <v>0</v>
-      </c>
       <c r="J21">
-        <f>SUM(H21:I21)</f>
+        <f>SUM(F21:H21)</f>
         <v>0</v>
       </c>
       <c r="K21">
-        <v>13</v>
+        <f>SUM(I21:J21)</f>
+        <v>0</v>
       </c>
       <c r="L21">
         <v>13</v>
@@ -2054,31 +2180,37 @@
         <v>13</v>
       </c>
       <c r="O21">
+        <v>13</v>
+      </c>
+      <c r="P21">
         <v>14</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>15</v>
       </c>
-      <c r="Q21">
-        <v>17</v>
-      </c>
       <c r="R21">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="S21">
         <v>17</v>
       </c>
-      <c r="T21" t="s">
+      <c r="T21">
         <v>16</v>
       </c>
-      <c r="U21" t="s">
+      <c r="U21">
+        <v>17</v>
+      </c>
+      <c r="V21" t="s">
+        <v>16</v>
+      </c>
+      <c r="W21" t="s">
         <v>21</v>
       </c>
-      <c r="V21" t="s">
+      <c r="X21" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -2101,19 +2233,19 @@
         <v>0</v>
       </c>
       <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
         <f>SUM(B22:E22)</f>
         <v>0</v>
       </c>
-      <c r="I22">
-        <f>SUM(F22:G22)</f>
-        <v>0</v>
-      </c>
       <c r="J22">
-        <f>SUM(H22:I22)</f>
+        <f>SUM(F22:H22)</f>
         <v>0</v>
       </c>
       <c r="K22">
-        <v>13</v>
+        <f>SUM(I22:J22)</f>
+        <v>0</v>
       </c>
       <c r="L22">
         <v>13</v>
@@ -2125,37 +2257,43 @@
         <v>13</v>
       </c>
       <c r="O22">
+        <v>13</v>
+      </c>
+      <c r="P22">
         <v>14</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>15</v>
       </c>
-      <c r="Q22">
-        <v>17</v>
-      </c>
       <c r="R22">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="S22">
         <v>17</v>
       </c>
-      <c r="T22" t="s">
+      <c r="T22">
+        <v>16</v>
+      </c>
+      <c r="U22">
+        <v>17</v>
+      </c>
+      <c r="V22" t="s">
         <v>12</v>
       </c>
-      <c r="U22" t="s">
+      <c r="W22" t="s">
         <v>21</v>
       </c>
-      <c r="V22" t="s">
+      <c r="X22" t="s">
         <v>32</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V22" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V22">
-      <sortCondition descending="1" ref="I1:I22"/>
+  <autoFilter ref="A1:X22" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X22">
+      <sortCondition descending="1" ref="K1:K22"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V23">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X23">
     <sortCondition descending="1" ref="J1:J23"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F137C3-C139-4E93-A1AA-DE6255C9CBAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393FD514-47A3-4281-B4B1-27AF21471AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6DC662A2-343A-4284-B4F3-E8BBCF4A3089}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="2" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2'!$A$1:$X$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2'!$A$1:$Z$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="58">
   <si>
     <t>Nombre</t>
   </si>
@@ -207,6 +207,12 @@
   </si>
   <si>
     <t>Ranking 7</t>
+  </si>
+  <si>
+    <t>Semana 8</t>
+  </si>
+  <si>
+    <t>Ranking 8</t>
   </si>
 </sst>
 </file>
@@ -578,25 +584,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0244A2-6A9A-442F-B635-0C9297E0559B}">
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.1796875" customWidth="1"/>
-    <col min="11" max="11" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="18" width="8.54296875" customWidth="1"/>
-    <col min="19" max="19" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.90625" customWidth="1"/>
-    <col min="21" max="21" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.1796875" customWidth="1"/>
+    <col min="12" max="12" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="20" width="8.54296875" customWidth="1"/>
+    <col min="21" max="21" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.90625" customWidth="1"/>
+    <col min="23" max="23" width="13.6328125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -622,55 +628,61 @@
         <v>54</v>
       </c>
       <c r="I1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>49</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>4</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>5</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>6</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>45</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>47</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>50</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>53</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>55</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
+        <v>57</v>
+      </c>
+      <c r="U1" t="s">
         <v>7</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>51</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>8</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>9</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>10</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -696,37 +708,37 @@
         <v>696</v>
       </c>
       <c r="I2">
+        <v>638</v>
+      </c>
+      <c r="J2">
         <f>SUM(B2:E2)</f>
         <v>2741</v>
       </c>
-      <c r="J2">
-        <f>SUM(F2:H2)</f>
-        <v>1607</v>
-      </c>
       <c r="K2">
-        <f>SUM(I2:J2)</f>
-        <v>4348</v>
+        <f>SUM(F2:I2)</f>
+        <v>2245</v>
       </c>
       <c r="L2">
+        <f>SUM(J2:K2)</f>
+        <v>4986</v>
+      </c>
+      <c r="M2">
         <v>1</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>3</v>
-      </c>
-      <c r="N2">
-        <v>1</v>
       </c>
       <c r="O2">
         <v>1</v>
       </c>
       <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
         <v>4</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>3</v>
-      </c>
-      <c r="R2">
-        <v>1</v>
       </c>
       <c r="S2">
         <v>1</v>
@@ -737,17 +749,23 @@
       <c r="U2">
         <v>1</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2" t="s">
         <v>12</v>
       </c>
-      <c r="W2" t="s">
-        <v>13</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -773,25 +791,25 @@
         <v>515</v>
       </c>
       <c r="I3">
+        <v>36</v>
+      </c>
+      <c r="J3">
         <f>SUM(B3:E3)</f>
         <v>2496</v>
       </c>
-      <c r="J3">
-        <f>SUM(F3:H3)</f>
-        <v>1739</v>
-      </c>
       <c r="K3">
-        <f>SUM(I3:J3)</f>
-        <v>4235</v>
+        <f>SUM(F3:I3)</f>
+        <v>1775</v>
       </c>
       <c r="L3">
+        <f>SUM(J3:K3)</f>
+        <v>4271</v>
+      </c>
+      <c r="M3">
         <v>2</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>6</v>
-      </c>
-      <c r="N3">
-        <v>2</v>
       </c>
       <c r="O3">
         <v>2</v>
@@ -800,31 +818,37 @@
         <v>2</v>
       </c>
       <c r="Q3">
+        <v>2</v>
+      </c>
+      <c r="R3">
         <v>1</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>4</v>
       </c>
-      <c r="S3">
-        <v>2</v>
-      </c>
       <c r="T3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="U3">
         <v>2</v>
       </c>
-      <c r="V3" t="s">
+      <c r="V3">
+        <v>5</v>
+      </c>
+      <c r="W3">
+        <v>2</v>
+      </c>
+      <c r="X3" t="s">
         <v>16</v>
       </c>
-      <c r="W3" t="s">
+      <c r="Y3" t="s">
         <v>17</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Z3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -850,99 +874,105 @@
         <v>553</v>
       </c>
       <c r="I4">
+        <v>650</v>
+      </c>
+      <c r="J4">
         <f>SUM(B4:E4)</f>
         <v>2255</v>
       </c>
-      <c r="J4">
-        <f>SUM(F4:H4)</f>
-        <v>1180</v>
-      </c>
       <c r="K4">
-        <f>SUM(I4:J4)</f>
-        <v>3435</v>
+        <f>SUM(F4:I4)</f>
+        <v>1830</v>
       </c>
       <c r="L4">
+        <f>SUM(J4:K4)</f>
+        <v>4085</v>
+      </c>
+      <c r="M4">
         <v>4</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>2</v>
-      </c>
-      <c r="N4">
-        <v>3</v>
       </c>
       <c r="O4">
         <v>3</v>
       </c>
       <c r="P4">
+        <v>3</v>
+      </c>
+      <c r="Q4">
         <v>5</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>12</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>2</v>
       </c>
-      <c r="S4">
-        <v>3</v>
-      </c>
       <c r="T4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U4">
         <v>3</v>
       </c>
-      <c r="V4" t="s">
+      <c r="V4">
+        <v>4</v>
+      </c>
+      <c r="W4">
+        <v>3</v>
+      </c>
+      <c r="X4" t="s">
         <v>16</v>
       </c>
-      <c r="W4" t="s">
-        <v>13</v>
-      </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>411</v>
+        <v>576</v>
       </c>
       <c r="C5">
-        <v>645</v>
+        <v>554</v>
       </c>
       <c r="D5">
-        <v>427</v>
+        <v>563</v>
       </c>
       <c r="E5">
-        <v>393</v>
+        <v>324</v>
       </c>
       <c r="F5">
-        <v>481</v>
+        <v>301</v>
       </c>
       <c r="G5">
-        <v>491</v>
+        <v>445</v>
       </c>
       <c r="H5">
-        <v>456</v>
+        <v>534</v>
       </c>
       <c r="I5">
+        <v>638</v>
+      </c>
+      <c r="J5">
         <f>SUM(B5:E5)</f>
-        <v>1876</v>
-      </c>
-      <c r="J5">
-        <f>SUM(F5:H5)</f>
-        <v>1428</v>
+        <v>2017</v>
       </c>
       <c r="K5">
-        <f>SUM(I5:J5)</f>
-        <v>3304</v>
+        <f>SUM(F5:I5)</f>
+        <v>1918</v>
       </c>
       <c r="L5">
-        <v>5</v>
+        <f>SUM(J5:K5)</f>
+        <v>3935</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N5">
         <v>5</v>
@@ -951,111 +981,123 @@
         <v>4</v>
       </c>
       <c r="P5">
+        <v>6</v>
+      </c>
+      <c r="Q5">
+        <v>6</v>
+      </c>
+      <c r="R5">
+        <v>4</v>
+      </c>
+      <c r="S5">
         <v>3</v>
       </c>
-      <c r="Q5">
-        <v>2</v>
-      </c>
-      <c r="R5">
-        <v>5</v>
-      </c>
-      <c r="S5">
-        <v>5</v>
-      </c>
       <c r="T5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U5">
         <v>4</v>
       </c>
-      <c r="V5" t="s">
+      <c r="V5">
+        <v>2</v>
+      </c>
+      <c r="W5">
+        <v>4</v>
+      </c>
+      <c r="X5" t="s">
         <v>12</v>
       </c>
-      <c r="W5" t="s">
-        <v>21</v>
-      </c>
-      <c r="X5" t="s">
-        <v>18</v>
+      <c r="Y5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="B6">
-        <v>576</v>
+        <v>411</v>
       </c>
       <c r="C6">
-        <v>554</v>
+        <v>645</v>
       </c>
       <c r="D6">
-        <v>563</v>
+        <v>427</v>
       </c>
       <c r="E6">
-        <v>324</v>
+        <v>393</v>
       </c>
       <c r="F6">
-        <v>301</v>
+        <v>481</v>
       </c>
       <c r="G6">
-        <v>445</v>
+        <v>491</v>
       </c>
       <c r="H6">
-        <v>534</v>
+        <v>456</v>
       </c>
       <c r="I6">
+        <v>319</v>
+      </c>
+      <c r="J6">
         <f>SUM(B6:E6)</f>
-        <v>2017</v>
-      </c>
-      <c r="J6">
-        <f>SUM(F6:H6)</f>
-        <v>1280</v>
+        <v>1876</v>
       </c>
       <c r="K6">
-        <f>SUM(I6:J6)</f>
-        <v>3297</v>
+        <f>SUM(F6:I6)</f>
+        <v>1747</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <f>SUM(J6:K6)</f>
+        <v>3623</v>
       </c>
       <c r="M6">
         <v>5</v>
       </c>
       <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>5</v>
+      </c>
+      <c r="P6">
         <v>4</v>
       </c>
-      <c r="O6">
-        <v>6</v>
-      </c>
-      <c r="P6">
-        <v>6</v>
-      </c>
       <c r="Q6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>5</v>
       </c>
-      <c r="V6" t="s">
+      <c r="V6">
+        <v>6</v>
+      </c>
+      <c r="W6">
+        <v>5</v>
+      </c>
+      <c r="X6" t="s">
         <v>12</v>
       </c>
-      <c r="W6" t="s">
-        <v>13</v>
-      </c>
-      <c r="X6" t="s">
-        <v>14</v>
+      <c r="Y6" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -1081,99 +1123,105 @@
         <v>455</v>
       </c>
       <c r="I7">
+        <v>422</v>
+      </c>
+      <c r="J7">
         <f>SUM(B7:E7)</f>
         <v>1600</v>
       </c>
-      <c r="J7">
-        <f>SUM(F7:H7)</f>
-        <v>1457</v>
-      </c>
       <c r="K7">
-        <f>SUM(I7:J7)</f>
-        <v>3057</v>
+        <f>SUM(F7:I7)</f>
+        <v>1879</v>
       </c>
       <c r="L7">
+        <f>SUM(J7:K7)</f>
+        <v>3479</v>
+      </c>
+      <c r="M7">
         <v>6</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>4</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>6</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>7</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>1</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>5</v>
-      </c>
-      <c r="R7">
-        <v>6</v>
       </c>
       <c r="S7">
         <v>6</v>
       </c>
       <c r="T7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U7">
         <v>6</v>
       </c>
-      <c r="V7" t="s">
+      <c r="V7">
+        <v>3</v>
+      </c>
+      <c r="W7">
+        <v>6</v>
+      </c>
+      <c r="X7" t="s">
         <v>16</v>
       </c>
-      <c r="W7" t="s">
+      <c r="Y7" t="s">
         <v>21</v>
       </c>
-      <c r="X7" t="s">
+      <c r="Z7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B8">
-        <v>345</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D8">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="E8">
-        <v>238</v>
+        <v>381</v>
       </c>
       <c r="F8">
-        <v>70</v>
+        <v>177</v>
       </c>
       <c r="G8">
-        <v>225</v>
+        <v>306</v>
       </c>
       <c r="H8">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="I8">
+        <v>393</v>
+      </c>
+      <c r="J8">
         <f>SUM(B8:E8)</f>
-        <v>1010</v>
-      </c>
-      <c r="J8">
-        <f>SUM(F8:H8)</f>
-        <v>582</v>
+        <v>798</v>
       </c>
       <c r="K8">
-        <f>SUM(I8:J8)</f>
-        <v>1592</v>
+        <f>SUM(F8:I8)</f>
+        <v>1173</v>
       </c>
       <c r="L8">
-        <v>7</v>
+        <f>SUM(J8:K8)</f>
+        <v>1971</v>
       </c>
       <c r="M8">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="N8">
         <v>7</v>
@@ -1182,72 +1230,78 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S8">
         <v>7</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U8">
+        <v>8</v>
+      </c>
+      <c r="V8">
         <v>7</v>
       </c>
-      <c r="V8" t="s">
-        <v>12</v>
-      </c>
-      <c r="W8" t="s">
-        <v>13</v>
+      <c r="W8">
+        <v>7</v>
       </c>
       <c r="X8" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="C9">
+        <v>223</v>
+      </c>
+      <c r="D9">
+        <v>204</v>
+      </c>
+      <c r="E9">
+        <v>238</v>
+      </c>
+      <c r="F9">
+        <v>70</v>
+      </c>
+      <c r="G9">
         <v>225</v>
       </c>
-      <c r="D9">
-        <v>192</v>
-      </c>
-      <c r="E9">
-        <v>381</v>
-      </c>
-      <c r="F9">
-        <v>177</v>
-      </c>
-      <c r="G9">
-        <v>306</v>
-      </c>
       <c r="H9">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="I9">
+        <v>360</v>
+      </c>
+      <c r="J9">
         <f>SUM(B9:E9)</f>
-        <v>798</v>
-      </c>
-      <c r="J9">
-        <f>SUM(F9:H9)</f>
-        <v>780</v>
+        <v>1010</v>
       </c>
       <c r="K9">
-        <f>SUM(I9:J9)</f>
-        <v>1578</v>
+        <f>SUM(F9:I9)</f>
+        <v>942</v>
       </c>
       <c r="L9">
-        <v>13</v>
+        <f>SUM(J9:K9)</f>
+        <v>1952</v>
       </c>
       <c r="M9">
         <v>7</v>
@@ -1256,37 +1310,43 @@
         <v>8</v>
       </c>
       <c r="O9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="R9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S9">
         <v>8</v>
       </c>
       <c r="T9">
+        <v>8</v>
+      </c>
+      <c r="U9">
         <v>7</v>
       </c>
-      <c r="U9">
+      <c r="V9">
+        <v>9</v>
+      </c>
+      <c r="W9">
         <v>8</v>
       </c>
-      <c r="V9" t="s">
-        <v>16</v>
-      </c>
-      <c r="W9" t="s">
-        <v>13</v>
-      </c>
       <c r="X9" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -1312,173 +1372,185 @@
         <v>256</v>
       </c>
       <c r="I10">
+        <v>130</v>
+      </c>
+      <c r="J10">
         <f>SUM(B10:E10)</f>
         <v>529</v>
       </c>
-      <c r="J10">
-        <f>SUM(F10:H10)</f>
-        <v>687</v>
-      </c>
       <c r="K10">
-        <f>SUM(I10:J10)</f>
-        <v>1216</v>
+        <f>SUM(F10:I10)</f>
+        <v>817</v>
       </c>
       <c r="L10">
+        <f>SUM(J10:K10)</f>
+        <v>1346</v>
+      </c>
+      <c r="M10">
         <v>8</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>11</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>12</v>
-      </c>
-      <c r="O10">
-        <v>9</v>
       </c>
       <c r="P10">
         <v>9</v>
       </c>
       <c r="Q10">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="S10">
         <v>9</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U10">
         <v>9</v>
       </c>
-      <c r="V10" t="s">
+      <c r="V10">
+        <v>10</v>
+      </c>
+      <c r="W10">
+        <v>9</v>
+      </c>
+      <c r="X10" t="s">
         <v>16</v>
       </c>
-      <c r="W10" t="s">
-        <v>13</v>
-      </c>
-      <c r="X10" t="s">
+      <c r="Y10" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B11">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="C11">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>282</v>
+        <v>139</v>
       </c>
       <c r="G11">
-        <v>198</v>
+        <v>280</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="I11">
+        <v>383</v>
+      </c>
+      <c r="J11">
         <f>SUM(B11:E11)</f>
-        <v>503</v>
-      </c>
-      <c r="J11">
-        <f>SUM(F11:H11)</f>
-        <v>480</v>
+        <v>28</v>
       </c>
       <c r="K11">
-        <f>SUM(I11:J11)</f>
-        <v>983</v>
+        <f>SUM(F11:I11)</f>
+        <v>1033</v>
       </c>
       <c r="L11">
-        <v>9</v>
+        <f>SUM(J11:K11)</f>
+        <v>1061</v>
       </c>
       <c r="M11">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N11">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O11">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P11">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R11">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="S11">
         <v>10</v>
       </c>
       <c r="T11">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="U11">
+        <v>16</v>
+      </c>
+      <c r="V11">
+        <v>8</v>
+      </c>
+      <c r="W11">
         <v>10</v>
       </c>
-      <c r="V11" t="s">
+      <c r="X11" t="s">
         <v>16</v>
       </c>
-      <c r="W11" t="s">
-        <v>13</v>
-      </c>
-      <c r="X11" t="s">
+      <c r="Y11" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B12">
         <v>62</v>
       </c>
       <c r="C12">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D12">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="E12">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F12">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G12">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
         <f>SUM(B12:E12)</f>
-        <v>496</v>
-      </c>
-      <c r="J12">
-        <f>SUM(F12:H12)</f>
-        <v>484</v>
+        <v>503</v>
       </c>
       <c r="K12">
-        <f>SUM(I12:J12)</f>
-        <v>980</v>
+        <f>SUM(F12:I12)</f>
+        <v>480</v>
       </c>
       <c r="L12">
-        <v>10</v>
+        <f>SUM(J12:K12)</f>
+        <v>983</v>
       </c>
       <c r="M12">
         <v>9</v>
@@ -1487,87 +1559,93 @@
         <v>10</v>
       </c>
       <c r="O12">
+        <v>9</v>
+      </c>
+      <c r="P12">
+        <v>11</v>
+      </c>
+      <c r="Q12">
+        <v>8</v>
+      </c>
+      <c r="R12">
+        <v>11</v>
+      </c>
+      <c r="S12">
+        <v>13</v>
+      </c>
+      <c r="T12">
+        <v>13</v>
+      </c>
+      <c r="U12">
         <v>10</v>
       </c>
-      <c r="P12">
-        <v>7</v>
-      </c>
-      <c r="Q12">
+      <c r="V12">
+        <v>13</v>
+      </c>
+      <c r="W12">
+        <v>11</v>
+      </c>
+      <c r="X12" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
+        <v>62</v>
+      </c>
+      <c r="C13">
+        <v>222</v>
+      </c>
+      <c r="D13">
+        <v>148</v>
+      </c>
+      <c r="E13">
+        <v>64</v>
+      </c>
+      <c r="F13">
+        <v>285</v>
+      </c>
+      <c r="G13">
+        <v>199</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <f>SUM(B13:E13)</f>
+        <v>496</v>
+      </c>
+      <c r="K13">
+        <f>SUM(F13:I13)</f>
+        <v>484</v>
+      </c>
+      <c r="L13">
+        <f>SUM(J13:K13)</f>
+        <v>980</v>
+      </c>
+      <c r="M13">
         <v>10</v>
       </c>
-      <c r="R12">
-        <v>13</v>
-      </c>
-      <c r="S12">
-        <v>11</v>
-      </c>
-      <c r="T12">
-        <v>11</v>
-      </c>
-      <c r="U12">
-        <v>11</v>
-      </c>
-      <c r="V12" t="s">
-        <v>12</v>
-      </c>
-      <c r="W12" t="s">
-        <v>13</v>
-      </c>
-      <c r="X12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13">
-        <v>28</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>139</v>
-      </c>
-      <c r="G13">
-        <v>280</v>
-      </c>
-      <c r="H13">
-        <v>231</v>
-      </c>
-      <c r="I13">
-        <f>SUM(B13:E13)</f>
-        <v>28</v>
-      </c>
-      <c r="J13">
-        <f>SUM(F13:H13)</f>
-        <v>650</v>
-      </c>
-      <c r="K13">
-        <f>SUM(I13:J13)</f>
-        <v>678</v>
-      </c>
-      <c r="L13">
-        <v>12</v>
-      </c>
-      <c r="M13">
-        <v>13</v>
-      </c>
       <c r="N13">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q13">
         <v>7</v>
@@ -1576,25 +1654,31 @@
         <v>10</v>
       </c>
       <c r="S13">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="U13">
+        <v>11</v>
+      </c>
+      <c r="V13">
         <v>12</v>
       </c>
-      <c r="V13" t="s">
-        <v>16</v>
-      </c>
-      <c r="W13" t="s">
-        <v>21</v>
+      <c r="W13">
+        <v>12</v>
       </c>
       <c r="X13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1620,445 +1704,481 @@
         <v>139</v>
       </c>
       <c r="I14">
+        <v>158</v>
+      </c>
+      <c r="J14">
         <f>SUM(B14:E14)</f>
         <v>145</v>
       </c>
-      <c r="J14">
-        <f>SUM(F14:H14)</f>
-        <v>448</v>
-      </c>
       <c r="K14">
-        <f>SUM(I14:J14)</f>
-        <v>593</v>
+        <f>SUM(F14:I14)</f>
+        <v>606</v>
       </c>
       <c r="L14">
-        <v>13</v>
+        <f>SUM(J14:K14)</f>
+        <v>751</v>
       </c>
       <c r="M14">
         <v>13</v>
       </c>
       <c r="N14">
+        <v>13</v>
+      </c>
+      <c r="O14">
         <v>11</v>
       </c>
-      <c r="O14">
-        <v>13</v>
-      </c>
       <c r="P14">
+        <v>13</v>
+      </c>
+      <c r="Q14">
         <v>11</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>14</v>
       </c>
-      <c r="R14">
+      <c r="S14">
         <v>11</v>
       </c>
-      <c r="S14">
+      <c r="T14">
+        <v>10</v>
+      </c>
+      <c r="U14">
         <v>12</v>
       </c>
-      <c r="T14">
-        <v>13</v>
-      </c>
-      <c r="U14">
-        <v>13</v>
-      </c>
-      <c r="V14" t="s">
+      <c r="V14">
+        <v>11</v>
+      </c>
+      <c r="W14">
+        <v>13</v>
+      </c>
+      <c r="X14" t="s">
         <v>12</v>
       </c>
-      <c r="W14" t="s">
+      <c r="Y14" t="s">
         <v>17</v>
       </c>
-      <c r="X14" t="s">
+      <c r="Z14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>443</v>
+      </c>
+      <c r="J15">
+        <f>SUM(B15:E15)</f>
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <f>SUM(F15:I15)</f>
+        <v>443</v>
+      </c>
+      <c r="L15">
+        <f>SUM(J15:K15)</f>
+        <v>443</v>
+      </c>
+      <c r="M15">
+        <v>13</v>
+      </c>
+      <c r="N15">
+        <v>13</v>
+      </c>
+      <c r="O15">
+        <v>13</v>
+      </c>
+      <c r="P15">
+        <v>13</v>
+      </c>
+      <c r="Q15">
+        <v>14</v>
+      </c>
+      <c r="R15">
+        <v>15</v>
+      </c>
+      <c r="S15">
+        <v>13</v>
+      </c>
+      <c r="T15">
+        <v>4</v>
+      </c>
+      <c r="U15">
+        <v>17</v>
+      </c>
+      <c r="V15">
+        <v>14</v>
+      </c>
+      <c r="W15">
+        <v>14</v>
+      </c>
+      <c r="X15" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>28</v>
       </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
         <v>59</v>
       </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
         <v>254</v>
       </c>
-      <c r="H15">
+      <c r="H16">
         <v>62</v>
       </c>
-      <c r="I15">
-        <f>SUM(B15:E15)</f>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <f>SUM(B16:E16)</f>
         <v>59</v>
       </c>
-      <c r="J15">
-        <f>SUM(F15:H15)</f>
+      <c r="K16">
+        <f>SUM(F16:I16)</f>
         <v>316</v>
       </c>
-      <c r="K15">
-        <f>SUM(I15:J15)</f>
+      <c r="L16">
+        <f>SUM(J16:K16)</f>
         <v>375</v>
       </c>
-      <c r="L15">
-        <v>13</v>
-      </c>
-      <c r="M15">
-        <v>13</v>
-      </c>
-      <c r="N15">
-        <v>13</v>
-      </c>
-      <c r="O15">
+      <c r="M16">
+        <v>13</v>
+      </c>
+      <c r="N16">
+        <v>13</v>
+      </c>
+      <c r="O16">
+        <v>13</v>
+      </c>
+      <c r="P16">
         <v>12</v>
       </c>
-      <c r="P15">
+      <c r="Q16">
         <v>14</v>
       </c>
-      <c r="Q15">
+      <c r="R16">
         <v>8</v>
       </c>
-      <c r="R15">
+      <c r="S16">
         <v>12</v>
       </c>
-      <c r="S15">
+      <c r="T16">
+        <v>13</v>
+      </c>
+      <c r="U16">
         <v>14</v>
       </c>
-      <c r="T15">
+      <c r="V16">
+        <v>15</v>
+      </c>
+      <c r="W16">
+        <v>15</v>
+      </c>
+      <c r="X16" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>84</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <f>SUM(B17:E17)</f>
+        <v>84</v>
+      </c>
+      <c r="K17">
+        <f>SUM(F17:I17)</f>
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <f>SUM(J17:K17)</f>
+        <v>84</v>
+      </c>
+      <c r="M17">
+        <v>13</v>
+      </c>
+      <c r="N17">
+        <v>12</v>
+      </c>
+      <c r="O17">
+        <v>13</v>
+      </c>
+      <c r="P17">
+        <v>13</v>
+      </c>
+      <c r="Q17">
         <v>14</v>
       </c>
-      <c r="U15">
+      <c r="R17">
+        <v>15</v>
+      </c>
+      <c r="S17">
+        <v>13</v>
+      </c>
+      <c r="T17">
+        <v>13</v>
+      </c>
+      <c r="U17">
+        <v>13</v>
+      </c>
+      <c r="V17">
+        <v>16</v>
+      </c>
+      <c r="W17">
+        <v>16</v>
+      </c>
+      <c r="X17" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18">
+        <v>39</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <f>SUM(B18:E18)</f>
+        <v>39</v>
+      </c>
+      <c r="K18">
+        <f>SUM(F18:I18)</f>
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <f>SUM(J18:K18)</f>
+        <v>39</v>
+      </c>
+      <c r="M18">
+        <v>11</v>
+      </c>
+      <c r="N18">
+        <v>13</v>
+      </c>
+      <c r="O18">
+        <v>13</v>
+      </c>
+      <c r="P18">
+        <v>13</v>
+      </c>
+      <c r="Q18">
         <v>14</v>
       </c>
-      <c r="V15" t="s">
+      <c r="R18">
+        <v>15</v>
+      </c>
+      <c r="S18">
+        <v>13</v>
+      </c>
+      <c r="T18">
+        <v>13</v>
+      </c>
+      <c r="U18">
+        <v>15</v>
+      </c>
+      <c r="V18">
+        <v>16</v>
+      </c>
+      <c r="W18">
+        <v>17</v>
+      </c>
+      <c r="X18" t="s">
         <v>12</v>
       </c>
-      <c r="W15" t="s">
-        <v>13</v>
-      </c>
-      <c r="X15" t="s">
+      <c r="Y18" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>84</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <f>SUM(B16:E16)</f>
-        <v>84</v>
-      </c>
-      <c r="J16">
-        <f>SUM(F16:H16)</f>
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <f>SUM(I16:J16)</f>
-        <v>84</v>
-      </c>
-      <c r="L16">
-        <v>13</v>
-      </c>
-      <c r="M16">
-        <v>12</v>
-      </c>
-      <c r="N16">
-        <v>13</v>
-      </c>
-      <c r="O16">
-        <v>13</v>
-      </c>
-      <c r="P16">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <f>SUM(B19:E19)</f>
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <f>SUM(F19:I19)</f>
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <f>SUM(J19:K19)</f>
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>13</v>
+      </c>
+      <c r="N19">
+        <v>13</v>
+      </c>
+      <c r="O19">
+        <v>13</v>
+      </c>
+      <c r="P19">
+        <v>13</v>
+      </c>
+      <c r="Q19">
         <v>14</v>
       </c>
-      <c r="Q16">
+      <c r="R19">
         <v>15</v>
       </c>
-      <c r="R16">
-        <v>13</v>
-      </c>
-      <c r="S16">
-        <v>13</v>
-      </c>
-      <c r="T16">
-        <v>15</v>
-      </c>
-      <c r="U16">
-        <v>15</v>
-      </c>
-      <c r="V16" t="s">
-        <v>12</v>
-      </c>
-      <c r="W16" t="s">
-        <v>21</v>
-      </c>
-      <c r="X16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17">
-        <v>39</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <f>SUM(B17:E17)</f>
-        <v>39</v>
-      </c>
-      <c r="J17">
-        <f>SUM(F17:H17)</f>
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <f>SUM(I17:J17)</f>
-        <v>39</v>
-      </c>
-      <c r="L17">
-        <v>11</v>
-      </c>
-      <c r="M17">
-        <v>13</v>
-      </c>
-      <c r="N17">
-        <v>13</v>
-      </c>
-      <c r="O17">
-        <v>13</v>
-      </c>
-      <c r="P17">
-        <v>14</v>
-      </c>
-      <c r="Q17">
-        <v>15</v>
-      </c>
-      <c r="R17">
-        <v>13</v>
-      </c>
-      <c r="S17">
-        <v>15</v>
-      </c>
-      <c r="T17">
-        <v>16</v>
-      </c>
-      <c r="U17">
-        <v>16</v>
-      </c>
-      <c r="V17" t="s">
-        <v>12</v>
-      </c>
-      <c r="W17" t="s">
-        <v>13</v>
-      </c>
-      <c r="X17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <f>SUM(B18:E18)</f>
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <f>SUM(F18:H18)</f>
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <f>SUM(I18:J18)</f>
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>13</v>
-      </c>
-      <c r="M18">
-        <v>13</v>
-      </c>
-      <c r="N18">
-        <v>13</v>
-      </c>
-      <c r="O18">
-        <v>13</v>
-      </c>
-      <c r="P18">
-        <v>14</v>
-      </c>
-      <c r="Q18">
-        <v>15</v>
-      </c>
-      <c r="R18">
-        <v>13</v>
-      </c>
-      <c r="S18">
-        <v>17</v>
-      </c>
-      <c r="T18">
-        <v>16</v>
-      </c>
-      <c r="U18">
-        <v>17</v>
-      </c>
-      <c r="V18" t="s">
-        <v>16</v>
-      </c>
-      <c r="W18" t="s">
-        <v>13</v>
-      </c>
-      <c r="X18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <f>SUM(B19:E19)</f>
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <f>SUM(F19:H19)</f>
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <f>SUM(I19:J19)</f>
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>13</v>
-      </c>
-      <c r="M19">
-        <v>13</v>
-      </c>
-      <c r="N19">
-        <v>13</v>
-      </c>
-      <c r="O19">
-        <v>13</v>
-      </c>
-      <c r="P19">
-        <v>14</v>
-      </c>
-      <c r="Q19">
-        <v>15</v>
-      </c>
-      <c r="R19">
-        <v>13</v>
-      </c>
       <c r="S19">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T19">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="U19">
         <v>17</v>
       </c>
-      <c r="V19" t="s">
-        <v>12</v>
-      </c>
-      <c r="W19" t="s">
-        <v>13</v>
+      <c r="V19">
+        <v>16</v>
+      </c>
+      <c r="W19">
+        <v>18</v>
       </c>
       <c r="X19" t="s">
-        <v>29</v>
+        <v>16</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2082,19 +2202,19 @@
         <v>0</v>
       </c>
       <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
         <f>SUM(B20:E20)</f>
         <v>0</v>
       </c>
-      <c r="J20">
-        <f>SUM(F20:H20)</f>
-        <v>0</v>
-      </c>
       <c r="K20">
-        <f>SUM(I20:J20)</f>
+        <f>SUM(F20:I20)</f>
         <v>0</v>
       </c>
       <c r="L20">
-        <v>13</v>
+        <f>SUM(J20:K20)</f>
+        <v>0</v>
       </c>
       <c r="M20">
         <v>13</v>
@@ -2106,36 +2226,42 @@
         <v>13</v>
       </c>
       <c r="P20">
+        <v>13</v>
+      </c>
+      <c r="Q20">
         <v>14</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <v>15</v>
       </c>
-      <c r="R20">
-        <v>13</v>
-      </c>
       <c r="S20">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T20">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="U20">
         <v>17</v>
       </c>
-      <c r="V20" t="s">
+      <c r="V20">
         <v>16</v>
       </c>
-      <c r="W20" t="s">
-        <v>13</v>
+      <c r="W20">
+        <v>18</v>
       </c>
       <c r="X20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z20" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2159,19 +2285,19 @@
         <v>0</v>
       </c>
       <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
         <f>SUM(B21:E21)</f>
         <v>0</v>
       </c>
-      <c r="J21">
-        <f>SUM(F21:H21)</f>
-        <v>0</v>
-      </c>
       <c r="K21">
-        <f>SUM(I21:J21)</f>
+        <f>SUM(F21:I21)</f>
         <v>0</v>
       </c>
       <c r="L21">
-        <v>13</v>
+        <f>SUM(J21:K21)</f>
+        <v>0</v>
       </c>
       <c r="M21">
         <v>13</v>
@@ -2183,34 +2309,40 @@
         <v>13</v>
       </c>
       <c r="P21">
+        <v>13</v>
+      </c>
+      <c r="Q21">
         <v>14</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <v>15</v>
       </c>
-      <c r="R21">
-        <v>13</v>
-      </c>
       <c r="S21">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T21">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="U21">
         <v>17</v>
       </c>
-      <c r="V21" t="s">
+      <c r="V21">
         <v>16</v>
       </c>
-      <c r="W21" t="s">
-        <v>21</v>
+      <c r="W21">
+        <v>18</v>
       </c>
       <c r="X21" t="s">
-        <v>31</v>
+        <v>16</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -2236,19 +2368,19 @@
         <v>0</v>
       </c>
       <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
         <f>SUM(B22:E22)</f>
         <v>0</v>
       </c>
-      <c r="J22">
-        <f>SUM(F22:H22)</f>
-        <v>0</v>
-      </c>
       <c r="K22">
-        <f>SUM(I22:J22)</f>
+        <f>SUM(F22:I22)</f>
         <v>0</v>
       </c>
       <c r="L22">
-        <v>13</v>
+        <f>SUM(J22:K22)</f>
+        <v>0</v>
       </c>
       <c r="M22">
         <v>13</v>
@@ -2260,41 +2392,47 @@
         <v>13</v>
       </c>
       <c r="P22">
+        <v>13</v>
+      </c>
+      <c r="Q22">
         <v>14</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>15</v>
       </c>
-      <c r="R22">
-        <v>13</v>
-      </c>
       <c r="S22">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="T22">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="U22">
         <v>17</v>
       </c>
-      <c r="V22" t="s">
+      <c r="V22">
+        <v>16</v>
+      </c>
+      <c r="W22">
+        <v>18</v>
+      </c>
+      <c r="X22" t="s">
         <v>12</v>
       </c>
-      <c r="W22" t="s">
+      <c r="Y22" t="s">
         <v>21</v>
       </c>
-      <c r="X22" t="s">
+      <c r="Z22" t="s">
         <v>32</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X22" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X22">
-      <sortCondition descending="1" ref="K1:K22"/>
+  <autoFilter ref="A1:Z22" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z22">
+      <sortCondition descending="1" ref="L1:L22"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X23">
-    <sortCondition descending="1" ref="J1:J23"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z23">
+    <sortCondition descending="1" ref="K1:K23"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393FD514-47A3-4281-B4B1-27AF21471AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D7BA5C-4544-404C-9F85-116DF1404664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6DC662A2-343A-4284-B4F3-E8BBCF4A3089}"/>
   </bookViews>
@@ -708,19 +708,19 @@
         <v>696</v>
       </c>
       <c r="I2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="J2">
-        <f>SUM(B2:E2)</f>
+        <f t="shared" ref="J2:J22" si="0">SUM(B2:E2)</f>
         <v>2741</v>
       </c>
       <c r="K2">
-        <f>SUM(F2:I2)</f>
-        <v>2245</v>
+        <f t="shared" ref="K2:K22" si="1">SUM(F2:I2)</f>
+        <v>2247</v>
       </c>
       <c r="L2">
-        <f>SUM(J2:K2)</f>
-        <v>4986</v>
+        <f t="shared" ref="L2:L22" si="2">SUM(J2:K2)</f>
+        <v>4988</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -791,19 +791,19 @@
         <v>515</v>
       </c>
       <c r="I3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J3">
-        <f>SUM(B3:E3)</f>
+        <f t="shared" si="0"/>
         <v>2496</v>
       </c>
       <c r="K3">
-        <f>SUM(F3:I3)</f>
-        <v>1775</v>
+        <f t="shared" si="1"/>
+        <v>1777</v>
       </c>
       <c r="L3">
-        <f>SUM(J3:K3)</f>
-        <v>4271</v>
+        <f t="shared" si="2"/>
+        <v>4273</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -874,19 +874,19 @@
         <v>553</v>
       </c>
       <c r="I4">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="J4">
-        <f>SUM(B4:E4)</f>
+        <f t="shared" si="0"/>
         <v>2255</v>
       </c>
       <c r="K4">
-        <f>SUM(F4:I4)</f>
-        <v>1830</v>
+        <f t="shared" si="1"/>
+        <v>1831</v>
       </c>
       <c r="L4">
-        <f>SUM(J4:K4)</f>
-        <v>4085</v>
+        <f t="shared" si="2"/>
+        <v>4086</v>
       </c>
       <c r="M4">
         <v>4</v>
@@ -957,19 +957,19 @@
         <v>534</v>
       </c>
       <c r="I5">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="J5">
-        <f>SUM(B5:E5)</f>
+        <f t="shared" si="0"/>
         <v>2017</v>
       </c>
       <c r="K5">
-        <f>SUM(F5:I5)</f>
-        <v>1918</v>
+        <f t="shared" si="1"/>
+        <v>1920</v>
       </c>
       <c r="L5">
-        <f>SUM(J5:K5)</f>
-        <v>3935</v>
+        <f t="shared" si="2"/>
+        <v>3937</v>
       </c>
       <c r="M5">
         <v>3</v>
@@ -1043,15 +1043,15 @@
         <v>319</v>
       </c>
       <c r="J6">
-        <f>SUM(B6:E6)</f>
+        <f t="shared" si="0"/>
         <v>1876</v>
       </c>
       <c r="K6">
-        <f>SUM(F6:I6)</f>
+        <f t="shared" si="1"/>
         <v>1747</v>
       </c>
       <c r="L6">
-        <f>SUM(J6:K6)</f>
+        <f t="shared" si="2"/>
         <v>3623</v>
       </c>
       <c r="M6">
@@ -1123,19 +1123,19 @@
         <v>455</v>
       </c>
       <c r="I7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J7">
-        <f>SUM(B7:E7)</f>
+        <f t="shared" si="0"/>
         <v>1600</v>
       </c>
       <c r="K7">
-        <f>SUM(F7:I7)</f>
-        <v>1879</v>
+        <f t="shared" si="1"/>
+        <v>1881</v>
       </c>
       <c r="L7">
-        <f>SUM(J7:K7)</f>
-        <v>3479</v>
+        <f t="shared" si="2"/>
+        <v>3481</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -1206,19 +1206,19 @@
         <v>297</v>
       </c>
       <c r="I8">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J8">
-        <f>SUM(B8:E8)</f>
+        <f t="shared" si="0"/>
         <v>798</v>
       </c>
       <c r="K8">
-        <f>SUM(F8:I8)</f>
-        <v>1173</v>
+        <f t="shared" si="1"/>
+        <v>1175</v>
       </c>
       <c r="L8">
-        <f>SUM(J8:K8)</f>
-        <v>1971</v>
+        <f t="shared" si="2"/>
+        <v>1973</v>
       </c>
       <c r="M8">
         <v>13</v>
@@ -1289,19 +1289,19 @@
         <v>287</v>
       </c>
       <c r="I9">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J9">
-        <f>SUM(B9:E9)</f>
+        <f t="shared" si="0"/>
         <v>1010</v>
       </c>
       <c r="K9">
-        <f>SUM(F9:I9)</f>
-        <v>942</v>
+        <f t="shared" si="1"/>
+        <v>944</v>
       </c>
       <c r="L9">
-        <f>SUM(J9:K9)</f>
-        <v>1952</v>
+        <f t="shared" si="2"/>
+        <v>1954</v>
       </c>
       <c r="M9">
         <v>7</v>
@@ -1372,19 +1372,19 @@
         <v>256</v>
       </c>
       <c r="I10">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J10">
-        <f>SUM(B10:E10)</f>
+        <f t="shared" si="0"/>
         <v>529</v>
       </c>
       <c r="K10">
-        <f>SUM(F10:I10)</f>
-        <v>817</v>
+        <f t="shared" si="1"/>
+        <v>818</v>
       </c>
       <c r="L10">
-        <f>SUM(J10:K10)</f>
-        <v>1346</v>
+        <f t="shared" si="2"/>
+        <v>1347</v>
       </c>
       <c r="M10">
         <v>8</v>
@@ -1455,19 +1455,19 @@
         <v>231</v>
       </c>
       <c r="I11">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J11">
-        <f>SUM(B11:E11)</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="K11">
-        <f>SUM(F11:I11)</f>
-        <v>1033</v>
+        <f t="shared" si="1"/>
+        <v>1035</v>
       </c>
       <c r="L11">
-        <f>SUM(J11:K11)</f>
-        <v>1061</v>
+        <f t="shared" si="2"/>
+        <v>1063</v>
       </c>
       <c r="M11">
         <v>12</v>
@@ -1541,15 +1541,15 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <f>SUM(B12:E12)</f>
+        <f t="shared" si="0"/>
         <v>503</v>
       </c>
       <c r="K12">
-        <f>SUM(F12:I12)</f>
+        <f t="shared" si="1"/>
         <v>480</v>
       </c>
       <c r="L12">
-        <f>SUM(J12:K12)</f>
+        <f t="shared" si="2"/>
         <v>983</v>
       </c>
       <c r="M12">
@@ -1624,15 +1624,15 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <f>SUM(B13:E13)</f>
+        <f t="shared" si="0"/>
         <v>496</v>
       </c>
       <c r="K13">
-        <f>SUM(F13:I13)</f>
+        <f t="shared" si="1"/>
         <v>484</v>
       </c>
       <c r="L13">
-        <f>SUM(J13:K13)</f>
+        <f t="shared" si="2"/>
         <v>980</v>
       </c>
       <c r="M13">
@@ -1704,19 +1704,19 @@
         <v>139</v>
       </c>
       <c r="I14">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J14">
-        <f>SUM(B14:E14)</f>
+        <f t="shared" si="0"/>
         <v>145</v>
       </c>
       <c r="K14">
-        <f>SUM(F14:I14)</f>
-        <v>606</v>
+        <f t="shared" si="1"/>
+        <v>608</v>
       </c>
       <c r="L14">
-        <f>SUM(J14:K14)</f>
-        <v>751</v>
+        <f t="shared" si="2"/>
+        <v>753</v>
       </c>
       <c r="M14">
         <v>13</v>
@@ -1790,15 +1790,15 @@
         <v>443</v>
       </c>
       <c r="J15">
-        <f>SUM(B15:E15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K15">
-        <f>SUM(F15:I15)</f>
+        <f t="shared" si="1"/>
         <v>443</v>
       </c>
       <c r="L15">
-        <f>SUM(J15:K15)</f>
+        <f t="shared" si="2"/>
         <v>443</v>
       </c>
       <c r="M15">
@@ -1873,15 +1873,15 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <f>SUM(B16:E16)</f>
+        <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="K16">
-        <f>SUM(F16:I16)</f>
+        <f t="shared" si="1"/>
         <v>316</v>
       </c>
       <c r="L16">
-        <f>SUM(J16:K16)</f>
+        <f t="shared" si="2"/>
         <v>375</v>
       </c>
       <c r="M16">
@@ -1956,15 +1956,15 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <f>SUM(B17:E17)</f>
+        <f t="shared" si="0"/>
         <v>84</v>
       </c>
       <c r="K17">
-        <f>SUM(F17:I17)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L17">
-        <f>SUM(J17:K17)</f>
+        <f t="shared" si="2"/>
         <v>84</v>
       </c>
       <c r="M17">
@@ -2039,15 +2039,15 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <f>SUM(B18:E18)</f>
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="K18">
-        <f>SUM(F18:I18)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L18">
-        <f>SUM(J18:K18)</f>
+        <f t="shared" si="2"/>
         <v>39</v>
       </c>
       <c r="M18">
@@ -2122,15 +2122,15 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <f>SUM(B19:E19)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K19">
-        <f>SUM(F19:I19)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L19">
-        <f>SUM(J19:K19)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M19">
@@ -2205,15 +2205,15 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <f>SUM(B20:E20)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K20">
-        <f>SUM(F20:I20)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L20">
-        <f>SUM(J20:K20)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M20">
@@ -2288,15 +2288,15 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <f>SUM(B21:E21)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K21">
-        <f>SUM(F21:I21)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L21">
-        <f>SUM(J21:K21)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M21">
@@ -2371,15 +2371,15 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <f>SUM(B22:E22)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K22">
-        <f>SUM(F22:I22)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L22">
-        <f>SUM(J22:K22)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M22">

--- a/reto_cuatachos.xlsx
+++ b/reto_cuatachos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mar6mx\Documents\CTCHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D7BA5C-4544-404C-9F85-116DF1404664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D2F16C-7C83-4E5F-A132-FA0516176000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6DC662A2-343A-4284-B4F3-E8BBCF4A3089}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="2" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2'!$A$1:$Z$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2'!$A$1:$AD$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="62">
   <si>
     <t>Nombre</t>
   </si>
@@ -213,6 +213,18 @@
   </si>
   <si>
     <t>Ranking 8</t>
+  </si>
+  <si>
+    <t>Semana 9</t>
+  </si>
+  <si>
+    <t>Subt. M 3</t>
+  </si>
+  <si>
+    <t>Ranking 9</t>
+  </si>
+  <si>
+    <t>Ranking Mens. 3</t>
   </si>
 </sst>
 </file>
@@ -584,25 +596,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA0244A2-6A9A-442F-B635-0C9297E0559B}">
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:AD22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.1796875" customWidth="1"/>
-    <col min="12" max="12" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="8.54296875" customWidth="1"/>
-    <col min="21" max="21" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.90625" customWidth="1"/>
-    <col min="23" max="23" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.7265625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="8.1796875" customWidth="1"/>
+    <col min="14" max="14" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="23" width="8.54296875" customWidth="1"/>
+    <col min="24" max="24" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="13.90625" customWidth="1"/>
+    <col min="27" max="27" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -631,58 +643,70 @@
         <v>56</v>
       </c>
       <c r="J1" t="s">
+        <v>58</v>
+      </c>
+      <c r="K1" t="s">
         <v>3</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>49</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N1" t="s">
         <v>4</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>5</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>6</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>45</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>47</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>50</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>53</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>55</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>57</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
+        <v>60</v>
+      </c>
+      <c r="X1" t="s">
         <v>7</v>
       </c>
-      <c r="V1" t="s">
+      <c r="Y1" t="s">
         <v>51</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Z1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA1" t="s">
         <v>8</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AB1" t="s">
         <v>9</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AC1" t="s">
         <v>10</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AD1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -711,61 +735,74 @@
         <v>640</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2:J22" si="0">SUM(B2:E2)</f>
+        <v>853</v>
+      </c>
+      <c r="K2">
+        <f>SUM(B2:E2)</f>
         <v>2741</v>
       </c>
-      <c r="K2">
-        <f t="shared" ref="K2:K22" si="1">SUM(F2:I2)</f>
+      <c r="L2">
+        <f>SUM(F2:I2)</f>
         <v>2247</v>
       </c>
-      <c r="L2">
-        <f t="shared" ref="L2:L22" si="2">SUM(J2:K2)</f>
-        <v>4988</v>
-      </c>
       <c r="M2">
-        <v>1</v>
+        <f>J2</f>
+        <v>853</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <f>SUM(K2:M2)</f>
+        <v>5841</v>
       </c>
       <c r="O2">
         <v>1</v>
       </c>
       <c r="P2">
+        <v>3</v>
+      </c>
+      <c r="Q2">
         <v>1</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
         <v>4</v>
       </c>
-      <c r="R2">
+      <c r="T2">
         <v>3</v>
-      </c>
-      <c r="S2">
-        <v>1</v>
-      </c>
-      <c r="T2">
-        <v>2</v>
       </c>
       <c r="U2">
         <v>1</v>
       </c>
       <c r="V2">
+        <v>2</v>
+      </c>
+      <c r="W2">
+        <v>2</v>
+      </c>
+      <c r="X2">
         <v>1</v>
       </c>
-      <c r="W2">
+      <c r="Y2">
         <v>1</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Z2">
+        <v>2</v>
+      </c>
+      <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
         <v>12</v>
       </c>
-      <c r="Y2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="AC2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -794,61 +831,74 @@
         <v>38</v>
       </c>
       <c r="J3">
-        <f t="shared" si="0"/>
+        <v>938</v>
+      </c>
+      <c r="K3">
+        <f>SUM(B3:E3)</f>
         <v>2496</v>
       </c>
-      <c r="K3">
-        <f t="shared" si="1"/>
+      <c r="L3">
+        <f>SUM(F3:I3)</f>
         <v>1777</v>
       </c>
-      <c r="L3">
-        <f t="shared" si="2"/>
-        <v>4273</v>
-      </c>
       <c r="M3">
-        <v>2</v>
+        <f>J3</f>
+        <v>938</v>
       </c>
       <c r="N3">
-        <v>6</v>
+        <f>SUM(K3:M3)</f>
+        <v>5211</v>
       </c>
       <c r="O3">
         <v>2</v>
       </c>
       <c r="P3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q3">
         <v>2</v>
       </c>
       <c r="R3">
+        <v>2</v>
+      </c>
+      <c r="S3">
+        <v>2</v>
+      </c>
+      <c r="T3">
         <v>1</v>
       </c>
-      <c r="S3">
+      <c r="U3">
         <v>4</v>
       </c>
-      <c r="T3">
+      <c r="V3">
         <v>12</v>
       </c>
-      <c r="U3">
+      <c r="W3">
+        <v>1</v>
+      </c>
+      <c r="X3">
         <v>2</v>
       </c>
-      <c r="V3">
+      <c r="Y3">
         <v>5</v>
       </c>
-      <c r="W3">
+      <c r="Z3">
+        <v>1</v>
+      </c>
+      <c r="AA3">
         <v>2</v>
       </c>
-      <c r="X3" t="s">
+      <c r="AB3" t="s">
         <v>16</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AC3" t="s">
         <v>17</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AD3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -877,61 +927,74 @@
         <v>651</v>
       </c>
       <c r="J4">
-        <f t="shared" si="0"/>
+        <v>569</v>
+      </c>
+      <c r="K4">
+        <f>SUM(B4:E4)</f>
         <v>2255</v>
       </c>
-      <c r="K4">
-        <f t="shared" si="1"/>
+      <c r="L4">
+        <f>SUM(F4:I4)</f>
         <v>1831</v>
       </c>
-      <c r="L4">
-        <f t="shared" si="2"/>
-        <v>4086</v>
-      </c>
       <c r="M4">
+        <f>J4</f>
+        <v>569</v>
+      </c>
+      <c r="N4">
+        <f>SUM(K4:M4)</f>
+        <v>4655</v>
+      </c>
+      <c r="O4">
         <v>4</v>
       </c>
-      <c r="N4">
+      <c r="P4">
         <v>2</v>
       </c>
-      <c r="O4">
+      <c r="Q4">
         <v>3</v>
       </c>
-      <c r="P4">
+      <c r="R4">
         <v>3</v>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>5</v>
       </c>
-      <c r="R4">
+      <c r="T4">
         <v>12</v>
       </c>
-      <c r="S4">
+      <c r="U4">
         <v>2</v>
       </c>
-      <c r="T4">
+      <c r="V4">
         <v>1</v>
       </c>
-      <c r="U4">
+      <c r="W4">
+        <v>4</v>
+      </c>
+      <c r="X4">
         <v>3</v>
       </c>
-      <c r="V4">
+      <c r="Y4">
         <v>4</v>
       </c>
-      <c r="W4">
+      <c r="Z4">
+        <v>4</v>
+      </c>
+      <c r="AA4">
         <v>3</v>
       </c>
-      <c r="X4" t="s">
+      <c r="AB4" t="s">
         <v>16</v>
       </c>
-      <c r="Y4" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z4" t="s">
+      <c r="AC4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -960,61 +1023,74 @@
         <v>640</v>
       </c>
       <c r="J5">
-        <f t="shared" si="0"/>
+        <v>325</v>
+      </c>
+      <c r="K5">
+        <f>SUM(B5:E5)</f>
         <v>2017</v>
       </c>
-      <c r="K5">
-        <f t="shared" si="1"/>
+      <c r="L5">
+        <f>SUM(F5:I5)</f>
         <v>1920</v>
       </c>
-      <c r="L5">
-        <f t="shared" si="2"/>
-        <v>3937</v>
-      </c>
       <c r="M5">
+        <f>J5</f>
+        <v>325</v>
+      </c>
+      <c r="N5">
+        <f>SUM(K5:M5)</f>
+        <v>4262</v>
+      </c>
+      <c r="O5">
         <v>3</v>
       </c>
-      <c r="N5">
+      <c r="P5">
         <v>5</v>
       </c>
-      <c r="O5">
+      <c r="Q5">
         <v>4</v>
       </c>
-      <c r="P5">
+      <c r="R5">
         <v>6</v>
       </c>
-      <c r="Q5">
+      <c r="S5">
         <v>6</v>
       </c>
-      <c r="R5">
+      <c r="T5">
         <v>4</v>
       </c>
-      <c r="S5">
+      <c r="U5">
         <v>3</v>
       </c>
-      <c r="T5">
+      <c r="V5">
         <v>3</v>
       </c>
-      <c r="U5">
+      <c r="W5">
+        <v>8</v>
+      </c>
+      <c r="X5">
         <v>4</v>
       </c>
-      <c r="V5">
+      <c r="Y5">
         <v>2</v>
       </c>
-      <c r="W5">
+      <c r="Z5">
+        <v>8</v>
+      </c>
+      <c r="AA5">
         <v>4</v>
       </c>
-      <c r="X5" t="s">
+      <c r="AB5" t="s">
         <v>12</v>
       </c>
-      <c r="Y5" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z5" t="s">
+      <c r="AC5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -1043,61 +1119,74 @@
         <v>319</v>
       </c>
       <c r="J6">
-        <f t="shared" si="0"/>
+        <v>623</v>
+      </c>
+      <c r="K6">
+        <f>SUM(B6:E6)</f>
         <v>1876</v>
       </c>
-      <c r="K6">
-        <f t="shared" si="1"/>
+      <c r="L6">
+        <f>SUM(F6:I6)</f>
         <v>1747</v>
       </c>
-      <c r="L6">
-        <f t="shared" si="2"/>
-        <v>3623</v>
-      </c>
       <c r="M6">
-        <v>5</v>
+        <f>J6</f>
+        <v>623</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <f>SUM(K6:M6)</f>
+        <v>4246</v>
       </c>
       <c r="O6">
         <v>5</v>
       </c>
       <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>5</v>
+      </c>
+      <c r="R6">
         <v>4</v>
       </c>
-      <c r="Q6">
+      <c r="S6">
         <v>3</v>
       </c>
-      <c r="R6">
+      <c r="T6">
         <v>2</v>
-      </c>
-      <c r="S6">
-        <v>5</v>
-      </c>
-      <c r="T6">
-        <v>9</v>
       </c>
       <c r="U6">
         <v>5</v>
       </c>
       <c r="V6">
+        <v>9</v>
+      </c>
+      <c r="W6">
+        <v>3</v>
+      </c>
+      <c r="X6">
+        <v>5</v>
+      </c>
+      <c r="Y6">
         <v>6</v>
       </c>
-      <c r="W6">
+      <c r="Z6">
+        <v>3</v>
+      </c>
+      <c r="AA6">
         <v>5</v>
       </c>
-      <c r="X6" t="s">
+      <c r="AB6" t="s">
         <v>12</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="AC6" t="s">
         <v>21</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AD6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -1126,37 +1215,38 @@
         <v>424</v>
       </c>
       <c r="J7">
-        <f t="shared" si="0"/>
+        <v>308</v>
+      </c>
+      <c r="K7">
+        <f>SUM(B7:E7)</f>
         <v>1600</v>
       </c>
-      <c r="K7">
-        <f t="shared" si="1"/>
+      <c r="L7">
+        <f>SUM(F7:I7)</f>
         <v>1881</v>
       </c>
-      <c r="L7">
-        <f t="shared" si="2"/>
-        <v>3481</v>
-      </c>
       <c r="M7">
-        <v>6</v>
+        <f>J7</f>
+        <v>308</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <f>SUM(K7:M7)</f>
+        <v>3789</v>
       </c>
       <c r="O7">
         <v>6</v>
       </c>
       <c r="P7">
+        <v>4</v>
+      </c>
+      <c r="Q7">
+        <v>6</v>
+      </c>
+      <c r="R7">
         <v>7</v>
       </c>
-      <c r="Q7">
+      <c r="S7">
         <v>1</v>
-      </c>
-      <c r="R7">
-        <v>5</v>
-      </c>
-      <c r="S7">
-        <v>6</v>
       </c>
       <c r="T7">
         <v>5</v>
@@ -1165,22 +1255,34 @@
         <v>6</v>
       </c>
       <c r="V7">
+        <v>5</v>
+      </c>
+      <c r="W7">
+        <v>9</v>
+      </c>
+      <c r="X7">
+        <v>6</v>
+      </c>
+      <c r="Y7">
         <v>3</v>
       </c>
-      <c r="W7">
+      <c r="Z7">
+        <v>9</v>
+      </c>
+      <c r="AA7">
         <v>6</v>
       </c>
-      <c r="X7" t="s">
+      <c r="AB7" t="s">
         <v>16</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="AC7" t="s">
         <v>21</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="AD7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1209,61 +1311,74 @@
         <v>395</v>
       </c>
       <c r="J8">
-        <f t="shared" si="0"/>
+        <v>131</v>
+      </c>
+      <c r="K8">
+        <f>SUM(B8:E8)</f>
         <v>798</v>
       </c>
-      <c r="K8">
-        <f t="shared" si="1"/>
+      <c r="L8">
+        <f>SUM(F8:I8)</f>
         <v>1175</v>
       </c>
-      <c r="L8">
-        <f t="shared" si="2"/>
-        <v>1973</v>
-      </c>
       <c r="M8">
-        <v>13</v>
+        <f>J8</f>
+        <v>131</v>
       </c>
       <c r="N8">
+        <f>SUM(K8:M8)</f>
+        <v>2104</v>
+      </c>
+      <c r="O8">
+        <v>13</v>
+      </c>
+      <c r="P8">
         <v>7</v>
       </c>
-      <c r="O8">
+      <c r="Q8">
         <v>8</v>
       </c>
-      <c r="P8">
+      <c r="R8">
         <v>5</v>
       </c>
-      <c r="Q8">
+      <c r="S8">
         <v>10</v>
-      </c>
-      <c r="R8">
-        <v>6</v>
-      </c>
-      <c r="S8">
-        <v>7</v>
       </c>
       <c r="T8">
         <v>6</v>
       </c>
       <c r="U8">
+        <v>7</v>
+      </c>
+      <c r="V8">
+        <v>6</v>
+      </c>
+      <c r="W8">
+        <v>11</v>
+      </c>
+      <c r="X8">
         <v>8</v>
       </c>
-      <c r="V8">
+      <c r="Y8">
         <v>7</v>
       </c>
-      <c r="W8">
+      <c r="Z8">
+        <v>11</v>
+      </c>
+      <c r="AA8">
         <v>7</v>
       </c>
-      <c r="X8" t="s">
+      <c r="AB8" t="s">
         <v>16</v>
       </c>
-      <c r="Y8" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z8" t="s">
+      <c r="AC8" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1292,22 +1407,23 @@
         <v>362</v>
       </c>
       <c r="J9">
-        <f t="shared" si="0"/>
+        <v>131</v>
+      </c>
+      <c r="K9">
+        <f>SUM(B9:E9)</f>
         <v>1010</v>
       </c>
-      <c r="K9">
-        <f t="shared" si="1"/>
+      <c r="L9">
+        <f>SUM(F9:I9)</f>
         <v>944</v>
       </c>
-      <c r="L9">
-        <f t="shared" si="2"/>
-        <v>1954</v>
-      </c>
       <c r="M9">
-        <v>7</v>
+        <f>J9</f>
+        <v>131</v>
       </c>
       <c r="N9">
-        <v>8</v>
+        <f>SUM(K9:M9)</f>
+        <v>2085</v>
       </c>
       <c r="O9">
         <v>7</v>
@@ -1316,37 +1432,49 @@
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="R9">
+        <v>8</v>
+      </c>
+      <c r="S9">
+        <v>13</v>
+      </c>
+      <c r="T9">
         <v>9</v>
       </c>
-      <c r="S9">
+      <c r="U9">
         <v>8</v>
       </c>
-      <c r="T9">
+      <c r="V9">
         <v>8</v>
       </c>
-      <c r="U9">
+      <c r="W9">
+        <v>12</v>
+      </c>
+      <c r="X9">
         <v>7</v>
       </c>
-      <c r="V9">
+      <c r="Y9">
         <v>9</v>
       </c>
-      <c r="W9">
+      <c r="Z9">
+        <v>12</v>
+      </c>
+      <c r="AA9">
         <v>8</v>
       </c>
-      <c r="X9" t="s">
+      <c r="AB9" t="s">
         <v>12</v>
       </c>
-      <c r="Y9" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z9" t="s">
+      <c r="AC9" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -1375,61 +1503,74 @@
         <v>131</v>
       </c>
       <c r="J10">
-        <f t="shared" si="0"/>
+        <v>341</v>
+      </c>
+      <c r="K10">
+        <f>SUM(B10:E10)</f>
         <v>529</v>
       </c>
-      <c r="K10">
-        <f t="shared" si="1"/>
+      <c r="L10">
+        <f>SUM(F10:I10)</f>
         <v>818</v>
       </c>
-      <c r="L10">
-        <f t="shared" si="2"/>
-        <v>1347</v>
-      </c>
       <c r="M10">
+        <f>J10</f>
+        <v>341</v>
+      </c>
+      <c r="N10">
+        <f>SUM(K10:M10)</f>
+        <v>1688</v>
+      </c>
+      <c r="O10">
         <v>8</v>
       </c>
-      <c r="N10">
+      <c r="P10">
         <v>11</v>
       </c>
-      <c r="O10">
+      <c r="Q10">
         <v>12</v>
       </c>
-      <c r="P10">
+      <c r="R10">
         <v>9</v>
-      </c>
-      <c r="Q10">
-        <v>9</v>
-      </c>
-      <c r="R10">
-        <v>13</v>
       </c>
       <c r="S10">
         <v>9</v>
       </c>
       <c r="T10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U10">
         <v>9</v>
       </c>
       <c r="V10">
+        <v>11</v>
+      </c>
+      <c r="W10">
+        <v>7</v>
+      </c>
+      <c r="X10">
+        <v>9</v>
+      </c>
+      <c r="Y10">
         <v>10</v>
       </c>
-      <c r="W10">
+      <c r="Z10">
+        <v>7</v>
+      </c>
+      <c r="AA10">
         <v>9</v>
       </c>
-      <c r="X10" t="s">
+      <c r="AB10" t="s">
         <v>16</v>
       </c>
-      <c r="Y10" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z10" t="s">
+      <c r="AC10" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -1458,81 +1599,94 @@
         <v>385</v>
       </c>
       <c r="J11">
-        <f t="shared" si="0"/>
+        <v>427</v>
+      </c>
+      <c r="K11">
+        <f>SUM(B11:E11)</f>
         <v>28</v>
       </c>
-      <c r="K11">
-        <f t="shared" si="1"/>
+      <c r="L11">
+        <f>SUM(F11:I11)</f>
         <v>1035</v>
       </c>
-      <c r="L11">
-        <f t="shared" si="2"/>
-        <v>1063</v>
-      </c>
       <c r="M11">
+        <f>J11</f>
+        <v>427</v>
+      </c>
+      <c r="N11">
+        <f>SUM(K11:M11)</f>
+        <v>1490</v>
+      </c>
+      <c r="O11">
         <v>12</v>
       </c>
-      <c r="N11">
-        <v>13</v>
-      </c>
-      <c r="O11">
-        <v>13</v>
-      </c>
       <c r="P11">
         <v>13</v>
       </c>
       <c r="Q11">
+        <v>13</v>
+      </c>
+      <c r="R11">
+        <v>13</v>
+      </c>
+      <c r="S11">
         <v>12</v>
-      </c>
-      <c r="R11">
-        <v>7</v>
-      </c>
-      <c r="S11">
-        <v>10</v>
       </c>
       <c r="T11">
         <v>7</v>
       </c>
       <c r="U11">
+        <v>10</v>
+      </c>
+      <c r="V11">
+        <v>7</v>
+      </c>
+      <c r="W11">
+        <v>6</v>
+      </c>
+      <c r="X11">
         <v>16</v>
       </c>
-      <c r="V11">
+      <c r="Y11">
         <v>8</v>
       </c>
-      <c r="W11">
+      <c r="Z11">
+        <v>6</v>
+      </c>
+      <c r="AA11">
         <v>10</v>
       </c>
-      <c r="X11" t="s">
+      <c r="AB11" t="s">
         <v>16</v>
       </c>
-      <c r="Y11" t="s">
+      <c r="AC11" t="s">
         <v>21</v>
       </c>
-      <c r="Z11" t="s">
+      <c r="AD11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>62</v>
       </c>
       <c r="C12">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D12">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="E12">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F12">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="G12">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1541,81 +1695,94 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <f t="shared" si="0"/>
-        <v>503</v>
+        <v>141</v>
       </c>
       <c r="K12">
-        <f t="shared" si="1"/>
-        <v>480</v>
+        <f>SUM(B12:E12)</f>
+        <v>496</v>
       </c>
       <c r="L12">
-        <f t="shared" si="2"/>
-        <v>983</v>
+        <f>SUM(F12:I12)</f>
+        <v>484</v>
       </c>
       <c r="M12">
+        <f>J12</f>
+        <v>141</v>
+      </c>
+      <c r="N12">
+        <f>SUM(K12:M12)</f>
+        <v>1121</v>
+      </c>
+      <c r="O12">
+        <v>10</v>
+      </c>
+      <c r="P12">
         <v>9</v>
       </c>
-      <c r="N12">
+      <c r="Q12">
         <v>10</v>
       </c>
-      <c r="O12">
-        <v>9</v>
-      </c>
-      <c r="P12">
+      <c r="R12">
+        <v>10</v>
+      </c>
+      <c r="S12">
+        <v>7</v>
+      </c>
+      <c r="T12">
+        <v>10</v>
+      </c>
+      <c r="U12">
+        <v>13</v>
+      </c>
+      <c r="V12">
+        <v>13</v>
+      </c>
+      <c r="W12">
+        <v>10</v>
+      </c>
+      <c r="X12">
         <v>11</v>
       </c>
-      <c r="Q12">
-        <v>8</v>
-      </c>
-      <c r="R12">
+      <c r="Y12">
+        <v>12</v>
+      </c>
+      <c r="Z12">
+        <v>10</v>
+      </c>
+      <c r="AA12">
         <v>11</v>
       </c>
-      <c r="S12">
-        <v>13</v>
-      </c>
-      <c r="T12">
-        <v>13</v>
-      </c>
-      <c r="U12">
-        <v>10</v>
-      </c>
-      <c r="V12">
-        <v>13</v>
-      </c>
-      <c r="W12">
-        <v>11</v>
-      </c>
-      <c r="X12" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z12" t="s">
+      <c r="AB12" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD12" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B13">
         <v>62</v>
       </c>
       <c r="C13">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D13">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="E13">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F13">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G13">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -1624,61 +1791,74 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <f t="shared" si="0"/>
-        <v>496</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <f t="shared" si="1"/>
-        <v>484</v>
+        <f>SUM(B13:E13)</f>
+        <v>503</v>
       </c>
       <c r="L13">
-        <f t="shared" si="2"/>
-        <v>980</v>
+        <f>SUM(F13:I13)</f>
+        <v>480</v>
       </c>
       <c r="M13">
-        <v>10</v>
+        <f>J13</f>
+        <v>0</v>
       </c>
       <c r="N13">
+        <f>SUM(K13:M13)</f>
+        <v>983</v>
+      </c>
+      <c r="O13">
         <v>9</v>
-      </c>
-      <c r="O13">
-        <v>10</v>
       </c>
       <c r="P13">
         <v>10</v>
       </c>
       <c r="Q13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R13">
+        <v>11</v>
+      </c>
+      <c r="S13">
+        <v>8</v>
+      </c>
+      <c r="T13">
+        <v>11</v>
+      </c>
+      <c r="U13">
+        <v>13</v>
+      </c>
+      <c r="V13">
+        <v>13</v>
+      </c>
+      <c r="W13">
+        <v>15</v>
+      </c>
+      <c r="X13">
         <v>10</v>
       </c>
-      <c r="S13">
-        <v>13</v>
-      </c>
-      <c r="T13">
-        <v>13</v>
-      </c>
-      <c r="U13">
-        <v>11</v>
-      </c>
-      <c r="V13">
+      <c r="Y13">
+        <v>13</v>
+      </c>
+      <c r="Z13">
+        <v>15</v>
+      </c>
+      <c r="AA13">
         <v>12</v>
       </c>
-      <c r="W13">
-        <v>12</v>
-      </c>
-      <c r="X13" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z13" t="s">
+      <c r="AB13" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD13" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1707,25 +1887,26 @@
         <v>160</v>
       </c>
       <c r="J14">
-        <f t="shared" si="0"/>
+        <v>125</v>
+      </c>
+      <c r="K14">
+        <f>SUM(B14:E14)</f>
         <v>145</v>
       </c>
-      <c r="K14">
-        <f t="shared" si="1"/>
+      <c r="L14">
+        <f>SUM(F14:I14)</f>
         <v>608</v>
       </c>
-      <c r="L14">
-        <f t="shared" si="2"/>
-        <v>753</v>
-      </c>
       <c r="M14">
-        <v>13</v>
+        <f>J14</f>
+        <v>125</v>
       </c>
       <c r="N14">
-        <v>13</v>
+        <f>SUM(K14:M14)</f>
+        <v>878</v>
       </c>
       <c r="O14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P14">
         <v>13</v>
@@ -1734,34 +1915,46 @@
         <v>11</v>
       </c>
       <c r="R14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S14">
         <v>11</v>
       </c>
       <c r="T14">
+        <v>14</v>
+      </c>
+      <c r="U14">
+        <v>11</v>
+      </c>
+      <c r="V14">
         <v>10</v>
       </c>
-      <c r="U14">
+      <c r="W14">
+        <v>13</v>
+      </c>
+      <c r="X14">
         <v>12</v>
       </c>
-      <c r="V14">
+      <c r="Y14">
         <v>11</v>
       </c>
-      <c r="W14">
-        <v>13</v>
-      </c>
-      <c r="X14" t="s">
+      <c r="Z14">
+        <v>13</v>
+      </c>
+      <c r="AA14">
+        <v>13</v>
+      </c>
+      <c r="AB14" t="s">
         <v>12</v>
       </c>
-      <c r="Y14" t="s">
+      <c r="AC14" t="s">
         <v>17</v>
       </c>
-      <c r="Z14" t="s">
+      <c r="AD14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>30</v>
       </c>
@@ -1790,22 +1983,23 @@
         <v>443</v>
       </c>
       <c r="J15">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="K15">
-        <f t="shared" si="1"/>
+        <f>SUM(B15:E15)</f>
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <f>SUM(F15:I15)</f>
         <v>443</v>
       </c>
-      <c r="L15">
-        <f t="shared" si="2"/>
-        <v>443</v>
-      </c>
       <c r="M15">
-        <v>13</v>
+        <f>J15</f>
+        <v>428</v>
       </c>
       <c r="N15">
-        <v>13</v>
+        <f>SUM(K15:M15)</f>
+        <v>871</v>
       </c>
       <c r="O15">
         <v>13</v>
@@ -1814,37 +2008,49 @@
         <v>13</v>
       </c>
       <c r="Q15">
+        <v>13</v>
+      </c>
+      <c r="R15">
+        <v>13</v>
+      </c>
+      <c r="S15">
         <v>14</v>
       </c>
-      <c r="R15">
+      <c r="T15">
         <v>15</v>
       </c>
-      <c r="S15">
-        <v>13</v>
-      </c>
-      <c r="T15">
+      <c r="U15">
+        <v>13</v>
+      </c>
+      <c r="V15">
         <v>4</v>
       </c>
-      <c r="U15">
+      <c r="W15">
+        <v>5</v>
+      </c>
+      <c r="X15">
         <v>17</v>
       </c>
-      <c r="V15">
+      <c r="Y15">
         <v>14</v>
       </c>
-      <c r="W15">
+      <c r="Z15">
+        <v>5</v>
+      </c>
+      <c r="AA15">
         <v>14</v>
       </c>
-      <c r="X15" t="s">
+      <c r="AB15" t="s">
         <v>16</v>
       </c>
-      <c r="Y15" t="s">
+      <c r="AC15" t="s">
         <v>21</v>
       </c>
-      <c r="Z15" t="s">
+      <c r="AD15" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -1873,61 +2079,74 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <f t="shared" si="0"/>
+        <v>102</v>
+      </c>
+      <c r="K16">
+        <f>SUM(B16:E16)</f>
         <v>59</v>
       </c>
-      <c r="K16">
-        <f t="shared" si="1"/>
+      <c r="L16">
+        <f>SUM(F16:I16)</f>
         <v>316</v>
       </c>
-      <c r="L16">
-        <f t="shared" si="2"/>
-        <v>375</v>
-      </c>
       <c r="M16">
-        <v>13</v>
+        <f>J16</f>
+        <v>102</v>
       </c>
       <c r="N16">
-        <v>13</v>
+        <f>SUM(K16:M16)</f>
+        <v>477</v>
       </c>
       <c r="O16">
         <v>13</v>
       </c>
       <c r="P16">
+        <v>13</v>
+      </c>
+      <c r="Q16">
+        <v>13</v>
+      </c>
+      <c r="R16">
         <v>12</v>
       </c>
-      <c r="Q16">
+      <c r="S16">
         <v>14</v>
       </c>
-      <c r="R16">
+      <c r="T16">
         <v>8</v>
       </c>
-      <c r="S16">
+      <c r="U16">
         <v>12</v>
       </c>
-      <c r="T16">
-        <v>13</v>
-      </c>
-      <c r="U16">
+      <c r="V16">
+        <v>13</v>
+      </c>
+      <c r="W16">
         <v>14</v>
       </c>
-      <c r="V16">
+      <c r="X16">
+        <v>14</v>
+      </c>
+      <c r="Y16">
         <v>15</v>
       </c>
-      <c r="W16">
+      <c r="Z16">
+        <v>14</v>
+      </c>
+      <c r="AA16">
         <v>15</v>
       </c>
-      <c r="X16" t="s">
+      <c r="AB16" t="s">
         <v>12</v>
       </c>
-      <c r="Y16" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z16" t="s">
+      <c r="AC16" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -1956,61 +2175,74 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <f>SUM(B17:E17)</f>
         <v>84</v>
       </c>
-      <c r="K17">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="L17">
-        <f t="shared" si="2"/>
+        <f>SUM(F17:I17)</f>
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <f>J17</f>
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <f>SUM(K17:M17)</f>
         <v>84</v>
       </c>
-      <c r="M17">
-        <v>13</v>
-      </c>
-      <c r="N17">
+      <c r="O17">
+        <v>13</v>
+      </c>
+      <c r="P17">
         <v>12</v>
       </c>
-      <c r="O17">
-        <v>13</v>
-      </c>
-      <c r="P17">
-        <v>13</v>
-      </c>
       <c r="Q17">
+        <v>13</v>
+      </c>
+      <c r="R17">
+        <v>13</v>
+      </c>
+      <c r="S17">
         <v>14</v>
       </c>
-      <c r="R17">
+      <c r="T17">
         <v>15</v>
       </c>
-      <c r="S17">
-        <v>13</v>
-      </c>
-      <c r="T17">
-        <v>13</v>
-      </c>
       <c r="U17">
         <v>13</v>
       </c>
       <c r="V17">
+        <v>13</v>
+      </c>
+      <c r="W17">
+        <v>15</v>
+      </c>
+      <c r="X17">
+        <v>13</v>
+      </c>
+      <c r="Y17">
         <v>16</v>
       </c>
-      <c r="W17">
+      <c r="Z17">
+        <v>15</v>
+      </c>
+      <c r="AA17">
         <v>16</v>
       </c>
-      <c r="X17" t="s">
+      <c r="AB17" t="s">
         <v>12</v>
       </c>
-      <c r="Y17" t="s">
+      <c r="AC17" t="s">
         <v>21</v>
       </c>
-      <c r="Z17" t="s">
+      <c r="AD17" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -2039,61 +2271,74 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <f>SUM(B18:E18)</f>
         <v>39</v>
       </c>
-      <c r="K18">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="L18">
-        <f t="shared" si="2"/>
+        <f>SUM(F18:I18)</f>
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <f>J18</f>
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <f>SUM(K18:M18)</f>
         <v>39</v>
       </c>
-      <c r="M18">
+      <c r="O18">
         <v>11</v>
       </c>
-      <c r="N18">
-        <v>13</v>
-      </c>
-      <c r="O18">
-        <v>13</v>
-      </c>
       <c r="P18">
         <v>13</v>
       </c>
       <c r="Q18">
+        <v>13</v>
+      </c>
+      <c r="R18">
+        <v>13</v>
+      </c>
+      <c r="S18">
         <v>14</v>
       </c>
-      <c r="R18">
+      <c r="T18">
         <v>15</v>
       </c>
-      <c r="S18">
-        <v>13</v>
-      </c>
-      <c r="T18">
-        <v>13</v>
-      </c>
       <c r="U18">
+        <v>13</v>
+      </c>
+      <c r="V18">
+        <v>13</v>
+      </c>
+      <c r="W18">
         <v>15</v>
       </c>
-      <c r="V18">
+      <c r="X18">
+        <v>15</v>
+      </c>
+      <c r="Y18">
         <v>16</v>
       </c>
-      <c r="W18">
+      <c r="Z18">
+        <v>15</v>
+      </c>
+      <c r="AA18">
         <v>17</v>
       </c>
-      <c r="X18" t="s">
+      <c r="AB18" t="s">
         <v>12</v>
       </c>
-      <c r="Y18" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z18" t="s">
+      <c r="AC18" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -2122,22 +2367,23 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K19">
-        <f t="shared" si="1"/>
+        <f>SUM(B19:E19)</f>
         <v>0</v>
       </c>
       <c r="L19">
-        <f t="shared" si="2"/>
+        <f>SUM(F19:I19)</f>
         <v>0</v>
       </c>
       <c r="M19">
-        <v>13</v>
+        <f>J19</f>
+        <v>0</v>
       </c>
       <c r="N19">
-        <v>13</v>
+        <f>SUM(K19:M19)</f>
+        <v>0</v>
       </c>
       <c r="O19">
         <v>13</v>
@@ -2146,37 +2392,49 @@
         <v>13</v>
       </c>
       <c r="Q19">
+        <v>13</v>
+      </c>
+      <c r="R19">
+        <v>13</v>
+      </c>
+      <c r="S19">
         <v>14</v>
       </c>
-      <c r="R19">
+      <c r="T19">
         <v>15</v>
       </c>
-      <c r="S19">
-        <v>13</v>
-      </c>
-      <c r="T19">
-        <v>13</v>
-      </c>
       <c r="U19">
+        <v>13</v>
+      </c>
+      <c r="V19">
+        <v>13</v>
+      </c>
+      <c r="W19">
+        <v>15</v>
+      </c>
+      <c r="X19">
         <v>17</v>
       </c>
-      <c r="V19">
+      <c r="Y19">
         <v>16</v>
       </c>
-      <c r="W19">
+      <c r="Z19">
+        <v>15</v>
+      </c>
+      <c r="AA19">
         <v>18</v>
       </c>
-      <c r="X19" t="s">
+      <c r="AB19" t="s">
         <v>16</v>
       </c>
-      <c r="Y19" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z19" t="s">
+      <c r="AC19" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -2205,22 +2463,23 @@
         <v>0</v>
       </c>
       <c r="J20">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K20">
-        <f t="shared" si="1"/>
+        <f>SUM(B20:E20)</f>
         <v>0</v>
       </c>
       <c r="L20">
-        <f t="shared" si="2"/>
+        <f>SUM(F20:I20)</f>
         <v>0</v>
       </c>
       <c r="M20">
-        <v>13</v>
+        <f>J20</f>
+        <v>0</v>
       </c>
       <c r="N20">
-        <v>13</v>
+        <f>SUM(K20:M20)</f>
+        <v>0</v>
       </c>
       <c r="O20">
         <v>13</v>
@@ -2229,37 +2488,49 @@
         <v>13</v>
       </c>
       <c r="Q20">
+        <v>13</v>
+      </c>
+      <c r="R20">
+        <v>13</v>
+      </c>
+      <c r="S20">
         <v>14</v>
       </c>
-      <c r="R20">
+      <c r="T20">
         <v>15</v>
       </c>
-      <c r="S20">
-        <v>13</v>
-      </c>
-      <c r="T20">
-        <v>13</v>
-      </c>
       <c r="U20">
+        <v>13</v>
+      </c>
+      <c r="V20">
+        <v>13</v>
+      </c>
+      <c r="W20">
+        <v>15</v>
+      </c>
+      <c r="X20">
         <v>17</v>
       </c>
-      <c r="V20">
+      <c r="Y20">
         <v>16</v>
       </c>
-      <c r="W20">
+      <c r="Z20">
+        <v>15</v>
+      </c>
+      <c r="AA20">
         <v>18</v>
       </c>
-      <c r="X20" t="s">
+      <c r="AB20" t="s">
         <v>12</v>
       </c>
-      <c r="Y20" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z20" t="s">
+      <c r="AC20" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD20" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -2288,22 +2559,23 @@
         <v>0</v>
       </c>
       <c r="J21">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K21">
-        <f t="shared" si="1"/>
+        <f>SUM(B21:E21)</f>
         <v>0</v>
       </c>
       <c r="L21">
-        <f t="shared" si="2"/>
+        <f>SUM(F21:I21)</f>
         <v>0</v>
       </c>
       <c r="M21">
-        <v>13</v>
+        <f>J21</f>
+        <v>0</v>
       </c>
       <c r="N21">
-        <v>13</v>
+        <f>SUM(K21:M21)</f>
+        <v>0</v>
       </c>
       <c r="O21">
         <v>13</v>
@@ -2312,37 +2584,49 @@
         <v>13</v>
       </c>
       <c r="Q21">
+        <v>13</v>
+      </c>
+      <c r="R21">
+        <v>13</v>
+      </c>
+      <c r="S21">
         <v>14</v>
       </c>
-      <c r="R21">
+      <c r="T21">
         <v>15</v>
       </c>
-      <c r="S21">
-        <v>13</v>
-      </c>
-      <c r="T21">
-        <v>13</v>
-      </c>
       <c r="U21">
+        <v>13</v>
+      </c>
+      <c r="V21">
+        <v>13</v>
+      </c>
+      <c r="W21">
+        <v>15</v>
+      </c>
+      <c r="X21">
         <v>17</v>
       </c>
-      <c r="V21">
+      <c r="Y21">
         <v>16</v>
       </c>
-      <c r="W21">
+      <c r="Z21">
+        <v>15</v>
+      </c>
+      <c r="AA21">
         <v>18</v>
       </c>
-      <c r="X21" t="s">
+      <c r="AB21" t="s">
         <v>16</v>
       </c>
-      <c r="Y21" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z21" t="s">
+      <c r="AC21" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD21" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -2371,22 +2655,23 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K22">
-        <f t="shared" si="1"/>
+        <f>SUM(B22:E22)</f>
         <v>0</v>
       </c>
       <c r="L22">
-        <f t="shared" si="2"/>
+        <f>SUM(F22:I22)</f>
         <v>0</v>
       </c>
       <c r="M22">
-        <v>13</v>
+        <f>J22</f>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>13</v>
+        <f>SUM(K22:M22)</f>
+        <v>0</v>
       </c>
       <c r="O22">
         <v>13</v>
@@ -2395,44 +2680,56 @@
         <v>13</v>
       </c>
       <c r="Q22">
+        <v>13</v>
+      </c>
+      <c r="R22">
+        <v>13</v>
+      </c>
+      <c r="S22">
         <v>14</v>
       </c>
-      <c r="R22">
+      <c r="T22">
         <v>15</v>
       </c>
-      <c r="S22">
-        <v>13</v>
-      </c>
-      <c r="T22">
-        <v>13</v>
-      </c>
       <c r="U22">
+        <v>13</v>
+      </c>
+      <c r="V22">
+        <v>13</v>
+      </c>
+      <c r="W22">
+        <v>15</v>
+      </c>
+      <c r="X22">
         <v>17</v>
       </c>
-      <c r="V22">
+      <c r="Y22">
         <v>16</v>
       </c>
-      <c r="W22">
+      <c r="Z22">
+        <v>15</v>
+      </c>
+      <c r="AA22">
         <v>18</v>
       </c>
-      <c r="X22" t="s">
+      <c r="AB22" t="s">
         <v>12</v>
       </c>
-      <c r="Y22" t="s">
+      <c r="AC22" t="s">
         <v>21</v>
       </c>
-      <c r="Z22" t="s">
+      <c r="AD22" t="s">
         <v>32</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z22" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z22">
-      <sortCondition descending="1" ref="L1:L22"/>
+  <autoFilter ref="A1:AD22" xr:uid="{A5432D6A-F34B-4E36-BD49-ACE58FF91028}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD22">
+      <sortCondition descending="1" ref="N1:N22"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z23">
-    <sortCondition descending="1" ref="K1:K23"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD23">
+    <sortCondition descending="1" ref="L1:L23"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
